--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB86967-D1D5-40F5-9307-B8F9D3ADC558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E73A28A-4D19-446E-8763-04A6D2808937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="11" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -37,13 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="297">
   <si>
     <t>ALL</t>
-  </si>
-  <si>
-    <t>Enum&lt;ShapeType&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>PartsType</t>
@@ -382,12 +378,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>[에픽알01]</t>
-  </si>
-  <si>
-    <t>[레전더리알01]</t>
-  </si>
-  <si>
     <t>일반 알이다. 온기가 느껴진다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -688,9 +678,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>list&lt;int&gt;</t>
-  </si>
-  <si>
     <t>Colors</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1157,6 +1144,13 @@
   <si>
     <t>느려졌지만, 행복해보인다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;string&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullablestring</t>
   </si>
 </sst>
 </file>
@@ -1968,126 +1962,126 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2096,15 +2090,15 @@
         <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2113,15 +2107,15 @@
         <v>200</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2130,15 +2124,15 @@
         <v>400</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2147,15 +2141,15 @@
         <v>300</v>
       </c>
       <c r="F11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -2164,155 +2158,155 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
         <v>78</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16">
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
         <v>96</v>
       </c>
-      <c r="B17" t="s">
-        <v>99</v>
-      </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2321,15 +2315,15 @@
         <v>250</v>
       </c>
       <c r="F23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2338,7 +2332,7 @@
         <v>260</v>
       </c>
       <c r="F24" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2427,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>0</v>
@@ -2438,104 +2432,104 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>114</v>
-      </c>
       <c r="K3" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K4">
         <f>F4/2</f>
@@ -2544,34 +2538,34 @@
     </row>
     <row r="5" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5">
         <v>7</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K5">
         <f t="shared" ref="K5:K9" si="0">F5/2</f>
@@ -2580,34 +2574,34 @@
     </row>
     <row r="6" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6">
         <v>7</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
@@ -2616,34 +2610,34 @@
     </row>
     <row r="7" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
@@ -2652,34 +2646,34 @@
     </row>
     <row r="8" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
@@ -2688,34 +2682,34 @@
     </row>
     <row r="9" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F9">
         <v>300</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
@@ -2724,28 +2718,28 @@
     </row>
     <row r="10" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10">
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -2753,34 +2747,34 @@
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F11">
         <v>500</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K11">
         <f t="shared" ref="K11:K13" si="1">F11/2</f>
@@ -2789,34 +2783,34 @@
     </row>
     <row r="12" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F12">
         <v>500</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K12">
         <f t="shared" si="1"/>
@@ -2825,34 +2819,34 @@
     </row>
     <row r="13" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F13">
         <v>500</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K13">
         <f t="shared" si="1"/>
@@ -2899,53 +2893,53 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2959,13 +2953,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2979,13 +2973,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2999,13 +2993,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3019,13 +3013,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3039,13 +3033,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3059,13 +3053,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3085,7 +3079,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F49BF-A4DD-4B19-8FB8-F431AABBF38F}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.375" customWidth="1"/>
@@ -3114,47 +3108,47 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3165,13 +3159,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3182,13 +3176,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3199,13 +3193,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3216,13 +3210,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3233,13 +3227,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3250,16 +3244,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -3267,13 +3261,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -3284,16 +3278,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="D12">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -3301,52 +3295,18 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
         <v>1</v>
       </c>
     </row>
@@ -3388,112 +3348,112 @@
         <v>0</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>75</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>224</v>
-      </c>
       <c r="I3" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" t="s">
         <v>217</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E4" t="s">
-        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3517,265 +3477,265 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C27" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B28" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3823,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>0</v>
@@ -3840,628 +3800,628 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F4" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H4" s="11">
         <v>10</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F5" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H5" s="11">
         <v>10</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H6" s="11">
         <v>10</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H7" s="11">
         <v>10</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F8" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H8" s="11">
         <v>10</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F9" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H9" s="11">
         <v>10</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F10" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H10" s="11">
         <v>10</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F11" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H11" s="11">
         <v>10</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F12" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H12" s="11">
         <v>10</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F13" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H13" s="11">
         <v>10</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>262</v>
-      </c>
       <c r="F14" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H14" s="11">
         <v>10</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F15" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H15" s="11">
         <v>10</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F16" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H16" s="11">
         <v>10</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F17" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H17" s="11">
         <v>10</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>218</v>
-      </c>
       <c r="F18" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H18" s="11">
         <v>10</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F19" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H19" s="11">
         <v>10</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F20" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H20" s="11">
         <v>10</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F21" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H21" s="11">
         <v>10</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F22" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H22" s="11">
         <v>10</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F23" s="11" t="b">
         <v>0</v>
@@ -4471,24 +4431,24 @@
         <v>10</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F24" s="11" t="b">
         <v>0</v>
@@ -4498,24 +4458,24 @@
         <v>10</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F25" s="11" t="b">
         <v>0</v>
@@ -4525,24 +4485,24 @@
         <v>10</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F26" s="11" t="b">
         <v>0</v>
@@ -4552,152 +4512,152 @@
         <v>10</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F27" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H27" s="11">
         <v>10</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H28" s="11">
         <v>10</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H29" s="11">
         <v>10</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F30" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H30" s="11">
         <v>10</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F31" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H31" s="11">
         <v>10</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -4745,59 +4705,59 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -4808,13 +4768,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -4825,13 +4785,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -4842,13 +4802,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
         <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" t="s">
-        <v>45</v>
       </c>
       <c r="D7">
         <v>15</v>
@@ -4857,7 +4817,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -4899,42 +4859,42 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="D3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -5365,61 +5325,61 @@
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1800</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -5446,40 +5406,40 @@
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
         <v>72</v>
       </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -5507,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>0</v>
@@ -5518,70 +5478,70 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="E2" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -5610,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>0</v>
@@ -5618,72 +5578,72 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" t="s">
         <v>134</v>
-      </c>
-      <c r="B6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E73A28A-4D19-446E-8763-04A6D2808937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D1A1DD-1C5D-4230-9389-CDF0FDA6C3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="11" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="298">
   <si>
     <t>ALL</t>
   </si>
@@ -1151,6 +1151,10 @@
   </si>
   <si>
     <t>nullablestring</t>
+  </si>
+  <si>
+    <t>Size</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4828,16 +4832,17 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48BD49A-A9D0-46FB-B798-026EB3CD9B33}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="12.875" customWidth="1"/>
     <col min="5" max="5" width="14.25" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4856,8 +4861,11 @@
       <c r="F1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
@@ -4876,8 +4884,11 @@
       <c r="F2" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
@@ -4896,8 +4907,11 @@
       <c r="F3" s="8" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4916,8 +4930,11 @@
       <c r="F4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -4936,8 +4953,11 @@
       <c r="F5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -4956,8 +4976,11 @@
       <c r="F6">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -4976,8 +4999,11 @@
       <c r="F7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -4996,8 +5022,11 @@
       <c r="F8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -5016,8 +5045,11 @@
       <c r="F9">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -5036,8 +5068,11 @@
       <c r="F10">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -5056,8 +5091,11 @@
       <c r="F11">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -5076,8 +5114,11 @@
       <c r="F12">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -5096,8 +5137,11 @@
       <c r="F13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -5116,8 +5160,11 @@
       <c r="F14">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -5136,8 +5183,11 @@
       <c r="F15">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -5156,8 +5206,11 @@
       <c r="F16">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -5176,8 +5229,11 @@
       <c r="F17">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -5196,8 +5252,11 @@
       <c r="F18">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -5216,8 +5275,11 @@
       <c r="F19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -5236,8 +5298,11 @@
       <c r="F20">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -5256,8 +5321,11 @@
       <c r="F21">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -5276,8 +5344,11 @@
       <c r="F22">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -5294,6 +5365,9 @@
         <v>1800</v>
       </c>
       <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="G23">
         <v>20</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D1A1DD-1C5D-4230-9389-CDF0FDA6C3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0352C0C-03DC-437F-B5D8-7A69162A046E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="299">
   <si>
     <t>ALL</t>
   </si>
@@ -1154,6 +1154,10 @@
   </si>
   <si>
     <t>Size</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_lettuce</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4673,7 +4677,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2444F32-CF16-41C0-B4D3-AE1758A9A6E6}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -4682,9 +4686,10 @@
     <col min="5" max="5" width="13.875" customWidth="1"/>
     <col min="6" max="6" width="15.125" customWidth="1"/>
     <col min="7" max="7" width="28.875" customWidth="1"/>
+    <col min="8" max="8" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4706,8 +4711,11 @@
       <c r="G1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>24</v>
       </c>
@@ -4729,8 +4737,11 @@
       <c r="G2" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>29</v>
       </c>
@@ -4752,8 +4763,11 @@
       <c r="G3" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -4769,8 +4783,11 @@
       <c r="E4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -4787,7 +4804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -4804,7 +4821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -4925,13 +4942,13 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -4948,13 +4965,13 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -4971,13 +4988,13 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4994,13 +5011,13 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -5017,13 +5034,13 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -5040,10 +5057,10 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -5063,13 +5080,13 @@
         <v>40</v>
       </c>
       <c r="E10">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -5086,13 +5103,13 @@
         <v>45</v>
       </c>
       <c r="E11">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -5109,13 +5126,13 @@
         <v>50</v>
       </c>
       <c r="E12">
-        <v>1800</v>
+        <v>180</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -5132,13 +5149,13 @@
         <v>55</v>
       </c>
       <c r="E13">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -5155,13 +5172,13 @@
         <v>60</v>
       </c>
       <c r="E14">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G14">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -5178,13 +5195,13 @@
         <v>65</v>
       </c>
       <c r="E15">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="G15">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -5201,13 +5218,13 @@
         <v>70</v>
       </c>
       <c r="E16">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="F16">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -5224,13 +5241,13 @@
         <v>75</v>
       </c>
       <c r="E17">
-        <v>1800</v>
+        <v>240</v>
       </c>
       <c r="F17">
-        <v>14</v>
+        <v>7.5</v>
       </c>
       <c r="G17">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -5247,13 +5264,13 @@
         <v>80</v>
       </c>
       <c r="E18">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="F18">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G18">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -5270,13 +5287,13 @@
         <v>85</v>
       </c>
       <c r="E19">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="F19">
-        <v>16</v>
+        <v>8.5</v>
       </c>
       <c r="G19">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -5293,13 +5310,13 @@
         <v>90</v>
       </c>
       <c r="E20">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G20">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -5316,13 +5333,13 @@
         <v>95</v>
       </c>
       <c r="E21">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>9.5</v>
       </c>
       <c r="G21">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -5339,13 +5356,13 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G22">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -5362,13 +5379,13 @@
         <v>105</v>
       </c>
       <c r="E23">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="G23">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0352C0C-03DC-437F-B5D8-7A69162A046E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4506CC-274C-45FC-8991-348103622C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="PartsData" sheetId="1" r:id="rId3"/>
     <sheet name="FoodData" sheetId="4" r:id="rId4"/>
     <sheet name="LevelData" sheetId="5" r:id="rId5"/>
-    <sheet name="BuffData" sheetId="7" r:id="rId6"/>
-    <sheet name="ItemData" sheetId="9" r:id="rId7"/>
-    <sheet name="EggData" sheetId="10" r:id="rId8"/>
-    <sheet name="AccessoriesData" sheetId="12" r:id="rId9"/>
-    <sheet name="ShopData" sheetId="11" r:id="rId10"/>
-    <sheet name="EventData" sheetId="14" r:id="rId11"/>
-    <sheet name="GachaData" sheetId="13" r:id="rId12"/>
-    <sheet name="SnailGuide" sheetId="15" r:id="rId13"/>
+    <sheet name="LevelUpAdvantage" sheetId="16" r:id="rId6"/>
+    <sheet name="BuffData" sheetId="7" r:id="rId7"/>
+    <sheet name="ItemData" sheetId="9" r:id="rId8"/>
+    <sheet name="EggData" sheetId="10" r:id="rId9"/>
+    <sheet name="AccessoriesData" sheetId="12" r:id="rId10"/>
+    <sheet name="ShopData" sheetId="11" r:id="rId11"/>
+    <sheet name="EventData" sheetId="14" r:id="rId12"/>
+    <sheet name="GachaData" sheetId="13" r:id="rId13"/>
+    <sheet name="SnailGuide" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="302">
   <si>
     <t>ALL</t>
   </si>
@@ -120,10 +121,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>RequiredExp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NeedFullPoint</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1158,6 +1155,22 @@
   </si>
   <si>
     <t>food_lettuce</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelUpTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedFullPointPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedHappyPointPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acceleration</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2002,7 +2015,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
@@ -2016,13 +2029,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>10</v>
@@ -2030,58 +2043,58 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2098,7 +2111,7 @@
         <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2115,7 +2128,7 @@
         <v>200</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2132,7 +2145,7 @@
         <v>400</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2140,7 +2153,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2149,7 +2162,7 @@
         <v>300</v>
       </c>
       <c r="F11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2166,155 +2179,155 @@
         <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
         <v>77</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16">
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
         <v>96</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
         <v>93</v>
-      </c>
-      <c r="B18" t="s">
-        <v>94</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" t="s">
         <v>119</v>
-      </c>
-      <c r="B23" t="s">
-        <v>120</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2323,15 +2336,15 @@
         <v>250</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2340,7 +2353,7 @@
         <v>260</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2388,6 +2401,108 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="38.375" customWidth="1"/>
+    <col min="5" max="5" width="33.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E79052-7558-4F08-8689-6E3AEA3B2BB4}">
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2440,34 +2555,34 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>20</v>
@@ -2475,69 +2590,69 @@
     </row>
     <row r="3" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I3" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K4">
         <f>F4/2</f>
@@ -2546,34 +2661,34 @@
     </row>
     <row r="5" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F5">
         <v>7</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K5">
         <f t="shared" ref="K5:K9" si="0">F5/2</f>
@@ -2582,34 +2697,34 @@
     </row>
     <row r="6" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F6">
         <v>7</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
@@ -2618,34 +2733,34 @@
     </row>
     <row r="7" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H7" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I7" t="b">
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
@@ -2654,34 +2769,34 @@
     </row>
     <row r="8" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
@@ -2690,34 +2805,34 @@
     </row>
     <row r="9" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9">
         <v>300</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
@@ -2726,28 +2841,28 @@
     </row>
     <row r="10" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -2755,34 +2870,34 @@
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11">
         <v>500</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K11">
         <f t="shared" ref="K11:K13" si="1">F11/2</f>
@@ -2791,34 +2906,34 @@
     </row>
     <row r="12" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12">
         <v>500</v>
       </c>
       <c r="G12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K12">
         <f t="shared" si="1"/>
@@ -2827,34 +2942,34 @@
     </row>
     <row r="13" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13">
         <v>500</v>
       </c>
       <c r="G13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K13">
         <f t="shared" si="1"/>
@@ -2867,7 +2982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458B497A-C730-4596-89CB-D0A93B688F99}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2901,53 +3016,53 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2961,13 +3076,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2981,13 +3096,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3001,13 +3116,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3021,13 +3136,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3041,13 +3156,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3061,13 +3176,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3085,7 +3200,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F49BF-A4DD-4B19-8FB8-F431AABBF38F}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3116,47 +3231,47 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3167,13 +3282,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3184,13 +3299,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3201,13 +3316,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3218,13 +3333,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3235,13 +3350,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3252,13 +3367,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -3269,13 +3384,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -3286,13 +3401,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -3303,13 +3418,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -3324,7 +3439,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D9379-7367-49DF-A5FF-B5D057BE72CF}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3379,89 +3494,89 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>216</v>
-      </c>
       <c r="F3" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>221</v>
-      </c>
       <c r="J3" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>239</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" t="s">
         <v>211</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>212</v>
       </c>
-      <c r="C4" t="s">
-        <v>213</v>
-      </c>
       <c r="D4" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -3493,7 +3608,7 @@
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3518,7 +3633,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -3526,7 +3641,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -3534,7 +3649,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3542,7 +3657,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -3550,7 +3665,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -3558,7 +3673,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -3566,7 +3681,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -3574,7 +3689,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3582,7 +3697,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -3590,7 +3705,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -3598,7 +3713,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -3606,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -3614,7 +3729,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -3622,7 +3737,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -3630,10 +3745,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" t="s">
         <v>205</v>
-      </c>
-      <c r="C18" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -3641,7 +3756,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -3649,7 +3764,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -3657,7 +3772,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -3665,10 +3780,10 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -3676,7 +3791,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -3684,7 +3799,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -3692,7 +3807,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -3700,50 +3815,50 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3808,42 +3923,42 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1</v>
@@ -3855,581 +3970,581 @@
         <v>17</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F4" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="11">
         <v>10</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F5" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H5" s="11">
         <v>10</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H6" s="11">
         <v>10</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H7" s="11">
         <v>10</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F8" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H8" s="11">
         <v>10</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F9" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H9" s="11">
         <v>10</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F10" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H10" s="11">
         <v>10</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F11" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H11" s="11">
         <v>10</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E12" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="F12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>258</v>
-      </c>
-      <c r="F12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>259</v>
       </c>
       <c r="H12" s="11">
         <v>10</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F13" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H13" s="11">
         <v>10</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F14" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H14" s="11">
         <v>10</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F15" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H15" s="11">
         <v>10</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F16" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H16" s="11">
         <v>10</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F17" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H17" s="11">
         <v>10</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F18" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H18" s="11">
         <v>10</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F19" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H19" s="11">
         <v>10</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F20" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H20" s="11">
         <v>10</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F21" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H21" s="11">
         <v>10</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F22" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H22" s="11">
         <v>10</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F23" s="11" t="b">
         <v>0</v>
@@ -4439,24 +4554,24 @@
         <v>10</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>14</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F24" s="11" t="b">
         <v>0</v>
@@ -4466,24 +4581,24 @@
         <v>10</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F25" s="11" t="b">
         <v>0</v>
@@ -4493,24 +4608,24 @@
         <v>10</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>14</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F26" s="11" t="b">
         <v>0</v>
@@ -4520,152 +4635,152 @@
         <v>10</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="F27" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H27" s="11">
         <v>10</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H28" s="11">
         <v>10</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H29" s="11">
         <v>10</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F30" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H30" s="11">
         <v>10</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F31" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H31" s="11">
         <v>10</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4717,13 +4832,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>20</v>
@@ -4732,36 +4847,36 @@
         <v>20</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>4</v>
@@ -4769,13 +4884,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -4784,18 +4899,18 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -4806,13 +4921,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -4823,13 +4938,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
         <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
       </c>
       <c r="D7">
         <v>15</v>
@@ -4838,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4910,22 +5025,22 @@
         <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>23</v>
-      </c>
       <c r="D3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -4956,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>3600</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -4979,7 +5094,7 @@
         <v>3</v>
       </c>
       <c r="B6">
-        <v>50</v>
+        <v>3600</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -5002,7 +5117,7 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="C7">
         <v>25</v>
@@ -5025,7 +5140,7 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>150</v>
+        <v>3600</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -5048,7 +5163,7 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>200</v>
+        <v>3600</v>
       </c>
       <c r="C9">
         <v>35</v>
@@ -5071,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="B10">
-        <v>250</v>
+        <v>3600</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -5094,7 +5209,7 @@
         <v>8</v>
       </c>
       <c r="B11">
-        <v>300</v>
+        <v>3600</v>
       </c>
       <c r="C11">
         <v>45</v>
@@ -5117,7 +5232,7 @@
         <v>9</v>
       </c>
       <c r="B12">
-        <v>350</v>
+        <v>3600</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -5140,7 +5255,7 @@
         <v>10</v>
       </c>
       <c r="B13">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="C13">
         <v>55</v>
@@ -5163,7 +5278,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>450</v>
+        <v>3600</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -5186,7 +5301,7 @@
         <v>12</v>
       </c>
       <c r="B15">
-        <v>500</v>
+        <v>3600</v>
       </c>
       <c r="C15">
         <v>65</v>
@@ -5209,7 +5324,7 @@
         <v>13</v>
       </c>
       <c r="B16">
-        <v>550</v>
+        <v>3600</v>
       </c>
       <c r="C16">
         <v>70</v>
@@ -5232,7 +5347,7 @@
         <v>14</v>
       </c>
       <c r="B17">
-        <v>600</v>
+        <v>3600</v>
       </c>
       <c r="C17">
         <v>75</v>
@@ -5255,7 +5370,7 @@
         <v>15</v>
       </c>
       <c r="B18">
-        <v>650</v>
+        <v>3600</v>
       </c>
       <c r="C18">
         <v>80</v>
@@ -5278,7 +5393,7 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>700</v>
+        <v>3600</v>
       </c>
       <c r="C19">
         <v>85</v>
@@ -5301,7 +5416,7 @@
         <v>17</v>
       </c>
       <c r="B20">
-        <v>750</v>
+        <v>3600</v>
       </c>
       <c r="C20">
         <v>90</v>
@@ -5324,7 +5439,7 @@
         <v>18</v>
       </c>
       <c r="B21">
-        <v>800</v>
+        <v>3600</v>
       </c>
       <c r="C21">
         <v>95</v>
@@ -5347,7 +5462,7 @@
         <v>19</v>
       </c>
       <c r="B22">
-        <v>850</v>
+        <v>3600</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5370,7 +5485,7 @@
         <v>20</v>
       </c>
       <c r="B23">
-        <v>900</v>
+        <v>3600</v>
       </c>
       <c r="C23">
         <v>105</v>
@@ -5386,6 +5501,78 @@
       </c>
       <c r="G23">
         <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F1A7F3-09F6-4D37-9AF6-9380FF50317C}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.25" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.5</v>
+      </c>
+      <c r="B4">
+        <v>0.5</v>
+      </c>
+      <c r="C4">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -5394,7 +5581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52956C56-C508-4E59-B61A-55300084C3C6}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5424,53 +5611,53 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>1800</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -5479,7 +5666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6AA64B-9C5B-493D-8ADD-D4B51FF2294C}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5502,21 +5689,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>4</v>
@@ -5524,13 +5711,13 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
         <v>71</v>
       </c>
-      <c r="B4" t="s">
-        <v>72</v>
-      </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -5539,7 +5726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8799056C-300F-4910-A643-17063CC9919B}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5569,172 +5756,70 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="E2" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" t="s">
         <v>159</v>
       </c>
-      <c r="C5" t="s">
-        <v>160</v>
-      </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="38.375" customWidth="1"/>
-    <col min="5" max="5" width="33.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4506CC-274C-45FC-8991-348103622C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A6AEF1-886E-4A4F-AEA3-2416618A8B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="303">
   <si>
     <t>ALL</t>
   </si>
@@ -1171,6 +1171,10 @@
   </si>
   <si>
     <t>Acceleration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseHappyPointTime</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4964,17 +4968,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48BD49A-A9D0-46FB-B798-026EB3CD9B33}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="12.875" customWidth="1"/>
     <col min="5" max="5" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4996,8 +5001,11 @@
       <c r="G1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
@@ -5019,8 +5027,11 @@
       <c r="G2" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
@@ -5037,13 +5048,16 @@
         <v>44</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5060,13 +5074,16 @@
         <v>120</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5083,13 +5100,16 @@
         <v>120</v>
       </c>
       <c r="F5">
+        <v>120</v>
+      </c>
+      <c r="G5">
         <v>1.5</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5106,13 +5126,16 @@
         <v>120</v>
       </c>
       <c r="F6">
+        <v>120</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -5129,13 +5152,16 @@
         <v>180</v>
       </c>
       <c r="F7">
+        <v>180</v>
+      </c>
+      <c r="G7">
         <v>2.5</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -5152,13 +5178,16 @@
         <v>180</v>
       </c>
       <c r="F8">
+        <v>180</v>
+      </c>
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -5175,13 +5204,16 @@
         <v>180</v>
       </c>
       <c r="F9">
+        <v>180</v>
+      </c>
+      <c r="G9">
         <v>3.5</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -5198,13 +5230,16 @@
         <v>180</v>
       </c>
       <c r="F10">
+        <v>180</v>
+      </c>
+      <c r="G10">
         <v>4</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -5221,13 +5256,16 @@
         <v>180</v>
       </c>
       <c r="F11">
+        <v>180</v>
+      </c>
+      <c r="G11">
         <v>4.5</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -5244,13 +5282,16 @@
         <v>180</v>
       </c>
       <c r="F12">
+        <v>180</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -5267,13 +5308,16 @@
         <v>240</v>
       </c>
       <c r="F13">
+        <v>240</v>
+      </c>
+      <c r="G13">
         <v>5.5</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -5290,13 +5334,16 @@
         <v>240</v>
       </c>
       <c r="F14">
+        <v>240</v>
+      </c>
+      <c r="G14">
         <v>6</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -5313,13 +5360,16 @@
         <v>240</v>
       </c>
       <c r="F15">
+        <v>240</v>
+      </c>
+      <c r="G15">
         <v>6.5</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -5336,13 +5386,16 @@
         <v>240</v>
       </c>
       <c r="F16">
+        <v>240</v>
+      </c>
+      <c r="G16">
         <v>7</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -5359,13 +5412,16 @@
         <v>240</v>
       </c>
       <c r="F17">
+        <v>240</v>
+      </c>
+      <c r="G17">
         <v>7.5</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -5382,13 +5438,16 @@
         <v>300</v>
       </c>
       <c r="F18">
+        <v>300</v>
+      </c>
+      <c r="G18">
         <v>8</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -5405,13 +5464,16 @@
         <v>300</v>
       </c>
       <c r="F19">
+        <v>300</v>
+      </c>
+      <c r="G19">
         <v>8.5</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -5428,13 +5490,16 @@
         <v>300</v>
       </c>
       <c r="F20">
+        <v>300</v>
+      </c>
+      <c r="G20">
         <v>9</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -5451,13 +5516,16 @@
         <v>300</v>
       </c>
       <c r="F21">
+        <v>300</v>
+      </c>
+      <c r="G21">
         <v>9.5</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -5474,13 +5542,16 @@
         <v>300</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="G22">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -5497,9 +5568,12 @@
         <v>300</v>
       </c>
       <c r="F23">
+        <v>300</v>
+      </c>
+      <c r="G23">
         <v>10.5</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>11</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A6AEF1-886E-4A4F-AEA3-2416618A8B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CC7DFF-D559-4831-B96F-2547DC0B1FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="303">
   <si>
     <t>ALL</t>
   </si>
@@ -5074,7 +5074,7 @@
         <v>120</v>
       </c>
       <c r="F4">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -5100,7 +5100,7 @@
         <v>120</v>
       </c>
       <c r="F5">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G5">
         <v>1.5</v>
@@ -5126,7 +5126,7 @@
         <v>120</v>
       </c>
       <c r="F6">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -5152,7 +5152,7 @@
         <v>180</v>
       </c>
       <c r="F7">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="G7">
         <v>2.5</v>
@@ -5178,7 +5178,7 @@
         <v>180</v>
       </c>
       <c r="F8">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -5204,7 +5204,7 @@
         <v>180</v>
       </c>
       <c r="F9">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G9">
         <v>3.5</v>
@@ -5230,7 +5230,7 @@
         <v>180</v>
       </c>
       <c r="F10">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G10">
         <v>4</v>
@@ -5256,7 +5256,7 @@
         <v>180</v>
       </c>
       <c r="F11">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G11">
         <v>4.5</v>
@@ -5282,7 +5282,7 @@
         <v>180</v>
       </c>
       <c r="F12">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5308,7 +5308,7 @@
         <v>240</v>
       </c>
       <c r="F13">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G13">
         <v>5.5</v>
@@ -5334,7 +5334,7 @@
         <v>240</v>
       </c>
       <c r="F14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -5360,7 +5360,7 @@
         <v>240</v>
       </c>
       <c r="F15">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="G15">
         <v>6.5</v>
@@ -5386,7 +5386,7 @@
         <v>240</v>
       </c>
       <c r="F16">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="G16">
         <v>7</v>
@@ -5412,7 +5412,7 @@
         <v>240</v>
       </c>
       <c r="F17">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="G17">
         <v>7.5</v>
@@ -5438,7 +5438,7 @@
         <v>300</v>
       </c>
       <c r="F18">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -5464,7 +5464,7 @@
         <v>300</v>
       </c>
       <c r="F19">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G19">
         <v>8.5</v>
@@ -5490,7 +5490,7 @@
         <v>300</v>
       </c>
       <c r="F20">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G20">
         <v>9</v>
@@ -5516,7 +5516,7 @@
         <v>300</v>
       </c>
       <c r="F21">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G21">
         <v>9.5</v>
@@ -5542,7 +5542,7 @@
         <v>300</v>
       </c>
       <c r="F22">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -5568,7 +5568,7 @@
         <v>300</v>
       </c>
       <c r="F23">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="G23">
         <v>10.5</v>
@@ -5586,15 +5586,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F1A7F3-09F6-4D37-9AF6-9380FF50317C}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.25" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5604,8 +5605,11 @@
       <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>20</v>
       </c>
@@ -5615,8 +5619,11 @@
       <c r="C2" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>300</v>
       </c>
@@ -5626,8 +5633,11 @@
       <c r="C3" s="8" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.5</v>
       </c>
@@ -5638,7 +5648,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5647,6 +5657,9 @@
       </c>
       <c r="C5">
         <v>0.5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CC7DFF-D559-4831-B96F-2547DC0B1FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A810D25F-3B70-4301-96E3-0ACA5557EA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="304">
   <si>
     <t>ALL</t>
   </si>
@@ -1175,6 +1175,10 @@
   </si>
   <si>
     <t>UseHappyPointTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Double</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4851,7 +4855,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>27</v>
@@ -5620,7 +5624,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>23</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -5704,7 +5708,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>9</v>
+        <v>303</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>26</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A810D25F-3B70-4301-96E3-0ACA5557EA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B90B11D-CD72-43BB-B82B-0B77E17F7582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="1980" yWindow="3285" windowWidth="20910" windowHeight="11835" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="307">
   <si>
     <t>ALL</t>
   </si>
@@ -1179,6 +1179,17 @@
   </si>
   <si>
     <t>Double</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeformGroup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullableint</t>
+  </si>
+  <si>
+    <t>[부드러움]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1186,7 +1197,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1262,6 +1273,23 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1373,7 +1401,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1411,12 +1439,62 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 10" xfId="1" xr:uid="{6B9E6416-5075-49D2-A13D-39D9EF488B06}"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1980,16 +2058,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2801ABBC-ECD4-42AF-8E66-C3E5B26CC90B}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="43.125" customWidth="1"/>
+    <col min="3" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="43.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -2005,11 +2083,14 @@
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2025,11 +2106,14 @@
       <c r="E2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -2045,11 +2129,14 @@
       <c r="E3" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -2059,11 +2146,11 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -2073,11 +2160,11 @@
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -2087,11 +2174,11 @@
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2101,152 +2188,161 @@
       <c r="C7">
         <v>3</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="8" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="E8">
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
         <v>100</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="9" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="13">
         <v>2</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="13">
         <v>200</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="10" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="13">
         <v>3</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="13">
         <v>400</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="11" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="13">
         <v>4</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="13">
         <v>300</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="12" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="13">
         <v>5</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="13">
         <v>50</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" s="13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="C13" s="14">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="14">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" s="14" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="14">
         <v>3</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="14">
         <v>4</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" s="14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -2256,11 +2352,11 @@
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -2270,11 +2366,11 @@
       <c r="C18">
         <v>2</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>92</v>
       </c>
@@ -2284,11 +2380,11 @@
       <c r="C19">
         <v>3</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -2298,11 +2394,11 @@
       <c r="C20">
         <v>4</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -2312,11 +2408,11 @@
       <c r="C21">
         <v>5</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -2326,11 +2422,11 @@
       <c r="C22">
         <v>6</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -2343,11 +2439,11 @@
       <c r="E23">
         <v>250</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>116</v>
       </c>
@@ -2360,48 +2456,56 @@
       <c r="E24">
         <v>260</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>129</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A3">
-    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="20" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2 B1">
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:E3">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  <conditionalFormatting sqref="D3:F3">
+    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3872,12 +3976,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B90B11D-CD72-43BB-B82B-0B77E17F7582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3250E662-7698-45E4-BF96-6D26F88F8001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="3285" windowWidth="20910" windowHeight="11835" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="1980" yWindow="3285" windowWidth="21195" windowHeight="11835" tabRatio="866" activeTab="8" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -18,15 +18,16 @@
     <sheet name="PartsData" sheetId="1" r:id="rId3"/>
     <sheet name="FoodData" sheetId="4" r:id="rId4"/>
     <sheet name="LevelData" sheetId="5" r:id="rId5"/>
-    <sheet name="LevelUpAdvantage" sheetId="16" r:id="rId6"/>
-    <sheet name="BuffData" sheetId="7" r:id="rId7"/>
-    <sheet name="ItemData" sheetId="9" r:id="rId8"/>
-    <sheet name="EggData" sheetId="10" r:id="rId9"/>
-    <sheet name="AccessoriesData" sheetId="12" r:id="rId10"/>
-    <sheet name="ShopData" sheetId="11" r:id="rId11"/>
-    <sheet name="EventData" sheetId="14" r:id="rId12"/>
-    <sheet name="GachaData" sheetId="13" r:id="rId13"/>
-    <sheet name="SnailGuide" sheetId="15" r:id="rId14"/>
+    <sheet name="BubbleData" sheetId="17" r:id="rId6"/>
+    <sheet name="LevelUpAdvantage" sheetId="16" r:id="rId7"/>
+    <sheet name="BuffData" sheetId="7" r:id="rId8"/>
+    <sheet name="ItemData" sheetId="9" r:id="rId9"/>
+    <sheet name="EggData" sheetId="10" r:id="rId10"/>
+    <sheet name="AccessoriesData" sheetId="12" r:id="rId11"/>
+    <sheet name="ShopData" sheetId="11" r:id="rId12"/>
+    <sheet name="EventData" sheetId="14" r:id="rId13"/>
+    <sheet name="GachaData" sheetId="13" r:id="rId14"/>
+    <sheet name="SnailGuide" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="311">
   <si>
     <t>ALL</t>
   </si>
@@ -639,10 +640,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>pangcoin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>egg_common</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1190,6 +1187,26 @@
   </si>
   <si>
     <t>[부드러움]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoinCoolTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 말풍선</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bubble_coin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_coin</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1197,7 +1214,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1273,15 +1290,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -1401,7 +1409,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1440,9 +1448,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2104,10 +2109,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -2127,10 +2132,10 @@
         <v>41</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>10</v>
@@ -2223,7 +2228,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>59</v>
@@ -2243,7 +2248,7 @@
         <v>400</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>60</v>
@@ -2254,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C11" s="13">
         <v>4</v>
@@ -2263,10 +2268,10 @@
         <v>300</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2286,59 +2291,59 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="14">
-        <v>1</v>
-      </c>
-      <c r="G13" s="14" t="s">
+      <c r="C13" s="13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13">
         <v>2</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13">
         <v>3</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="13">
         <v>4</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="13" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2496,16 +2501,16 @@
     <cfRule type="duplicateValues" dxfId="10" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2513,6 +2518,108 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8799056C-300F-4910-A643-17063CC9919B}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="3" width="18.375" customWidth="1"/>
+    <col min="4" max="4" width="39.75" customWidth="1"/>
+    <col min="5" max="5" width="39.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2614,7 +2721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E79052-7558-4F08-8689-6E3AEA3B2BB4}">
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3094,7 +3201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458B497A-C730-4596-89CB-D0A93B688F99}">
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3140,7 +3247,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>24</v>
@@ -3312,7 +3419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F49BF-A4DD-4B19-8FB8-F431AABBF38F}">
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3551,7 +3658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D9379-7367-49DF-A5FF-B5D057BE72CF}">
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3618,25 +3725,25 @@
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>73</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>73</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -3650,45 +3757,45 @@
         <v>69</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>215</v>
-      </c>
       <c r="F3" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>220</v>
-      </c>
       <c r="J3" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" t="s">
         <v>210</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>211</v>
       </c>
-      <c r="C4" t="s">
-        <v>212</v>
-      </c>
       <c r="D4" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3720,7 +3827,7 @@
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3745,7 +3852,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -3753,7 +3860,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -3761,7 +3868,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3769,7 +3876,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -3777,7 +3884,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -3785,7 +3892,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -3793,7 +3900,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -3801,7 +3908,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3809,7 +3916,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -3817,7 +3924,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -3825,7 +3932,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -3833,7 +3940,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -3841,7 +3948,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -3849,7 +3956,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -3857,10 +3964,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" t="s">
         <v>204</v>
-      </c>
-      <c r="C18" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -3868,7 +3975,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -3876,7 +3983,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -3884,7 +3991,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -3892,10 +3999,10 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -3903,7 +4010,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -3911,7 +4018,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -3919,7 +4026,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -3927,61 +4034,61 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4041,10 +4148,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>26</v>
@@ -4053,7 +4160,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>24</v>
@@ -4067,7 +4174,7 @@
         <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>84</v>
@@ -4082,7 +4189,7 @@
         <v>17</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>155</v>
@@ -4093,10 +4200,10 @@
     </row>
     <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>52</v>
@@ -4105,27 +4212,27 @@
         <v>11</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F4" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H4" s="11">
         <v>10</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>52</v>
@@ -4134,27 +4241,27 @@
         <v>11</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F5" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H5" s="11">
         <v>10</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>52</v>
@@ -4163,27 +4270,27 @@
         <v>11</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H6" s="11">
         <v>10</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>52</v>
@@ -4192,27 +4299,27 @@
         <v>11</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H7" s="11">
         <v>10</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>52</v>
@@ -4221,27 +4328,27 @@
         <v>11</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F8" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H8" s="11">
         <v>10</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>52</v>
@@ -4250,27 +4357,27 @@
         <v>11</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F9" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H9" s="11">
         <v>10</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>52</v>
@@ -4279,27 +4386,27 @@
         <v>11</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F10" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H10" s="11">
         <v>10</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>52</v>
@@ -4308,27 +4415,27 @@
         <v>11</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F11" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H11" s="11">
         <v>10</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>52</v>
@@ -4337,27 +4444,27 @@
         <v>11</v>
       </c>
       <c r="E12" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="F12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>257</v>
-      </c>
-      <c r="F12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>258</v>
       </c>
       <c r="H12" s="11">
         <v>10</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>52</v>
@@ -4366,27 +4473,27 @@
         <v>11</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F13" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H13" s="11">
         <v>10</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>52</v>
@@ -4395,27 +4502,27 @@
         <v>11</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F14" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H14" s="11">
         <v>10</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>52</v>
@@ -4424,27 +4531,27 @@
         <v>11</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F15" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H15" s="11">
         <v>10</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>52</v>
@@ -4453,27 +4560,27 @@
         <v>11</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F16" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H16" s="11">
         <v>10</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>52</v>
@@ -4482,56 +4589,56 @@
         <v>11</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F17" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H17" s="11">
         <v>10</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>11</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F18" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H18" s="11">
         <v>10</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>52</v>
@@ -4540,27 +4647,27 @@
         <v>13</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F19" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H19" s="11">
         <v>10</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>52</v>
@@ -4569,27 +4676,27 @@
         <v>13</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F20" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H20" s="11">
         <v>10</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>52</v>
@@ -4598,27 +4705,27 @@
         <v>13</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F21" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H21" s="11">
         <v>10</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>52</v>
@@ -4627,27 +4734,27 @@
         <v>13</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F22" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H22" s="11">
         <v>10</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>52</v>
@@ -4656,7 +4763,7 @@
         <v>14</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F23" s="11" t="b">
         <v>0</v>
@@ -4666,15 +4773,15 @@
         <v>10</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>52</v>
@@ -4683,7 +4790,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F24" s="11" t="b">
         <v>0</v>
@@ -4693,15 +4800,15 @@
         <v>10</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>52</v>
@@ -4710,7 +4817,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F25" s="11" t="b">
         <v>0</v>
@@ -4720,15 +4827,15 @@
         <v>10</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>52</v>
@@ -4737,7 +4844,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F26" s="11" t="b">
         <v>0</v>
@@ -4747,152 +4854,152 @@
         <v>10</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F27" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H27" s="11">
         <v>10</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H28" s="11">
         <v>10</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H29" s="11">
         <v>10</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F30" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H30" s="11">
         <v>10</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F31" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H31" s="11">
         <v>10</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -5011,7 +5118,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -5076,7 +5183,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48BD49A-A9D0-46FB-B798-026EB3CD9B33}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -5085,9 +5192,12 @@
     <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.75" customWidth="1"/>
     <col min="8" max="8" width="15.625" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="15.25" customWidth="1"/>
+    <col min="11" max="11" width="17.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -5112,8 +5222,17 @@
       <c r="H1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
@@ -5138,13 +5257,22 @@
       <c r="H2" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
@@ -5156,16 +5284,25 @@
         <v>44</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>49</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5190,8 +5327,17 @@
       <c r="H4">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <v>1800</v>
+      </c>
+      <c r="J4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5216,8 +5362,17 @@
       <c r="H5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <v>1800</v>
+      </c>
+      <c r="J5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5242,8 +5397,17 @@
       <c r="H6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <v>1800</v>
+      </c>
+      <c r="J6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -5268,8 +5432,17 @@
       <c r="H7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <v>1800</v>
+      </c>
+      <c r="J7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -5294,8 +5467,17 @@
       <c r="H8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <v>1800</v>
+      </c>
+      <c r="J8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -5320,8 +5502,17 @@
       <c r="H9">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <v>1800</v>
+      </c>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -5346,8 +5537,17 @@
       <c r="H10">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <v>1800</v>
+      </c>
+      <c r="J10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -5372,8 +5572,17 @@
       <c r="H11">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <v>1800</v>
+      </c>
+      <c r="J11" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -5398,8 +5607,17 @@
       <c r="H12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <v>1800</v>
+      </c>
+      <c r="J12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -5424,8 +5642,17 @@
       <c r="H13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <v>1800</v>
+      </c>
+      <c r="J13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -5450,8 +5677,17 @@
       <c r="H14">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <v>1800</v>
+      </c>
+      <c r="J14" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -5476,8 +5712,17 @@
       <c r="H15">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <v>1800</v>
+      </c>
+      <c r="J15" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -5502,8 +5747,17 @@
       <c r="H16">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <v>1800</v>
+      </c>
+      <c r="J16" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -5528,8 +5782,17 @@
       <c r="H17">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <v>1800</v>
+      </c>
+      <c r="J17" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -5554,8 +5817,17 @@
       <c r="H18">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <v>1200</v>
+      </c>
+      <c r="J18" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -5580,8 +5852,17 @@
       <c r="H19">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <v>1200</v>
+      </c>
+      <c r="J19" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -5606,8 +5887,17 @@
       <c r="H20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <v>1200</v>
+      </c>
+      <c r="J20" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -5632,8 +5922,17 @@
       <c r="H21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <v>1200</v>
+      </c>
+      <c r="J21" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -5658,8 +5957,17 @@
       <c r="H22">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <v>1200</v>
+      </c>
+      <c r="J22" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -5683,6 +5991,15 @@
       </c>
       <c r="H23">
         <v>11</v>
+      </c>
+      <c r="I23">
+        <v>1200</v>
+      </c>
+      <c r="J23" t="s">
+        <v>70</v>
+      </c>
+      <c r="K23">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5693,6 +6010,53 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE7402E-9381-444B-A1AD-921D46BBAC61}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="23.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F1A7F3-09F6-4D37-9AF6-9380FF50317C}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5728,18 +6092,18 @@
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>301</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>67</v>
@@ -5776,7 +6140,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52956C56-C508-4E59-B61A-55300084C3C6}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5812,7 +6176,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>26</v>
@@ -5861,7 +6225,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6AA64B-9C5B-493D-8ADD-D4B51FF2294C}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5912,109 +6276,7 @@
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8799056C-300F-4910-A643-17063CC9919B}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="3" width="18.375" customWidth="1"/>
-    <col min="4" max="4" width="39.75" customWidth="1"/>
-    <col min="5" max="5" width="39.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3250E662-7698-45E4-BF96-6D26F88F8001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBDB175-FEEB-45D3-80D8-97E772337A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="3285" windowWidth="21195" windowHeight="11835" tabRatio="866" activeTab="8" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="1980" yWindow="3285" windowWidth="21195" windowHeight="11835" tabRatio="866" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="312">
   <si>
     <t>ALL</t>
   </si>
@@ -1207,6 +1207,10 @@
   </si>
   <si>
     <t>item_coin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[코인]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5334,7 +5338,7 @@
         <v>70</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -5369,7 +5373,7 @@
         <v>70</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -5404,7 +5408,7 @@
         <v>70</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -5439,7 +5443,7 @@
         <v>70</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -5474,7 +5478,7 @@
         <v>70</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -5509,7 +5513,7 @@
         <v>70</v>
       </c>
       <c r="K9">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -5544,7 +5548,7 @@
         <v>70</v>
       </c>
       <c r="K10">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -5579,7 +5583,7 @@
         <v>70</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -5614,7 +5618,7 @@
         <v>70</v>
       </c>
       <c r="K12">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -5649,7 +5653,7 @@
         <v>70</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -5684,7 +5688,7 @@
         <v>70</v>
       </c>
       <c r="K14">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -5719,7 +5723,7 @@
         <v>70</v>
       </c>
       <c r="K15">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -5754,7 +5758,7 @@
         <v>70</v>
       </c>
       <c r="K16">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -5789,7 +5793,7 @@
         <v>70</v>
       </c>
       <c r="K17">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -5824,7 +5828,7 @@
         <v>70</v>
       </c>
       <c r="K18">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -5859,7 +5863,7 @@
         <v>70</v>
       </c>
       <c r="K19">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -5894,7 +5898,7 @@
         <v>70</v>
       </c>
       <c r="K20">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -5929,7 +5933,7 @@
         <v>70</v>
       </c>
       <c r="K21">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5964,7 +5968,7 @@
         <v>70</v>
       </c>
       <c r="K22">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -5999,7 +6003,7 @@
         <v>70</v>
       </c>
       <c r="K23">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -6011,42 +6015,55 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE7402E-9381-444B-A1AD-921D46BBAC61}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="23.875" customWidth="1"/>
+    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" t="s">
         <v>309</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>308</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBDB175-FEEB-45D3-80D8-97E772337A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B6990B-F5A2-4936-B967-09222A461E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="3285" windowWidth="21195" windowHeight="11835" tabRatio="866" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="2" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="316">
   <si>
     <t>ALL</t>
   </si>
@@ -1211,6 +1211,22 @@
   </si>
   <si>
     <t>[코인]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody03_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4101,7 +4117,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -4755,7 +4771,7 @@
     </row>
     <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>173</v>
+        <v>312</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>275</v>
@@ -4764,25 +4780,27 @@
         <v>52</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>171</v>
+        <v>313</v>
       </c>
       <c r="F23" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>314</v>
+      </c>
       <c r="H23" s="11">
         <v>10</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>168</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>275</v>
@@ -4794,7 +4812,7 @@
         <v>14</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c r="F24" s="11" t="b">
         <v>0</v>
@@ -4804,12 +4822,12 @@
         <v>10</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>271</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>275</v>
@@ -4821,7 +4839,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F25" s="11" t="b">
         <v>0</v>
@@ -4831,12 +4849,12 @@
         <v>10</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>275</v>
@@ -4848,7 +4866,7 @@
         <v>14</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F26" s="11" t="b">
         <v>0</v>
@@ -4858,12 +4876,12 @@
         <v>10</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>275</v>
@@ -4872,27 +4890,25 @@
         <v>52</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>187</v>
+        <v>270</v>
       </c>
       <c r="F27" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>227</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G27" s="11"/>
       <c r="H27" s="11">
         <v>10</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>275</v>
@@ -4904,24 +4920,24 @@
         <v>165</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="F28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="H28" s="11">
         <v>10</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>275</v>
@@ -4933,24 +4949,24 @@
         <v>165</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H29" s="11">
         <v>10</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>275</v>
@@ -4962,24 +4978,24 @@
         <v>165</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F30" s="11" t="b">
         <v>1</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H30" s="11">
         <v>10</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>275</v>
@@ -4997,12 +5013,41 @@
         <v>1</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>264</v>
+        <v>179</v>
       </c>
       <c r="H31" s="11">
         <v>10</v>
       </c>
       <c r="I31" s="11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F32" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="H32" s="11">
+        <v>10</v>
+      </c>
+      <c r="I32" s="11" t="s">
         <v>234</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B6990B-F5A2-4936-B967-09222A461E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6526126-32E1-42AA-B7FC-6A9C3A8C563D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="2" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="EventData" sheetId="14" r:id="rId13"/>
     <sheet name="GachaData" sheetId="13" r:id="rId14"/>
     <sheet name="SnailGuide" sheetId="15" r:id="rId15"/>
+    <sheet name="LanguageData" sheetId="18" r:id="rId16"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="330">
   <si>
     <t>ALL</t>
   </si>
@@ -1227,6 +1228,59 @@
   </si>
   <si>
     <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레벨]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}살</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이02]</t>
+  </si>
+  <si>
+    <t>commonfeeler05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler05_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler05_c02</t>
+  </si>
+  <si>
+    <t>분홍 얼룩 고양이 귀.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>갈색 얼룩 고양이 귀.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_zucchini</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_tofu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>ResourceSize</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3824,6 +3878,53 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD86155D-B955-41F0-BC82-EF0EDA2597DB}">
   <dimension ref="A1:C31"/>
@@ -4117,7 +4218,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.875" customWidth="1"/>
@@ -5049,6 +5150,64 @@
       </c>
       <c r="I32" s="11" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F33" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H33" s="11">
+        <v>10</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F34" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="H34" s="11">
+        <v>10</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -5203,6 +5362,9 @@
       <c r="E6">
         <v>5</v>
       </c>
+      <c r="H6" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -5222,6 +5384,9 @@
       </c>
       <c r="F7" t="s">
         <v>68</v>
+      </c>
+      <c r="H7" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -6060,55 +6225,67 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE7402E-9381-444B-A1AD-921D46BBAC61}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="23.875" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>311</v>
       </c>
       <c r="B4" t="s">
         <v>309</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
         <v>308</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6526126-32E1-42AA-B7FC-6A9C3A8C563D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860FBB81-F5A4-4BD1-900A-3A2F6F7616F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="408">
   <si>
     <t>ALL</t>
   </si>
@@ -134,10 +134,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Name</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>String</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -302,10 +298,6 @@
   </si>
   <si>
     <t>[포만감01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Info</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -832,10 +824,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>일반달팽이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>아주 전형적인 달팽이.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -872,415 +860,643 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>버섯 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler01_c01</t>
+  </si>
+  <si>
+    <t>commonfeeler04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler02</t>
+  </si>
+  <si>
+    <t>commonfeeler03</t>
+  </si>
+  <si>
+    <t>[일반_뱅글더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_만두더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PartsId04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColorId04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_껍질04]</t>
+  </si>
+  <si>
+    <t>[일반_껍질05]</t>
+  </si>
+  <si>
+    <t>[일반_껍질06]</t>
+  </si>
+  <si>
+    <t>[일반_껍질07]</t>
+  </si>
+  <si>
+    <t>commonshell01_c08</t>
+  </si>
+  <si>
+    <t>[일반_명주달팽이껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_긴껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_긴껍질02]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질03]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질04]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질05]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질06]</t>
+  </si>
+  <si>
+    <t>commonshell02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler04_c02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈03]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈04]</t>
+  </si>
+  <si>
+    <t>commoneyes02</t>
+  </si>
+  <si>
+    <t>commoneyes03</t>
+  </si>
+  <si>
+    <t>commoneyes04</t>
+  </si>
+  <si>
+    <t>PartsGroupId</t>
+  </si>
+  <si>
+    <t>[일반그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반그룹], [레어그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum&lt;PartsType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_몸02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸03]</t>
+  </si>
+  <si>
+    <t>SortOrder</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullableint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_일반더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_일반더듬이02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_뚱뚱몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚱뚱몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;string&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullablestring</t>
+  </si>
+  <si>
+    <t>Size</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_lettuce</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelUpTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedFullPointPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedHappyPointPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acceleration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseHappyPointTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Double</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeformGroup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullableint</t>
+  </si>
+  <si>
+    <t>[부드러움]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoinCoolTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 말풍선</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bubble_coin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_coin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[코인]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody03_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레벨]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}살</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이02]</t>
+  </si>
+  <si>
+    <t>commonfeeler05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler05_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler05_c02</t>
+  </si>
+  <si>
+    <t>food_zucchini</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_tofu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>ResourceSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NameId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[상추]</t>
+  </si>
+  <si>
+    <t>[토마토]</t>
+  </si>
+  <si>
+    <t>InfoId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[포만감01]</t>
+  </si>
+  <si>
+    <t>[팽이코인정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>팽이코인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반알01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어알01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[모자01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[모자02정보]</t>
+  </si>
+  <si>
+    <t>[가방01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연두색의 껍질.</t>
+  </si>
+  <si>
+    <t>갈색의 껍질.</t>
+  </si>
+  <si>
+    <t>초록색의 껍질.</t>
+  </si>
+  <si>
+    <t>보라색의 껍질.</t>
+  </si>
+  <si>
+    <t>파란색의 껍질.</t>
+  </si>
+  <si>
+    <t>누군가를 열렬히 좋아하다가 생긴 무늬 껍질.</t>
+  </si>
+  <si>
+    <t>상추가 너무 좋아서 껍질에 새기기로 했다.</t>
+  </si>
+  <si>
+    <t>명주 달팽이의 껍질.</t>
+  </si>
+  <si>
+    <t>아프리카 왕달팽이의 껍질. (금와)</t>
+  </si>
+  <si>
+    <t>돌맹이를 깎아 만든 껍질. 농담이다.</t>
+  </si>
+  <si>
+    <t>나쵸칩에 맛들린 달팽이의 일탈 껍질.</t>
+  </si>
+  <si>
+    <t>갈색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>파란색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>주황색의 민무늬 껍질.</t>
+  </si>
+  <si>
     <t>당근이 너무 좋아서 집으로 삼기로 했다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연두색의 몸.</t>
+  </si>
+  <si>
+    <t>분홍색의 몸.</t>
+  </si>
+  <si>
+    <t>갈색의 몸.</t>
+  </si>
+  <si>
+    <t>느려졌지만, 행복해보인다.</t>
+  </si>
+  <si>
+    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
+  </si>
+  <si>
+    <t>웃는 달팽이의 눈.</t>
+  </si>
+  <si>
+    <t>눈치보는 달팽이의 눈.</t>
+  </si>
+  <si>
+    <t>무념무상의 눈.</t>
   </si>
   <si>
     <t>정신없이 버섯을 먹다보니 변해있었다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>초록색의 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>갈색의 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>연두색의 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>연두색의 몸.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯 더듬이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler01_c01</t>
-  </si>
-  <si>
-    <t>commonfeeler04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler02</t>
-  </si>
-  <si>
-    <t>commonfeeler03</t>
-  </si>
-  <si>
-    <t>[일반_뱅글더듬이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_만두더듬이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오글거리는 드라마를 봤더니 변해있었다.</t>
+  </si>
+  <si>
+    <t>만두를 먹어보고 싶었던 더듬이.</t>
   </si>
   <si>
     <t>연두색의 더듬이.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>갈색의 더듬이.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>오글거리는 드라마를 봤더니 변해있었다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>만두를 먹어보고 싶었던 더듬이.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PartsId04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColorId04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_껍질04]</t>
-  </si>
-  <si>
-    <t>[일반_껍질05]</t>
-  </si>
-  <si>
-    <t>[일반_껍질06]</t>
-  </si>
-  <si>
-    <t>[일반_껍질07]</t>
-  </si>
-  <si>
-    <t>commonshell01_c08</t>
-  </si>
-  <si>
-    <t>보라색의 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>파란색의 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>누군가를 열렬히 좋아하다가 생긴 무늬 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>상추가 너무 좋아서 껍질에 새기기로 했다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>명주 달팽이의 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_명주달팽이껍질]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_긴껍질01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_긴껍질02]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질03]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질04]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질05]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질06]</t>
-  </si>
-  <si>
-    <t>commonshell02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonshell02_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>아프리카 왕달팽이의 껍질. (금와)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>나쵸칩에 맛들린 달팽이의 일탈 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>갈색의 민무늬 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>파란색의 민무늬 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주황색의 민무늬 껍질.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌맹이를 깎아 만든 껍질. 농담이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler04_c02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_눈02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈03]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈04]</t>
-  </si>
-  <si>
-    <t>commoneyes02</t>
-  </si>
-  <si>
-    <t>commoneyes03</t>
-  </si>
-  <si>
-    <t>commoneyes04</t>
-  </si>
-  <si>
-    <t>웃는 달팽이의 눈.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>눈치보는 달팽이의 눈.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>무념무상의 눈.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PartsGroupId</t>
-  </si>
-  <si>
-    <t>[일반그룹]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[레어그룹]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반그룹], [레어그룹]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum&lt;PartsType&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_몸02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸03]</t>
-  </si>
-  <si>
-    <t>분홍색의 몸.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>갈색의 몸.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SortOrder</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nullableint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_일반더듬이01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_일반더듬이02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_뚱뚱몸01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>뚱뚱몸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody02_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>느려졌지만, 행복해보인다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;string&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nullablestring</t>
-  </si>
-  <si>
-    <t>Size</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>food_lettuce</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelUpTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeedFullPointPercent</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeedHappyPointPercent</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Acceleration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseHappyPointTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Double</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DeformGroup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nullableint</t>
-  </si>
-  <si>
-    <t>[부드러움]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CoinCoolTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 말풍선</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bubble_coin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_coin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[코인]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody03_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kr</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[레벨]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{0}살</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이02]</t>
-  </si>
-  <si>
-    <t>commonfeeler05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler05_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler05_c02</t>
+  </si>
+  <si>
+    <t>갈색 얼룩 고양이 귀.</t>
   </si>
   <si>
     <t>분홍 얼룩 고양이 귀.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>갈색 얼룩 고양이 귀.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>food_zucchini</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>food_tofu</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>ResourceSize</t>
+  </si>
+  <si>
+    <t>[일반_껍질01정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질02정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질03정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질04정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질05정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질06정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질07정보]</t>
+  </si>
+  <si>
+    <t>[일반_명주달팽이껍질정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질01정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질02정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질03정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질04정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질05정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질06정보]</t>
+  </si>
+  <si>
+    <t>[레어_당근껍질정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸03정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_뚱뚱몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈03정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈04정보]</t>
+  </si>
+  <si>
+    <t>[일반_버섯더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_뱅글더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_만두더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_일반더듬이01정보]</t>
+  </si>
+  <si>
+    <t>[일반_일반더듬이02정보]</t>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01정보]</t>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이02정보]</t>
+  </si>
+  <si>
+    <t>껍질01</t>
+  </si>
+  <si>
+    <t>껍질02</t>
+  </si>
+  <si>
+    <t>껍질03</t>
+  </si>
+  <si>
+    <t>껍질04</t>
+  </si>
+  <si>
+    <t>껍질05</t>
+  </si>
+  <si>
+    <t>껍질06</t>
+  </si>
+  <si>
+    <t>껍질07</t>
+  </si>
+  <si>
+    <t>명주달팽이껍질</t>
+  </si>
+  <si>
+    <t>긴껍질01</t>
+  </si>
+  <si>
+    <t>긴껍질02</t>
+  </si>
+  <si>
+    <t>긴껍질03</t>
+  </si>
+  <si>
+    <t>긴껍질04</t>
+  </si>
+  <si>
+    <t>긴껍질05</t>
+  </si>
+  <si>
+    <t>긴껍질06</t>
+  </si>
+  <si>
+    <t>버섯더듬이</t>
+  </si>
+  <si>
+    <t>뱅글더듬이</t>
+  </si>
+  <si>
+    <t>만두더듬이</t>
+  </si>
+  <si>
+    <t>일반더듬이01</t>
+  </si>
+  <si>
+    <t>일반더듬이02</t>
+  </si>
+  <si>
+    <t>고양이더듬이01</t>
+  </si>
+  <si>
+    <t>고양이더듬이02</t>
+  </si>
+  <si>
+    <t>레어_당근껍질</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸02</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸03</t>
+  </si>
+  <si>
+    <t>일반달팽이_뚱뚱몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_손몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈01</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈02</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈03</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈04</t>
+  </si>
+  <si>
+    <t>일반 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_일반달팽이]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2183,10 +2399,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -2200,16 +2416,16 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>10</v>
@@ -2217,58 +2433,58 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2285,7 +2501,7 @@
         <v>100</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2302,10 +2518,10 @@
         <v>200</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2322,10 +2538,10 @@
         <v>400</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2333,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C11" s="13">
         <v>4</v>
@@ -2342,10 +2558,10 @@
         <v>300</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2362,155 +2578,155 @@
         <v>50</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="13">
         <v>1</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C14" s="13">
         <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>76</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="C15" s="13">
         <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" s="13">
         <v>4</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="G19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="G21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2519,15 +2735,15 @@
         <v>250</v>
       </c>
       <c r="G23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -2536,7 +2752,7 @@
         <v>260</v>
       </c>
       <c r="G24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2593,16 +2809,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8799056C-300F-4910-A643-17063CC9919B}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="3" width="18.375" customWidth="1"/>
-    <col min="4" max="4" width="39.75" customWidth="1"/>
-    <col min="5" max="5" width="39.875" customWidth="1"/>
+    <col min="1" max="2" width="17.625" customWidth="1"/>
+    <col min="3" max="4" width="18.375" customWidth="1"/>
+    <col min="5" max="5" width="39.75" customWidth="1"/>
+    <col min="6" max="6" width="39.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2610,102 +2826,118 @@
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>0</v>
-      </c>
       <c r="E1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="B3" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>86</v>
-      </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" t="s">
+        <v>304</v>
+      </c>
+      <c r="F4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" t="s">
         <v>156</v>
       </c>
-      <c r="D4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
       <c r="E5" t="s">
-        <v>277</v>
+        <v>305</v>
+      </c>
+      <c r="F5" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="38.375" customWidth="1"/>
-    <col min="5" max="5" width="33.25" customWidth="1"/>
+    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="38.375" customWidth="1"/>
+    <col min="6" max="6" width="33.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2713,80 +2945,98 @@
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="B3" s="8" t="s">
-        <v>116</v>
+        <v>297</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="E5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" t="s">
         <v>130</v>
       </c>
-      <c r="B6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" t="s">
-        <v>133</v>
+      <c r="E6" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -2848,34 +3098,34 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>20</v>
@@ -2883,69 +3133,69 @@
     </row>
     <row r="3" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K4">
         <f>F4/2</f>
@@ -2954,34 +3204,34 @@
     </row>
     <row r="5" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>7</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K5">
         <f t="shared" ref="K5:K9" si="0">F5/2</f>
@@ -2990,34 +3240,34 @@
     </row>
     <row r="6" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F6">
         <v>7</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K6">
         <f t="shared" si="0"/>
@@ -3026,34 +3276,34 @@
     </row>
     <row r="7" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F7">
         <v>12</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
@@ -3062,34 +3312,34 @@
     </row>
     <row r="8" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
@@ -3098,34 +3348,34 @@
     </row>
     <row r="9" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F9">
         <v>300</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
@@ -3134,28 +3384,28 @@
     </row>
     <row r="10" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -3163,34 +3413,34 @@
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F11">
         <v>500</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K11">
         <f t="shared" ref="K11:K13" si="1">F11/2</f>
@@ -3199,34 +3449,34 @@
     </row>
     <row r="12" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F12">
         <v>500</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K12">
         <f t="shared" si="1"/>
@@ -3235,34 +3485,34 @@
     </row>
     <row r="13" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>500</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K13">
         <f t="shared" si="1"/>
@@ -3315,13 +3565,13 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>24</v>
@@ -3329,33 +3579,33 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3369,13 +3619,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3389,13 +3639,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3409,13 +3659,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3429,13 +3679,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3449,13 +3699,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3469,13 +3719,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3527,7 +3777,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>23</v>
@@ -3541,30 +3791,30 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3575,13 +3825,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3592,13 +3842,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3609,13 +3859,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3626,13 +3876,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3643,13 +3893,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3660,13 +3910,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -3677,13 +3927,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -3694,13 +3944,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -3711,13 +3961,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -3790,86 +4040,86 @@
         <v>24</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>25</v>
+        <v>297</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="H3" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>219</v>
-      </c>
       <c r="J3" s="8" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
-        <v>211</v>
+        <v>407</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3880,10 +4130,10 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3900,23 +4150,671 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>316</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>308</v>
+      </c>
+      <c r="B16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B22" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B23" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="B24" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" t="s">
         <v>317</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" t="s">
         <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B27" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B28" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="B29" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="B30" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="B31" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B32" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="B33" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="B34" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="B35" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="B36" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B37" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B38" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="B39" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="B40" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B41" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B43" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B44" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B45" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="B46" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="B47" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="B48" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="B49" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="B50" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="B51" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="B52" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3948,7 +4846,7 @@
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -3973,7 +4871,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -3981,7 +4879,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -3989,7 +4887,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3997,7 +4895,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -4005,7 +4903,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -4013,7 +4911,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -4021,7 +4919,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -4029,7 +4927,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -4037,7 +4935,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -4045,7 +4943,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -4053,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -4061,7 +4959,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -4069,7 +4967,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -4077,7 +4975,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -4085,10 +4983,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -4096,7 +4994,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -4104,7 +5002,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -4112,7 +5010,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -4120,10 +5018,10 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -4131,7 +5029,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -4139,7 +5037,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -4147,7 +5045,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -4155,50 +5053,50 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4218,21 +5116,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.875" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17.125" customWidth="1"/>
-    <col min="6" max="6" width="14.375" customWidth="1"/>
-    <col min="7" max="7" width="28.5" customWidth="1"/>
-    <col min="8" max="8" width="16.125" customWidth="1"/>
-    <col min="9" max="9" width="52.125" customWidth="1"/>
+    <col min="1" max="2" width="21.875" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="14.375" customWidth="1"/>
+    <col min="8" max="8" width="28.5" customWidth="1"/>
+    <col min="9" max="9" width="16.125" customWidth="1"/>
+    <col min="10" max="10" width="52.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4246,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>2</v>
@@ -4255,13 +5153,16 @@
         <v>2</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -4269,945 +5170,1044 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G4" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" s="11">
+        <v>10</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="I5" s="11">
+        <v>10</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="I6" s="11">
+        <v>10</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="I7" s="11">
+        <v>10</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="I8" s="11">
+        <v>10</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I9" s="11">
+        <v>10</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I10" s="11">
+        <v>10</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="G11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="I11" s="11">
+        <v>10</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="I12" s="11">
+        <v>10</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G13" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="I13" s="11">
+        <v>10</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G14" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="I14" s="11">
+        <v>10</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G15" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="I15" s="11">
+        <v>10</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G16" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="I16" s="11">
+        <v>10</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G17" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="I17" s="11">
+        <v>10</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="G18" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="11">
+        <v>10</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G19" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="I19" s="11">
+        <v>10</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="11">
+        <v>10</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="G21" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="11">
+        <v>10</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="G22" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="I22" s="11">
+        <v>10</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="G23" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="I23" s="11">
+        <v>10</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11">
+        <v>10</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="G25" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11">
+        <v>10</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="G26" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11">
+        <v>10</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="G27" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11">
+        <v>10</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="H4" s="11">
+      <c r="F28" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="G28" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I28" s="11">
         <v>10</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="H5" s="11">
+      <c r="J28" s="11" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G29" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="I29" s="11">
         <v>10</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J29" s="11" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="B30" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G30" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" s="11">
         <v>10</v>
       </c>
-      <c r="I6" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F7" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="J30" s="11" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G31" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I31" s="11">
         <v>10</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="J31" s="11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G32" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="H8" s="11">
+      <c r="I32" s="11">
         <v>10</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="J32" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G33" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I33" s="11">
         <v>10</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F10" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="H10" s="11">
+      <c r="J33" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G34" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="I34" s="11">
         <v>10</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="H11" s="11">
-        <v>10</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="H12" s="11">
-        <v>10</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F13" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="H13" s="11">
-        <v>10</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F14" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="H14" s="11">
-        <v>10</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F15" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="H15" s="11">
-        <v>10</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F16" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="H16" s="11">
-        <v>10</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F17" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="H17" s="11">
-        <v>10</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="F18" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="H18" s="11">
-        <v>10</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="H19" s="11">
-        <v>10</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F20" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="11">
-        <v>10</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F21" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" s="11">
-        <v>10</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="F22" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="H22" s="11">
-        <v>10</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="F23" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="H23" s="11">
-        <v>10</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="F24" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11">
-        <v>10</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="F25" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11">
-        <v>10</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="F26" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11">
-        <v>10</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="F27" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11">
-        <v>10</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="F28" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="H28" s="11">
-        <v>10</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="F29" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="H29" s="11">
-        <v>10</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F30" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="11">
-        <v>10</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F31" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31" s="11">
-        <v>10</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F32" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="H32" s="11">
-        <v>10</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="F33" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H33" s="11">
-        <v>10</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="F34" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="H34" s="11">
-        <v>10</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>324</v>
+      <c r="J34" s="11" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5262,10 +6262,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>20</v>
@@ -5277,33 +6277,33 @@
         <v>23</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>297</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>4</v>
@@ -5311,13 +6311,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>298</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -5326,18 +6326,18 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>299</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -5348,13 +6348,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -5363,18 +6363,18 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D7">
         <v>15</v>
@@ -5383,15 +6383,16 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5486,34 +6487,34 @@
         <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -5545,7 +6546,7 @@
         <v>1800</v>
       </c>
       <c r="J4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K4">
         <v>10</v>
@@ -5580,7 +6581,7 @@
         <v>1800</v>
       </c>
       <c r="J5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K5">
         <v>11</v>
@@ -5615,7 +6616,7 @@
         <v>1800</v>
       </c>
       <c r="J6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -5650,7 +6651,7 @@
         <v>1800</v>
       </c>
       <c r="J7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K7">
         <v>13</v>
@@ -5685,7 +6686,7 @@
         <v>1800</v>
       </c>
       <c r="J8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K8">
         <v>14</v>
@@ -5720,7 +6721,7 @@
         <v>1800</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K9">
         <v>15</v>
@@ -5755,7 +6756,7 @@
         <v>1800</v>
       </c>
       <c r="J10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K10">
         <v>16</v>
@@ -5790,7 +6791,7 @@
         <v>1800</v>
       </c>
       <c r="J11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K11">
         <v>17</v>
@@ -5825,7 +6826,7 @@
         <v>1800</v>
       </c>
       <c r="J12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K12">
         <v>18</v>
@@ -5860,7 +6861,7 @@
         <v>1800</v>
       </c>
       <c r="J13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K13">
         <v>19</v>
@@ -5895,7 +6896,7 @@
         <v>1800</v>
       </c>
       <c r="J14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K14">
         <v>20</v>
@@ -5930,7 +6931,7 @@
         <v>1800</v>
       </c>
       <c r="J15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K15">
         <v>21</v>
@@ -5965,7 +6966,7 @@
         <v>1800</v>
       </c>
       <c r="J16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K16">
         <v>22</v>
@@ -6000,7 +7001,7 @@
         <v>1800</v>
       </c>
       <c r="J17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K17">
         <v>23</v>
@@ -6035,7 +7036,7 @@
         <v>1200</v>
       </c>
       <c r="J18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K18">
         <v>24</v>
@@ -6070,7 +7071,7 @@
         <v>1200</v>
       </c>
       <c r="J19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K19">
         <v>25</v>
@@ -6105,7 +7106,7 @@
         <v>1200</v>
       </c>
       <c r="J20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K20">
         <v>26</v>
@@ -6140,7 +7141,7 @@
         <v>1200</v>
       </c>
       <c r="J21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K21">
         <v>27</v>
@@ -6175,7 +7176,7 @@
         <v>1200</v>
       </c>
       <c r="J22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K22">
         <v>28</v>
@@ -6210,7 +7211,7 @@
         <v>1200</v>
       </c>
       <c r="J23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K23">
         <v>30</v>
@@ -6252,10 +7253,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -6263,13 +7264,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>10</v>
@@ -6277,16 +7278,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="B4" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -6331,21 +7332,21 @@
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -6370,7 +7371,7 @@
         <v>0.5</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -6412,50 +7413,50 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>69</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>1800</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -6466,15 +7467,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF6AA64B-9C5B-493D-8ADD-D4B51FF2294C}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="34.625" customWidth="1"/>
-    <col min="3" max="3" width="37.625" customWidth="1"/>
+    <col min="1" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="34.625" customWidth="1"/>
+    <col min="4" max="4" width="37.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -6482,40 +7483,52 @@
         <v>0</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>69</v>
+        <v>297</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>310</v>
+        <v>302</v>
+      </c>
+      <c r="D4" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860FBB81-F5A4-4BD1-900A-3A2F6F7616F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C230FE-235C-40B4-8E39-68A6A6C95A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="420">
   <si>
     <t>ALL</t>
   </si>
@@ -1498,6 +1498,42 @@
   <si>
     <t>[도감_일반달팽이]</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[이름없음]</t>
+  </si>
+  <si>
+    <t>이름 없음</t>
+  </si>
+  <si>
+    <t>[달팽이목록]</t>
+  </si>
+  <si>
+    <t>달팽이 목록</t>
+  </si>
+  <si>
+    <t>[음식목록]</t>
+  </si>
+  <si>
+    <t>음식 목록</t>
+  </si>
+  <si>
+    <t>[보유중인알]</t>
+  </si>
+  <si>
+    <t>보유중인 알</t>
+  </si>
+  <si>
+    <t>[상점]</t>
+  </si>
+  <si>
+    <t>상점</t>
+  </si>
+  <si>
+    <t>[먹이기]</t>
+  </si>
+  <si>
+    <t>먹이기</t>
   </si>
 </sst>
 </file>
@@ -2764,43 +2800,43 @@
   <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="24" priority="23"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:F3">
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1">
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2 B1">
-    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:F3">
-    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2968,7 +3004,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4130,7 +4166,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -4815,6 +4851,54 @@
       </c>
       <c r="B85" s="11" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>408</v>
+      </c>
+      <c r="B86" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>410</v>
+      </c>
+      <c r="B87" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>412</v>
+      </c>
+      <c r="B88" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>414</v>
+      </c>
+      <c r="B89" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>416</v>
+      </c>
+      <c r="B90" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>418</v>
+      </c>
+      <c r="B91" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5102,12 +5186,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7497,7 +7581,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>25</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C230FE-235C-40B4-8E39-68A6A6C95A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4078EA2A-6AD0-4338-9861-4773C1137B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="1350" yWindow="2100" windowWidth="21195" windowHeight="11835" tabRatio="866" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="424">
   <si>
     <t>ALL</t>
   </si>
@@ -1534,6 +1534,19 @@
   </si>
   <si>
     <t>먹이기</t>
+  </si>
+  <si>
+    <t>rarity_common</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarity_rare</t>
+  </si>
+  <si>
+    <t>rarity_epic</t>
+  </si>
+  <si>
+    <t>rarity_legendary</t>
   </si>
 </sst>
 </file>
@@ -2627,6 +2640,9 @@
       <c r="C13" s="13">
         <v>1</v>
       </c>
+      <c r="D13" s="13" t="s">
+        <v>420</v>
+      </c>
       <c r="G13" s="13" t="s">
         <v>78</v>
       </c>
@@ -2641,6 +2657,9 @@
       <c r="C14" s="13">
         <v>2</v>
       </c>
+      <c r="D14" s="13" t="s">
+        <v>421</v>
+      </c>
       <c r="G14" s="13" t="s">
         <v>79</v>
       </c>
@@ -2655,6 +2674,9 @@
       <c r="C15" s="13">
         <v>3</v>
       </c>
+      <c r="D15" s="13" t="s">
+        <v>422</v>
+      </c>
       <c r="G15" s="13" t="s">
         <v>80</v>
       </c>
@@ -2669,6 +2691,9 @@
       <c r="C16" s="13">
         <v>4</v>
       </c>
+      <c r="D16" s="13" t="s">
+        <v>423</v>
+      </c>
       <c r="G16" s="13" t="s">
         <v>81</v>
       </c>
@@ -2683,6 +2708,7 @@
       <c r="C17">
         <v>1</v>
       </c>
+      <c r="D17" s="13"/>
       <c r="G17" t="s">
         <v>94</v>
       </c>
@@ -2697,6 +2723,7 @@
       <c r="C18">
         <v>2</v>
       </c>
+      <c r="D18" s="13"/>
       <c r="G18" t="s">
         <v>92</v>
       </c>
@@ -2711,6 +2738,7 @@
       <c r="C19">
         <v>3</v>
       </c>
+      <c r="D19" s="13"/>
       <c r="G19" t="s">
         <v>98</v>
       </c>
@@ -2725,6 +2753,7 @@
       <c r="C20">
         <v>4</v>
       </c>
+      <c r="D20" s="13"/>
       <c r="G20" t="s">
         <v>110</v>
       </c>
@@ -2739,6 +2768,7 @@
       <c r="C21">
         <v>5</v>
       </c>
+      <c r="D21" s="13"/>
       <c r="G21" t="s">
         <v>95</v>
       </c>
@@ -2753,6 +2783,7 @@
       <c r="C22">
         <v>6</v>
       </c>
+      <c r="D22" s="13"/>
       <c r="G22" t="s">
         <v>134</v>
       </c>
@@ -2767,6 +2798,7 @@
       <c r="C23">
         <v>1</v>
       </c>
+      <c r="D23" s="13"/>
       <c r="E23">
         <v>250</v>
       </c>
@@ -2784,6 +2816,7 @@
       <c r="C24">
         <v>2</v>
       </c>
+      <c r="D24" s="13"/>
       <c r="E24">
         <v>260</v>
       </c>
@@ -2800,43 +2833,43 @@
   <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="24" priority="23"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B2:C2 B1">
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:C3">
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="duplicateValues" dxfId="18" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="32"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="23" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:F3">
-    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:C2 B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:C3">
-    <cfRule type="duplicateValues" dxfId="4" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="1" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5186,12 +5219,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4078EA2A-6AD0-4338-9861-4773C1137B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4517C16B-C37E-4A35-8221-4BA488C2E042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1350" yWindow="2100" windowWidth="21195" windowHeight="11835" tabRatio="866" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="1920" yWindow="3225" windowWidth="21195" windowHeight="11835" tabRatio="866" firstSheet="7" activeTab="16" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="GachaData" sheetId="13" r:id="rId14"/>
     <sheet name="SnailGuide" sheetId="15" r:id="rId15"/>
     <sheet name="LanguageData" sheetId="18" r:id="rId16"/>
+    <sheet name="UnlockData" sheetId="19" r:id="rId17"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="437">
   <si>
     <t>ALL</t>
   </si>
@@ -1547,6 +1548,56 @@
   </si>
   <si>
     <t>rarity_legendary</t>
+  </si>
+  <si>
+    <t>Enum&lt;RarityType&gt;</t>
+  </si>
+  <si>
+    <t>HatchTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedConditionValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;ConditionType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConditionType</t>
+  </si>
+  <si>
+    <t>ConditionType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SnailCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유중인 달팽이 개수 조건</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SnailLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달성한 달팽이 레벨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해금조건01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PayItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비용을 지불필요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2402,10 +2453,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2801ABBC-ECD4-42AF-8E66-C3E5B26CC90B}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="3" max="6" width="17.625" customWidth="1"/>
     <col min="7" max="7" width="43.125" customWidth="1"/>
@@ -2822,6 +2873,48 @@
       </c>
       <c r="G24" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>428</v>
+      </c>
+      <c r="B25" t="s">
+        <v>430</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>428</v>
+      </c>
+      <c r="B26" t="s">
+        <v>432</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="G26" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>428</v>
+      </c>
+      <c r="B27" t="s">
+        <v>435</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+      <c r="G27" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -2878,16 +2971,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8799056C-300F-4910-A643-17063CC9919B}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="17.625" customWidth="1"/>
-    <col min="3" max="4" width="18.375" customWidth="1"/>
-    <col min="5" max="5" width="39.75" customWidth="1"/>
-    <col min="6" max="6" width="39.875" customWidth="1"/>
+    <col min="1" max="3" width="17.625" customWidth="1"/>
+    <col min="4" max="5" width="18.375" customWidth="1"/>
+    <col min="6" max="6" width="39.75" customWidth="1"/>
+    <col min="7" max="7" width="39.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2898,16 +2991,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>0</v>
-      </c>
       <c r="F1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -2915,19 +3011,22 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -2935,55 +3034,64 @@
         <v>297</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>84</v>
       </c>
       <c r="B4" t="s">
         <v>84</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>180</v>
+      </c>
+      <c r="D4" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>154</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>304</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>85</v>
       </c>
       <c r="B5" t="s">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5">
+        <v>600</v>
+      </c>
+      <c r="D5" t="s">
         <v>155</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>156</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>305</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>250</v>
       </c>
     </row>
@@ -4932,6 +5040,84 @@
       </c>
       <c r="B91" t="s">
         <v>419</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33BFE4A4-9490-45E8-A658-7D004AD5D50A}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6336,19 +6522,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2444F32-CF16-41C0-B4D3-AE1758A9A6E6}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.625" customWidth="1"/>
-    <col min="5" max="5" width="13.875" customWidth="1"/>
-    <col min="6" max="6" width="15.125" customWidth="1"/>
-    <col min="7" max="7" width="28.875" customWidth="1"/>
-    <col min="8" max="8" width="20.375" customWidth="1"/>
+    <col min="3" max="5" width="13.625" customWidth="1"/>
+    <col min="6" max="6" width="13.875" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="28.875" customWidth="1"/>
+    <col min="9" max="9" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -6371,10 +6557,13 @@
         <v>0</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -6385,22 +6574,25 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>20</v>
+        <v>424</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>20</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -6411,22 +6603,25 @@
         <v>297</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -6436,17 +6631,20 @@
       <c r="C4" t="s">
         <v>298</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>3</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -6456,14 +6654,17 @@
       <c r="C5" t="s">
         <v>299</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5">
         <v>7</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -6473,17 +6674,20 @@
       <c r="C6" t="s">
         <v>62</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6">
         <v>7</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>5</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -6493,16 +6697,19 @@
       <c r="C7" t="s">
         <v>63</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7">
         <v>15</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>67</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>294</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4517C16B-C37E-4A35-8221-4BA488C2E042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1FFB17-BFA5-4FE3-AE0A-82A89FEB8750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="3225" windowWidth="21195" windowHeight="11835" tabRatio="866" firstSheet="7" activeTab="16" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="1" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="470">
   <si>
     <t>ALL</t>
   </si>
@@ -1598,6 +1598,123 @@
   <si>
     <t>비용을 지불필요</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[음식]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달팽이알]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[악세서리]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[자유시장]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[오늘의추천]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[구매하기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>음식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세서리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자유시장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘의 추천</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매하기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화시킬알없음]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화완료]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화 완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화시킬 알이 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody01_c04</t>
+  </si>
+  <si>
+    <t>commonbody01_c05</t>
+  </si>
+  <si>
+    <t>commonbody01_c06</t>
+  </si>
+  <si>
+    <t>commonbody03_c02</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸04]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸05]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸06]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸04정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸05정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸06정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈05]</t>
+  </si>
+  <si>
+    <t>commoneyes05</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈05정보]</t>
   </si>
 </sst>
 </file>
@@ -4307,7 +4424,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5040,6 +5157,78 @@
       </c>
       <c r="B91" t="s">
         <v>419</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>437</v>
+      </c>
+      <c r="B92" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>438</v>
+      </c>
+      <c r="B93" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>439</v>
+      </c>
+      <c r="B94" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>440</v>
+      </c>
+      <c r="B95" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>441</v>
+      </c>
+      <c r="B96" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>442</v>
+      </c>
+      <c r="B97" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>449</v>
+      </c>
+      <c r="B98" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>451</v>
+      </c>
+      <c r="B99" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>452</v>
+      </c>
+      <c r="B100" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -5128,7 +5317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD86155D-B955-41F0-BC82-EF0EDA2597DB}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
@@ -5321,84 +5510,124 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>262</v>
-      </c>
-      <c r="C22" t="s">
-        <v>261</v>
+        <v>455</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>262</v>
+      </c>
+      <c r="C25" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C27" t="s">
-        <v>217</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>164</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>164</v>
+      </c>
+      <c r="B36" t="s">
         <v>179</v>
       </c>
     </row>
@@ -5419,7 +5648,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="21.875" customWidth="1"/>
@@ -6107,10 +6336,10 @@
     </row>
     <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>259</v>
+        <v>459</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>259</v>
+        <v>459</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>248</v>
@@ -6122,27 +6351,27 @@
         <v>13</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="G22" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>262</v>
+        <v>455</v>
       </c>
       <c r="I22" s="11">
         <v>10</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>362</v>
+        <v>462</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>282</v>
+        <v>460</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>282</v>
+        <v>460</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>248</v>
@@ -6154,27 +6383,27 @@
         <v>13</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>283</v>
+        <v>168</v>
       </c>
       <c r="G23" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>284</v>
+        <v>456</v>
       </c>
       <c r="I23" s="11">
         <v>10</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>363</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>171</v>
+        <v>461</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>171</v>
+        <v>461</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>248</v>
@@ -6183,28 +6412,30 @@
         <v>51</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G24" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>457</v>
+      </c>
       <c r="I24" s="11">
         <v>10</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>364</v>
+        <v>464</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>248</v>
@@ -6213,28 +6444,30 @@
         <v>51</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="G25" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>262</v>
+      </c>
       <c r="I25" s="11">
         <v>10</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>248</v>
@@ -6243,28 +6476,30 @@
         <v>51</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="G26" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>284</v>
+      </c>
       <c r="I26" s="11">
         <v>10</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>243</v>
+        <v>465</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>243</v>
+        <v>465</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>248</v>
@@ -6273,28 +6508,30 @@
         <v>51</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="G27" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>458</v>
+      </c>
       <c r="I27" s="11">
         <v>10</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>367</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>248</v>
@@ -6303,30 +6540,28 @@
         <v>51</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="G28" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H28" s="11"/>
       <c r="I28" s="11">
         <v>10</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>248</v>
@@ -6335,30 +6570,28 @@
         <v>51</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="G29" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>173</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H29" s="11"/>
       <c r="I29" s="11">
         <v>10</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>248</v>
@@ -6367,30 +6600,28 @@
         <v>51</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="G30" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>175</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H30" s="11"/>
       <c r="I30" s="11">
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>248</v>
@@ -6399,30 +6630,28 @@
         <v>51</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="G31" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>177</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H31" s="11"/>
       <c r="I31" s="11">
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>258</v>
+        <v>467</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>258</v>
+        <v>467</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>248</v>
@@ -6431,33 +6660,31 @@
         <v>51</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>219</v>
+        <v>468</v>
       </c>
       <c r="G32" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>240</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H32" s="11"/>
       <c r="I32" s="11">
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>372</v>
+        <v>469</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>288</v>
+        <v>184</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>288</v>
+        <v>184</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>51</v>
@@ -6466,30 +6693,30 @@
         <v>163</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>290</v>
+        <v>185</v>
       </c>
       <c r="G33" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>291</v>
+        <v>218</v>
       </c>
       <c r="I33" s="11">
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>289</v>
+        <v>222</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>289</v>
+        <v>222</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>51</v>
@@ -6498,18 +6725,178 @@
         <v>163</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="G34" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>292</v>
+        <v>173</v>
       </c>
       <c r="I34" s="11">
         <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G35" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I35" s="11">
+        <v>10</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G36" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="I36" s="11">
+        <v>10</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="I37" s="11">
+        <v>10</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G38" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I38" s="11">
+        <v>10</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="I39" s="11">
+        <v>10</v>
+      </c>
+      <c r="J39" s="11" t="s">
         <v>374</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1FFB17-BFA5-4FE3-AE0A-82A89FEB8750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0E124E-4EC3-4A0E-A06E-3E6DDA867E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="1" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="472">
   <si>
     <t>ALL</t>
   </si>
@@ -1715,6 +1715,14 @@
   </si>
   <si>
     <t>[일반달팽이_눈05정보]</t>
+  </si>
+  <si>
+    <t>[준비중]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비중입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4424,7 +4432,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5229,6 +5237,14 @@
       </c>
       <c r="B100" t="s">
         <v>453</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>470</v>
+      </c>
+      <c r="B101" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E0E124E-4EC3-4A0E-A06E-3E6DDA867E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB587D7-C2B4-4A4A-9644-07D41B070B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="11" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="473">
   <si>
     <t>ALL</t>
   </si>
@@ -1722,6 +1722,10 @@
   </si>
   <si>
     <t>준비중입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiscountCostCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1924,7 +1928,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1963,6 +1967,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3349,21 +3356,21 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E79052-7558-4F08-8689-6E3AEA3B2BB4}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="17.625" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="17.75" customWidth="1"/>
-    <col min="7" max="7" width="28.125" customWidth="1"/>
-    <col min="8" max="8" width="23.125" customWidth="1"/>
-    <col min="9" max="9" width="19.375" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="6" max="7" width="17.75" customWidth="1"/>
+    <col min="8" max="8" width="28.125" customWidth="1"/>
+    <col min="9" max="9" width="23.125" customWidth="1"/>
+    <col min="10" max="10" width="19.375" customWidth="1"/>
+    <col min="11" max="11" width="16.125" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3389,16 +3396,19 @@
         <v>0</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>0</v>
-      </c>
       <c r="K1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>88</v>
       </c>
@@ -3418,22 +3428,25 @@
         <v>71</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>101</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>89</v>
       </c>
@@ -3453,22 +3466,25 @@
         <v>65</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -3487,24 +3503,27 @@
       <c r="F4">
         <v>5</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="14">
+        <v>3</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
         <v>70</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <f>F4/2</f>
         <v>2.5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -3523,24 +3542,27 @@
       <c r="F5">
         <v>7</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="14">
+        <v>4</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
         <v>70</v>
       </c>
-      <c r="K5">
-        <f t="shared" ref="K5:K9" si="0">F5/2</f>
+      <c r="L5">
+        <f t="shared" ref="L5:L9" si="0">F5/2</f>
         <v>3.5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -3559,24 +3581,27 @@
       <c r="F6">
         <v>7</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="14">
+        <v>4</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
         <v>70</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>93</v>
       </c>
@@ -3595,24 +3620,27 @@
       <c r="F7">
         <v>12</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="14">
+        <v>8</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="I7" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
         <v>70</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -3631,24 +3659,27 @@
       <c r="F8">
         <v>50</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="14">
+        <v>35</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
         <v>70</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>91</v>
       </c>
@@ -3667,24 +3698,27 @@
       <c r="F9">
         <v>300</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="14">
+        <v>210</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
         <v>70</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -3703,17 +3737,18 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="14"/>
+      <c r="H10" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>111</v>
       </c>
@@ -3732,24 +3767,27 @@
       <c r="F11">
         <v>500</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="14">
+        <v>350</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>70</v>
       </c>
-      <c r="K11">
-        <f t="shared" ref="K11:K13" si="1">F11/2</f>
+      <c r="L11">
+        <f t="shared" ref="L11:L13" si="1">F11/2</f>
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>111</v>
       </c>
@@ -3768,24 +3806,27 @@
       <c r="F12">
         <v>500</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="14">
+        <v>350</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="I12" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
         <v>70</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>111</v>
       </c>
@@ -3804,19 +3845,22 @@
       <c r="F13">
         <v>500</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="14">
+        <v>350</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
         <v>70</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB587D7-C2B4-4A4A-9644-07D41B070B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E09323D-C25B-4E8F-A139-B0B6F51F7256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="11" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="2" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="477">
   <si>
     <t>ALL</t>
   </si>
@@ -1726,6 +1726,22 @@
   </si>
   <si>
     <t>DiscountCostCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_아이스크림01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody01_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_아이스크림01정보]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5708,10 +5724,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="21.875" customWidth="1"/>
+    <col min="1" max="1" width="24.125" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="21.25" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
@@ -6292,7 +6309,7 @@
         <v>200</v>
       </c>
       <c r="I18" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>358</v>
@@ -6588,40 +6605,42 @@
     </row>
     <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>171</v>
+        <v>473</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>171</v>
+        <v>473</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>248</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>51</v>
+        <v>155</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>169</v>
+        <v>474</v>
       </c>
       <c r="G28" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>475</v>
+      </c>
       <c r="I28" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>364</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>248</v>
@@ -6633,7 +6652,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="G29" s="11" t="b">
         <v>0</v>
@@ -6643,15 +6662,15 @@
         <v>10</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>248</v>
@@ -6663,7 +6682,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G30" s="11" t="b">
         <v>0</v>
@@ -6673,15 +6692,15 @@
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>248</v>
@@ -6693,7 +6712,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G31" s="11" t="b">
         <v>0</v>
@@ -6703,15 +6722,15 @@
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>467</v>
+        <v>243</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>467</v>
+        <v>243</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>248</v>
@@ -6723,7 +6742,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>468</v>
+        <v>246</v>
       </c>
       <c r="G32" s="11" t="b">
         <v>0</v>
@@ -6733,15 +6752,15 @@
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>469</v>
+        <v>367</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>184</v>
+        <v>467</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>184</v>
+        <v>467</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>248</v>
@@ -6750,30 +6769,28 @@
         <v>51</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>163</v>
+        <v>14</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>185</v>
+        <v>468</v>
       </c>
       <c r="G33" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H33" s="11"/>
       <c r="I33" s="11">
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>368</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>248</v>
@@ -6785,27 +6802,27 @@
         <v>163</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="G34" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
       <c r="I34" s="11">
         <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>248</v>
@@ -6817,27 +6834,27 @@
         <v>163</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G35" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I35" s="11">
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>248</v>
@@ -6849,27 +6866,27 @@
         <v>163</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G36" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I36" s="11">
         <v>10</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>248</v>
@@ -6887,24 +6904,24 @@
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="I37" s="11">
         <v>10</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>51</v>
@@ -6913,27 +6930,27 @@
         <v>163</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>290</v>
+        <v>219</v>
       </c>
       <c r="G38" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="I38" s="11">
         <v>10</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>249</v>
@@ -6951,12 +6968,44 @@
         <v>1</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I39" s="11">
         <v>10</v>
       </c>
       <c r="J39" s="11" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="I40" s="11">
+        <v>10</v>
+      </c>
+      <c r="J40" s="11" t="s">
         <v>374</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E09323D-C25B-4E8F-A139-B0B6F51F7256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EDE61C-8BFF-40C7-B2F3-A9A3140FC935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="2" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="3" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="482">
   <si>
     <t>ALL</t>
   </si>
@@ -1742,6 +1742,26 @@
   </si>
   <si>
     <t>[일반달팽이_아이스크림01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[상추정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[토마토정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[애호박정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[두부정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_tomato</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -7136,6 +7156,9 @@
       <c r="F4">
         <v>3</v>
       </c>
+      <c r="H4" t="s">
+        <v>477</v>
+      </c>
       <c r="I4" t="s">
         <v>266</v>
       </c>
@@ -7159,6 +7182,12 @@
       <c r="F5">
         <v>5</v>
       </c>
+      <c r="H5" t="s">
+        <v>478</v>
+      </c>
+      <c r="I5" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -7179,6 +7208,9 @@
       <c r="F6">
         <v>5</v>
       </c>
+      <c r="H6" t="s">
+        <v>479</v>
+      </c>
       <c r="I6" t="s">
         <v>293</v>
       </c>
@@ -7204,6 +7236,9 @@
       </c>
       <c r="G7" t="s">
         <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>480</v>
       </c>
       <c r="I7" t="s">
         <v>294</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EDE61C-8BFF-40C7-B2F3-A9A3140FC935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDC284E-0EA9-4455-BFC7-931B5D0C0B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="3" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="486">
   <si>
     <t>ALL</t>
   </si>
@@ -1762,6 +1762,22 @@
   </si>
   <si>
     <t>food_tomato</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>etc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mask</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 카테고리 : 마스크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 카테고리 : 기타</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2621,7 +2637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2801ABBC-ECD4-42AF-8E66-C3E5B26CC90B}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -3045,30 +3061,38 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>428</v>
-      </c>
-      <c r="B25" t="s">
-        <v>430</v>
+        <v>114</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>483</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25">
+        <v>251</v>
       </c>
       <c r="G25" t="s">
-        <v>431</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>428</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>432</v>
+        <v>482</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26">
+        <v>255</v>
       </c>
       <c r="G26" t="s">
-        <v>433</v>
+        <v>485</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -3076,12 +3100,40 @@
         <v>428</v>
       </c>
       <c r="B27" t="s">
+        <v>430</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>428</v>
+      </c>
+      <c r="B28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>428</v>
+      </c>
+      <c r="B29" t="s">
         <v>435</v>
       </c>
-      <c r="C27">
+      <c r="C29">
         <v>3</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G29" t="s">
         <v>436</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDC284E-0EA9-4455-BFC7-931B5D0C0B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F72387-B556-43CF-A47E-798691D97774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="494">
   <si>
     <t>ALL</t>
   </si>
@@ -1765,19 +1765,48 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>etc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>mask</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>악세 카테고리 : 마스크</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>악세 카테고리 : 기타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[모자]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[가방]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[마스크]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[기타]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방</t>
+  </si>
+  <si>
+    <t>마스크</t>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>Mask</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3064,7 +3093,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3074,7 +3103,7 @@
         <v>251</v>
       </c>
       <c r="G25" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -3082,7 +3111,7 @@
         <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -3092,7 +3121,7 @@
         <v>255</v>
       </c>
       <c r="G26" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -4564,7 +4593,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5379,9 +5408,42 @@
         <v>471</v>
       </c>
     </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>484</v>
+      </c>
+      <c r="B102" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>485</v>
+      </c>
+      <c r="B103" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>486</v>
+      </c>
+      <c r="B104" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>487</v>
+      </c>
+      <c r="B105" t="s">
+        <v>491</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F72387-B556-43CF-A47E-798691D97774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD41A109-D99C-4065-8275-F06219A56148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="498">
   <si>
     <t>ALL</t>
   </si>
@@ -1807,6 +1807,22 @@
   </si>
   <si>
     <t>Etc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[옷장]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[장착중]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옷장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장착중</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4593,7 +4609,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5438,6 +5454,22 @@
       </c>
       <c r="B105" t="s">
         <v>491</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>494</v>
+      </c>
+      <c r="B106" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>495</v>
+      </c>
+      <c r="B107" t="s">
+        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD41A109-D99C-4065-8275-F06219A56148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F8D38E-4B65-4514-91C9-00B89EE5205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="10" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="501">
   <si>
     <t>ALL</t>
   </si>
@@ -1823,6 +1823,18 @@
   </si>
   <si>
     <t>장착중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>etc01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[천사링01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[천사링01정보]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3369,7 +3381,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -3479,6 +3491,23 @@
       </c>
       <c r="E6" t="s">
         <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D7" t="s">
+        <v>498</v>
+      </c>
+      <c r="E7" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F8D38E-4B65-4514-91C9-00B89EE5205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4326DC7-F8E6-498F-9FFC-0A00E10AD730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="10" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="504">
   <si>
     <t>ALL</t>
   </si>
@@ -1835,6 +1835,18 @@
   </si>
   <si>
     <t>[천사링01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mask01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해골마스크]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해골마스크정보]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3381,7 +3393,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -3508,6 +3520,23 @@
       </c>
       <c r="E7" t="s">
         <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>502</v>
+      </c>
+      <c r="B8" t="s">
+        <v>502</v>
+      </c>
+      <c r="C8" t="s">
+        <v>492</v>
+      </c>
+      <c r="D8" t="s">
+        <v>501</v>
+      </c>
+      <c r="E8" t="s">
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4326DC7-F8E6-498F-9FFC-0A00E10AD730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7511EEF-09C3-4045-8FCE-F8CB2ECE6E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="10" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="17" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="SnailGuide" sheetId="15" r:id="rId15"/>
     <sheet name="LanguageData" sheetId="18" r:id="rId16"/>
     <sheet name="UnlockData" sheetId="19" r:id="rId17"/>
+    <sheet name="GameConfig" sheetId="20" r:id="rId18"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="507">
   <si>
     <t>ALL</t>
   </si>
@@ -646,22 +647,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>eyes_yellow01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>eyes_black01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>mucus_purple01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>mucus_white01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Enum&lt;RarityType&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -704,1149 +689,1169 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>commonfeeler02_c01</t>
+  </si>
+  <si>
+    <t>commonfeeler03_c01</t>
+  </si>
+  <si>
+    <t>commonfeeler04_c01</t>
+  </si>
+  <si>
+    <t>commonbody01_c01</t>
+  </si>
+  <si>
+    <t>commonbody01_c02</t>
+  </si>
+  <si>
+    <t>commonbody01_c03</t>
+  </si>
+  <si>
+    <t>[일반_버섯더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell01_c01</t>
+  </si>
+  <si>
+    <t>commonshell01_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell01_c02</t>
+  </si>
+  <si>
+    <t>commonshell01_c03</t>
+  </si>
+  <si>
+    <t>commonshell01_c04</t>
+  </si>
+  <si>
+    <t>commonshell01_c05</t>
+  </si>
+  <si>
+    <t>commonshell01_c06</t>
+  </si>
+  <si>
+    <t>commonshell01_c07</t>
+  </si>
+  <si>
+    <t>commonshell02_c01</t>
+  </si>
+  <si>
+    <t>commonshell02_c02</t>
+  </si>
+  <si>
+    <t>commonshell02_c03</t>
+  </si>
+  <si>
+    <t>commonshell02_c04</t>
+  </si>
+  <si>
+    <t>commonshell02_c05</t>
+  </si>
+  <si>
+    <t>commonshell02_c06</t>
+  </si>
+  <si>
+    <t>rareshell01_c01</t>
+  </si>
+  <si>
+    <t>[일반_껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_껍질02]</t>
+  </si>
+  <si>
+    <t>[일반_껍질03]</t>
+  </si>
+  <si>
+    <t>[레어_당근껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아주 전형적인 달팽이.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PartsId01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColorId01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell01_c08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PartsId02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColorId02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PartsId03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColorId03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>commonfeeler01_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler02_c01</t>
-  </si>
-  <si>
-    <t>commonfeeler02_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler03_c01</t>
-  </si>
-  <si>
-    <t>commonfeeler03_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler04_c01</t>
-  </si>
-  <si>
-    <t>commonfeeler04_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler04_c02</t>
-  </si>
-  <si>
-    <t>commonbody01_c01</t>
-  </si>
-  <si>
-    <t>commonbody01_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody01_c02</t>
-  </si>
-  <si>
-    <t>commonbody01_c03</t>
-  </si>
-  <si>
-    <t>[일반_버섯더듬이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonfeeler02</t>
+  </si>
+  <si>
+    <t>commonfeeler03</t>
+  </si>
+  <si>
+    <t>[일반_뱅글더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_만두더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PartsId04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColorId04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_껍질04]</t>
+  </si>
+  <si>
+    <t>[일반_껍질05]</t>
+  </si>
+  <si>
+    <t>[일반_껍질06]</t>
+  </si>
+  <si>
+    <t>[일반_껍질07]</t>
+  </si>
+  <si>
+    <t>commonshell01_c08</t>
+  </si>
+  <si>
+    <t>[일반_명주달팽이껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_긴껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_긴껍질02]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질03]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질04]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질05]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질06]</t>
+  </si>
+  <si>
+    <t>commonshell02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈03]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈04]</t>
+  </si>
+  <si>
+    <t>commoneyes02</t>
+  </si>
+  <si>
+    <t>commoneyes03</t>
+  </si>
+  <si>
+    <t>commoneyes04</t>
+  </si>
+  <si>
+    <t>PartsGroupId</t>
+  </si>
+  <si>
+    <t>[일반그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반그룹], [레어그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enum&lt;PartsType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_몸02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸03]</t>
+  </si>
+  <si>
+    <t>SortOrder</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullableint</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_일반더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_일반더듬이02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_뚱뚱몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;string&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullablestring</t>
+  </si>
+  <si>
+    <t>Size</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_lettuce</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelUpTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedFullPointPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedHappyPointPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acceleration</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseHappyPointTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Double</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeformGroup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullableint</t>
+  </si>
+  <si>
+    <t>[부드러움]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoinCoolTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 말풍선</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bubble_coin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>item_coin</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[코인]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody03_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kr</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레벨]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}살</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이02]</t>
+  </si>
+  <si>
+    <t>food_zucchini</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_tofu</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>ResourceSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NameId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[상추]</t>
+  </si>
+  <si>
+    <t>[토마토]</t>
+  </si>
+  <si>
+    <t>InfoId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[포만감01]</t>
+  </si>
+  <si>
+    <t>[팽이코인정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>팽이코인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반알01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어알01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[모자01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[모자02정보]</t>
+  </si>
+  <si>
+    <t>[가방01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>연두색의 껍질.</t>
+  </si>
+  <si>
+    <t>갈색의 껍질.</t>
+  </si>
+  <si>
+    <t>초록색의 껍질.</t>
+  </si>
+  <si>
+    <t>보라색의 껍질.</t>
+  </si>
+  <si>
+    <t>파란색의 껍질.</t>
+  </si>
+  <si>
+    <t>누군가를 열렬히 좋아하다가 생긴 무늬 껍질.</t>
+  </si>
+  <si>
+    <t>상추가 너무 좋아서 껍질에 새기기로 했다.</t>
+  </si>
+  <si>
+    <t>명주 달팽이의 껍질.</t>
+  </si>
+  <si>
+    <t>아프리카 왕달팽이의 껍질. (금와)</t>
+  </si>
+  <si>
+    <t>돌맹이를 깎아 만든 껍질. 농담이다.</t>
+  </si>
+  <si>
+    <t>나쵸칩에 맛들린 달팽이의 일탈 껍질.</t>
+  </si>
+  <si>
+    <t>갈색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>파란색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>주황색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>당근이 너무 좋아서 집으로 삼기로 했다.</t>
+  </si>
+  <si>
+    <t>연두색의 몸.</t>
+  </si>
+  <si>
+    <t>분홍색의 몸.</t>
+  </si>
+  <si>
+    <t>갈색의 몸.</t>
+  </si>
+  <si>
+    <t>느려졌지만, 행복해보인다.</t>
+  </si>
+  <si>
+    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
+  </si>
+  <si>
+    <t>웃는 달팽이의 눈.</t>
+  </si>
+  <si>
+    <t>눈치보는 달팽이의 눈.</t>
+  </si>
+  <si>
+    <t>무념무상의 눈.</t>
+  </si>
+  <si>
+    <t>정신없이 버섯을 먹다보니 변해있었다.</t>
+  </si>
+  <si>
+    <t>오글거리는 드라마를 봤더니 변해있었다.</t>
+  </si>
+  <si>
+    <t>만두를 먹어보고 싶었던 더듬이.</t>
+  </si>
+  <si>
+    <t>연두색의 더듬이.</t>
+  </si>
+  <si>
+    <t>갈색의 더듬이.</t>
+  </si>
+  <si>
+    <t>갈색 얼룩 고양이 귀.</t>
+  </si>
+  <si>
+    <t>분홍 얼룩 고양이 귀.</t>
+  </si>
+  <si>
+    <t>[일반_껍질01정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질02정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질03정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질04정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질05정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질06정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질07정보]</t>
+  </si>
+  <si>
+    <t>[일반_명주달팽이껍질정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질01정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질02정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질03정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질04정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질05정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질06정보]</t>
+  </si>
+  <si>
+    <t>[레어_당근껍질정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸03정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_뚱뚱몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈03정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈04정보]</t>
+  </si>
+  <si>
+    <t>[일반_버섯더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_뱅글더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_만두더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_일반더듬이01정보]</t>
+  </si>
+  <si>
+    <t>[일반_일반더듬이02정보]</t>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01정보]</t>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이02정보]</t>
+  </si>
+  <si>
+    <t>껍질01</t>
+  </si>
+  <si>
+    <t>껍질02</t>
+  </si>
+  <si>
+    <t>껍질03</t>
+  </si>
+  <si>
+    <t>껍질04</t>
+  </si>
+  <si>
+    <t>껍질05</t>
+  </si>
+  <si>
+    <t>껍질06</t>
+  </si>
+  <si>
+    <t>껍질07</t>
+  </si>
+  <si>
+    <t>명주달팽이껍질</t>
+  </si>
+  <si>
+    <t>긴껍질01</t>
+  </si>
+  <si>
+    <t>긴껍질02</t>
+  </si>
+  <si>
+    <t>긴껍질03</t>
+  </si>
+  <si>
+    <t>긴껍질04</t>
+  </si>
+  <si>
+    <t>긴껍질05</t>
+  </si>
+  <si>
+    <t>긴껍질06</t>
+  </si>
+  <si>
+    <t>버섯더듬이</t>
+  </si>
+  <si>
+    <t>뱅글더듬이</t>
+  </si>
+  <si>
+    <t>만두더듬이</t>
+  </si>
+  <si>
+    <t>일반더듬이01</t>
+  </si>
+  <si>
+    <t>일반더듬이02</t>
+  </si>
+  <si>
+    <t>고양이더듬이01</t>
+  </si>
+  <si>
+    <t>고양이더듬이02</t>
+  </si>
+  <si>
+    <t>레어_당근껍질</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸02</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸03</t>
+  </si>
+  <si>
+    <t>일반달팽이_뚱뚱몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_손몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈01</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈02</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈03</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈04</t>
+  </si>
+  <si>
+    <t>일반 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_일반달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[이름없음]</t>
+  </si>
+  <si>
+    <t>이름 없음</t>
+  </si>
+  <si>
+    <t>[달팽이목록]</t>
+  </si>
+  <si>
+    <t>달팽이 목록</t>
+  </si>
+  <si>
+    <t>[음식목록]</t>
+  </si>
+  <si>
+    <t>음식 목록</t>
+  </si>
+  <si>
+    <t>[보유중인알]</t>
+  </si>
+  <si>
+    <t>보유중인 알</t>
+  </si>
+  <si>
+    <t>[상점]</t>
+  </si>
+  <si>
+    <t>상점</t>
+  </si>
+  <si>
+    <t>[먹이기]</t>
+  </si>
+  <si>
+    <t>먹이기</t>
+  </si>
+  <si>
+    <t>rarity_common</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarity_rare</t>
+  </si>
+  <si>
+    <t>rarity_epic</t>
+  </si>
+  <si>
+    <t>rarity_legendary</t>
+  </si>
+  <si>
+    <t>Enum&lt;RarityType&gt;</t>
+  </si>
+  <si>
+    <t>HatchTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedConditionValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;ConditionType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConditionType</t>
+  </si>
+  <si>
+    <t>ConditionType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SnailCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유중인 달팽이 개수 조건</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SnailLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달성한 달팽이 레벨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해금조건01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PayItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비용을 지불필요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[음식]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달팽이알]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[악세서리]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[자유시장]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[오늘의추천]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[구매하기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>음식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세서리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자유시장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘의 추천</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매하기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화시킬알없음]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화완료]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화 완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화시킬 알이 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody01_c04</t>
+  </si>
+  <si>
+    <t>commonbody01_c05</t>
+  </si>
+  <si>
+    <t>commonbody01_c06</t>
+  </si>
+  <si>
+    <t>commonbody03_c02</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸04]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸05]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸06]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸04정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸05정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸06정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈05]</t>
+  </si>
+  <si>
+    <t>commoneyes05</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈05정보]</t>
+  </si>
+  <si>
+    <t>[준비중]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비중입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiscountCostCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_아이스크림01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody01_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_아이스크림01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[상추정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[토마토정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[애호박정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[두부정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_tomato</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 카테고리 : 마스크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 카테고리 : 기타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[모자]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[가방]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[마스크]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[기타]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방</t>
+  </si>
+  <si>
+    <t>마스크</t>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>Mask</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[옷장]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[장착중]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옷장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장착중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>etc01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[천사링01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[천사링01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mask01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해골마스크]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해골마스크정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_오목더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_오목더듬이02]</t>
+  </si>
+  <si>
+    <t>commonfeeler02_c02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_오목더듬이01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell01</t>
+  </si>
+  <si>
+    <t>commonshell02</t>
+  </si>
+  <si>
+    <t>rareshell01</t>
+  </si>
+  <si>
+    <t>commonbody01</t>
+  </si>
+  <si>
+    <t>commonbody02</t>
+  </si>
+  <si>
+    <t>commonbody03</t>
+  </si>
+  <si>
+    <t>rarebody01</t>
   </si>
   <si>
     <t>commonfeeler01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonshell01_c01</t>
-  </si>
-  <si>
-    <t>commonshell01_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonshell01_c02</t>
-  </si>
-  <si>
-    <t>commonshell01_c03</t>
-  </si>
-  <si>
-    <t>commonshell01_c04</t>
-  </si>
-  <si>
-    <t>commonshell01_c05</t>
-  </si>
-  <si>
-    <t>commonshell01_c06</t>
-  </si>
-  <si>
-    <t>commonshell01_c07</t>
-  </si>
-  <si>
-    <t>commonshell02_c01</t>
-  </si>
-  <si>
-    <t>commonshell02_c02</t>
-  </si>
-  <si>
-    <t>commonshell02_c03</t>
-  </si>
-  <si>
-    <t>commonshell02_c04</t>
-  </si>
-  <si>
-    <t>commonshell02_c05</t>
-  </si>
-  <si>
-    <t>commonshell02_c06</t>
-  </si>
-  <si>
-    <t>rareshell01_c01</t>
-  </si>
-  <si>
-    <t>rareshell01_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근 껍따구</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_껍질01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_껍질02]</t>
-  </si>
-  <si>
-    <t>[일반_껍질03]</t>
-  </si>
-  <si>
-    <t>[레어_당근껍질]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>아주 전형적인 달팽이.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rareshell01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PartsId01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColorId01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonshell01_c08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PartsId02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColorId02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PartsId03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColorId03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>버섯 더듬이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler01_c01</t>
   </si>
   <si>
     <t>commonfeeler04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler02</t>
-  </si>
-  <si>
-    <t>commonfeeler03</t>
-  </si>
-  <si>
-    <t>[일반_뱅글더듬이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_만두더듬이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PartsId04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColorId04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_껍질04]</t>
-  </si>
-  <si>
-    <t>[일반_껍질05]</t>
-  </si>
-  <si>
-    <t>[일반_껍질06]</t>
-  </si>
-  <si>
-    <t>[일반_껍질07]</t>
-  </si>
-  <si>
-    <t>commonshell01_c08</t>
-  </si>
-  <si>
-    <t>[일반_명주달팽이껍질]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_긴껍질01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_긴껍질02]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질03]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질04]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질05]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질06]</t>
-  </si>
-  <si>
-    <t>commonshell02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonshell02_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler04_c02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_눈02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈03]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈04]</t>
-  </si>
-  <si>
-    <t>commoneyes02</t>
-  </si>
-  <si>
-    <t>commoneyes03</t>
-  </si>
-  <si>
-    <t>commoneyes04</t>
-  </si>
-  <si>
-    <t>PartsGroupId</t>
-  </si>
-  <si>
-    <t>[일반그룹]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[레어그룹]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반그룹], [레어그룹]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enum&lt;PartsType&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_몸02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸03]</t>
-  </si>
-  <si>
-    <t>SortOrder</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nullableint</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_일반더듬이01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_일반더듬이02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_뚱뚱몸01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>뚱뚱몸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody02_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;string&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nullablestring</t>
-  </si>
-  <si>
-    <t>Size</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>food_lettuce</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelUpTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeedFullPointPercent</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeedHappyPointPercent</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Acceleration</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UseHappyPointTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Double</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DeformGroup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>nullableint</t>
-  </si>
-  <si>
-    <t>[부드러움]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CoinCoolTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 말풍선</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>bubble_coin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_coin</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[코인]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody03_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kr</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[레벨]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{0}살</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이02]</t>
-  </si>
-  <si>
-    <t>commonfeeler05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler05_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonfeeler05_c02</t>
-  </si>
-  <si>
-    <t>food_zucchini</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>food_tofu</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>ResourceSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NameId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[상추]</t>
-  </si>
-  <si>
-    <t>[토마토]</t>
-  </si>
-  <si>
-    <t>InfoId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[포만감01]</t>
-  </si>
-  <si>
-    <t>[팽이코인정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>팽이코인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반알01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[레어알01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 알</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>레어 알</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[모자01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[모자02정보]</t>
-  </si>
-  <si>
-    <t>[가방01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>모자1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>모자2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가방1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>연두색의 껍질.</t>
-  </si>
-  <si>
-    <t>갈색의 껍질.</t>
-  </si>
-  <si>
-    <t>초록색의 껍질.</t>
-  </si>
-  <si>
-    <t>보라색의 껍질.</t>
-  </si>
-  <si>
-    <t>파란색의 껍질.</t>
-  </si>
-  <si>
-    <t>누군가를 열렬히 좋아하다가 생긴 무늬 껍질.</t>
-  </si>
-  <si>
-    <t>상추가 너무 좋아서 껍질에 새기기로 했다.</t>
-  </si>
-  <si>
-    <t>명주 달팽이의 껍질.</t>
-  </si>
-  <si>
-    <t>아프리카 왕달팽이의 껍질. (금와)</t>
-  </si>
-  <si>
-    <t>돌맹이를 깎아 만든 껍질. 농담이다.</t>
-  </si>
-  <si>
-    <t>나쵸칩에 맛들린 달팽이의 일탈 껍질.</t>
-  </si>
-  <si>
-    <t>갈색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>파란색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>주황색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>당근이 너무 좋아서 집으로 삼기로 했다.</t>
-  </si>
-  <si>
-    <t>연두색의 몸.</t>
-  </si>
-  <si>
-    <t>분홍색의 몸.</t>
-  </si>
-  <si>
-    <t>갈색의 몸.</t>
-  </si>
-  <si>
-    <t>느려졌지만, 행복해보인다.</t>
-  </si>
-  <si>
-    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
-  </si>
-  <si>
-    <t>웃는 달팽이의 눈.</t>
-  </si>
-  <si>
-    <t>눈치보는 달팽이의 눈.</t>
-  </si>
-  <si>
-    <t>무념무상의 눈.</t>
-  </si>
-  <si>
-    <t>정신없이 버섯을 먹다보니 변해있었다.</t>
-  </si>
-  <si>
-    <t>오글거리는 드라마를 봤더니 변해있었다.</t>
-  </si>
-  <si>
-    <t>만두를 먹어보고 싶었던 더듬이.</t>
-  </si>
-  <si>
-    <t>연두색의 더듬이.</t>
-  </si>
-  <si>
-    <t>갈색의 더듬이.</t>
-  </si>
-  <si>
-    <t>갈색 얼룩 고양이 귀.</t>
-  </si>
-  <si>
-    <t>분홍 얼룩 고양이 귀.</t>
-  </si>
-  <si>
-    <t>[일반_껍질01정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질02정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질03정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질04정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질05정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질06정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질07정보]</t>
-  </si>
-  <si>
-    <t>[일반_명주달팽이껍질정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질01정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질02정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질03정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질04정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질05정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질06정보]</t>
-  </si>
-  <si>
-    <t>[레어_당근껍질정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸02정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸03정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_뚱뚱몸01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈02정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈03정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈04정보]</t>
-  </si>
-  <si>
-    <t>[일반_버섯더듬이정보]</t>
-  </si>
-  <si>
-    <t>[일반_뱅글더듬이정보]</t>
-  </si>
-  <si>
-    <t>[일반_만두더듬이정보]</t>
-  </si>
-  <si>
-    <t>[일반_일반더듬이01정보]</t>
-  </si>
-  <si>
-    <t>[일반_일반더듬이02정보]</t>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이01정보]</t>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이02정보]</t>
-  </si>
-  <si>
-    <t>껍질01</t>
-  </si>
-  <si>
-    <t>껍질02</t>
-  </si>
-  <si>
-    <t>껍질03</t>
-  </si>
-  <si>
-    <t>껍질04</t>
-  </si>
-  <si>
-    <t>껍질05</t>
-  </si>
-  <si>
-    <t>껍질06</t>
-  </si>
-  <si>
-    <t>껍질07</t>
-  </si>
-  <si>
-    <t>명주달팽이껍질</t>
-  </si>
-  <si>
-    <t>긴껍질01</t>
-  </si>
-  <si>
-    <t>긴껍질02</t>
-  </si>
-  <si>
-    <t>긴껍질03</t>
-  </si>
-  <si>
-    <t>긴껍질04</t>
-  </si>
-  <si>
-    <t>긴껍질05</t>
-  </si>
-  <si>
-    <t>긴껍질06</t>
-  </si>
-  <si>
-    <t>버섯더듬이</t>
-  </si>
-  <si>
-    <t>뱅글더듬이</t>
-  </si>
-  <si>
-    <t>만두더듬이</t>
-  </si>
-  <si>
-    <t>일반더듬이01</t>
-  </si>
-  <si>
-    <t>일반더듬이02</t>
-  </si>
-  <si>
-    <t>고양이더듬이01</t>
-  </si>
-  <si>
-    <t>고양이더듬이02</t>
-  </si>
-  <si>
-    <t>레어_당근껍질</t>
-  </si>
-  <si>
-    <t>일반달팽이_몸01</t>
-  </si>
-  <si>
-    <t>일반달팽이_몸02</t>
-  </si>
-  <si>
-    <t>일반달팽이_몸03</t>
-  </si>
-  <si>
-    <t>일반달팽이_뚱뚱몸01</t>
-  </si>
-  <si>
-    <t>일반달팽이_손몸01</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈01</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈02</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈03</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈04</t>
-  </si>
-  <si>
-    <t>일반 달팽이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[도감_일반달팽이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[이름없음]</t>
-  </si>
-  <si>
-    <t>이름 없음</t>
-  </si>
-  <si>
-    <t>[달팽이목록]</t>
-  </si>
-  <si>
-    <t>달팽이 목록</t>
-  </si>
-  <si>
-    <t>[음식목록]</t>
-  </si>
-  <si>
-    <t>음식 목록</t>
-  </si>
-  <si>
-    <t>[보유중인알]</t>
-  </si>
-  <si>
-    <t>보유중인 알</t>
-  </si>
-  <si>
-    <t>[상점]</t>
-  </si>
-  <si>
-    <t>상점</t>
-  </si>
-  <si>
-    <t>[먹이기]</t>
-  </si>
-  <si>
-    <t>먹이기</t>
-  </si>
-  <si>
-    <t>rarity_common</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rarity_rare</t>
-  </si>
-  <si>
-    <t>rarity_epic</t>
-  </si>
-  <si>
-    <t>rarity_legendary</t>
-  </si>
-  <si>
-    <t>Enum&lt;RarityType&gt;</t>
-  </si>
-  <si>
-    <t>HatchTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeedConditionValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum&lt;ConditionType&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConditionType</t>
-  </si>
-  <si>
-    <t>ConditionType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SnailCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>보유중인 달팽이 개수 조건</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SnailLevel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>달성한 달팽이 레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[해금조건01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PayItem</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>비용을 지불필요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[음식]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[달팽이알]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[악세서리]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[자유시장]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[오늘의추천]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[구매하기]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>음식</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>달팽이 알</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악세서리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>자유시장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>오늘의 추천</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>구매하기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부화기]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부화기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부화시킬알없음]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부화완료]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부화 완료</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부화시킬 알이 없습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody01_c04</t>
-  </si>
-  <si>
-    <t>commonbody01_c05</t>
-  </si>
-  <si>
-    <t>commonbody01_c06</t>
-  </si>
-  <si>
-    <t>commonbody03_c02</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸04]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸05]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸06]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸04정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸05정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸06정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸02정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈05]</t>
-  </si>
-  <si>
-    <t>commoneyes05</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈05정보]</t>
-  </si>
-  <si>
-    <t>[준비중]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>준비중입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DiscountCostCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_아이스크림01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rarebody01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rarebody01_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_아이스크림01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[상추정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[토마토정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[애호박정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[두부정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>food_tomato</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악세 카테고리 : 마스크</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악세 카테고리 : 기타</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[모자]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[가방]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[마스크]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[기타]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>모자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가방</t>
-  </si>
-  <si>
-    <t>마스크</t>
-  </si>
-  <si>
-    <t>기타</t>
-  </si>
-  <si>
-    <t>Mask</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[옷장]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[장착중]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>옷장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>장착중</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>etc01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[천사링01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[천사링01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>mask01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[해골마스크]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[해골마스크정보]</t>
+  </si>
+  <si>
+    <t>MutationWeight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HappyDecayPerTick</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FullDecayPerTick</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Info</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PixelsPerSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PixelsPerSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoodGravity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2049,7 +2054,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2092,6 +2097,12 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2752,10 +2763,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -2775,10 +2786,10 @@
         <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>10</v>
@@ -2871,7 +2882,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>58</v>
@@ -2891,7 +2902,7 @@
         <v>400</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>59</v>
@@ -2902,7 +2913,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C11" s="13">
         <v>4</v>
@@ -2911,10 +2922,10 @@
         <v>300</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2945,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>78</v>
@@ -2962,7 +2973,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>79</v>
@@ -2979,7 +2990,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>80</v>
@@ -2996,7 +3007,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>81</v>
@@ -3133,7 +3144,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3143,7 +3154,7 @@
         <v>251</v>
       </c>
       <c r="G25" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -3151,7 +3162,7 @@
         <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -3161,49 +3172,49 @@
         <v>255</v>
       </c>
       <c r="G26" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="B27" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="B28" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="B29" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -3320,10 +3331,10 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>82</v>
@@ -3332,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>99</v>
@@ -3355,10 +3366,10 @@
         <v>154</v>
       </c>
       <c r="F4" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="G4" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3378,10 +3389,10 @@
         <v>156</v>
       </c>
       <c r="F5" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="G5" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3442,7 +3453,7 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>114</v>
@@ -3451,7 +3462,7 @@
         <v>123</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -3468,7 +3479,7 @@
         <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -3485,7 +3496,7 @@
         <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -3502,41 +3513,41 @@
         <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="B7" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="C7" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="D7" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="E7" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="B8" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="C8" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="D8" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="E8" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3657,7 +3668,7 @@
         <v>65</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>102</v>
@@ -4108,7 +4119,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>24</v>
@@ -4586,25 +4597,25 @@
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>71</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>71</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -4612,51 +4623,51 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>224</v>
-      </c>
       <c r="K3" s="8" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4695,15 +4706,15 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4740,7 +4751,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
         <v>46</v>
@@ -4748,7 +4759,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
         <v>69</v>
@@ -4759,12 +4770,12 @@
         <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
         <v>86</v>
@@ -4772,7 +4783,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -4783,7 +4794,7 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -4791,12 +4802,12 @@
         <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B16" t="s">
         <v>122</v>
@@ -4804,7 +4815,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="B17" t="s">
         <v>119</v>
@@ -4812,7 +4823,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B18" t="s">
         <v>131</v>
@@ -4823,7 +4834,7 @@
         <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -4831,7 +4842,7 @@
         <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -4839,695 +4850,695 @@
         <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="B22" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="B24" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B25" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="B26" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="B27" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="B28" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="B29" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="B30" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="B32" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B38" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="B41" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="B45" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="B47" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="B51" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="B86" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B87" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="B88" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="B89" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="B90" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="B91" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="B92" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="B93" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="B94" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B95" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="B96" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="B97" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="B98" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="B99" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B100" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="B101" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="B102" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="B103" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="B104" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="B105" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="B106" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="B107" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -5569,7 +5580,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>23</v>
@@ -5586,10 +5597,10 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>64</v>
@@ -5600,13 +5611,121 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B4" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="C4">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB314148-9221-49F7-832E-5D289BE3A143}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="67.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
@@ -5617,327 +5736,494 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD86155D-B955-41F0-BC82-EF0EDA2597DB}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.75" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.375" customWidth="1"/>
+    <col min="5" max="5" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+      <c r="C11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="C12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="C13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="C14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="C15" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="C16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>492</v>
+      </c>
+      <c r="C17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>493</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>262</v>
-      </c>
-      <c r="C25" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>495</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>498</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
+        <v>207</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>164</v>
-      </c>
       <c r="B32" t="s">
-        <v>172</v>
-      </c>
-      <c r="C32" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>164</v>
-      </c>
-      <c r="B34" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>164</v>
-      </c>
-      <c r="B35" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" t="s">
-        <v>179</v>
+        <v>499</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="A2">
+  <conditionalFormatting sqref="A2:B2">
     <cfRule type="duplicateValues" dxfId="3" priority="3"/>
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2">
+  <conditionalFormatting sqref="C2:D2">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
@@ -5948,7 +6234,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -6006,10 +6292,10 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>25</v>
@@ -6018,7 +6304,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>24</v>
@@ -6032,10 +6318,10 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>82</v>
@@ -6050,24 +6336,24 @@
         <v>17</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>153</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>51</v>
@@ -6076,30 +6362,30 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G4" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="I4" s="11">
         <v>10</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>51</v>
@@ -6108,30 +6394,30 @@
         <v>11</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G5" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I5" s="11">
         <v>10</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>51</v>
@@ -6140,30 +6426,30 @@
         <v>11</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="I6" s="11">
         <v>10</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>51</v>
@@ -6172,30 +6458,30 @@
         <v>11</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I7" s="11">
         <v>10</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>51</v>
@@ -6204,30 +6490,30 @@
         <v>11</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G8" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="I8" s="11">
         <v>10</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>51</v>
@@ -6236,30 +6522,30 @@
         <v>11</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G9" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="I9" s="11">
         <v>10</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>51</v>
@@ -6268,30 +6554,30 @@
         <v>11</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G10" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="I10" s="11">
         <v>10</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>51</v>
@@ -6300,30 +6586,30 @@
         <v>11</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G11" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="I11" s="11">
         <v>10</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>51</v>
@@ -6332,30 +6618,30 @@
         <v>11</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="G12" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="I12" s="11">
         <v>10</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>51</v>
@@ -6364,30 +6650,30 @@
         <v>11</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="G13" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="I13" s="11">
         <v>10</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>234</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>248</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>51</v>
@@ -6396,30 +6682,30 @@
         <v>11</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="G14" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="I14" s="11">
         <v>10</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>51</v>
@@ -6428,30 +6714,30 @@
         <v>11</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="G15" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="I15" s="11">
         <v>10</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>51</v>
@@ -6460,30 +6746,30 @@
         <v>11</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="G16" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="I16" s="11">
         <v>10</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>51</v>
@@ -6492,30 +6778,30 @@
         <v>11</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="G17" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="I17" s="11">
         <v>10</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>155</v>
@@ -6524,30 +6810,30 @@
         <v>11</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="G18" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="I18" s="11">
         <v>7</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>51</v>
@@ -6556,30 +6842,30 @@
         <v>13</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G19" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="I19" s="11">
         <v>10</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>51</v>
@@ -6588,30 +6874,30 @@
         <v>13</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G20" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I20" s="11">
         <v>10</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>51</v>
@@ -6620,30 +6906,30 @@
         <v>13</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G21" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I21" s="11">
         <v>10</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>51</v>
@@ -6652,30 +6938,30 @@
         <v>13</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G22" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="I22" s="11">
         <v>10</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>51</v>
@@ -6684,30 +6970,30 @@
         <v>13</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G23" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="I23" s="11">
         <v>10</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>51</v>
@@ -6716,30 +7002,30 @@
         <v>13</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G24" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="I24" s="11">
         <v>10</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>51</v>
@@ -6748,30 +7034,30 @@
         <v>13</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="G25" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="I25" s="11">
         <v>10</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>51</v>
@@ -6780,30 +7066,30 @@
         <v>13</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="G26" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="I26" s="11">
         <v>10</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>51</v>
@@ -6812,30 +7098,30 @@
         <v>13</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="G27" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="I27" s="11">
         <v>10</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>155</v>
@@ -6844,30 +7130,30 @@
         <v>13</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="G28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="I28" s="11">
         <v>7</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>51</v>
@@ -6876,7 +7162,7 @@
         <v>14</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G29" s="11" t="b">
         <v>0</v>
@@ -6886,18 +7172,18 @@
         <v>10</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>51</v>
@@ -6906,7 +7192,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="G30" s="11" t="b">
         <v>0</v>
@@ -6916,18 +7202,18 @@
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>51</v>
@@ -6936,7 +7222,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="G31" s="11" t="b">
         <v>0</v>
@@ -6946,18 +7232,18 @@
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>51</v>
@@ -6966,7 +7252,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="G32" s="11" t="b">
         <v>0</v>
@@ -6976,18 +7262,18 @@
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>51</v>
@@ -6996,7 +7282,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="G33" s="11" t="b">
         <v>0</v>
@@ -7006,231 +7292,167 @@
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G34" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="I34" s="11">
         <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>222</v>
+        <v>486</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>222</v>
+        <v>486</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="G35" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I35" s="11">
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>369</v>
+        <v>490</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>223</v>
+        <v>487</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>223</v>
+        <v>487</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G36" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>175</v>
+        <v>488</v>
       </c>
       <c r="I36" s="11">
         <v>10</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>370</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G37" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I37" s="11">
         <v>10</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>371</v>
+        <v>489</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="G38" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="I38" s="11">
         <v>10</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="G39" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="I39" s="11">
-        <v>10</v>
-      </c>
-      <c r="J39" s="11" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="G40" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="I40" s="11">
-        <v>10</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -7294,7 +7516,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>20</v>
@@ -7320,7 +7542,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>74</v>
@@ -7335,7 +7557,7 @@
         <v>66</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>4</v>
@@ -7349,7 +7571,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -7361,10 +7583,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="I4" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -7375,7 +7597,7 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -7387,10 +7609,10 @@
         <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="I5" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -7413,10 +7635,10 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="I6" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -7442,10 +7664,10 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="I7" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -7546,7 +7768,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
@@ -7558,19 +7780,19 @@
         <v>43</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>48</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>105</v>
@@ -8315,7 +8537,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -8329,7 +8551,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>10</v>
@@ -8337,16 +8559,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -8391,18 +8613,18 @@
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>66</v>
@@ -8475,7 +8697,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>25</v>
@@ -8498,7 +8720,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -8515,7 +8737,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -8567,10 +8789,10 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>4</v>
@@ -8584,10 +8806,10 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7511EEF-09C3-4045-8FCE-F8CB2ECE6E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4000D07-9BF0-4797-B8C9-FFD52C842FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="17" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="515">
   <si>
     <t>ALL</t>
   </si>
@@ -1852,6 +1852,38 @@
   </si>
   <si>
     <t>FoodGravity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[구매문구]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[판매문구]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[동의]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[거부]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>네</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}을(를) 판매할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}을(를) 구매할까요?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4678,7 +4710,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B111"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5539,6 +5571,38 @@
       </c>
       <c r="B107" t="s">
         <v>479</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>507</v>
+      </c>
+      <c r="B108" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>508</v>
+      </c>
+      <c r="B109" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>509</v>
+      </c>
+      <c r="B110" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>510</v>
+      </c>
+      <c r="B111" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4000D07-9BF0-4797-B8C9-FFD52C842FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF2CFBB-9CC0-4E70-B4C4-CCBBCB1CA3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="1410" yWindow="4515" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="516">
   <si>
     <t>ALL</t>
   </si>
@@ -1884,6 +1884,10 @@
   </si>
   <si>
     <t>{0}을(를) 구매할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SellAdvantage</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6298,7 +6302,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -6311,9 +6315,11 @@
     <col min="8" max="8" width="28.5" customWidth="1"/>
     <col min="9" max="9" width="16.125" customWidth="1"/>
     <col min="10" max="10" width="52.125" customWidth="1"/>
+    <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -6344,8 +6350,14 @@
       <c r="J1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -6376,8 +6388,14 @@
       <c r="J2" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -6408,8 +6426,14 @@
       <c r="J3" s="8" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>191</v>
       </c>
@@ -6440,8 +6464,14 @@
       <c r="J4" s="11" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>192</v>
       </c>
@@ -6472,8 +6502,14 @@
       <c r="J5" s="11" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K5" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>193</v>
       </c>
@@ -6504,8 +6540,14 @@
       <c r="J6" s="11" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>213</v>
       </c>
@@ -6536,8 +6578,14 @@
       <c r="J7" s="11" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>214</v>
       </c>
@@ -6568,8 +6616,14 @@
       <c r="J8" s="11" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>215</v>
       </c>
@@ -6600,8 +6654,14 @@
       <c r="J9" s="11" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K9" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>216</v>
       </c>
@@ -6632,8 +6692,14 @@
       <c r="J10" s="11" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>218</v>
       </c>
@@ -6664,8 +6730,14 @@
       <c r="J11" s="11" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>219</v>
       </c>
@@ -6696,8 +6768,14 @@
       <c r="J12" s="11" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>220</v>
       </c>
@@ -6728,8 +6806,14 @@
       <c r="J13" s="11" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>221</v>
       </c>
@@ -6760,8 +6844,14 @@
       <c r="J14" s="11" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>222</v>
       </c>
@@ -6792,8 +6882,14 @@
       <c r="J15" s="11" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>223</v>
       </c>
@@ -6824,8 +6920,14 @@
       <c r="J16" s="11" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
         <v>224</v>
       </c>
@@ -6856,8 +6958,14 @@
       <c r="J17" s="11" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K17" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>194</v>
       </c>
@@ -6888,8 +6996,14 @@
       <c r="J18" s="11" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K18" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
         <v>166</v>
       </c>
@@ -6920,8 +7034,14 @@
       <c r="J19" s="11" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K19" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>239</v>
       </c>
@@ -6952,8 +7072,14 @@
       <c r="J20" s="11" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K20" t="s">
+        <v>68</v>
+      </c>
+      <c r="L20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
         <v>240</v>
       </c>
@@ -6984,8 +7110,14 @@
       <c r="J21" s="11" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K21" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
         <v>441</v>
       </c>
@@ -7016,8 +7148,14 @@
       <c r="J22" s="11" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K22" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>442</v>
       </c>
@@ -7048,8 +7186,14 @@
       <c r="J23" s="11" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K23" t="s">
+        <v>68</v>
+      </c>
+      <c r="L23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
         <v>443</v>
       </c>
@@ -7080,8 +7224,14 @@
       <c r="J24" s="11" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K24" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>245</v>
       </c>
@@ -7112,8 +7262,14 @@
       <c r="J25" s="11" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K25" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
         <v>267</v>
       </c>
@@ -7144,8 +7300,14 @@
       <c r="J26" s="11" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K26" t="s">
+        <v>68</v>
+      </c>
+      <c r="L26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
         <v>447</v>
       </c>
@@ -7176,8 +7338,14 @@
       <c r="J27" s="11" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
         <v>455</v>
       </c>
@@ -7208,8 +7376,14 @@
       <c r="J28" s="11" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>167</v>
       </c>
@@ -7238,8 +7412,14 @@
       <c r="J29" s="11" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K29" t="s">
+        <v>68</v>
+      </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
         <v>227</v>
       </c>
@@ -7268,8 +7448,14 @@
       <c r="J30" s="11" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K30" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
         <v>228</v>
       </c>
@@ -7298,8 +7484,14 @@
       <c r="J31" s="11" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K31" t="s">
+        <v>68</v>
+      </c>
+      <c r="L31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
         <v>229</v>
       </c>
@@ -7328,8 +7520,14 @@
       <c r="J32" s="11" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K32" t="s">
+        <v>68</v>
+      </c>
+      <c r="L32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
         <v>449</v>
       </c>
@@ -7358,8 +7556,14 @@
       <c r="J33" s="11" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K33" t="s">
+        <v>68</v>
+      </c>
+      <c r="L33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
         <v>174</v>
       </c>
@@ -7390,8 +7594,14 @@
       <c r="J34" s="11" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K34" t="s">
+        <v>68</v>
+      </c>
+      <c r="L34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
         <v>486</v>
       </c>
@@ -7422,8 +7632,14 @@
       <c r="J35" s="11" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K35" t="s">
+        <v>68</v>
+      </c>
+      <c r="L35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
         <v>487</v>
       </c>
@@ -7454,8 +7670,14 @@
       <c r="J36" s="11" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K36" t="s">
+        <v>68</v>
+      </c>
+      <c r="L36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
         <v>273</v>
       </c>
@@ -7486,8 +7708,14 @@
       <c r="J37" s="11" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K37" t="s">
+        <v>68</v>
+      </c>
+      <c r="L37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
         <v>243</v>
       </c>
@@ -7517,6 +7745,12 @@
       </c>
       <c r="J38" s="11" t="s">
         <v>353</v>
+      </c>
+      <c r="K38" t="s">
+        <v>68</v>
+      </c>
+      <c r="L38">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7743,7 +7977,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48BD49A-A9D0-46FB-B798-026EB3CD9B33}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -7755,9 +7989,10 @@
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="15.25" customWidth="1"/>
     <col min="11" max="11" width="17.75" customWidth="1"/>
+    <col min="12" max="12" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7791,8 +8026,11 @@
       <c r="K1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>18</v>
       </c>
@@ -7826,8 +8064,11 @@
       <c r="K2" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
@@ -7861,8 +8102,11 @@
       <c r="K3" s="8" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="8" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -7896,8 +8140,11 @@
       <c r="K4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -7931,8 +8178,11 @@
       <c r="K5">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -7966,8 +8216,11 @@
       <c r="K6">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -8001,8 +8254,11 @@
       <c r="K7">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -8036,8 +8292,11 @@
       <c r="K8">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -8071,8 +8330,11 @@
       <c r="K9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -8106,8 +8368,11 @@
       <c r="K10">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -8141,8 +8406,11 @@
       <c r="K11">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -8176,8 +8444,11 @@
       <c r="K12">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>10</v>
       </c>
@@ -8211,8 +8482,11 @@
       <c r="K13">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L13">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>11</v>
       </c>
@@ -8246,8 +8520,11 @@
       <c r="K14">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
@@ -8281,8 +8558,11 @@
       <c r="K15">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L15">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -8316,8 +8596,11 @@
       <c r="K16">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L16">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>14</v>
       </c>
@@ -8351,8 +8634,11 @@
       <c r="K17">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>15</v>
       </c>
@@ -8386,8 +8672,11 @@
       <c r="K18">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L18">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>16</v>
       </c>
@@ -8421,8 +8710,11 @@
       <c r="K19">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L19">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>17</v>
       </c>
@@ -8456,8 +8748,11 @@
       <c r="K20">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -8491,8 +8786,11 @@
       <c r="K21">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -8526,8 +8824,11 @@
       <c r="K22">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -8560,6 +8861,9 @@
       </c>
       <c r="K23">
         <v>30</v>
+      </c>
+      <c r="L23">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF2CFBB-9CC0-4E70-B4C4-CCBBCB1CA3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64980010-97DF-42DB-B693-4831A1645AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="4515" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-24675" yWindow="2835" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="7" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="520">
   <si>
     <t>ALL</t>
   </si>
@@ -1888,6 +1888,22 @@
   </si>
   <si>
     <t>SellAdvantage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[이름변경]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름을 변경합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[변경]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4714,7 +4730,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B111"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5607,6 +5623,22 @@
       </c>
       <c r="B111" t="s">
         <v>512</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>516</v>
+      </c>
+      <c r="B112" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>518</v>
+      </c>
+      <c r="B113" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64980010-97DF-42DB-B693-4831A1645AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D409B0-510E-405D-88DF-95C203B59701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24675" yWindow="2835" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="7" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="524">
   <si>
     <t>ALL</t>
   </si>
@@ -1905,6 +1905,18 @@
   <si>
     <t>변경</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_feeler</t>
+  </si>
+  <si>
+    <t>icon_eyes</t>
+  </si>
+  <si>
+    <t>icon_body</t>
+  </si>
+  <si>
+    <t>icon_shell</t>
   </si>
 </sst>
 </file>
@@ -2913,6 +2925,9 @@
       <c r="C8" s="13">
         <v>1</v>
       </c>
+      <c r="D8" s="13" t="s">
+        <v>523</v>
+      </c>
       <c r="E8" s="13">
         <v>100</v>
       </c>
@@ -2930,6 +2945,9 @@
       <c r="C9" s="13">
         <v>2</v>
       </c>
+      <c r="D9" s="13" t="s">
+        <v>522</v>
+      </c>
       <c r="E9" s="13">
         <v>200</v>
       </c>
@@ -2950,6 +2968,9 @@
       <c r="C10" s="13">
         <v>3</v>
       </c>
+      <c r="D10" s="13" t="s">
+        <v>521</v>
+      </c>
       <c r="E10" s="13">
         <v>400</v>
       </c>
@@ -2969,6 +2990,9 @@
       </c>
       <c r="C11" s="13">
         <v>4</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>520</v>
       </c>
       <c r="E11" s="13">
         <v>300</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D409B0-510E-405D-88DF-95C203B59701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B677909-5D40-46A9-BA6D-5CA258F2A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24675" yWindow="2835" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="7" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="532">
   <si>
     <t>ALL</t>
   </si>
@@ -1917,6 +1917,37 @@
   </si>
   <si>
     <t>icon_shell</t>
+  </si>
+  <si>
+    <t>[레어_아이스크림콘껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell02</t>
+  </si>
+  <si>
+    <t>rareshell02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_아이스크림콘껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[확인]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화문구]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알이 부화했습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4754,7 +4785,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5663,6 +5694,22 @@
       </c>
       <c r="B113" t="s">
         <v>519</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>528</v>
+      </c>
+      <c r="B114" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>530</v>
+      </c>
+      <c r="B115" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -5846,7 +5893,7 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>1600</v>
@@ -5860,7 +5907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD86155D-B955-41F0-BC82-EF0EDA2597DB}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.625" bestFit="1" customWidth="1"/>
@@ -6133,13 +6180,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>171</v>
+        <v>526</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -6153,7 +6200,7 @@
         <v>494</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -6167,7 +6214,7 @@
         <v>494</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -6181,7 +6228,7 @@
         <v>494</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>437</v>
+        <v>173</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -6195,7 +6242,7 @@
         <v>494</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -6209,7 +6256,7 @@
         <v>494</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -6220,10 +6267,10 @@
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>247</v>
+        <v>439</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -6234,10 +6281,10 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -6251,7 +6298,7 @@
         <v>496</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>440</v>
+        <v>269</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -6262,10 +6309,10 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -6273,13 +6320,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>205</v>
+        <v>457</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -6290,10 +6337,10 @@
         <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>207</v>
+        <v>498</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -6307,7 +6354,7 @@
         <v>207</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>488</v>
+        <v>168</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -6318,10 +6365,10 @@
         <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>169</v>
+        <v>488</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -6332,12 +6379,26 @@
         <v>160</v>
       </c>
       <c r="B33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" t="s">
         <v>499</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C34" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>5</v>
       </c>
     </row>
@@ -6358,7 +6419,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -7061,48 +7122,48 @@
     </row>
     <row r="19" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>166</v>
+        <v>524</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>166</v>
+        <v>524</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>51</v>
+        <v>155</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>164</v>
+        <v>525</v>
       </c>
       <c r="G19" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>171</v>
+        <v>526</v>
       </c>
       <c r="I19" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>341</v>
+        <v>527</v>
       </c>
       <c r="K19" t="s">
         <v>68</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>234</v>
@@ -7120,13 +7181,13 @@
         <v>1</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I20" s="11">
         <v>10</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K20" t="s">
         <v>68</v>
@@ -7137,10 +7198,10 @@
     </row>
     <row r="21" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>234</v>
@@ -7158,13 +7219,13 @@
         <v>1</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I21" s="11">
         <v>10</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K21" t="s">
         <v>68</v>
@@ -7175,10 +7236,10 @@
     </row>
     <row r="22" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>441</v>
+        <v>240</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>441</v>
+        <v>240</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>234</v>
@@ -7196,13 +7257,13 @@
         <v>1</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>437</v>
+        <v>173</v>
       </c>
       <c r="I22" s="11">
         <v>10</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>444</v>
+        <v>343</v>
       </c>
       <c r="K22" t="s">
         <v>68</v>
@@ -7213,10 +7274,10 @@
     </row>
     <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>234</v>
@@ -7234,13 +7295,13 @@
         <v>1</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I23" s="11">
         <v>10</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K23" t="s">
         <v>68</v>
@@ -7251,10 +7312,10 @@
     </row>
     <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>234</v>
@@ -7272,13 +7333,13 @@
         <v>1</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I24" s="11">
         <v>10</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K24" t="s">
         <v>68</v>
@@ -7289,10 +7350,10 @@
     </row>
     <row r="25" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>245</v>
+        <v>443</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>245</v>
+        <v>443</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>234</v>
@@ -7304,19 +7365,19 @@
         <v>13</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>246</v>
+        <v>164</v>
       </c>
       <c r="G25" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>247</v>
+        <v>439</v>
       </c>
       <c r="I25" s="11">
         <v>10</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>344</v>
+        <v>446</v>
       </c>
       <c r="K25" t="s">
         <v>68</v>
@@ -7327,10 +7388,10 @@
     </row>
     <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>234</v>
@@ -7342,19 +7403,19 @@
         <v>13</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="G26" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="I26" s="11">
         <v>10</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K26" t="s">
         <v>68</v>
@@ -7365,10 +7426,10 @@
     </row>
     <row r="27" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>447</v>
+        <v>267</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>447</v>
+        <v>267</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>234</v>
@@ -7386,13 +7447,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>440</v>
+        <v>269</v>
       </c>
       <c r="I27" s="11">
         <v>10</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>448</v>
+        <v>345</v>
       </c>
       <c r="K27" t="s">
         <v>68</v>
@@ -7403,84 +7464,86 @@
     </row>
     <row r="28" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>234</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>155</v>
+        <v>51</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>456</v>
+        <v>268</v>
       </c>
       <c r="G28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="I28" s="11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="K28" t="s">
         <v>68</v>
       </c>
       <c r="L28">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>167</v>
+        <v>455</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>167</v>
+        <v>455</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>234</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>51</v>
+        <v>155</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>165</v>
+        <v>456</v>
       </c>
       <c r="G29" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>457</v>
+      </c>
       <c r="I29" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="K29" t="s">
         <v>68</v>
       </c>
       <c r="L29">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>234</v>
@@ -7492,7 +7555,7 @@
         <v>14</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="G30" s="11" t="b">
         <v>0</v>
@@ -7502,7 +7565,7 @@
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K30" t="s">
         <v>68</v>
@@ -7513,10 +7576,10 @@
     </row>
     <row r="31" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>234</v>
@@ -7528,7 +7591,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G31" s="11" t="b">
         <v>0</v>
@@ -7538,7 +7601,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K31" t="s">
         <v>68</v>
@@ -7549,10 +7612,10 @@
     </row>
     <row r="32" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>234</v>
@@ -7564,7 +7627,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G32" s="11" t="b">
         <v>0</v>
@@ -7574,7 +7637,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K32" t="s">
         <v>68</v>
@@ -7585,10 +7648,10 @@
     </row>
     <row r="33" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>449</v>
+        <v>229</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>449</v>
+        <v>229</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>234</v>
@@ -7600,7 +7663,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>450</v>
+        <v>232</v>
       </c>
       <c r="G33" s="11" t="b">
         <v>0</v>
@@ -7610,7 +7673,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>451</v>
+        <v>349</v>
       </c>
       <c r="K33" t="s">
         <v>68</v>
@@ -7621,10 +7684,10 @@
     </row>
     <row r="34" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>174</v>
+        <v>449</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>174</v>
+        <v>449</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>234</v>
@@ -7633,22 +7696,20 @@
         <v>51</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>175</v>
+        <v>450</v>
       </c>
       <c r="G34" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>205</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H34" s="11"/>
       <c r="I34" s="11">
         <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>350</v>
+        <v>451</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
@@ -7659,10 +7720,10 @@
     </row>
     <row r="35" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>486</v>
+        <v>174</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>486</v>
+        <v>174</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>234</v>
@@ -7674,19 +7735,19 @@
         <v>159</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="G35" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="I35" s="11">
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>490</v>
+        <v>350</v>
       </c>
       <c r="K35" t="s">
         <v>68</v>
@@ -7697,10 +7758,10 @@
     </row>
     <row r="36" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>234</v>
@@ -7718,7 +7779,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>488</v>
+        <v>168</v>
       </c>
       <c r="I36" s="11">
         <v>10</v>
@@ -7735,10 +7796,10 @@
     </row>
     <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>273</v>
+        <v>487</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>273</v>
+        <v>487</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>234</v>
@@ -7750,19 +7811,19 @@
         <v>159</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G37" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>169</v>
+        <v>488</v>
       </c>
       <c r="I37" s="11">
         <v>10</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K37" t="s">
         <v>68</v>
@@ -7773,10 +7834,10 @@
     </row>
     <row r="38" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>234</v>
@@ -7788,24 +7849,62 @@
         <v>159</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G38" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I38" s="11">
         <v>10</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>353</v>
+        <v>489</v>
       </c>
       <c r="K38" t="s">
         <v>68</v>
       </c>
       <c r="L38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I39" s="11">
+        <v>10</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="K39" t="s">
+        <v>68</v>
+      </c>
+      <c r="L39">
         <v>5</v>
       </c>
     </row>
@@ -8989,7 +9088,7 @@
         <v>264</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>263</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B677909-5D40-46A9-BA6D-5CA258F2A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B8B91B-2D9F-4D5C-93D2-FEFA08FC177B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="558">
   <si>
     <t>ALL</t>
   </si>
@@ -1947,6 +1947,110 @@
   </si>
   <si>
     <t>알이 부화했습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달팽이설정]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[설정]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korean(kr)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[한글]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>업데이트 및 재시작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[업데이트]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[UI크기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI크기(x{0})</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI 항상 최대화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[UI최대화]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알 관련</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알관련]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알 생성 금지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알생성금지]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[말풍선알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>배고픔 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[배고픔알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[관심알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>관심 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[코인알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[종료]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>종료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>말풍선 알림</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4785,7 +4889,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -5710,6 +5814,110 @@
       </c>
       <c r="B115" t="s">
         <v>531</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>532</v>
+      </c>
+      <c r="B116" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>534</v>
+      </c>
+      <c r="B117" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>537</v>
+      </c>
+      <c r="B118" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>539</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>540</v>
+      </c>
+      <c r="B120" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>543</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>545</v>
+      </c>
+      <c r="B122" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>547</v>
+      </c>
+      <c r="B123" s="10" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>548</v>
+      </c>
+      <c r="B124" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>550</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>551</v>
+      </c>
+      <c r="B126" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>553</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>555</v>
+      </c>
+      <c r="B128" t="s">
+        <v>556</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B8B91B-2D9F-4D5C-93D2-FEFA08FC177B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADA48CF-474B-42FC-8EB9-D14DC6FD8C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="559">
   <si>
     <t>ALL</t>
   </si>
@@ -1163,894 +1163,899 @@
     <t>파란색의 껍질.</t>
   </si>
   <si>
+    <t>상추가 너무 좋아서 껍질에 새기기로 했다.</t>
+  </si>
+  <si>
+    <t>명주 달팽이의 껍질.</t>
+  </si>
+  <si>
+    <t>아프리카 왕달팽이의 껍질. (금와)</t>
+  </si>
+  <si>
+    <t>돌맹이를 깎아 만든 껍질. 농담이다.</t>
+  </si>
+  <si>
+    <t>나쵸칩에 맛들린 달팽이의 일탈 껍질.</t>
+  </si>
+  <si>
+    <t>갈색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>파란색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>주황색의 민무늬 껍질.</t>
+  </si>
+  <si>
+    <t>당근이 너무 좋아서 집으로 삼기로 했다.</t>
+  </si>
+  <si>
+    <t>연두색의 몸.</t>
+  </si>
+  <si>
+    <t>분홍색의 몸.</t>
+  </si>
+  <si>
+    <t>갈색의 몸.</t>
+  </si>
+  <si>
+    <t>느려졌지만, 행복해보인다.</t>
+  </si>
+  <si>
+    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
+  </si>
+  <si>
+    <t>웃는 달팽이의 눈.</t>
+  </si>
+  <si>
+    <t>눈치보는 달팽이의 눈.</t>
+  </si>
+  <si>
+    <t>무념무상의 눈.</t>
+  </si>
+  <si>
+    <t>정신없이 버섯을 먹다보니 변해있었다.</t>
+  </si>
+  <si>
+    <t>오글거리는 드라마를 봤더니 변해있었다.</t>
+  </si>
+  <si>
+    <t>만두를 먹어보고 싶었던 더듬이.</t>
+  </si>
+  <si>
+    <t>연두색의 더듬이.</t>
+  </si>
+  <si>
+    <t>갈색의 더듬이.</t>
+  </si>
+  <si>
+    <t>갈색 얼룩 고양이 귀.</t>
+  </si>
+  <si>
+    <t>분홍 얼룩 고양이 귀.</t>
+  </si>
+  <si>
+    <t>[일반_껍질01정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질02정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질03정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질04정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질05정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질06정보]</t>
+  </si>
+  <si>
+    <t>[일반_껍질07정보]</t>
+  </si>
+  <si>
+    <t>[일반_명주달팽이껍질정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질01정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질02정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질03정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질04정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질05정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질06정보]</t>
+  </si>
+  <si>
+    <t>[레어_당근껍질정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸03정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_뚱뚱몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈01정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈03정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈04정보]</t>
+  </si>
+  <si>
+    <t>[일반_버섯더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_뱅글더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_만두더듬이정보]</t>
+  </si>
+  <si>
+    <t>[일반_일반더듬이01정보]</t>
+  </si>
+  <si>
+    <t>[일반_일반더듬이02정보]</t>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01정보]</t>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이02정보]</t>
+  </si>
+  <si>
+    <t>껍질01</t>
+  </si>
+  <si>
+    <t>껍질02</t>
+  </si>
+  <si>
+    <t>껍질03</t>
+  </si>
+  <si>
+    <t>껍질04</t>
+  </si>
+  <si>
+    <t>껍질05</t>
+  </si>
+  <si>
+    <t>껍질06</t>
+  </si>
+  <si>
+    <t>껍질07</t>
+  </si>
+  <si>
+    <t>명주달팽이껍질</t>
+  </si>
+  <si>
+    <t>긴껍질01</t>
+  </si>
+  <si>
+    <t>긴껍질02</t>
+  </si>
+  <si>
+    <t>긴껍질03</t>
+  </si>
+  <si>
+    <t>긴껍질04</t>
+  </si>
+  <si>
+    <t>긴껍질05</t>
+  </si>
+  <si>
+    <t>긴껍질06</t>
+  </si>
+  <si>
+    <t>버섯더듬이</t>
+  </si>
+  <si>
+    <t>뱅글더듬이</t>
+  </si>
+  <si>
+    <t>만두더듬이</t>
+  </si>
+  <si>
+    <t>일반더듬이01</t>
+  </si>
+  <si>
+    <t>일반더듬이02</t>
+  </si>
+  <si>
+    <t>고양이더듬이01</t>
+  </si>
+  <si>
+    <t>고양이더듬이02</t>
+  </si>
+  <si>
+    <t>레어_당근껍질</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸02</t>
+  </si>
+  <si>
+    <t>일반달팽이_몸03</t>
+  </si>
+  <si>
+    <t>일반달팽이_뚱뚱몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_손몸01</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈01</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈02</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈03</t>
+  </si>
+  <si>
+    <t>일반달팽이_눈04</t>
+  </si>
+  <si>
+    <t>일반 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_일반달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[이름없음]</t>
+  </si>
+  <si>
+    <t>이름 없음</t>
+  </si>
+  <si>
+    <t>[달팽이목록]</t>
+  </si>
+  <si>
+    <t>달팽이 목록</t>
+  </si>
+  <si>
+    <t>[음식목록]</t>
+  </si>
+  <si>
+    <t>음식 목록</t>
+  </si>
+  <si>
+    <t>[보유중인알]</t>
+  </si>
+  <si>
+    <t>보유중인 알</t>
+  </si>
+  <si>
+    <t>[상점]</t>
+  </si>
+  <si>
+    <t>상점</t>
+  </si>
+  <si>
+    <t>[먹이기]</t>
+  </si>
+  <si>
+    <t>먹이기</t>
+  </si>
+  <si>
+    <t>rarity_common</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarity_rare</t>
+  </si>
+  <si>
+    <t>rarity_epic</t>
+  </si>
+  <si>
+    <t>rarity_legendary</t>
+  </si>
+  <si>
+    <t>Enum&lt;RarityType&gt;</t>
+  </si>
+  <si>
+    <t>HatchTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedConditionValue</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;ConditionType&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConditionType</t>
+  </si>
+  <si>
+    <t>ConditionType</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SnailCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유중인 달팽이 개수 조건</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SnailLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달성한 달팽이 레벨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해금조건01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PayItem</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비용을 지불필요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[음식]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달팽이알]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[악세서리]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[자유시장]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[오늘의추천]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[구매하기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>음식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세서리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>자유시장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘의 추천</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매하기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화시킬알없음]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화완료]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화 완료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>부화시킬 알이 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody01_c04</t>
+  </si>
+  <si>
+    <t>commonbody01_c05</t>
+  </si>
+  <si>
+    <t>commonbody01_c06</t>
+  </si>
+  <si>
+    <t>commonbody03_c02</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸04]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸05]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸06]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸04정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸05정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_몸06정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸02]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_손몸02정보]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈05]</t>
+  </si>
+  <si>
+    <t>commoneyes05</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈05정보]</t>
+  </si>
+  <si>
+    <t>[준비중]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>준비중입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DiscountCostCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_아이스크림01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody01_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_아이스크림01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[상추정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[토마토정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[애호박정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[두부정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_tomato</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 카테고리 : 마스크</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>악세 카테고리 : 기타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[모자]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[가방]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[마스크]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[기타]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>모자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방</t>
+  </si>
+  <si>
+    <t>마스크</t>
+  </si>
+  <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>Mask</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[옷장]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[장착중]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>옷장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장착중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>etc01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[천사링01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[천사링01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mask01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해골마스크]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[해골마스크정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_오목더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_오목더듬이02]</t>
+  </si>
+  <si>
+    <t>commonfeeler02_c02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_고양이더듬이01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_오목더듬이01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell01</t>
+  </si>
+  <si>
+    <t>commonshell02</t>
+  </si>
+  <si>
+    <t>rareshell01</t>
+  </si>
+  <si>
+    <t>commonbody01</t>
+  </si>
+  <si>
+    <t>commonbody02</t>
+  </si>
+  <si>
+    <t>commonbody03</t>
+  </si>
+  <si>
+    <t>rarebody01</t>
+  </si>
+  <si>
+    <t>commonfeeler01</t>
+  </si>
+  <si>
+    <t>commonfeeler04</t>
+  </si>
+  <si>
+    <t>MutationWeight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HappyDecayPerTick</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FullDecayPerTick</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Info</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PixelsPerSpeed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PixelsPerSize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoodGravity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[구매문구]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[판매문구]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[동의]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[거부]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>네</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아니오</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}을(를) 판매할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}을(를) 구매할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SellAdvantage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[이름변경]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름을 변경합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[변경]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>변경</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_feeler</t>
+  </si>
+  <si>
+    <t>icon_eyes</t>
+  </si>
+  <si>
+    <t>icon_body</t>
+  </si>
+  <si>
+    <t>icon_shell</t>
+  </si>
+  <si>
+    <t>[레어_아이스크림콘껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell02</t>
+  </si>
+  <si>
+    <t>rareshell02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_아이스크림콘껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[확인]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[부화문구]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알이 부화했습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달팽이설정]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이 설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[설정]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korean(kr)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[한글]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>업데이트 및 재시작</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[업데이트]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[UI크기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI크기(x{0})</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI 항상 최대화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[UI최대화]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알 관련</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알관련]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알 생성 금지</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알생성금지]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[말풍선알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>배고픔 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[배고픔알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[관심알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>관심 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[코인알림]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>코인 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[종료]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>종료</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>말풍선 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>누군가를 열렬히 좋아하다가 생긴 무늬 껍질.</t>
-  </si>
-  <si>
-    <t>상추가 너무 좋아서 껍질에 새기기로 했다.</t>
-  </si>
-  <si>
-    <t>명주 달팽이의 껍질.</t>
-  </si>
-  <si>
-    <t>아프리카 왕달팽이의 껍질. (금와)</t>
-  </si>
-  <si>
-    <t>돌맹이를 깎아 만든 껍질. 농담이다.</t>
-  </si>
-  <si>
-    <t>나쵸칩에 맛들린 달팽이의 일탈 껍질.</t>
-  </si>
-  <si>
-    <t>갈색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>파란색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>주황색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>당근이 너무 좋아서 집으로 삼기로 했다.</t>
-  </si>
-  <si>
-    <t>연두색의 몸.</t>
-  </si>
-  <si>
-    <t>분홍색의 몸.</t>
-  </si>
-  <si>
-    <t>갈색의 몸.</t>
-  </si>
-  <si>
-    <t>느려졌지만, 행복해보인다.</t>
-  </si>
-  <si>
-    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
-  </si>
-  <si>
-    <t>웃는 달팽이의 눈.</t>
-  </si>
-  <si>
-    <t>눈치보는 달팽이의 눈.</t>
-  </si>
-  <si>
-    <t>무념무상의 눈.</t>
-  </si>
-  <si>
-    <t>정신없이 버섯을 먹다보니 변해있었다.</t>
-  </si>
-  <si>
-    <t>오글거리는 드라마를 봤더니 변해있었다.</t>
-  </si>
-  <si>
-    <t>만두를 먹어보고 싶었던 더듬이.</t>
-  </si>
-  <si>
-    <t>연두색의 더듬이.</t>
-  </si>
-  <si>
-    <t>갈색의 더듬이.</t>
-  </si>
-  <si>
-    <t>갈색 얼룩 고양이 귀.</t>
-  </si>
-  <si>
-    <t>분홍 얼룩 고양이 귀.</t>
-  </si>
-  <si>
-    <t>[일반_껍질01정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질02정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질03정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질04정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질05정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질06정보]</t>
-  </si>
-  <si>
-    <t>[일반_껍질07정보]</t>
-  </si>
-  <si>
-    <t>[일반_명주달팽이껍질정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질01정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질02정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질03정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질04정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질05정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질06정보]</t>
-  </si>
-  <si>
-    <t>[레어_당근껍질정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸02정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸03정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_뚱뚱몸01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈01정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈02정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈03정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈04정보]</t>
-  </si>
-  <si>
-    <t>[일반_버섯더듬이정보]</t>
-  </si>
-  <si>
-    <t>[일반_뱅글더듬이정보]</t>
-  </si>
-  <si>
-    <t>[일반_만두더듬이정보]</t>
-  </si>
-  <si>
-    <t>[일반_일반더듬이01정보]</t>
-  </si>
-  <si>
-    <t>[일반_일반더듬이02정보]</t>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이01정보]</t>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이02정보]</t>
-  </si>
-  <si>
-    <t>껍질01</t>
-  </si>
-  <si>
-    <t>껍질02</t>
-  </si>
-  <si>
-    <t>껍질03</t>
-  </si>
-  <si>
-    <t>껍질04</t>
-  </si>
-  <si>
-    <t>껍질05</t>
-  </si>
-  <si>
-    <t>껍질06</t>
-  </si>
-  <si>
-    <t>껍질07</t>
-  </si>
-  <si>
-    <t>명주달팽이껍질</t>
-  </si>
-  <si>
-    <t>긴껍질01</t>
-  </si>
-  <si>
-    <t>긴껍질02</t>
-  </si>
-  <si>
-    <t>긴껍질03</t>
-  </si>
-  <si>
-    <t>긴껍질04</t>
-  </si>
-  <si>
-    <t>긴껍질05</t>
-  </si>
-  <si>
-    <t>긴껍질06</t>
-  </si>
-  <si>
-    <t>버섯더듬이</t>
-  </si>
-  <si>
-    <t>뱅글더듬이</t>
-  </si>
-  <si>
-    <t>만두더듬이</t>
-  </si>
-  <si>
-    <t>일반더듬이01</t>
-  </si>
-  <si>
-    <t>일반더듬이02</t>
-  </si>
-  <si>
-    <t>고양이더듬이01</t>
-  </si>
-  <si>
-    <t>고양이더듬이02</t>
-  </si>
-  <si>
-    <t>레어_당근껍질</t>
-  </si>
-  <si>
-    <t>일반달팽이_몸01</t>
-  </si>
-  <si>
-    <t>일반달팽이_몸02</t>
-  </si>
-  <si>
-    <t>일반달팽이_몸03</t>
-  </si>
-  <si>
-    <t>일반달팽이_뚱뚱몸01</t>
-  </si>
-  <si>
-    <t>일반달팽이_손몸01</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈01</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈02</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈03</t>
-  </si>
-  <si>
-    <t>일반달팽이_눈04</t>
-  </si>
-  <si>
-    <t>일반 달팽이</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[도감_일반달팽이]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[이름없음]</t>
-  </si>
-  <si>
-    <t>이름 없음</t>
-  </si>
-  <si>
-    <t>[달팽이목록]</t>
-  </si>
-  <si>
-    <t>달팽이 목록</t>
-  </si>
-  <si>
-    <t>[음식목록]</t>
-  </si>
-  <si>
-    <t>음식 목록</t>
-  </si>
-  <si>
-    <t>[보유중인알]</t>
-  </si>
-  <si>
-    <t>보유중인 알</t>
-  </si>
-  <si>
-    <t>[상점]</t>
-  </si>
-  <si>
-    <t>상점</t>
-  </si>
-  <si>
-    <t>[먹이기]</t>
-  </si>
-  <si>
-    <t>먹이기</t>
-  </si>
-  <si>
-    <t>rarity_common</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rarity_rare</t>
-  </si>
-  <si>
-    <t>rarity_epic</t>
-  </si>
-  <si>
-    <t>rarity_legendary</t>
-  </si>
-  <si>
-    <t>Enum&lt;RarityType&gt;</t>
-  </si>
-  <si>
-    <t>HatchTime</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NeedConditionValue</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum&lt;ConditionType&gt;</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ConditionType</t>
-  </si>
-  <si>
-    <t>ConditionType</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SnailCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>보유중인 달팽이 개수 조건</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SnailLevel</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>달성한 달팽이 레벨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[해금조건01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PayItem</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>비용을 지불필요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[음식]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[달팽이알]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[악세서리]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[자유시장]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[오늘의추천]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[구매하기]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>음식</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>달팽이 알</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악세서리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>자유시장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>오늘의 추천</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>구매하기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부화기]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부화기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부화시킬알없음]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부화완료]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부화 완료</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>부화시킬 알이 없습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonbody01_c04</t>
-  </si>
-  <si>
-    <t>commonbody01_c05</t>
-  </si>
-  <si>
-    <t>commonbody01_c06</t>
-  </si>
-  <si>
-    <t>commonbody03_c02</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸04]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸05]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸06]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸04정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸05정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_몸06정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸02]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_손몸02정보]</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈05]</t>
-  </si>
-  <si>
-    <t>commoneyes05</t>
-  </si>
-  <si>
-    <t>[일반달팽이_눈05정보]</t>
-  </si>
-  <si>
-    <t>[준비중]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>준비중입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DiscountCostCount</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_아이스크림01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rarebody01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rarebody01_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반달팽이_아이스크림01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[상추정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[토마토정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[애호박정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[두부정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>food_tomato</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악세 카테고리 : 마스크</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>악세 카테고리 : 기타</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[모자]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[가방]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[마스크]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[기타]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>모자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가방</t>
-  </si>
-  <si>
-    <t>마스크</t>
-  </si>
-  <si>
-    <t>기타</t>
-  </si>
-  <si>
-    <t>Mask</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[옷장]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[장착중]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>옷장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>장착중</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>etc01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[천사링01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[천사링01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>mask01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[해골마스크]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[해골마스크정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_오목더듬이01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_오목더듬이02]</t>
-  </si>
-  <si>
-    <t>commonfeeler02_c02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_고양이더듬이01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_오목더듬이01정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>commonshell01</t>
-  </si>
-  <si>
-    <t>commonshell02</t>
-  </si>
-  <si>
-    <t>rareshell01</t>
-  </si>
-  <si>
-    <t>commonbody01</t>
-  </si>
-  <si>
-    <t>commonbody02</t>
-  </si>
-  <si>
-    <t>commonbody03</t>
-  </si>
-  <si>
-    <t>rarebody01</t>
-  </si>
-  <si>
-    <t>commonfeeler01</t>
-  </si>
-  <si>
-    <t>commonfeeler04</t>
-  </si>
-  <si>
-    <t>MutationWeight</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HappyDecayPerTick</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FullDecayPerTick</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Info</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PixelsPerSpeed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PixelsPerSize</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FoodGravity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[구매문구]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[판매문구]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[동의]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[거부]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>네</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>아니오</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{0}을(를) 판매할까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{0}을(를) 구매할까요?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SellAdvantage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[이름변경]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름을 변경합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[변경]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>변경</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_feeler</t>
-  </si>
-  <si>
-    <t>icon_eyes</t>
-  </si>
-  <si>
-    <t>icon_body</t>
-  </si>
-  <si>
-    <t>icon_shell</t>
-  </si>
-  <si>
-    <t>[레어_아이스크림콘껍질]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rareshell02</t>
-  </si>
-  <si>
-    <t>rareshell02_c01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[레어_아이스크림콘껍질정보]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[확인]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>확인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[부화문구]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>알이 부화했습니다!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[달팽이설정]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>달팽이 설정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[설정]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>설정</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Korean(kr)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[한글]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>업데이트 및 재시작</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[업데이트]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[UI크기]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI크기(x{0})</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI 항상 최대화</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[UI최대화]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>알 관련</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[알관련]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>알 생성 금지</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[알생성금지]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[말풍선알림]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>배고픔 알림</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[배고픔알림]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[관심알림]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>관심 알림</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[코인알림]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>코인 알림</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[종료]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>종료</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>말풍선 알림</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EatTime</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3061,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E8" s="13">
         <v>100</v>
@@ -3081,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E9" s="13">
         <v>200</v>
@@ -3104,7 +3109,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E10" s="13">
         <v>400</v>
@@ -3127,7 +3132,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E11" s="13">
         <v>300</v>
@@ -3167,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>78</v>
@@ -3184,7 +3189,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>79</v>
@@ -3201,7 +3206,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>80</v>
@@ -3218,7 +3223,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>81</v>
@@ -3355,7 +3360,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3365,7 +3370,7 @@
         <v>251</v>
       </c>
       <c r="G25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -3373,7 +3378,7 @@
         <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -3383,49 +3388,49 @@
         <v>255</v>
       </c>
       <c r="G26" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B27" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -3545,7 +3550,7 @@
         <v>279</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>82</v>
@@ -3729,36 +3734,36 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>480</v>
+      </c>
+      <c r="B7" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D7" t="s">
+        <v>479</v>
+      </c>
+      <c r="E7" t="s">
         <v>481</v>
-      </c>
-      <c r="B7" t="s">
-        <v>481</v>
-      </c>
-      <c r="C7" t="s">
-        <v>475</v>
-      </c>
-      <c r="D7" t="s">
-        <v>480</v>
-      </c>
-      <c r="E7" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>483</v>
+      </c>
+      <c r="B8" t="s">
+        <v>483</v>
+      </c>
+      <c r="C8" t="s">
+        <v>473</v>
+      </c>
+      <c r="D8" t="s">
+        <v>482</v>
+      </c>
+      <c r="E8" t="s">
         <v>484</v>
-      </c>
-      <c r="B8" t="s">
-        <v>484</v>
-      </c>
-      <c r="C8" t="s">
-        <v>474</v>
-      </c>
-      <c r="D8" t="s">
-        <v>483</v>
-      </c>
-      <c r="E8" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -3879,7 +3884,7 @@
         <v>65</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>102</v>
@@ -4872,7 +4877,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>191</v>
@@ -5066,7 +5071,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B22" t="s">
         <v>296</v>
@@ -5074,7 +5079,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B23" t="s">
         <v>297</v>
@@ -5082,7 +5087,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s">
         <v>298</v>
@@ -5090,7 +5095,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B25" t="s">
         <v>299</v>
@@ -5098,7 +5103,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B26" t="s">
         <v>300</v>
@@ -5106,127 +5111,127 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B27" t="s">
-        <v>301</v>
+        <v>557</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B32" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s">
         <v>162</v>
@@ -5234,82 +5239,82 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B49" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B51" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -5317,7 +5322,7 @@
         <v>191</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -5325,7 +5330,7 @@
         <v>192</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -5333,7 +5338,7 @@
         <v>193</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -5341,7 +5346,7 @@
         <v>213</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -5349,7 +5354,7 @@
         <v>214</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -5357,7 +5362,7 @@
         <v>215</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -5365,7 +5370,7 @@
         <v>216</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -5373,7 +5378,7 @@
         <v>218</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -5381,7 +5386,7 @@
         <v>219</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -5389,7 +5394,7 @@
         <v>220</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -5397,7 +5402,7 @@
         <v>221</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -5405,7 +5410,7 @@
         <v>222</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -5413,7 +5418,7 @@
         <v>223</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -5421,7 +5426,7 @@
         <v>224</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -5429,7 +5434,7 @@
         <v>194</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -5437,7 +5442,7 @@
         <v>166</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -5445,7 +5450,7 @@
         <v>239</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -5453,7 +5458,7 @@
         <v>240</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -5461,7 +5466,7 @@
         <v>245</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -5469,7 +5474,7 @@
         <v>267</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -5477,7 +5482,7 @@
         <v>167</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -5485,7 +5490,7 @@
         <v>227</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -5493,7 +5498,7 @@
         <v>228</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -5501,7 +5506,7 @@
         <v>229</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -5509,7 +5514,7 @@
         <v>174</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -5517,7 +5522,7 @@
         <v>209</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -5525,7 +5530,7 @@
         <v>210</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -5533,7 +5538,7 @@
         <v>243</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -5541,7 +5546,7 @@
         <v>244</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -5549,7 +5554,7 @@
         <v>273</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -5557,7 +5562,7 @@
         <v>274</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -5565,12 +5570,12 @@
         <v>195</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>196</v>
@@ -5578,346 +5583,346 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>389</v>
+      </c>
+      <c r="B86" t="s">
         <v>390</v>
-      </c>
-      <c r="B86" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>391</v>
+      </c>
+      <c r="B87" t="s">
         <v>392</v>
-      </c>
-      <c r="B87" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>393</v>
+      </c>
+      <c r="B88" t="s">
         <v>394</v>
-      </c>
-      <c r="B88" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
+        <v>395</v>
+      </c>
+      <c r="B89" t="s">
         <v>396</v>
-      </c>
-      <c r="B89" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>397</v>
+      </c>
+      <c r="B90" t="s">
         <v>398</v>
-      </c>
-      <c r="B90" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>399</v>
+      </c>
+      <c r="B91" t="s">
         <v>400</v>
-      </c>
-      <c r="B91" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B92" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B93" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B94" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B95" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B96" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B97" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>430</v>
+      </c>
+      <c r="B98" t="s">
         <v>431</v>
-      </c>
-      <c r="B98" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B99" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>433</v>
+      </c>
+      <c r="B100" t="s">
         <v>434</v>
-      </c>
-      <c r="B100" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>451</v>
+      </c>
+      <c r="B101" t="s">
         <v>452</v>
-      </c>
-      <c r="B101" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B102" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B103" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B104" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B105" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B106" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B107" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B108" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B109" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B110" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B111" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>515</v>
+      </c>
+      <c r="B112" t="s">
         <v>516</v>
-      </c>
-      <c r="B112" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>517</v>
+      </c>
+      <c r="B113" t="s">
         <v>518</v>
-      </c>
-      <c r="B113" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>527</v>
+      </c>
+      <c r="B114" t="s">
         <v>528</v>
-      </c>
-      <c r="B114" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>529</v>
+      </c>
+      <c r="B115" t="s">
         <v>530</v>
-      </c>
-      <c r="B115" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>531</v>
+      </c>
+      <c r="B116" t="s">
         <v>532</v>
-      </c>
-      <c r="B116" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>533</v>
+      </c>
+      <c r="B117" t="s">
         <v>534</v>
-      </c>
-      <c r="B117" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B118" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
+        <v>539</v>
+      </c>
+      <c r="B120" t="s">
         <v>540</v>
-      </c>
-      <c r="B120" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B122" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B124" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
+        <v>550</v>
+      </c>
+      <c r="B126" t="s">
         <v>551</v>
-      </c>
-      <c r="B126" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>552</v>
+      </c>
+      <c r="B127" s="10" t="s">
         <v>553</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>554</v>
+      </c>
+      <c r="B128" t="s">
         <v>555</v>
-      </c>
-      <c r="B128" t="s">
-        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -5959,7 +5964,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>23</v>
@@ -5976,10 +5981,10 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>64</v>
@@ -5990,10 +5995,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -6066,25 +6071,25 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>502</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -6170,7 +6175,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>10</v>
@@ -6181,7 +6186,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C4" t="s">
         <v>177</v>
@@ -6195,7 +6200,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C5" t="s">
         <v>178</v>
@@ -6209,7 +6214,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C6" t="s">
         <v>179</v>
@@ -6223,7 +6228,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C7" t="s">
         <v>180</v>
@@ -6237,7 +6242,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C8" t="s">
         <v>181</v>
@@ -6251,7 +6256,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C9" t="s">
         <v>182</v>
@@ -6265,7 +6270,7 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C10" t="s">
         <v>183</v>
@@ -6279,7 +6284,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C11" t="s">
         <v>200</v>
@@ -6293,7 +6298,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C12" t="s">
         <v>184</v>
@@ -6307,7 +6312,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C13" t="s">
         <v>185</v>
@@ -6321,7 +6326,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C14" t="s">
         <v>186</v>
@@ -6335,7 +6340,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C15" t="s">
         <v>187</v>
@@ -6349,7 +6354,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C16" t="s">
         <v>188</v>
@@ -6363,7 +6368,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C17" t="s">
         <v>189</v>
@@ -6377,7 +6382,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>190</v>
@@ -6391,10 +6396,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
+        <v>524</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>525</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>526</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -6405,7 +6410,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>171</v>
@@ -6419,7 +6424,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>172</v>
@@ -6433,7 +6438,7 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>173</v>
@@ -6447,10 +6452,10 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -6461,10 +6466,10 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -6475,10 +6480,10 @@
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -6489,7 +6494,7 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>247</v>
@@ -6503,7 +6508,7 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>269</v>
@@ -6517,10 +6522,10 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -6531,10 +6536,10 @@
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -6545,7 +6550,7 @@
         <v>160</v>
       </c>
       <c r="B30" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>205</v>
@@ -6576,7 +6581,7 @@
         <v>207</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -6601,7 +6606,7 @@
         <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>170</v>
@@ -6787,7 +6792,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K4" t="s">
         <v>68</v>
@@ -6825,7 +6830,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K5" t="s">
         <v>68</v>
@@ -6863,7 +6868,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K6" t="s">
         <v>68</v>
@@ -6901,7 +6906,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K7" t="s">
         <v>68</v>
@@ -6939,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K8" t="s">
         <v>68</v>
@@ -6977,7 +6982,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K9" t="s">
         <v>68</v>
@@ -7015,7 +7020,7 @@
         <v>10</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K10" t="s">
         <v>68</v>
@@ -7053,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K11" t="s">
         <v>68</v>
@@ -7091,7 +7096,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K12" t="s">
         <v>68</v>
@@ -7129,7 +7134,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K13" t="s">
         <v>68</v>
@@ -7167,7 +7172,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K14" t="s">
         <v>68</v>
@@ -7205,7 +7210,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K15" t="s">
         <v>68</v>
@@ -7243,7 +7248,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K16" t="s">
         <v>68</v>
@@ -7281,7 +7286,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K17" t="s">
         <v>68</v>
@@ -7319,7 +7324,7 @@
         <v>7</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K18" t="s">
         <v>68</v>
@@ -7330,10 +7335,10 @@
     </row>
     <row r="19" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>235</v>
@@ -7345,19 +7350,19 @@
         <v>11</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G19" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I19" s="11">
         <v>7</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K19" t="s">
         <v>68</v>
@@ -7395,7 +7400,7 @@
         <v>10</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K20" t="s">
         <v>68</v>
@@ -7433,7 +7438,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K21" t="s">
         <v>68</v>
@@ -7471,7 +7476,7 @@
         <v>10</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K22" t="s">
         <v>68</v>
@@ -7482,10 +7487,10 @@
     </row>
     <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>234</v>
@@ -7503,13 +7508,13 @@
         <v>1</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I23" s="11">
         <v>10</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K23" t="s">
         <v>68</v>
@@ -7520,10 +7525,10 @@
     </row>
     <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>234</v>
@@ -7541,13 +7546,13 @@
         <v>1</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I24" s="11">
         <v>10</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K24" t="s">
         <v>68</v>
@@ -7558,10 +7563,10 @@
     </row>
     <row r="25" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>234</v>
@@ -7579,13 +7584,13 @@
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I25" s="11">
         <v>10</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K25" t="s">
         <v>68</v>
@@ -7623,7 +7628,7 @@
         <v>10</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K26" t="s">
         <v>68</v>
@@ -7661,7 +7666,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K27" t="s">
         <v>68</v>
@@ -7672,10 +7677,10 @@
     </row>
     <row r="28" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>234</v>
@@ -7693,13 +7698,13 @@
         <v>1</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I28" s="11">
         <v>10</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K28" t="s">
         <v>68</v>
@@ -7710,10 +7715,10 @@
     </row>
     <row r="29" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>234</v>
@@ -7725,19 +7730,19 @@
         <v>13</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I29" s="11">
         <v>7</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K29" t="s">
         <v>68</v>
@@ -7773,7 +7778,7 @@
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K30" t="s">
         <v>68</v>
@@ -7809,7 +7814,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K31" t="s">
         <v>68</v>
@@ -7845,7 +7850,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K32" t="s">
         <v>68</v>
@@ -7881,7 +7886,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K33" t="s">
         <v>68</v>
@@ -7892,10 +7897,10 @@
     </row>
     <row r="34" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>234</v>
@@ -7907,7 +7912,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G34" s="11" t="b">
         <v>0</v>
@@ -7917,7 +7922,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
@@ -7955,7 +7960,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K35" t="s">
         <v>68</v>
@@ -7966,10 +7971,10 @@
     </row>
     <row r="36" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>234</v>
@@ -7993,7 +7998,7 @@
         <v>10</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K36" t="s">
         <v>68</v>
@@ -8004,10 +8009,10 @@
     </row>
     <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>234</v>
@@ -8025,13 +8030,13 @@
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I37" s="11">
         <v>10</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K37" t="s">
         <v>68</v>
@@ -8069,7 +8074,7 @@
         <v>10</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K38" t="s">
         <v>68</v>
@@ -8107,7 +8112,7 @@
         <v>10</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K39" t="s">
         <v>68</v>
@@ -8125,19 +8130,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2444F32-CF16-41C0-B4D3-AE1758A9A6E6}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="13.625" customWidth="1"/>
-    <col min="6" max="6" width="13.875" customWidth="1"/>
-    <col min="7" max="7" width="15.125" customWidth="1"/>
-    <col min="8" max="8" width="28.875" customWidth="1"/>
-    <col min="9" max="9" width="20.375" customWidth="1"/>
+    <col min="6" max="7" width="13.875" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="28.875" customWidth="1"/>
+    <col min="10" max="10" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -8163,10 +8168,13 @@
         <v>0</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -8177,7 +8185,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>20</v>
@@ -8186,16 +8194,19 @@
         <v>20</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -8215,16 +8226,19 @@
         <v>37</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -8243,14 +8257,17 @@
       <c r="F4">
         <v>3</v>
       </c>
-      <c r="H4" t="s">
-        <v>459</v>
+      <c r="G4">
+        <v>2</v>
       </c>
       <c r="I4" t="s">
+        <v>458</v>
+      </c>
+      <c r="J4" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -8269,14 +8286,17 @@
       <c r="F5">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
-        <v>460</v>
+      <c r="G5">
+        <v>2.5</v>
       </c>
       <c r="I5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>459</v>
+      </c>
+      <c r="J5" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -8295,14 +8315,17 @@
       <c r="F6">
         <v>5</v>
       </c>
-      <c r="H6" t="s">
-        <v>461</v>
+      <c r="G6">
+        <v>5</v>
       </c>
       <c r="I6" t="s">
+        <v>460</v>
+      </c>
+      <c r="J6" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -8321,13 +8344,16 @@
       <c r="F7">
         <v>10</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
         <v>67</v>
       </c>
-      <c r="H7" t="s">
-        <v>462</v>
-      </c>
       <c r="I7" t="s">
+        <v>461</v>
+      </c>
+      <c r="J7" t="s">
         <v>276</v>
       </c>
     </row>
@@ -8466,7 +8492,7 @@
         <v>105</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -8483,7 +8509,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F4">
         <v>240</v>
@@ -8521,7 +8547,7 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F5">
         <v>240</v>
@@ -8559,7 +8585,7 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="F6">
         <v>240</v>
@@ -8597,7 +8623,7 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="F7">
         <v>240</v>
@@ -8635,7 +8661,7 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="F8">
         <v>240</v>
@@ -8673,7 +8699,7 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="F9">
         <v>300</v>
@@ -8711,7 +8737,7 @@
         <v>40</v>
       </c>
       <c r="E10">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="F10">
         <v>300</v>
@@ -8749,7 +8775,7 @@
         <v>45</v>
       </c>
       <c r="E11">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>300</v>
@@ -8787,7 +8813,7 @@
         <v>50</v>
       </c>
       <c r="E12">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>300</v>
@@ -8825,7 +8851,7 @@
         <v>55</v>
       </c>
       <c r="E13">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>300</v>
@@ -8863,7 +8889,7 @@
         <v>60</v>
       </c>
       <c r="E14">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>300</v>
@@ -8901,7 +8927,7 @@
         <v>65</v>
       </c>
       <c r="E15">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>360</v>
@@ -8939,7 +8965,7 @@
         <v>70</v>
       </c>
       <c r="E16">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F16">
         <v>360</v>
@@ -8977,7 +9003,7 @@
         <v>75</v>
       </c>
       <c r="E17">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="F17">
         <v>360</v>
@@ -9015,7 +9041,7 @@
         <v>80</v>
       </c>
       <c r="E18">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F18">
         <v>360</v>
@@ -9053,7 +9079,7 @@
         <v>85</v>
       </c>
       <c r="E19">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F19">
         <v>360</v>
@@ -9091,7 +9117,7 @@
         <v>90</v>
       </c>
       <c r="E20">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F20">
         <v>360</v>
@@ -9129,7 +9155,7 @@
         <v>95</v>
       </c>
       <c r="E21">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F21">
         <v>360</v>
@@ -9167,7 +9193,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F22">
         <v>360</v>
@@ -9205,7 +9231,7 @@
         <v>105</v>
       </c>
       <c r="E23">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="F23">
         <v>360</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADA48CF-474B-42FC-8EB9-D14DC6FD8C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD72F746-83CD-43C1-A337-E51ED1D5ECC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="5" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -8512,7 +8512,7 @@
         <v>60</v>
       </c>
       <c r="F4">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -8521,7 +8521,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J4" t="s">
         <v>68</v>
@@ -8550,7 +8550,7 @@
         <v>60</v>
       </c>
       <c r="F5">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="G5">
         <v>1.5</v>
@@ -8559,13 +8559,13 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J5" t="s">
         <v>68</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5">
         <v>1.1000000000000001</v>
@@ -8588,7 +8588,7 @@
         <v>60</v>
       </c>
       <c r="F6">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -8597,13 +8597,13 @@
         <v>5</v>
       </c>
       <c r="I6">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J6" t="s">
         <v>68</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <v>1.2</v>
@@ -8626,7 +8626,7 @@
         <v>60</v>
       </c>
       <c r="F7">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>2.5</v>
@@ -8635,13 +8635,13 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J7" t="s">
         <v>68</v>
       </c>
       <c r="K7">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L7">
         <v>1.3</v>
@@ -8664,7 +8664,7 @@
         <v>80</v>
       </c>
       <c r="F8">
-        <v>240</v>
+        <v>80</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -8673,13 +8673,13 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J8" t="s">
         <v>68</v>
       </c>
       <c r="K8">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L8">
         <v>1.4</v>
@@ -8702,7 +8702,7 @@
         <v>80</v>
       </c>
       <c r="F9">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="G9">
         <v>3.5</v>
@@ -8711,13 +8711,13 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J9" t="s">
         <v>68</v>
       </c>
       <c r="K9">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L9">
         <v>1.5</v>
@@ -8740,7 +8740,7 @@
         <v>80</v>
       </c>
       <c r="F10">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="G10">
         <v>4</v>
@@ -8749,13 +8749,13 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J10" t="s">
         <v>68</v>
       </c>
       <c r="K10">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="L10">
         <v>1.6</v>
@@ -8778,7 +8778,7 @@
         <v>80</v>
       </c>
       <c r="F11">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="G11">
         <v>4.5</v>
@@ -8787,13 +8787,13 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J11" t="s">
         <v>68</v>
       </c>
       <c r="K11">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="L11">
         <v>1.7</v>
@@ -8816,7 +8816,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8825,13 +8825,13 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J12" t="s">
         <v>68</v>
       </c>
       <c r="K12">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="L12">
         <v>1.8</v>
@@ -8854,7 +8854,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>5.5</v>
@@ -8863,13 +8863,13 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J13" t="s">
         <v>68</v>
       </c>
       <c r="K13">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="L13">
         <v>1.9</v>
@@ -8892,7 +8892,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -8901,13 +8901,13 @@
         <v>8</v>
       </c>
       <c r="I14">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J14" t="s">
         <v>68</v>
       </c>
       <c r="K14">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -8930,7 +8930,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>6.5</v>
@@ -8939,13 +8939,13 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J15" t="s">
         <v>68</v>
       </c>
       <c r="K15">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="L15">
         <v>2.1</v>
@@ -8968,7 +8968,7 @@
         <v>120</v>
       </c>
       <c r="F16">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G16">
         <v>7</v>
@@ -8977,13 +8977,13 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J16" t="s">
         <v>68</v>
       </c>
       <c r="K16">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="L16">
         <v>2.2000000000000002</v>
@@ -9006,7 +9006,7 @@
         <v>120</v>
       </c>
       <c r="F17">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G17">
         <v>7.5</v>
@@ -9015,13 +9015,13 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="J17" t="s">
         <v>68</v>
       </c>
       <c r="K17">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="L17">
         <v>2.2999999999999998</v>
@@ -9044,7 +9044,7 @@
         <v>120</v>
       </c>
       <c r="F18">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -9053,13 +9053,13 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="J18" t="s">
         <v>68</v>
       </c>
       <c r="K18">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="L18">
         <v>2.4</v>
@@ -9082,7 +9082,7 @@
         <v>120</v>
       </c>
       <c r="F19">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G19">
         <v>8.5</v>
@@ -9091,13 +9091,13 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="J19" t="s">
         <v>68</v>
       </c>
       <c r="K19">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="L19">
         <v>2.5</v>
@@ -9120,7 +9120,7 @@
         <v>120</v>
       </c>
       <c r="F20">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G20">
         <v>9</v>
@@ -9129,13 +9129,13 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="J20" t="s">
         <v>68</v>
       </c>
       <c r="K20">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="L20">
         <v>2.6</v>
@@ -9158,7 +9158,7 @@
         <v>120</v>
       </c>
       <c r="F21">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G21">
         <v>9.5</v>
@@ -9167,13 +9167,13 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="J21" t="s">
         <v>68</v>
       </c>
       <c r="K21">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="L21">
         <v>2.7</v>
@@ -9196,7 +9196,7 @@
         <v>120</v>
       </c>
       <c r="F22">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -9205,13 +9205,13 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="J22" t="s">
         <v>68</v>
       </c>
       <c r="K22">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="L22">
         <v>2.8</v>
@@ -9234,7 +9234,7 @@
         <v>120</v>
       </c>
       <c r="F23">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G23">
         <v>10.5</v>
@@ -9243,13 +9243,13 @@
         <v>11</v>
       </c>
       <c r="I23">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="J23" t="s">
         <v>68</v>
       </c>
       <c r="K23">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="L23">
         <v>3</v>
@@ -9322,7 +9322,7 @@
         <v>264</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>263</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD72F746-83CD-43C1-A337-E51ED1D5ECC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C8DAC1-4894-4CDB-B5EE-E68CCC096987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="5" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="563">
   <si>
     <t>ALL</t>
   </si>
@@ -2056,6 +2056,22 @@
   </si>
   <si>
     <t>EatTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_종이몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody04_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_종이몸01정보]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6632,7 +6648,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -7752,11 +7768,9 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
-        <v>167</v>
-      </c>
+      <c r="A30" s="11"/>
       <c r="B30" s="11" t="s">
-        <v>167</v>
+        <v>559</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>234</v>
@@ -7765,20 +7779,22 @@
         <v>51</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>165</v>
+        <v>560</v>
       </c>
       <c r="G30" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>561</v>
+      </c>
       <c r="I30" s="11">
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>345</v>
+        <v>562</v>
       </c>
       <c r="K30" t="s">
         <v>68</v>
@@ -7789,10 +7805,10 @@
     </row>
     <row r="31" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>234</v>
@@ -7804,7 +7820,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>230</v>
+        <v>165</v>
       </c>
       <c r="G31" s="11" t="b">
         <v>0</v>
@@ -7814,7 +7830,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K31" t="s">
         <v>68</v>
@@ -7825,10 +7841,10 @@
     </row>
     <row r="32" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>234</v>
@@ -7840,7 +7856,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G32" s="11" t="b">
         <v>0</v>
@@ -7850,7 +7866,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K32" t="s">
         <v>68</v>
@@ -7861,10 +7877,10 @@
     </row>
     <row r="33" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>234</v>
@@ -7876,7 +7892,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G33" s="11" t="b">
         <v>0</v>
@@ -7886,7 +7902,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K33" t="s">
         <v>68</v>
@@ -7897,10 +7913,10 @@
     </row>
     <row r="34" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>448</v>
+        <v>229</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>448</v>
+        <v>229</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>234</v>
@@ -7912,7 +7928,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>449</v>
+        <v>232</v>
       </c>
       <c r="G34" s="11" t="b">
         <v>0</v>
@@ -7922,7 +7938,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>450</v>
+        <v>348</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
@@ -7933,10 +7949,10 @@
     </row>
     <row r="35" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>174</v>
+        <v>448</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>174</v>
+        <v>448</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>234</v>
@@ -7945,22 +7961,20 @@
         <v>51</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>175</v>
+        <v>449</v>
       </c>
       <c r="G35" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>205</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H35" s="11"/>
       <c r="I35" s="11">
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>349</v>
+        <v>450</v>
       </c>
       <c r="K35" t="s">
         <v>68</v>
@@ -7971,10 +7985,10 @@
     </row>
     <row r="36" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>485</v>
+        <v>174</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>485</v>
+        <v>174</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>234</v>
@@ -7986,19 +8000,19 @@
         <v>159</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="G36" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="I36" s="11">
         <v>10</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>489</v>
+        <v>349</v>
       </c>
       <c r="K36" t="s">
         <v>68</v>
@@ -8009,10 +8023,10 @@
     </row>
     <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>234</v>
@@ -8030,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>487</v>
+        <v>168</v>
       </c>
       <c r="I37" s="11">
         <v>10</v>
@@ -8047,10 +8061,10 @@
     </row>
     <row r="38" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>273</v>
+        <v>486</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>273</v>
+        <v>486</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>234</v>
@@ -8062,19 +8076,19 @@
         <v>159</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G38" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>169</v>
+        <v>487</v>
       </c>
       <c r="I38" s="11">
         <v>10</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K38" t="s">
         <v>68</v>
@@ -8085,10 +8099,10 @@
     </row>
     <row r="39" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>234</v>
@@ -8100,24 +8114,62 @@
         <v>159</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G39" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I39" s="11">
         <v>10</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>352</v>
+        <v>488</v>
       </c>
       <c r="K39" t="s">
         <v>68</v>
       </c>
       <c r="L39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="G40" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I40" s="11">
+        <v>10</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="K40" t="s">
+        <v>68</v>
+      </c>
+      <c r="L40">
         <v>5</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C8DAC1-4894-4CDB-B5EE-E68CCC096987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F30C9B-D9E8-4882-93FB-3AD7AB730E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="573">
   <si>
     <t>ALL</t>
   </si>
@@ -307,10 +307,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>팽이코인. 많은 것을 할 수 있다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[팽이코인]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -371,14 +367,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>일반 알이다. 온기가 느껴진다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>레어 알이다. 온기가 느껴진다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>enum&lt;CategoryType&gt;</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -502,10 +490,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>생일인 모양이다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[모자01]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -514,10 +498,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>근엄해지고 싶었다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ResourceKey</t>
   </si>
   <si>
@@ -548,10 +528,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>공부를 하려는 걸까?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[일반뽑기01]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1136,30 +1112,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>모자1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>모자2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가방1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>연두색의 껍질.</t>
   </si>
   <si>
     <t>갈색의 껍질.</t>
   </si>
   <si>
-    <t>초록색의 껍질.</t>
-  </si>
-  <si>
-    <t>보라색의 껍질.</t>
-  </si>
-  <si>
     <t>파란색의 껍질.</t>
   </si>
   <si>
@@ -1370,9 +1328,6 @@
     <t>긴껍질06</t>
   </si>
   <si>
-    <t>버섯더듬이</t>
-  </si>
-  <si>
     <t>뱅글더듬이</t>
   </si>
   <si>
@@ -1391,9 +1346,6 @@
     <t>고양이더듬이02</t>
   </si>
   <si>
-    <t>레어_당근껍질</t>
-  </si>
-  <si>
     <t>일반달팽이_몸01</t>
   </si>
   <si>
@@ -2072,6 +2024,98 @@
   </si>
   <si>
     <t>[일반달팽이_종이몸01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중절모</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생일꼬깔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>회사원 가방</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간색의 껍질.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>네잎클로버를 담은 껍질.
+오늘은 행운이 가득하기를!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바삭거리지만 어딘가 눅눅한 집.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내성적인 달팽이는 종이를 얼굴에 붙이기로 했다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>버섯 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_버섯더듬이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_오목더듬이01정보]</t>
+  </si>
+  <si>
+    <t>빵빵한 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어딘가 부어오른 더듬이.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗쪽은 빼고 주는게 좋습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이들의 기본중의 기본 식사.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이걸 싫어하는 달팽이가 있을까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>안심하세요! 염분을 뺀 순수한 두부입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>팽이코인. 많은 것을 할 수 있습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 알. 온기가 느껴집니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어 알. 온기가 느껴집니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>근엄해지고 싶었습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생일인 모양이네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어딘가로 출근하는 모습입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2983,10 +3027,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -3006,10 +3050,10 @@
         <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>10</v>
@@ -3082,7 +3126,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="E8" s="13">
         <v>100</v>
@@ -3102,13 +3146,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="E9" s="13">
         <v>200</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>58</v>
@@ -3125,13 +3169,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="E10" s="13">
         <v>400</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>59</v>
@@ -3142,22 +3186,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C11" s="13">
         <v>4</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="E11" s="13">
         <v>300</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -3179,7 +3223,7 @@
     </row>
     <row r="13" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>51</v>
@@ -3188,159 +3232,159 @@
         <v>1</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>75</v>
       </c>
       <c r="C14" s="13">
         <v>2</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" s="13">
         <v>3</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="13">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
         <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>93</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" s="13"/>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18" s="13"/>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" s="13"/>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="D20" s="13"/>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21" s="13"/>
       <c r="G21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22" s="13"/>
       <c r="G22" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3350,15 +3394,15 @@
         <v>250</v>
       </c>
       <c r="G23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C24">
         <v>2</v>
@@ -3368,15 +3412,15 @@
         <v>260</v>
       </c>
       <c r="G24" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3386,15 +3430,15 @@
         <v>251</v>
       </c>
       <c r="G25" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -3404,49 +3448,49 @@
         <v>255</v>
       </c>
       <c r="G26" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="B27" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="B28" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="B29" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="G29" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3590,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>25</v>
@@ -3555,7 +3599,7 @@
         <v>23</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -3563,30 +3607,30 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4">
         <v>180</v>
@@ -3595,36 +3639,36 @@
         <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F4" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="G4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>600</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="G5" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3671,7 +3715,7 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>5</v>
@@ -3685,101 +3729,101 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="B7" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="C7" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="D7" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="E7" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="B8" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="C8" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="D8" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="E8" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -3844,7 +3888,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>23</v>
@@ -3856,25 +3900,25 @@
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>20</v>
@@ -3882,16 +3926,16 @@
     </row>
     <row r="3" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>64</v>
@@ -3900,27 +3944,27 @@
         <v>65</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
@@ -3932,7 +3976,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -3941,16 +3985,16 @@
         <v>3</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L4">
         <f>F4/2</f>
@@ -3959,7 +4003,7 @@
     </row>
     <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
@@ -3971,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -3980,16 +4024,16 @@
         <v>4</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L5">
         <f t="shared" ref="L5:L9" si="0">F5/2</f>
@@ -3998,7 +4042,7 @@
     </row>
     <row r="6" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -4010,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -4019,16 +4063,16 @@
         <v>4</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L6">
         <f t="shared" si="0"/>
@@ -4037,7 +4081,7 @@
     </row>
     <row r="7" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -4049,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -4058,16 +4102,16 @@
         <v>8</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
@@ -4076,10 +4120,10 @@
     </row>
     <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
@@ -4088,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8">
         <v>50</v>
@@ -4097,16 +4141,16 @@
         <v>35</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L8">
         <f t="shared" si="0"/>
@@ -4115,19 +4159,19 @@
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F9">
         <v>300</v>
@@ -4136,16 +4180,16 @@
         <v>210</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9">
         <f t="shared" si="0"/>
@@ -4154,7 +4198,7 @@
     </row>
     <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
@@ -4166,17 +4210,17 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -4184,10 +4228,10 @@
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
         <v>51</v>
@@ -4196,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11">
         <v>500</v>
@@ -4205,16 +4249,16 @@
         <v>350</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L11">
         <f t="shared" ref="L11:L13" si="1">F11/2</f>
@@ -4223,10 +4267,10 @@
     </row>
     <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
@@ -4235,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12">
         <v>500</v>
@@ -4244,16 +4288,16 @@
         <v>350</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L12">
         <f t="shared" si="1"/>
@@ -4262,10 +4306,10 @@
     </row>
     <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
@@ -4274,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F13">
         <v>500</v>
@@ -4283,16 +4327,16 @@
         <v>350</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L13">
         <f t="shared" si="1"/>
@@ -4345,13 +4389,13 @@
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>24</v>
@@ -4362,30 +4406,30 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -4399,13 +4443,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -4419,13 +4463,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -4439,13 +4483,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -4459,13 +4503,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -4479,13 +4523,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B9">
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -4499,13 +4543,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -4557,7 +4601,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>23</v>
@@ -4574,21 +4618,21 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -4605,7 +4649,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
         <v>51</v>
@@ -4622,7 +4666,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
@@ -4639,7 +4683,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
         <v>51</v>
@@ -4656,13 +4700,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
         <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -4673,13 +4717,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
         <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -4690,7 +4734,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
         <v>51</v>
@@ -4707,13 +4751,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -4724,13 +4768,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
         <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -4741,13 +4785,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
         <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -4829,25 +4873,25 @@
         <v>23</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -4855,51 +4899,51 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>204</v>
-      </c>
       <c r="J3" s="8" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -4910,11 +4954,11 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="51.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -4938,15 +4982,15 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B4" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4983,962 +5027,1026 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>445</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>284</v>
+        <v>446</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>447</v>
       </c>
       <c r="B11" t="s">
-        <v>285</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>286</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
+        <v>448</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>567</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>569</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>284</v>
       </c>
       <c r="B20" t="s">
-        <v>294</v>
+        <v>570</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>285</v>
       </c>
       <c r="B21" t="s">
-        <v>295</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
-        <v>325</v>
+      <c r="A22" t="s">
+        <v>286</v>
       </c>
       <c r="B22" t="s">
-        <v>296</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
-        <v>326</v>
+      <c r="A23" t="s">
+        <v>116</v>
       </c>
       <c r="B23" t="s">
-        <v>297</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
-        <v>327</v>
+      <c r="A24" t="s">
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>298</v>
+        <v>551</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
-        <v>328</v>
+      <c r="A25" t="s">
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>299</v>
+        <v>552</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="B26" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="B27" t="s">
-        <v>557</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="B28" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="B29" t="s">
-        <v>302</v>
+        <v>317</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="B30" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s">
-        <v>304</v>
+        <v>544</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="B37" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B40" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s">
-        <v>162</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="B44" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s">
-        <v>318</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="B50" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B51" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="B52" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>356</v>
+        <v>341</v>
+      </c>
+      <c r="B53" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>357</v>
+        <v>342</v>
+      </c>
+      <c r="B54" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>358</v>
+        <v>343</v>
+      </c>
+      <c r="B55" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>359</v>
+        <v>344</v>
+      </c>
+      <c r="B56" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>223</v>
+        <v>513</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>368</v>
+        <v>555</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>267</v>
+        <v>188</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>382</v>
+        <v>556</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="11" t="s">
-        <v>209</v>
+        <v>549</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>371</v>
+        <v>557</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="11" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="11" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
-        <v>273</v>
+        <v>223</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="11" t="s">
-        <v>274</v>
+        <v>168</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>376</v>
+        <v>558</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="11" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="11" t="s">
-        <v>388</v>
+        <v>204</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>196</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>389</v>
-      </c>
-      <c r="B86" t="s">
-        <v>390</v>
+      <c r="A86" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>391</v>
-      </c>
-      <c r="B87" t="s">
-        <v>392</v>
+      <c r="A87" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>393</v>
-      </c>
-      <c r="B88" t="s">
-        <v>394</v>
+      <c r="A88" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>395</v>
-      </c>
-      <c r="B89" t="s">
-        <v>396</v>
+      <c r="A89" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>397</v>
-      </c>
-      <c r="B90" t="s">
-        <v>398</v>
+      <c r="A90" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>399</v>
-      </c>
-      <c r="B91" t="s">
-        <v>400</v>
+      <c r="A91" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>418</v>
-      </c>
-      <c r="B92" t="s">
-        <v>424</v>
+        <v>560</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>419</v>
-      </c>
-      <c r="B93" t="s">
-        <v>425</v>
+      <c r="A93" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>420</v>
+        <v>376</v>
       </c>
       <c r="B94" t="s">
-        <v>426</v>
+        <v>377</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>421</v>
+        <v>378</v>
       </c>
       <c r="B95" t="s">
-        <v>427</v>
+        <v>379</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>422</v>
+        <v>380</v>
       </c>
       <c r="B96" t="s">
-        <v>428</v>
+        <v>381</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>423</v>
+        <v>382</v>
       </c>
       <c r="B97" t="s">
-        <v>429</v>
+        <v>383</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>430</v>
+        <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>432</v>
+        <v>386</v>
       </c>
       <c r="B99" t="s">
-        <v>435</v>
+        <v>387</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="B100" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>451</v>
+        <v>406</v>
       </c>
       <c r="B101" t="s">
-        <v>452</v>
+        <v>412</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>465</v>
+        <v>407</v>
       </c>
       <c r="B102" t="s">
-        <v>469</v>
+        <v>413</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>466</v>
+        <v>408</v>
       </c>
       <c r="B103" t="s">
-        <v>470</v>
+        <v>414</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>467</v>
+        <v>409</v>
       </c>
       <c r="B104" t="s">
-        <v>471</v>
+        <v>415</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>468</v>
+        <v>410</v>
       </c>
       <c r="B105" t="s">
-        <v>472</v>
+        <v>416</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>475</v>
+        <v>417</v>
       </c>
       <c r="B106" t="s">
-        <v>477</v>
+        <v>418</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>476</v>
+        <v>419</v>
       </c>
       <c r="B107" t="s">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>506</v>
+        <v>420</v>
       </c>
       <c r="B108" t="s">
-        <v>513</v>
+        <v>421</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>507</v>
+        <v>438</v>
       </c>
       <c r="B109" t="s">
-        <v>512</v>
+        <v>439</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>508</v>
+        <v>452</v>
       </c>
       <c r="B110" t="s">
-        <v>510</v>
+        <v>456</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>509</v>
+        <v>453</v>
       </c>
       <c r="B111" t="s">
-        <v>511</v>
+        <v>457</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>515</v>
+        <v>454</v>
       </c>
       <c r="B112" t="s">
-        <v>516</v>
+        <v>458</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>517</v>
+        <v>455</v>
       </c>
       <c r="B113" t="s">
-        <v>518</v>
+        <v>459</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>527</v>
+        <v>462</v>
       </c>
       <c r="B114" t="s">
-        <v>528</v>
+        <v>464</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="B115" t="s">
-        <v>530</v>
+        <v>465</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="B116" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>533</v>
+        <v>494</v>
       </c>
       <c r="B117" t="s">
-        <v>534</v>
+        <v>499</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>536</v>
+        <v>495</v>
       </c>
       <c r="B118" t="s">
-        <v>535</v>
+        <v>497</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>538</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>537</v>
+        <v>496</v>
+      </c>
+      <c r="B119" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>539</v>
+        <v>502</v>
       </c>
       <c r="B120" t="s">
-        <v>540</v>
+        <v>503</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>542</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>541</v>
+        <v>504</v>
+      </c>
+      <c r="B121" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="B122" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>546</v>
-      </c>
-      <c r="B123" s="10" t="s">
-        <v>545</v>
+        <v>516</v>
+      </c>
+      <c r="B123" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
       <c r="B124" t="s">
-        <v>556</v>
+        <v>519</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>549</v>
-      </c>
-      <c r="B125" s="10" t="s">
-        <v>548</v>
+        <v>520</v>
+      </c>
+      <c r="B125" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="B126" t="s">
-        <v>551</v>
+        <v>522</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>552</v>
+        <v>525</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>553</v>
+        <v>524</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>554</v>
+        <v>526</v>
       </c>
       <c r="B128" t="s">
-        <v>555</v>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>529</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>531</v>
+      </c>
+      <c r="B130" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>533</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>534</v>
+      </c>
+      <c r="B132" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>536</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>537</v>
+      </c>
+      <c r="B134" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>539</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>541</v>
+      </c>
+      <c r="B136" t="s">
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -5980,16 +6088,16 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5997,10 +6105,10 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>64</v>
@@ -6011,10 +6119,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="B4" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -6067,19 +6175,19 @@
         <v>23</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -6087,25 +6195,25 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -6165,7 +6273,7 @@
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>25</v>
@@ -6191,7 +6299,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>10</v>
@@ -6202,10 +6310,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -6216,10 +6324,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -6230,10 +6338,10 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -6244,10 +6352,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -6258,10 +6366,10 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -6272,10 +6380,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -6286,10 +6394,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -6300,10 +6408,10 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -6314,10 +6422,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -6328,10 +6436,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -6342,10 +6450,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -6356,10 +6464,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -6370,10 +6478,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -6384,10 +6492,10 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C17" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -6398,10 +6506,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -6412,10 +6520,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -6426,10 +6534,10 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -6440,10 +6548,10 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -6454,10 +6562,10 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -6468,10 +6576,10 @@
         <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -6482,10 +6590,10 @@
         <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -6496,10 +6604,10 @@
         <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -6510,10 +6618,10 @@
         <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -6524,10 +6632,10 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -6538,10 +6646,10 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -6552,10 +6660,10 @@
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -6563,13 +6671,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -6577,13 +6685,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B31" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -6591,13 +6699,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -6605,13 +6713,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -6619,13 +6727,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -6714,10 +6822,10 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>25</v>
@@ -6726,7 +6834,7 @@
         <v>16</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>24</v>
@@ -6735,7 +6843,7 @@
         <v>24</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>20</v>
@@ -6746,13 +6854,13 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>1</v>
@@ -6764,30 +6872,30 @@
         <v>17</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>51</v>
@@ -6796,19 +6904,19 @@
         <v>11</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G4" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I4" s="11">
         <v>10</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="K4" t="s">
         <v>68</v>
@@ -6819,13 +6927,13 @@
     </row>
     <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>51</v>
@@ -6834,19 +6942,19 @@
         <v>11</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G5" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I5" s="11">
         <v>10</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="K5" t="s">
         <v>68</v>
@@ -6857,13 +6965,13 @@
     </row>
     <row r="6" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>51</v>
@@ -6872,19 +6980,19 @@
         <v>11</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I6" s="11">
         <v>10</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="K6" t="s">
         <v>68</v>
@@ -6895,13 +7003,13 @@
     </row>
     <row r="7" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>51</v>
@@ -6910,19 +7018,19 @@
         <v>11</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I7" s="11">
         <v>10</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="K7" t="s">
         <v>68</v>
@@ -6933,13 +7041,13 @@
     </row>
     <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>51</v>
@@ -6948,19 +7056,19 @@
         <v>11</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G8" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I8" s="11">
         <v>10</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="K8" t="s">
         <v>68</v>
@@ -6971,13 +7079,13 @@
     </row>
     <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>51</v>
@@ -6986,19 +7094,19 @@
         <v>11</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G9" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I9" s="11">
         <v>10</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="K9" t="s">
         <v>68</v>
@@ -7009,13 +7117,13 @@
     </row>
     <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>51</v>
@@ -7024,19 +7132,19 @@
         <v>11</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G10" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I10" s="11">
         <v>10</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="K10" t="s">
         <v>68</v>
@@ -7047,13 +7155,13 @@
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>51</v>
@@ -7062,19 +7170,19 @@
         <v>11</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G11" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I11" s="11">
         <v>10</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="K11" t="s">
         <v>68</v>
@@ -7085,13 +7193,13 @@
     </row>
     <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>51</v>
@@ -7100,19 +7208,19 @@
         <v>11</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G12" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I12" s="11">
         <v>10</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="K12" t="s">
         <v>68</v>
@@ -7123,13 +7231,13 @@
     </row>
     <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>51</v>
@@ -7138,19 +7246,19 @@
         <v>11</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G13" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I13" s="11">
         <v>10</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="K13" t="s">
         <v>68</v>
@@ -7161,13 +7269,13 @@
     </row>
     <row r="14" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>51</v>
@@ -7176,19 +7284,19 @@
         <v>11</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G14" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I14" s="11">
         <v>10</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="K14" t="s">
         <v>68</v>
@@ -7199,13 +7307,13 @@
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>51</v>
@@ -7214,19 +7322,19 @@
         <v>11</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G15" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I15" s="11">
         <v>10</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="K15" t="s">
         <v>68</v>
@@ -7237,13 +7345,13 @@
     </row>
     <row r="16" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>51</v>
@@ -7252,19 +7360,19 @@
         <v>11</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G16" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I16" s="11">
         <v>10</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="K16" t="s">
         <v>68</v>
@@ -7275,13 +7383,13 @@
     </row>
     <row r="17" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>51</v>
@@ -7290,19 +7398,19 @@
         <v>11</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G17" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I17" s="11">
         <v>10</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="K17" t="s">
         <v>68</v>
@@ -7313,34 +7421,34 @@
     </row>
     <row r="18" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G18" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="I18" s="11">
         <v>7</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="K18" t="s">
         <v>68</v>
@@ -7351,34 +7459,34 @@
     </row>
     <row r="19" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>11</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="G19" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="I19" s="11">
         <v>7</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="K19" t="s">
         <v>68</v>
@@ -7389,13 +7497,13 @@
     </row>
     <row r="20" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>51</v>
@@ -7404,19 +7512,19 @@
         <v>13</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G20" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I20" s="11">
         <v>10</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="K20" t="s">
         <v>68</v>
@@ -7427,13 +7535,13 @@
     </row>
     <row r="21" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>51</v>
@@ -7442,19 +7550,19 @@
         <v>13</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G21" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I21" s="11">
         <v>10</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="K21" t="s">
         <v>68</v>
@@ -7465,13 +7573,13 @@
     </row>
     <row r="22" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>51</v>
@@ -7480,19 +7588,19 @@
         <v>13</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G22" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I22" s="11">
         <v>10</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="K22" t="s">
         <v>68</v>
@@ -7503,13 +7611,13 @@
     </row>
     <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>51</v>
@@ -7518,19 +7626,19 @@
         <v>13</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G23" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="I23" s="11">
         <v>10</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="K23" t="s">
         <v>68</v>
@@ -7541,13 +7649,13 @@
     </row>
     <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>51</v>
@@ -7556,19 +7664,19 @@
         <v>13</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G24" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="I24" s="11">
         <v>10</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="K24" t="s">
         <v>68</v>
@@ -7579,13 +7687,13 @@
     </row>
     <row r="25" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>51</v>
@@ -7594,19 +7702,19 @@
         <v>13</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G25" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="I25" s="11">
         <v>10</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="K25" t="s">
         <v>68</v>
@@ -7617,13 +7725,13 @@
     </row>
     <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>51</v>
@@ -7632,19 +7740,19 @@
         <v>13</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="G26" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I26" s="11">
         <v>10</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="K26" t="s">
         <v>68</v>
@@ -7655,13 +7763,13 @@
     </row>
     <row r="27" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>51</v>
@@ -7670,19 +7778,19 @@
         <v>13</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="G27" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="I27" s="11">
         <v>10</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="K27" t="s">
         <v>68</v>
@@ -7693,13 +7801,13 @@
     </row>
     <row r="28" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>51</v>
@@ -7708,19 +7816,19 @@
         <v>13</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="G28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="I28" s="11">
         <v>10</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="K28" t="s">
         <v>68</v>
@@ -7731,34 +7839,34 @@
     </row>
     <row r="29" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="G29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="I29" s="11">
         <v>7</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="K29" t="s">
         <v>68</v>
@@ -7770,10 +7878,10 @@
     <row r="30" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11"/>
       <c r="B30" s="11" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>51</v>
@@ -7782,19 +7890,19 @@
         <v>13</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="G30" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="I30" s="11">
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="K30" t="s">
         <v>68</v>
@@ -7805,13 +7913,13 @@
     </row>
     <row r="31" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>51</v>
@@ -7820,7 +7928,7 @@
         <v>14</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G31" s="11" t="b">
         <v>0</v>
@@ -7830,7 +7938,7 @@
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="K31" t="s">
         <v>68</v>
@@ -7841,13 +7949,13 @@
     </row>
     <row r="32" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>51</v>
@@ -7856,7 +7964,7 @@
         <v>14</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G32" s="11" t="b">
         <v>0</v>
@@ -7866,7 +7974,7 @@
         <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="K32" t="s">
         <v>68</v>
@@ -7877,13 +7985,13 @@
     </row>
     <row r="33" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>234</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>51</v>
@@ -7892,7 +8000,7 @@
         <v>14</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G33" s="11" t="b">
         <v>0</v>
@@ -7902,7 +8010,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="K33" t="s">
         <v>68</v>
@@ -7913,13 +8021,13 @@
     </row>
     <row r="34" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>51</v>
@@ -7928,7 +8036,7 @@
         <v>14</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G34" s="11" t="b">
         <v>0</v>
@@ -7938,7 +8046,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
@@ -7949,13 +8057,13 @@
     </row>
     <row r="35" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>51</v>
@@ -7964,7 +8072,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="G35" s="11" t="b">
         <v>0</v>
@@ -7974,7 +8082,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="K35" t="s">
         <v>68</v>
@@ -7985,34 +8093,34 @@
     </row>
     <row r="36" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G36" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I36" s="11">
         <v>10</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>349</v>
+        <v>559</v>
       </c>
       <c r="K36" t="s">
         <v>68</v>
@@ -8023,34 +8131,34 @@
     </row>
     <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G37" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I37" s="11">
         <v>10</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="K37" t="s">
         <v>68</v>
@@ -8061,34 +8169,34 @@
     </row>
     <row r="38" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G38" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="I38" s="11">
         <v>10</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="K38" t="s">
         <v>68</v>
@@ -8099,34 +8207,34 @@
     </row>
     <row r="39" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G39" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="I39" s="11">
         <v>10</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="K39" t="s">
         <v>68</v>
@@ -8137,34 +8245,34 @@
     </row>
     <row r="40" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>51</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="G40" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I40" s="11">
         <v>10</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="K40" t="s">
         <v>68</v>
@@ -8237,7 +8345,7 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>20</v>
@@ -8266,10 +8374,10 @@
         <v>30</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>21</v>
@@ -8278,13 +8386,13 @@
         <v>37</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>66</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>4</v>
@@ -8298,7 +8406,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
@@ -8313,10 +8421,10 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="J4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -8327,7 +8435,7 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D5" t="s">
         <v>51</v>
@@ -8342,10 +8450,10 @@
         <v>2.5</v>
       </c>
       <c r="I5" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="J5" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -8371,10 +8479,10 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="J6" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -8403,10 +8511,10 @@
         <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="J7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -8514,37 +8622,37 @@
         <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>48</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -9346,7 +9454,7 @@
         <v>25</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -9360,7 +9468,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>10</v>
@@ -9368,16 +9476,16 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -9422,18 +9530,18 @@
         <v>20</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>66</v>
@@ -9506,7 +9614,7 @@
         <v>44</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>25</v>
@@ -9529,7 +9637,7 @@
         <v>40</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -9546,7 +9654,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -9598,10 +9706,10 @@
         <v>27</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>4</v>
@@ -9615,10 +9723,10 @@
         <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F30C9B-D9E8-4882-93FB-3AD7AB730E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5127AC2-6937-4C39-ABE7-F5AE0F671831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="634">
   <si>
     <t>ALL</t>
   </si>
@@ -2116,6 +2116,246 @@
   </si>
   <si>
     <t>어딘가로 출근하는 모습입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_아이스크림달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_아이스크림달팽이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 아이스크림 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가 달팽이 위로 아이스크림을 쏟았어요!
+하지만 달팽이는 생각보다 나쁘지 않았나 봅니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardId01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardCount01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardCount02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardId02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardId03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardCount03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicfeeler01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘더듬이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘눈]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epiceyes01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘눈정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라멘으로 감싼 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>말랑하고 눅눅한 라멘을 몸에 감고있습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>젓가락 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>젓가락 형태로 발전한 더듬이.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_라멘껍질02]</t>
+  </si>
+  <si>
+    <t>epicshell01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicshell01_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicshell01_c02</t>
+  </si>
+  <si>
+    <t>[에픽_라멘껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가 달팽이 위로 라멘을 쏟았어요!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라멘그릇(빨간색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라멘그릇(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나루토마키를 닮은  눈.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라멘 어묵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽알01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>egg_epic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽알01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반그룹], [레어그룹], [에픽그룹]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tomatobody</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_토마토바디]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_토마토바디정보]</t>
+  </si>
+  <si>
+    <t>[일반_토마토바디정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토색을 닮은 몸.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tomatofeeler</t>
+  </si>
+  <si>
+    <t>[일반_토마토더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_토마토더듬이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토를 닮은 더듬이.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tomatoshell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_토마토껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_토마토껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왕 토마토</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토를 통째로 집으로 쓰고 있습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commoneyes06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈06]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈06정보]</t>
+  </si>
+  <si>
+    <t>슬픈 눈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어딘가 슬퍼보이는 눈입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2318,7 +2558,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2366,6 +2606,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3547,7 +3798,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8799056C-300F-4910-A643-17063CC9919B}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="17.625" customWidth="1"/>
@@ -3656,7 +3907,7 @@
         <v>84</v>
       </c>
       <c r="C5">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="D5" t="s">
         <v>149</v>
@@ -3669,6 +3920,29 @@
       </c>
       <c r="G5" t="s">
         <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B6" t="s">
+        <v>609</v>
+      </c>
+      <c r="C6">
+        <v>600</v>
+      </c>
+      <c r="D6" t="s">
+        <v>588</v>
+      </c>
+      <c r="E6" t="s">
+        <v>610</v>
+      </c>
+      <c r="F6" t="s">
+        <v>611</v>
+      </c>
+      <c r="G6" t="s">
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -3834,7 +4108,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E79052-7558-4F08-8689-6E3AEA3B2BB4}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
@@ -4036,7 +4310,7 @@
         <v>69</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L9" si="0">F5/2</f>
+        <f t="shared" ref="L5:L10" si="0">F5/2</f>
         <v>3.5</v>
       </c>
     </row>
@@ -4174,10 +4448,10 @@
         <v>69</v>
       </c>
       <c r="F9">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G9" s="14">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>100</v>
@@ -4193,29 +4467,31 @@
       </c>
       <c r="L9">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
+        <v>609</v>
+      </c>
+      <c r="C10" t="s">
+        <v>588</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
         <v>68</v>
       </c>
-      <c r="C10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>69</v>
-      </c>
       <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="14"/>
+        <v>300</v>
+      </c>
+      <c r="G10" s="14">
+        <v>250</v>
+      </c>
       <c r="H10" s="9" t="s">
         <v>100</v>
       </c>
@@ -4223,31 +4499,36 @@
         <v>101</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ref="L10:L11" si="1">F10/2</f>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="B11" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
         <v>51</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>69</v>
       </c>
       <c r="F11">
-        <v>500</v>
-      </c>
-      <c r="G11" s="14">
-        <v>350</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G11" s="14"/>
       <c r="H11" s="9" t="s">
         <v>100</v>
       </c>
@@ -4255,14 +4536,7 @@
         <v>101</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L11">
-        <f t="shared" ref="L11:L13" si="1">F11/2</f>
-        <v>250</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4270,7 +4544,7 @@
         <v>108</v>
       </c>
       <c r="B12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
@@ -4300,7 +4574,7 @@
         <v>69</v>
       </c>
       <c r="L12">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L12:L14" si="2">F12/2</f>
         <v>250</v>
       </c>
     </row>
@@ -4309,7 +4583,7 @@
         <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
@@ -4339,7 +4613,46 @@
         <v>69</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14">
+        <v>500</v>
+      </c>
+      <c r="G14" s="14">
+        <v>350</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
     </row>
@@ -4808,23 +5121,26 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{852D9379-7367-49DF-A5FF-B5D057BE72CF}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="72" customWidth="1"/>
-    <col min="4" max="4" width="16.125" customWidth="1"/>
-    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="16.5" customWidth="1"/>
-    <col min="8" max="8" width="15.875" customWidth="1"/>
-    <col min="9" max="9" width="17.5" customWidth="1"/>
-    <col min="10" max="10" width="15.875" customWidth="1"/>
-    <col min="11" max="11" width="17.5" customWidth="1"/>
+    <col min="1" max="2" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="72" customWidth="1"/>
+    <col min="5" max="5" width="22.5" customWidth="1"/>
+    <col min="6" max="6" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="16.5" customWidth="1"/>
+    <col min="9" max="9" width="15.875" customWidth="1"/>
+    <col min="10" max="10" width="17.5" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
+    <col min="12" max="12" width="17.5" customWidth="1"/>
+    <col min="13" max="13" width="17.25" customWidth="1"/>
+    <col min="14" max="14" width="13.875" customWidth="1"/>
+    <col min="15" max="16" width="14" customWidth="1"/>
+    <col min="17" max="18" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4838,28 +5154,49 @@
         <v>0</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>0</v>
-      </c>
       <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>0</v>
-      </c>
       <c r="I1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>0</v>
-      </c>
       <c r="K1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>24</v>
       </c>
@@ -4870,31 +5207,52 @@
         <v>23</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -4905,56 +5263,99 @@
         <v>276</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="M3" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>573</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>573</v>
       </c>
       <c r="C4" t="s">
-        <v>375</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" t="s">
-        <v>194</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -6047,6 +6448,158 @@
       </c>
       <c r="B136" t="s">
         <v>542</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>573</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>574</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A139" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A140" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A141" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A142" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A143" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A144" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A145" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A146" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A147" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>615</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A149" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A150" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A151" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A152" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A153" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A154" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A155" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -6756,7 +7309,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -7497,86 +8050,86 @@
     </row>
     <row r="20" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>160</v>
+        <v>598</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>160</v>
+        <v>598</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>228</v>
+        <v>587</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>51</v>
+        <v>588</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>158</v>
+        <v>600</v>
       </c>
       <c r="G20" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>165</v>
+        <v>601</v>
       </c>
       <c r="I20" s="11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>329</v>
+        <v>603</v>
       </c>
       <c r="K20" t="s">
         <v>68</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>233</v>
+        <v>599</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>233</v>
+        <v>599</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>228</v>
+        <v>587</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>51</v>
+        <v>588</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>158</v>
+        <v>600</v>
       </c>
       <c r="G21" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>166</v>
+        <v>602</v>
       </c>
       <c r="I21" s="11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>330</v>
+        <v>603</v>
       </c>
       <c r="K21" t="s">
         <v>68</v>
       </c>
       <c r="L21">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>228</v>
@@ -7594,13 +8147,13 @@
         <v>1</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I22" s="11">
         <v>10</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="K22" t="s">
         <v>68</v>
@@ -7611,10 +8164,10 @@
     </row>
     <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>427</v>
+        <v>233</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>427</v>
+        <v>233</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>228</v>
@@ -7632,13 +8185,13 @@
         <v>1</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>423</v>
+        <v>166</v>
       </c>
       <c r="I23" s="11">
         <v>10</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>430</v>
+        <v>330</v>
       </c>
       <c r="K23" t="s">
         <v>68</v>
@@ -7649,10 +8202,10 @@
     </row>
     <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>428</v>
+        <v>234</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>428</v>
+        <v>234</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>228</v>
@@ -7670,13 +8223,13 @@
         <v>1</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>424</v>
+        <v>167</v>
       </c>
       <c r="I24" s="11">
         <v>10</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>431</v>
+        <v>331</v>
       </c>
       <c r="K24" t="s">
         <v>68</v>
@@ -7687,10 +8240,10 @@
     </row>
     <row r="25" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>228</v>
@@ -7708,13 +8261,13 @@
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I25" s="11">
         <v>10</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K25" t="s">
         <v>68</v>
@@ -7725,10 +8278,10 @@
     </row>
     <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>239</v>
+        <v>428</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>239</v>
+        <v>428</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>228</v>
@@ -7740,19 +8293,19 @@
         <v>13</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="G26" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>241</v>
+        <v>424</v>
       </c>
       <c r="I26" s="11">
         <v>10</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>332</v>
+        <v>431</v>
       </c>
       <c r="K26" t="s">
         <v>68</v>
@@ -7763,10 +8316,10 @@
     </row>
     <row r="27" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>261</v>
+        <v>429</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>261</v>
+        <v>429</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>228</v>
@@ -7778,19 +8331,19 @@
         <v>13</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="G27" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>263</v>
+        <v>425</v>
       </c>
       <c r="I27" s="11">
         <v>10</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>333</v>
+        <v>432</v>
       </c>
       <c r="K27" t="s">
         <v>68</v>
@@ -7801,10 +8354,10 @@
     </row>
     <row r="28" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>433</v>
+        <v>614</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>433</v>
+        <v>614</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>228</v>
@@ -7816,19 +8369,19 @@
         <v>13</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="G28" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="I28" s="11">
         <v>10</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>434</v>
+        <v>616</v>
       </c>
       <c r="K28" t="s">
         <v>68</v>
@@ -7839,46 +8392,48 @@
     </row>
     <row r="29" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>441</v>
+        <v>239</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>441</v>
+        <v>239</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>228</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>442</v>
+        <v>240</v>
       </c>
       <c r="G29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>443</v>
+        <v>241</v>
       </c>
       <c r="I29" s="11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>444</v>
+        <v>332</v>
       </c>
       <c r="K29" t="s">
         <v>68</v>
       </c>
       <c r="L29">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11"/>
+      <c r="A30" s="11" t="s">
+        <v>261</v>
+      </c>
       <c r="B30" s="11" t="s">
-        <v>546</v>
+        <v>261</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>228</v>
@@ -7890,19 +8445,19 @@
         <v>13</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>547</v>
+        <v>262</v>
       </c>
       <c r="G30" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>548</v>
+        <v>263</v>
       </c>
       <c r="I30" s="11">
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>549</v>
+        <v>333</v>
       </c>
       <c r="K30" t="s">
         <v>68</v>
@@ -7913,10 +8468,10 @@
     </row>
     <row r="31" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>161</v>
+        <v>433</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>161</v>
+        <v>433</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>228</v>
@@ -7925,20 +8480,22 @@
         <v>51</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>159</v>
+        <v>262</v>
       </c>
       <c r="G31" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>426</v>
+      </c>
       <c r="I31" s="11">
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>334</v>
+        <v>434</v>
       </c>
       <c r="K31" t="s">
         <v>68</v>
@@ -7949,46 +8506,48 @@
     </row>
     <row r="32" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>221</v>
+        <v>441</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>221</v>
+        <v>441</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>228</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>224</v>
+        <v>442</v>
       </c>
       <c r="G32" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>443</v>
+      </c>
       <c r="I32" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>335</v>
+        <v>444</v>
       </c>
       <c r="K32" t="s">
         <v>68</v>
       </c>
       <c r="L32">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>222</v>
+        <v>546</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>222</v>
+        <v>546</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>228</v>
@@ -7997,20 +8556,22 @@
         <v>51</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>225</v>
+        <v>547</v>
       </c>
       <c r="G33" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>548</v>
+      </c>
       <c r="I33" s="11">
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>336</v>
+        <v>549</v>
       </c>
       <c r="K33" t="s">
         <v>68</v>
@@ -8021,46 +8582,46 @@
     </row>
     <row r="34" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>223</v>
+        <v>591</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>223</v>
+        <v>591</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>228</v>
+        <v>587</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>51</v>
+        <v>588</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>226</v>
+        <v>592</v>
       </c>
       <c r="G34" s="11" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>337</v>
+        <v>593</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
       </c>
       <c r="L34">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>435</v>
+        <v>161</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>435</v>
+        <v>161</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>228</v>
@@ -8072,7 +8633,7 @@
         <v>14</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>436</v>
+        <v>159</v>
       </c>
       <c r="G35" s="11" t="b">
         <v>0</v>
@@ -8082,7 +8643,7 @@
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>437</v>
+        <v>334</v>
       </c>
       <c r="K35" t="s">
         <v>68</v>
@@ -8093,10 +8654,10 @@
     </row>
     <row r="36" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>168</v>
+        <v>221</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>228</v>
@@ -8105,22 +8666,20 @@
         <v>51</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="G36" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="11" t="s">
-        <v>199</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H36" s="11"/>
       <c r="I36" s="11">
         <v>10</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>559</v>
+        <v>335</v>
       </c>
       <c r="K36" t="s">
         <v>68</v>
@@ -8131,10 +8690,10 @@
     </row>
     <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>472</v>
+        <v>222</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>472</v>
+        <v>222</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>228</v>
@@ -8143,22 +8702,20 @@
         <v>51</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="G37" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>162</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H37" s="11"/>
       <c r="I37" s="11">
         <v>10</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>476</v>
+        <v>336</v>
       </c>
       <c r="K37" t="s">
         <v>68</v>
@@ -8169,10 +8726,10 @@
     </row>
     <row r="38" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>473</v>
+        <v>223</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>473</v>
+        <v>223</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>228</v>
@@ -8181,22 +8738,20 @@
         <v>51</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="G38" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>474</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H38" s="11"/>
       <c r="I38" s="11">
         <v>10</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>476</v>
+        <v>337</v>
       </c>
       <c r="K38" t="s">
         <v>68</v>
@@ -8207,10 +8762,10 @@
     </row>
     <row r="39" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>267</v>
+        <v>435</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>267</v>
+        <v>435</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>228</v>
@@ -8219,22 +8774,20 @@
         <v>51</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>202</v>
+        <v>436</v>
       </c>
       <c r="G39" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>163</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H39" s="11"/>
       <c r="I39" s="11">
         <v>10</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="K39" t="s">
         <v>68</v>
@@ -8245,10 +8798,10 @@
     </row>
     <row r="40" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
-        <v>237</v>
+        <v>630</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>237</v>
+        <v>630</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>228</v>
@@ -8257,28 +8810,359 @@
         <v>51</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>200</v>
+        <v>14</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>629</v>
       </c>
       <c r="G40" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>164</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H40" s="11"/>
       <c r="I40" s="11">
         <v>10</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>341</v>
+        <v>631</v>
       </c>
       <c r="K40" t="s">
         <v>68</v>
       </c>
       <c r="L40">
         <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="G41" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11">
+        <v>5</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="K41" t="s">
+        <v>68</v>
+      </c>
+      <c r="L41">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="G42" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="I42" s="11">
+        <v>10</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="K42" t="s">
+        <v>68</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G43" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I43" s="11">
+        <v>10</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="K43" t="s">
+        <v>68</v>
+      </c>
+      <c r="L43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G44" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="I44" s="11">
+        <v>10</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="K44" t="s">
+        <v>68</v>
+      </c>
+      <c r="L44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="G45" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="I45" s="11">
+        <v>10</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="K45" t="s">
+        <v>68</v>
+      </c>
+      <c r="L45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G46" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="I46" s="11">
+        <v>10</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="K46" t="s">
+        <v>68</v>
+      </c>
+      <c r="L46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="G47" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11">
+        <v>10</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="K47" t="s">
+        <v>68</v>
+      </c>
+      <c r="L47">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F48" t="s">
+        <v>619</v>
+      </c>
+      <c r="G48" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11">
+        <v>10</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="K48" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="G49" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="11">
+        <v>10</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="K49" t="s">
+        <v>68</v>
+      </c>
+      <c r="L49">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5127AC2-6937-4C39-ABE7-F5AE0F671831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68EA314-DE19-4469-A570-F27727FB0164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="639">
   <si>
     <t>ALL</t>
   </si>
@@ -2356,6 +2356,26 @@
   </si>
   <si>
     <t>어딘가 슬퍼보이는 눈입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>plantshell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_화분껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_화분껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스테리아 껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등에 있는 식물은 비상식량입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5355,7 +5375,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -6600,6 +6620,22 @@
       </c>
       <c r="B155" s="10" t="s">
         <v>633</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A156" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A157" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="B157" s="10" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -7309,7 +7345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -8512,7 +8548,7 @@
         <v>441</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>149</v>
@@ -9163,6 +9199,41 @@
       </c>
       <c r="L49">
         <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="G50" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" s="11">
+        <v>7</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="K50" t="s">
+        <v>68</v>
+      </c>
+      <c r="L50">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68EA314-DE19-4469-A570-F27727FB0164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D13FAF-B296-4525-A2DF-E6ABFB8471CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="732">
   <si>
     <t>ALL</t>
   </si>
@@ -2376,6 +2376,376 @@
   </si>
   <si>
     <t>등에 있는 식물은 비상식량입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>즐겨찾기 설정으로 등록할 수 있어요!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_즐겨찾기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_이끼바디]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_이끼바디정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_이끼껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonshell03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_이끼껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_토양몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_토양몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody01_c07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈07]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈07정보]</t>
+  </si>
+  <si>
+    <t>plantfeeler</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_새싹더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_새싹더듬이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_즐겨찾기2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>즐겨찾기는 최대 두개만 등록할 수 있어요!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mellonshell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메론빵 껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>향긋한 메론 냄새가 납니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_메론빵껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_메론빵껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>새싹 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리 위로 싹이 났습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_물개몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_물개몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물을 너무 좋아하더니 물개가 되어버렸네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물개 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_토마토달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 토마토 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_토마토달팽이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토를 너무 좋아하던 달팽이는…
+자신이 토마토가 되기로 했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_라멘달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_라멘달팽이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 라멘 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라멘에 칭칭 감겨있는 이 달팽이는 눅눅하고 따뜻한 감촉에 이대로 지내기로 했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_화분달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_화분달팽이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. 화분 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등 뒤에 있는 식물은 어느정도 자라면 먹으면서 크기를 유지한답니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarefeeler01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_아귀더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_아귀더듬이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초롱아귀 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가를 유인하려는걸까?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈08]</t>
+  </si>
+  <si>
+    <t>[일반달팽이_눈08정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>앵두 입술</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>도돔하니 귀여운 입술입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareeyes02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_오리눈]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_오리눈정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_물개눈]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_물개눈정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareeyes01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오리 얼굴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물을 좋아한다는 점은 닮았네요!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물개 얼굴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어딘가 맹해보이는 물개얼굴입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_오리몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarebody03_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_오리몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tubeshell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_튜브껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_튜브껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>tubeshell_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>duckfeeler</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_오리머리]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_오리머리정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오리 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>오리 머리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어딘가 뽀송해보이는 오리 몸입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여름 휴가를 가려는 모양입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리 위에 깃털이 솟아올랐습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜브(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_오리달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[도감_오리달팽이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. 오리 달팽이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여름 휴가를 떠나는 오리 모양의 달패이입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_parts</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PartsResourceKey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_parts_red</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_parts_white</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoopResourceKey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>poop_green</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>poop_red</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>poop_brown</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoopCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PoopTime</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2636,7 +3006,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4330,7 +4700,7 @@
         <v>69</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L10" si="0">F5/2</f>
+        <f t="shared" ref="L5:L9" si="0">F5/2</f>
         <v>3.5</v>
       </c>
     </row>
@@ -4525,7 +4895,7 @@
         <v>68</v>
       </c>
       <c r="L10">
-        <f t="shared" ref="L10:L11" si="1">F10/2</f>
+        <f t="shared" ref="L10" si="1">F10/2</f>
         <v>150</v>
       </c>
     </row>
@@ -5348,15 +5718,163 @@
         <v>441</v>
       </c>
       <c r="M4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4">
+        <v>300</v>
+      </c>
+      <c r="O4" t="s">
         <v>28</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>670</v>
+      </c>
+      <c r="B5" t="s">
+        <v>670</v>
+      </c>
+      <c r="C5" t="s">
+        <v>672</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>614</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="M5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5">
+        <v>300</v>
+      </c>
+      <c r="O5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>674</v>
+      </c>
+      <c r="B6" t="s">
+        <v>674</v>
+      </c>
+      <c r="C6" t="s">
+        <v>675</v>
+      </c>
+      <c r="D6" t="s">
+        <v>588</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="M6" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6">
+        <v>600</v>
+      </c>
+      <c r="O6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>678</v>
+      </c>
+      <c r="B7" t="s">
+        <v>678</v>
+      </c>
+      <c r="C7" t="s">
+        <v>679</v>
+      </c>
+      <c r="D7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="M7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N7">
+        <v>400</v>
+      </c>
+      <c r="O7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+    </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
+      <c r="A8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B8" t="s">
+        <v>718</v>
+      </c>
+      <c r="C8" t="s">
+        <v>719</v>
+      </c>
+      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="M8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8">
+        <v>500</v>
+      </c>
+      <c r="O8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C9" s="17"/>
@@ -5375,7 +5893,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B187"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -6636,6 +7154,246 @@
       </c>
       <c r="B157" s="10" t="s">
         <v>638</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A158" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A159" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="B160" s="10" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A161" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B162" s="10" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A163" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A165" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B165" s="10" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>670</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>672</v>
+      </c>
+      <c r="B167" s="10" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>674</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>675</v>
+      </c>
+      <c r="B169" s="10" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>678</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>679</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A173" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A174" s="11" t="s">
+        <v>687</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A175" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="B175" s="10" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A176" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A177" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="B177" s="10" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A178" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A179" s="11" t="s">
+        <v>695</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="B181" s="10" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A183" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="B183" s="10" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A184" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A185" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>718</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>719</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -7345,7 +8103,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -8162,10 +8920,10 @@
     </row>
     <row r="22" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>160</v>
+        <v>644</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>160</v>
+        <v>644</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>228</v>
@@ -8174,22 +8932,20 @@
         <v>51</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>158</v>
+        <v>645</v>
       </c>
       <c r="G22" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>165</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H22" s="11"/>
       <c r="I22" s="11">
         <v>10</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>329</v>
+        <v>646</v>
       </c>
       <c r="K22" t="s">
         <v>68</v>
@@ -8200,48 +8956,46 @@
     </row>
     <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>233</v>
+        <v>660</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>233</v>
+        <v>660</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>158</v>
+        <v>657</v>
       </c>
       <c r="G23" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>166</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H23" s="11"/>
       <c r="I23" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>330</v>
+        <v>661</v>
       </c>
       <c r="K23" t="s">
         <v>68</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>228</v>
@@ -8259,13 +9013,13 @@
         <v>1</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I24" s="11">
         <v>10</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="K24" t="s">
         <v>68</v>
@@ -8276,10 +9030,10 @@
     </row>
     <row r="25" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>427</v>
+        <v>233</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>427</v>
+        <v>233</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>228</v>
@@ -8297,13 +9051,13 @@
         <v>1</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>423</v>
+        <v>166</v>
       </c>
       <c r="I25" s="11">
         <v>10</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>430</v>
+        <v>330</v>
       </c>
       <c r="K25" t="s">
         <v>68</v>
@@ -8314,10 +9068,10 @@
     </row>
     <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>428</v>
+        <v>234</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>428</v>
+        <v>234</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>228</v>
@@ -8335,13 +9089,13 @@
         <v>1</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>424</v>
+        <v>167</v>
       </c>
       <c r="I26" s="11">
         <v>10</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>431</v>
+        <v>331</v>
       </c>
       <c r="K26" t="s">
         <v>68</v>
@@ -8352,10 +9106,10 @@
     </row>
     <row r="27" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>228</v>
@@ -8373,13 +9127,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I27" s="11">
         <v>10</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K27" t="s">
         <v>68</v>
@@ -8390,10 +9144,10 @@
     </row>
     <row r="28" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>614</v>
+        <v>428</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>614</v>
+        <v>428</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>228</v>
@@ -8411,13 +9165,13 @@
         <v>1</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>613</v>
+        <v>424</v>
       </c>
       <c r="I28" s="11">
         <v>10</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>616</v>
+        <v>431</v>
       </c>
       <c r="K28" t="s">
         <v>68</v>
@@ -8428,10 +9182,10 @@
     </row>
     <row r="29" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>239</v>
+        <v>429</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>239</v>
+        <v>429</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>228</v>
@@ -8443,19 +9197,19 @@
         <v>13</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="G29" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>241</v>
+        <v>425</v>
       </c>
       <c r="I29" s="11">
         <v>10</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>332</v>
+        <v>432</v>
       </c>
       <c r="K29" t="s">
         <v>68</v>
@@ -8466,10 +9220,10 @@
     </row>
     <row r="30" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>261</v>
+        <v>647</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>261</v>
+        <v>647</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>228</v>
@@ -8481,19 +9235,19 @@
         <v>13</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="G30" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>263</v>
+        <v>649</v>
       </c>
       <c r="I30" s="11">
         <v>10</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>333</v>
+        <v>648</v>
       </c>
       <c r="K30" t="s">
         <v>68</v>
@@ -8504,10 +9258,10 @@
     </row>
     <row r="31" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>433</v>
+        <v>614</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>433</v>
+        <v>614</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>228</v>
@@ -8519,19 +9273,19 @@
         <v>13</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="G31" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="I31" s="11">
         <v>10</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>434</v>
+        <v>616</v>
       </c>
       <c r="K31" t="s">
         <v>68</v>
@@ -8542,48 +9296,48 @@
     </row>
     <row r="32" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>441</v>
+        <v>239</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>441</v>
+        <v>239</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>442</v>
+        <v>240</v>
       </c>
       <c r="G32" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>443</v>
+        <v>241</v>
       </c>
       <c r="I32" s="11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>444</v>
+        <v>332</v>
       </c>
       <c r="K32" t="s">
         <v>68</v>
       </c>
       <c r="L32">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>546</v>
+        <v>641</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>546</v>
+        <v>641</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>228</v>
@@ -8595,19 +9349,17 @@
         <v>13</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>547</v>
+        <v>642</v>
       </c>
       <c r="G33" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>548</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H33" s="11"/>
       <c r="I33" s="11">
         <v>10</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>549</v>
+        <v>643</v>
       </c>
       <c r="K33" t="s">
         <v>68</v>
@@ -8618,46 +9370,48 @@
     </row>
     <row r="34" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>591</v>
+        <v>261</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>591</v>
+        <v>261</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>587</v>
+        <v>228</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>588</v>
+        <v>51</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>13</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>592</v>
+        <v>262</v>
       </c>
       <c r="G34" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>263</v>
+      </c>
       <c r="I34" s="11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>593</v>
+        <v>333</v>
       </c>
       <c r="K34" t="s">
         <v>68</v>
       </c>
       <c r="L34">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>161</v>
+        <v>433</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>161</v>
+        <v>433</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>228</v>
@@ -8666,20 +9420,22 @@
         <v>51</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>159</v>
+        <v>262</v>
       </c>
       <c r="G35" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>426</v>
+      </c>
       <c r="I35" s="11">
         <v>10</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>334</v>
+        <v>434</v>
       </c>
       <c r="K35" t="s">
         <v>68</v>
@@ -8690,46 +9446,48 @@
     </row>
     <row r="36" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>221</v>
+        <v>441</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>221</v>
+        <v>441</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>224</v>
+        <v>442</v>
       </c>
       <c r="G36" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>443</v>
+      </c>
       <c r="I36" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>335</v>
+        <v>444</v>
       </c>
       <c r="K36" t="s">
         <v>68</v>
       </c>
       <c r="L36">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>222</v>
+        <v>546</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>222</v>
+        <v>546</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>228</v>
@@ -8738,20 +9496,22 @@
         <v>51</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>225</v>
+        <v>547</v>
       </c>
       <c r="G37" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>548</v>
+      </c>
       <c r="I37" s="11">
         <v>10</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>336</v>
+        <v>549</v>
       </c>
       <c r="K37" t="s">
         <v>68</v>
@@ -8762,82 +9522,84 @@
     </row>
     <row r="38" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>223</v>
+        <v>591</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>223</v>
+        <v>591</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>228</v>
+        <v>587</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>51</v>
+        <v>588</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>226</v>
+        <v>592</v>
       </c>
       <c r="G38" s="11" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>337</v>
+        <v>593</v>
       </c>
       <c r="K38" t="s">
         <v>68</v>
       </c>
       <c r="L38">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>435</v>
+        <v>666</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>435</v>
+        <v>666</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>436</v>
+        <v>13</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>664</v>
       </c>
       <c r="G39" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>665</v>
+      </c>
       <c r="I39" s="11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>437</v>
+        <v>667</v>
       </c>
       <c r="K39" t="s">
         <v>68</v>
       </c>
       <c r="L39">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
-        <v>630</v>
+        <v>161</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>630</v>
+        <v>161</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>228</v>
@@ -8848,8 +9610,8 @@
       <c r="E40" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F40" s="19" t="s">
-        <v>629</v>
+      <c r="F40" s="12" t="s">
+        <v>159</v>
       </c>
       <c r="G40" s="11" t="b">
         <v>0</v>
@@ -8859,7 +9621,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>631</v>
+        <v>334</v>
       </c>
       <c r="K40" t="s">
         <v>68</v>
@@ -8870,46 +9632,46 @@
     </row>
     <row r="41" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
-        <v>586</v>
+        <v>221</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>586</v>
+        <v>221</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>587</v>
+        <v>228</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>588</v>
+        <v>51</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>589</v>
+        <v>224</v>
       </c>
       <c r="G41" s="11" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="11">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>590</v>
+        <v>335</v>
       </c>
       <c r="K41" t="s">
         <v>68</v>
       </c>
       <c r="L41">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>228</v>
@@ -8918,22 +9680,20 @@
         <v>51</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>169</v>
+        <v>225</v>
       </c>
       <c r="G42" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>199</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H42" s="11"/>
       <c r="I42" s="11">
         <v>10</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>559</v>
+        <v>336</v>
       </c>
       <c r="K42" t="s">
         <v>68</v>
@@ -8944,10 +9704,10 @@
     </row>
     <row r="43" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>472</v>
+        <v>223</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>472</v>
+        <v>223</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>228</v>
@@ -8956,22 +9716,20 @@
         <v>51</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="G43" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>162</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H43" s="11"/>
       <c r="I43" s="11">
         <v>10</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>476</v>
+        <v>337</v>
       </c>
       <c r="K43" t="s">
         <v>68</v>
@@ -8982,10 +9740,10 @@
     </row>
     <row r="44" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="11" t="s">
-        <v>473</v>
+        <v>435</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>473</v>
+        <v>435</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>228</v>
@@ -8994,22 +9752,20 @@
         <v>51</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>201</v>
+        <v>436</v>
       </c>
       <c r="G44" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>474</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H44" s="11"/>
       <c r="I44" s="11">
         <v>10</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>476</v>
+        <v>437</v>
       </c>
       <c r="K44" t="s">
         <v>68</v>
@@ -9018,12 +9774,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>267</v>
+        <v>630</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>267</v>
+        <v>630</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>228</v>
@@ -9032,22 +9788,20 @@
         <v>51</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>202</v>
+        <v>14</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>629</v>
       </c>
       <c r="G45" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>163</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H45" s="11"/>
       <c r="I45" s="11">
         <v>10</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>475</v>
+        <v>631</v>
       </c>
       <c r="K45" t="s">
         <v>68</v>
@@ -9056,12 +9810,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>237</v>
+        <v>650</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>237</v>
+        <v>650</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>228</v>
@@ -9070,22 +9824,20 @@
         <v>51</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>200</v>
+        <v>14</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>629</v>
       </c>
       <c r="G46" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>164</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H46" s="11"/>
       <c r="I46" s="11">
         <v>10</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>341</v>
+        <v>651</v>
       </c>
       <c r="K46" t="s">
         <v>68</v>
@@ -9096,22 +9848,22 @@
     </row>
     <row r="47" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
-        <v>585</v>
+        <v>687</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>585</v>
+        <v>687</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>587</v>
+        <v>228</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>588</v>
+        <v>51</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>583</v>
+        <v>14</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>629</v>
       </c>
       <c r="G47" s="11" t="b">
         <v>0</v>
@@ -9121,57 +9873,57 @@
         <v>10</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>584</v>
+        <v>688</v>
       </c>
       <c r="K47" t="s">
         <v>68</v>
       </c>
       <c r="L47">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>228</v>
+        <v>587</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>51</v>
+        <v>588</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="F48" t="s">
-        <v>619</v>
+        <v>14</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>589</v>
       </c>
       <c r="G48" s="11" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="11"/>
       <c r="I48" s="11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>621</v>
+        <v>590</v>
       </c>
       <c r="K48" t="s">
         <v>68</v>
       </c>
       <c r="L48">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
-        <v>625</v>
+        <v>168</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>625</v>
+        <v>168</v>
       </c>
       <c r="C49" s="11" t="s">
         <v>228</v>
@@ -9180,60 +9932,579 @@
         <v>51</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>624</v>
+        <v>153</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>169</v>
       </c>
       <c r="G49" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>199</v>
       </c>
       <c r="I49" s="11">
         <v>10</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>626</v>
+        <v>559</v>
       </c>
       <c r="K49" t="s">
         <v>68</v>
       </c>
       <c r="L49">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
-        <v>635</v>
+        <v>472</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>635</v>
+        <v>472</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>149</v>
+        <v>51</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>634</v>
+        <v>153</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="G50" s="11" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>162</v>
       </c>
       <c r="I50" s="11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>636</v>
+        <v>476</v>
       </c>
       <c r="K50" t="s">
         <v>68</v>
       </c>
       <c r="L50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G51" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="I51" s="11">
         <v>10</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="K51" t="s">
+        <v>68</v>
+      </c>
+      <c r="L51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="G52" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="I52" s="11">
+        <v>10</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="K52" t="s">
+        <v>68</v>
+      </c>
+      <c r="L52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="G53" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="I53" s="11">
+        <v>10</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="K53" t="s">
+        <v>68</v>
+      </c>
+      <c r="L53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="G54" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11">
+        <v>5</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="K54" t="s">
+        <v>68</v>
+      </c>
+      <c r="L54">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>652</v>
+      </c>
+      <c r="G55" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11">
+        <v>10</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="K55" t="s">
+        <v>68</v>
+      </c>
+      <c r="L55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F56" t="s">
+        <v>619</v>
+      </c>
+      <c r="G56" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11">
+        <v>10</v>
+      </c>
+      <c r="J56" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="K56" t="s">
+        <v>68</v>
+      </c>
+      <c r="L56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="G57" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11">
+        <v>10</v>
+      </c>
+      <c r="J57" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="K57" t="s">
+        <v>68</v>
+      </c>
+      <c r="L57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="G58" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11">
+        <v>7</v>
+      </c>
+      <c r="J58" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="K58" t="s">
+        <v>68</v>
+      </c>
+      <c r="L58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>682</v>
+      </c>
+      <c r="G59" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11">
+        <v>7</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="K59" t="s">
+        <v>68</v>
+      </c>
+      <c r="L59">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>691</v>
+      </c>
+      <c r="G60" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11">
+        <v>7</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="K60" t="s">
+        <v>68</v>
+      </c>
+      <c r="L60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>696</v>
+      </c>
+      <c r="G61" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11">
+        <v>7</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>695</v>
+      </c>
+      <c r="K61" t="s">
+        <v>68</v>
+      </c>
+      <c r="L61">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>701</v>
+      </c>
+      <c r="G62" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="I62" s="11">
+        <v>7</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="K62" t="s">
+        <v>68</v>
+      </c>
+      <c r="L62">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>706</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>705</v>
+      </c>
+      <c r="G63" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>708</v>
+      </c>
+      <c r="I63" s="11">
+        <v>7</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="K63" t="s">
+        <v>68</v>
+      </c>
+      <c r="L63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>710</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>709</v>
+      </c>
+      <c r="G64" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="11">
+        <v>7</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="K64" t="s">
+        <v>68</v>
+      </c>
+      <c r="L64">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9245,7 +10516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2444F32-CF16-41C0-B4D3-AE1758A9A6E6}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -9255,9 +10526,13 @@
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="9" width="28.875" customWidth="1"/>
     <col min="10" max="10" width="20.375" customWidth="1"/>
+    <col min="11" max="11" width="16.625" customWidth="1"/>
+    <col min="12" max="12" width="20.5" customWidth="1"/>
+    <col min="13" max="13" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -9288,8 +10563,20 @@
       <c r="J1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -9320,8 +10607,20 @@
       <c r="J2" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -9352,8 +10651,20 @@
       <c r="J3" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -9381,8 +10692,20 @@
       <c r="J4" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>722</v>
+      </c>
+      <c r="L4" t="s">
+        <v>727</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -9410,8 +10733,20 @@
       <c r="J5" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>724</v>
+      </c>
+      <c r="L5" t="s">
+        <v>728</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -9439,8 +10774,20 @@
       <c r="J6" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>722</v>
+      </c>
+      <c r="L6" t="s">
+        <v>727</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -9470,6 +10817,18 @@
       </c>
       <c r="J7" t="s">
         <v>270</v>
+      </c>
+      <c r="K7" t="s">
+        <v>725</v>
+      </c>
+      <c r="L7" t="s">
+        <v>729</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D13FAF-B296-4525-A2DF-E6ABFB8471CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747D7955-5580-45E3-B425-BDF4EFE1D71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="4" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="779">
   <si>
     <t>ALL</t>
   </si>
@@ -2746,6 +2746,192 @@
   </si>
   <si>
     <t>PoopTime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_clover</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[클로버]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[클로버정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[아이스크림모자1]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[아이스크림모자2]</t>
+  </si>
+  <si>
+    <t>[아이스크림모자1정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[아이스크림모자2정보]</t>
+  </si>
+  <si>
+    <t>icecreamhat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>icecreamhat2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이스크림 모자(딸기맛)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이스크림 모자(블루베리맛)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이스크림을 머리에 얹었습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>네잎 클로버.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜인지 행운이 따라올 것만 같습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_cucumber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[오이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[오이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[당근]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[당근정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_carrot</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>살짝 데친 미니 당근입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_blueberry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[블루베리]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[블루베리정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>블루베리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달콤한 블루베리 한 알입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_watermellon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수박]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수박정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[사과]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[사과정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_apple</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사과 조각</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달콤한 사과조각입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수박 조각</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작은 수박 조각입니다. 씨를 피해 먹어야겠군요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_radish</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[하얀무]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[하얀무정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하얀 무</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작은 하얀색의 무입니다. 수분이 가득하네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>food_bro</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[브로콜리]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[브로콜리정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>브로콜리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작은 나무같이 생겼네요.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4344,7 +4530,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -4490,6 +4676,40 @@
         <v>471</v>
       </c>
     </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B9" t="s">
+        <v>735</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>739</v>
+      </c>
+      <c r="E9" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B10" t="s">
+        <v>736</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
+        <v>740</v>
+      </c>
+      <c r="E10" t="s">
+        <v>738</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4498,7 +4718,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E79052-7558-4F08-8689-6E3AEA3B2BB4}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
@@ -4631,7 +4851,7 @@
         <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>747</v>
       </c>
       <c r="C4" t="s">
         <v>51</v>
@@ -4640,13 +4860,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" s="14">
         <v>3</v>
+      </c>
+      <c r="G4" s="8">
+        <v>2</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>100</v>
@@ -4658,11 +4878,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L4">
-        <f>F4/2</f>
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4670,7 +4889,7 @@
         <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>749</v>
       </c>
       <c r="C5" t="s">
         <v>51</v>
@@ -4679,13 +4898,13 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5">
-        <v>7</v>
-      </c>
-      <c r="G5" s="14">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>100</v>
@@ -4697,11 +4916,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L9" si="0">F5/2</f>
-        <v>3.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4709,7 +4927,7 @@
         <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>51</v>
@@ -4721,10 +4939,10 @@
         <v>69</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G6" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>100</v>
@@ -4739,8 +4957,7 @@
         <v>69</v>
       </c>
       <c r="L6">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4748,7 +4965,7 @@
         <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>51</v>
@@ -4760,10 +4977,10 @@
         <v>69</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G7" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>100</v>
@@ -4778,16 +4995,15 @@
         <v>69</v>
       </c>
       <c r="L7">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
@@ -4799,10 +5015,10 @@
         <v>69</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G8" s="14">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>100</v>
@@ -4817,238 +5033,624 @@
         <v>69</v>
       </c>
       <c r="L8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9" s="14">
+        <v>8</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ref="L9:L17" si="0">F9/2</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" t="s">
+        <v>733</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10">
+        <v>12</v>
+      </c>
+      <c r="G10" s="14">
+        <v>8</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ref="L10" si="1">F10/2</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>755</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11" s="8">
+        <v>3</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" t="s">
+        <v>760</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12" s="14">
+        <v>8</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ref="L12" si="2">F12/2</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" t="s">
+        <v>762</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>14</v>
+      </c>
+      <c r="G13" s="14">
+        <v>9</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" t="s">
+        <v>770</v>
+      </c>
+      <c r="C14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+      <c r="G14" s="14">
+        <v>9</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>775</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+      <c r="G15" s="14">
+        <v>9</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16">
+        <v>50</v>
+      </c>
+      <c r="G16" s="14">
+        <v>35</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="17" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>88</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B17" t="s">
         <v>141</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C17" t="s">
         <v>74</v>
       </c>
-      <c r="D9">
+      <c r="D17">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E17" t="s">
         <v>69</v>
       </c>
-      <c r="F9">
+      <c r="F17">
         <v>100</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G17" s="14">
         <v>80</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I17" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
         <v>69</v>
       </c>
-      <c r="L9">
+      <c r="L17">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="18" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>88</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B18" t="s">
         <v>609</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C18" t="s">
         <v>588</v>
       </c>
-      <c r="D10">
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E18" t="s">
         <v>68</v>
       </c>
-      <c r="F10">
+      <c r="F18">
         <v>300</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G18" s="14">
         <v>250</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
         <v>68</v>
       </c>
-      <c r="L10">
-        <f t="shared" ref="L10" si="1">F10/2</f>
+      <c r="L18">
+        <f t="shared" ref="L18" si="3">F18/2</f>
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="19" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>94</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B19" t="s">
         <v>68</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C19" t="s">
         <v>51</v>
       </c>
-      <c r="D11">
+      <c r="D19">
         <v>50</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E19" t="s">
         <v>69</v>
       </c>
-      <c r="F11">
+      <c r="F19">
         <v>1</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="9" t="s">
+      <c r="G19" s="14"/>
+      <c r="H19" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I19" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J11" t="b">
+      <c r="J19" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="20" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>108</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B20" t="s">
         <v>116</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C20" t="s">
         <v>51</v>
       </c>
-      <c r="D12">
+      <c r="D20">
         <v>1</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E20" t="s">
         <v>69</v>
       </c>
-      <c r="F12">
+      <c r="F20">
+        <v>100</v>
+      </c>
+      <c r="G20" s="14">
+        <v>70</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ref="L20:L22" si="4">F20/2</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21">
         <v>500</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G21" s="14">
         <v>350</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H21" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I21" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="s">
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
         <v>69</v>
       </c>
-      <c r="L12">
-        <f t="shared" ref="L12:L14" si="2">F12/2</f>
+      <c r="L21">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="22" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>108</v>
       </c>
-      <c r="B13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
         <v>51</v>
       </c>
-      <c r="D13">
+      <c r="D22">
         <v>1</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E22" t="s">
         <v>69</v>
       </c>
-      <c r="F13">
+      <c r="F22">
         <v>500</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G22" s="14">
         <v>350</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H22" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I22" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
         <v>69</v>
       </c>
-      <c r="L13">
-        <f t="shared" si="2"/>
+      <c r="L22">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>108</v>
       </c>
-      <c r="B14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B23" t="s">
+        <v>467</v>
+      </c>
+      <c r="C23" t="s">
         <v>51</v>
       </c>
-      <c r="D14">
+      <c r="D23">
         <v>1</v>
       </c>
-      <c r="E14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14">
+      <c r="E23" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23">
         <v>500</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G23" s="14">
         <v>350</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H23" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I23" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>69</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="2"/>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="s">
+        <v>68</v>
+      </c>
+      <c r="L23">
+        <f t="shared" ref="L23:L24" si="5">F23/2</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" t="s">
+        <v>470</v>
+      </c>
+      <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24">
+        <v>500</v>
+      </c>
+      <c r="G24" s="14">
+        <v>350</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="5"/>
         <v>250</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5893,7 +6495,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B187"/>
+  <dimension ref="A1:B205"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -7394,6 +7996,150 @@
       </c>
       <c r="B187" s="10" t="s">
         <v>721</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>735</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>736</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>737</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>738</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>733</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>734</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>749</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>750</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>755</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>756</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>762</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>763</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>760</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>761</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>770</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>771</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>775</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>776</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>778</v>
       </c>
     </row>
   </sheetData>
@@ -10516,7 +11262,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2444F32-CF16-41C0-B4D3-AE1758A9A6E6}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -10829,6 +11575,334 @@
       </c>
       <c r="N7">
         <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>733</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>733</v>
+      </c>
+      <c r="D8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="I8" t="s">
+        <v>734</v>
+      </c>
+      <c r="J8" t="s">
+        <v>732</v>
+      </c>
+      <c r="K8" t="s">
+        <v>722</v>
+      </c>
+      <c r="L8" t="s">
+        <v>727</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
+      </c>
+      <c r="N8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>747</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>747</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>748</v>
+      </c>
+      <c r="J9" t="s">
+        <v>746</v>
+      </c>
+      <c r="K9" t="s">
+        <v>722</v>
+      </c>
+      <c r="L9" t="s">
+        <v>727</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>749</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>749</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>750</v>
+      </c>
+      <c r="J10" t="s">
+        <v>751</v>
+      </c>
+      <c r="K10" t="s">
+        <v>724</v>
+      </c>
+      <c r="L10" t="s">
+        <v>728</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>755</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>755</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>756</v>
+      </c>
+      <c r="J11" t="s">
+        <v>754</v>
+      </c>
+      <c r="K11" t="s">
+        <v>724</v>
+      </c>
+      <c r="L11" t="s">
+        <v>728</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>760</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>760</v>
+      </c>
+      <c r="D12" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>17</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="I12" t="s">
+        <v>761</v>
+      </c>
+      <c r="J12" t="s">
+        <v>759</v>
+      </c>
+      <c r="K12" t="s">
+        <v>722</v>
+      </c>
+      <c r="L12" t="s">
+        <v>727</v>
+      </c>
+      <c r="M12">
+        <v>3</v>
+      </c>
+      <c r="N12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>762</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>762</v>
+      </c>
+      <c r="D13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>19</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>763</v>
+      </c>
+      <c r="J13" t="s">
+        <v>764</v>
+      </c>
+      <c r="K13" t="s">
+        <v>724</v>
+      </c>
+      <c r="L13" t="s">
+        <v>728</v>
+      </c>
+      <c r="M13">
+        <v>3</v>
+      </c>
+      <c r="N13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>770</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>770</v>
+      </c>
+      <c r="D14" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14">
+        <v>15</v>
+      </c>
+      <c r="F14">
+        <v>15</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="I14" t="s">
+        <v>771</v>
+      </c>
+      <c r="J14" t="s">
+        <v>769</v>
+      </c>
+      <c r="K14" t="s">
+        <v>725</v>
+      </c>
+      <c r="L14" t="s">
+        <v>729</v>
+      </c>
+      <c r="M14">
+        <v>3</v>
+      </c>
+      <c r="N14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>775</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>775</v>
+      </c>
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="I15" t="s">
+        <v>776</v>
+      </c>
+      <c r="J15" t="s">
+        <v>774</v>
+      </c>
+      <c r="K15" t="s">
+        <v>722</v>
+      </c>
+      <c r="L15" t="s">
+        <v>727</v>
+      </c>
+      <c r="M15">
+        <v>3</v>
+      </c>
+      <c r="N15">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747D7955-5580-45E3-B425-BDF4EFE1D71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC70784-5585-4E28-97C2-83FAB447CE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="789">
   <si>
     <t>ALL</t>
   </si>
@@ -2932,6 +2932,46 @@
   </si>
   <si>
     <t>작은 나무같이 생겼네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_수국껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell03_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_수국껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수국으로 둘러싸인 껍질입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수국 껍질(보라색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_수국껍질2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell03_c02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_수국껍질정보2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수국 껍질(파란색)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6495,7 +6535,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B205"/>
+  <dimension ref="A1:B209"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -8140,6 +8180,38 @@
       </c>
       <c r="B205" s="10" t="s">
         <v>778</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A207" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A208" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A209" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -8849,7 +8921,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -11250,6 +11322,82 @@
         <v>68</v>
       </c>
       <c r="L64">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" t="s">
+        <v>779</v>
+      </c>
+      <c r="G65" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="I65" s="11">
+        <v>7</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="K65" t="s">
+        <v>68</v>
+      </c>
+      <c r="L65">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" t="s">
+        <v>779</v>
+      </c>
+      <c r="G66" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="I66" s="11">
+        <v>7</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="K66" t="s">
+        <v>68</v>
+      </c>
+      <c r="L66">
         <v>6</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC70784-5585-4E28-97C2-83FAB447CE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F88C54-3DD1-4387-ABAC-F651B8C47F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="17" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -8392,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>10</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F88C54-3DD1-4387-ABAC-F651B8C47F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF91A78-BAD7-4D10-B0B3-EB4F6AA6A958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="17" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1961" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="793">
   <si>
     <t>ALL</t>
   </si>
@@ -2677,10 +2677,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>어딘가 뽀송해보이는 오리 몸입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>여름 휴가를 가려는 모양입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2972,6 +2968,26 @@
   </si>
   <si>
     <t>수국 껍질(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>삭제</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[삭제]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_재화부족]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요한 재화가 부족합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸에서 날개가 돋아났습니다. 날지는 못하나봐요.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4718,36 +4734,36 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C9" t="s">
         <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C10" t="s">
         <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -4891,7 +4907,7 @@
         <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C4" t="s">
         <v>51</v>
@@ -4929,7 +4945,7 @@
         <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C5" t="s">
         <v>51</v>
@@ -5120,7 +5136,7 @@
         <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C10" t="s">
         <v>74</v>
@@ -5159,7 +5175,7 @@
         <v>90</v>
       </c>
       <c r="B11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C11" t="s">
         <v>51</v>
@@ -5197,7 +5213,7 @@
         <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C12" t="s">
         <v>74</v>
@@ -5236,7 +5252,7 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C13" t="s">
         <v>74</v>
@@ -5274,7 +5290,7 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C14" t="s">
         <v>74</v>
@@ -5312,7 +5328,7 @@
         <v>90</v>
       </c>
       <c r="B15" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C15" t="s">
         <v>74</v>
@@ -6482,13 +6498,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>717</v>
+      </c>
+      <c r="B8" t="s">
+        <v>717</v>
+      </c>
+      <c r="C8" t="s">
         <v>718</v>
-      </c>
-      <c r="B8" t="s">
-        <v>718</v>
-      </c>
-      <c r="C8" t="s">
-        <v>719</v>
       </c>
       <c r="D8" t="s">
         <v>149</v>
@@ -6535,7 +6551,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B209"/>
+  <dimension ref="A1:B211"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -7987,7 +8003,7 @@
         <v>706</v>
       </c>
       <c r="B181" s="10" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
@@ -8003,7 +8019,7 @@
         <v>704</v>
       </c>
       <c r="B183" s="10" t="s">
-        <v>714</v>
+        <v>792</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
@@ -8011,7 +8027,7 @@
         <v>707</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
@@ -8019,199 +8035,215 @@
         <v>711</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B196" s="10" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B197" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B198" s="10" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B199" s="10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="11" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="B207" s="10" t="s">
         <v>782</v>
-      </c>
-      <c r="B207" s="10" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="11" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>783</v>
+        <v>782</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A210" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="11" t="s">
+        <v>790</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -11327,10 +11359,10 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>229</v>
@@ -11342,19 +11374,19 @@
         <v>11</v>
       </c>
       <c r="F65" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G65" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="I65" s="11">
         <v>7</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K65" t="s">
         <v>68</v>
@@ -11365,10 +11397,10 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>229</v>
@@ -11380,19 +11412,19 @@
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G66" s="11" t="b">
         <v>1</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="I66" s="11">
         <v>7</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K66" t="s">
         <v>68</v>
@@ -11546,16 +11578,16 @@
         <v>4</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="M3" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>730</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -11587,10 +11619,10 @@
         <v>245</v>
       </c>
       <c r="K4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -11628,10 +11660,10 @@
         <v>449</v>
       </c>
       <c r="K5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -11669,10 +11701,10 @@
         <v>269</v>
       </c>
       <c r="K6" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -11713,10 +11745,10 @@
         <v>270</v>
       </c>
       <c r="K7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -11727,13 +11759,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D8" t="s">
         <v>149</v>
@@ -11748,16 +11780,16 @@
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L8" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -11768,13 +11800,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
@@ -11789,16 +11821,16 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="J9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="K9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -11809,13 +11841,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
@@ -11830,16 +11862,16 @@
         <v>3</v>
       </c>
       <c r="I10" t="s">
+        <v>749</v>
+      </c>
+      <c r="J10" t="s">
         <v>750</v>
       </c>
-      <c r="J10" t="s">
-        <v>751</v>
-      </c>
       <c r="K10" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L10" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -11850,13 +11882,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D11" t="s">
         <v>51</v>
@@ -11871,16 +11903,16 @@
         <v>3</v>
       </c>
       <c r="I11" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="J11" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="K11" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -11891,13 +11923,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D12" t="s">
         <v>149</v>
@@ -11912,16 +11944,16 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="J12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K12" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -11932,13 +11964,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D13" t="s">
         <v>149</v>
@@ -11953,16 +11985,16 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
+        <v>762</v>
+      </c>
+      <c r="J13" t="s">
         <v>763</v>
       </c>
-      <c r="J13" t="s">
-        <v>764</v>
-      </c>
       <c r="K13" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M13">
         <v>3</v>
@@ -11973,13 +12005,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D14" t="s">
         <v>149</v>
@@ -11994,16 +12026,16 @@
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="J14" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="K14" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L14" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M14">
         <v>3</v>
@@ -12014,13 +12046,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D15" t="s">
         <v>149</v>
@@ -12035,16 +12067,16 @@
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="J15" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K15" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M15">
         <v>3</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF91A78-BAD7-4D10-B0B3-EB4F6AA6A958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B000F751-0770-456E-AEBD-AF5C0F0DD03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="2115" yWindow="2895" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1965" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="840">
   <si>
     <t>ALL</t>
   </si>
@@ -2988,6 +2988,194 @@
   </si>
   <si>
     <t>몸에서 날개가 돋아났습니다. 날지는 못하나봐요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[배고픔]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bubble_hungry</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>배고픔 말풍선</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_보유음식]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유중인 음식이 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_보유악세]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유중인 장식품이 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_용과껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dragonfruitshell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_용과껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용과 껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용과 달팽이(용and달팽이아님)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_금붕어껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_금붕어껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fishshell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금붕어 봉투</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등에 물에 사는 친구를 데리고 다니기로 했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SlotResourceKey</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>slot_epic</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>slot2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>slot_rare</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>slot_legendary</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_당구공껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ballshell01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_당구공껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_구매완료]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매를 완료했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_당구공껍질2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ballshell02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_당구공껍질2정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>검은 당구공</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파란 당구공</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당구공처럼 생겼다고 큐대로 쳐서는 안됩니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[멀티플레이어]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀티플레이어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[친구목록]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>친구 목록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[로비목록]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로비 목록</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[방]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방 만들기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[방만들기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로비ID로 진입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[로비ID로진입]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>랜덤 방으로 진입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[랜덤방으로진입]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3256,7 +3444,29 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 10" xfId="1" xr:uid="{6B9E6416-5075-49D2-A13D-39D9EF488B06}"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3864,16 +4074,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2801ABBC-ECD4-42AF-8E66-C3E5B26CC90B}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="43.125" customWidth="1"/>
+    <col min="3" max="7" width="17.625" customWidth="1"/>
+    <col min="8" max="8" width="43.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -3892,11 +4102,14 @@
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -3910,16 +4123,19 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -3933,16 +4149,19 @@
         <v>40</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -3952,11 +4171,11 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -3966,11 +4185,11 @@
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -3980,11 +4199,11 @@
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -3994,11 +4213,11 @@
       <c r="C7">
         <v>3</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>1</v>
       </c>
@@ -4011,14 +4230,14 @@
       <c r="D8" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="E8" s="13">
+      <c r="F8" s="13">
         <v>100</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="H8" s="13" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
@@ -4031,17 +4250,17 @@
       <c r="D9" s="13" t="s">
         <v>508</v>
       </c>
-      <c r="E9" s="13">
+      <c r="F9" s="13">
         <v>200</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="G9" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>1</v>
       </c>
@@ -4054,17 +4273,17 @@
       <c r="D10" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="E10" s="13">
+      <c r="F10" s="13">
         <v>400</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="G10" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="H10" s="13" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>1</v>
       </c>
@@ -4077,17 +4296,17 @@
       <c r="D11" s="13" t="s">
         <v>506</v>
       </c>
-      <c r="E11" s="13">
+      <c r="F11" s="13">
         <v>300</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="G11" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="H11" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>1</v>
       </c>
@@ -4097,14 +4316,14 @@
       <c r="C12" s="13">
         <v>5</v>
       </c>
-      <c r="E12" s="13">
+      <c r="F12" s="13">
         <v>50</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="H12" s="13" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>73</v>
       </c>
@@ -4117,11 +4336,14 @@
       <c r="D13" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="E13" s="13" t="s">
+        <v>812</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>73</v>
       </c>
@@ -4134,11 +4356,14 @@
       <c r="D14" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="E14" s="13" t="s">
+        <v>813</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>73</v>
       </c>
@@ -4151,11 +4376,14 @@
       <c r="D15" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="E15" s="13" t="s">
+        <v>811</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="13" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>82</v>
       </c>
@@ -4168,11 +4396,14 @@
       <c r="D16" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="E16" s="13" t="s">
+        <v>814</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -4183,11 +4414,12 @@
         <v>1</v>
       </c>
       <c r="D17" s="13"/>
-      <c r="G17" t="s">
+      <c r="E17" s="13"/>
+      <c r="H17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -4198,11 +4430,12 @@
         <v>2</v>
       </c>
       <c r="D18" s="13"/>
-      <c r="G18" t="s">
+      <c r="E18" s="13"/>
+      <c r="H18" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -4213,11 +4446,12 @@
         <v>3</v>
       </c>
       <c r="D19" s="13"/>
-      <c r="G19" t="s">
+      <c r="E19" s="13"/>
+      <c r="H19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -4228,11 +4462,12 @@
         <v>4</v>
       </c>
       <c r="D20" s="13"/>
-      <c r="G20" t="s">
+      <c r="E20" s="13"/>
+      <c r="H20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -4243,11 +4478,12 @@
         <v>5</v>
       </c>
       <c r="D21" s="13"/>
-      <c r="G21" t="s">
+      <c r="E21" s="13"/>
+      <c r="H21" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -4258,11 +4494,12 @@
         <v>6</v>
       </c>
       <c r="D22" s="13"/>
-      <c r="G22" t="s">
+      <c r="E22" s="13"/>
+      <c r="H22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>113</v>
       </c>
@@ -4273,14 +4510,15 @@
         <v>1</v>
       </c>
       <c r="D23" s="13"/>
-      <c r="E23">
+      <c r="E23" s="13"/>
+      <c r="F23">
         <v>250</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -4291,14 +4529,15 @@
         <v>2</v>
       </c>
       <c r="D24" s="13"/>
-      <c r="E24">
+      <c r="E24" s="13"/>
+      <c r="F24">
         <v>260</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -4309,14 +4548,15 @@
         <v>3</v>
       </c>
       <c r="D25" s="13"/>
-      <c r="E25">
+      <c r="E25" s="13"/>
+      <c r="F25">
         <v>251</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>111</v>
       </c>
@@ -4327,14 +4567,15 @@
         <v>4</v>
       </c>
       <c r="D26" s="13"/>
-      <c r="E26">
+      <c r="E26" s="13"/>
+      <c r="F26">
         <v>255</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>396</v>
       </c>
@@ -4344,11 +4585,11 @@
       <c r="C27">
         <v>1</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>396</v>
       </c>
@@ -4358,11 +4599,11 @@
       <c r="C28">
         <v>2</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>396</v>
       </c>
@@ -4372,56 +4613,60 @@
       <c r="C29">
         <v>3</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>404</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:A3">
-    <cfRule type="duplicateValues" dxfId="26" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:C2 B1">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:C3">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="18" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:F3">
-    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+  <conditionalFormatting sqref="D3:G3">
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1">
     <cfRule type="duplicateValues" dxfId="7" priority="1"/>
     <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6551,7 +6796,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B229"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -8244,6 +8489,150 @@
       </c>
       <c r="B211" s="10" t="s">
         <v>791</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A212" s="11" t="s">
+        <v>796</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A213" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A214" s="11" t="s">
+        <v>800</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A215" s="11" t="s">
+        <v>802</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A216" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A217" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A218" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A219" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A220" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A221" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A222" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A223" s="11" t="s">
+        <v>826</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A224" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A225" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="B225" s="10" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A227" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="B227" s="10" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A228" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A229" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -8953,7 +9342,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -11431,6 +11820,146 @@
       </c>
       <c r="L66">
         <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
+        <v>800</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>800</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>801</v>
+      </c>
+      <c r="G67" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" s="11">
+        <v>7</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>802</v>
+      </c>
+      <c r="K67" t="s">
+        <v>68</v>
+      </c>
+      <c r="L67">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>807</v>
+      </c>
+      <c r="G68" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" s="11">
+        <v>7</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="K68" t="s">
+        <v>68</v>
+      </c>
+      <c r="L68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>816</v>
+      </c>
+      <c r="G69" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" s="11">
+        <v>10</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="K69" t="s">
+        <v>68</v>
+      </c>
+      <c r="L69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>821</v>
+      </c>
+      <c r="G70" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" s="11">
+        <v>10</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="K70" t="s">
+        <v>68</v>
+      </c>
+      <c r="L70">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12992,7 +13521,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE7402E-9381-444B-A1AD-921D46BBAC61}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
@@ -13054,6 +13583,20 @@
       </c>
       <c r="D4" t="s">
         <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>793</v>
+      </c>
+      <c r="B5" t="s">
+        <v>794</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>795</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B000F751-0770-456E-AEBD-AF5C0F0DD03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8206E8C8-370F-4696-A24F-069BD58A3A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2115" yWindow="2895" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="842">
   <si>
     <t>ALL</t>
   </si>
@@ -3176,6 +3176,14 @@
   </si>
   <si>
     <t>[랜덤방으로진입]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_로비ID]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로비ID를 입력하세요.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6796,7 +6804,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B229"/>
+  <dimension ref="A1:B230"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -8633,6 +8641,14 @@
       </c>
       <c r="B229" s="10" t="s">
         <v>838</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>841</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8206E8C8-370F-4696-A24F-069BD58A3A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8F1B4A-9BC3-46C0-BFA8-D90D62E81C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="2895" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="1485" yWindow="2340" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2045" uniqueCount="842">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="856">
   <si>
     <t>ALL</t>
   </si>
@@ -3163,10 +3163,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>로비ID로 진입</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>[로비ID로진입]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3183,7 +3179,67 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>로비ID를 입력하세요.</t>
+    <t>[안내_방이탈]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_방진입]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택한 방으로 들어왔습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방을 나왔습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_방생성]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방을 생성했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_코드복사]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방ID를 복사했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방ID로 진입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>방ID를 입력하세요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_달팽이교체]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이를 교체했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_방교체]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선택한 방으로 이동할까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_중복방]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 있는 방입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6804,7 +6860,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B230"/>
+  <dimension ref="A1:B237"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -8629,26 +8685,82 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="11" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B228" s="10" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="11" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B229" s="10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A231" s="11" t="s">
         <v>840</v>
       </c>
-      <c r="B230" s="10" t="s">
+      <c r="B231" s="10" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A232" s="11" t="s">
         <v>841</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A233" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A234" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A235" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A236" s="11" t="s">
+        <v>852</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A237" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>855</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8F1B4A-9BC3-46C0-BFA8-D90D62E81C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AE01DA-9114-4BAF-B1B6-DC30F7A4E463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="2340" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="899">
   <si>
     <t>ALL</t>
   </si>
@@ -3240,6 +3240,176 @@
   </si>
   <si>
     <t>지금 있는 방입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_없는방]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>존재하지 않는 방입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_알배치]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알 목록에서 부화시킬 알을 선택해주세요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateEggPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateEggPlusPercent</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateEggCooltime</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateEggCount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_알생성]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알을 얻었어요!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_천조각몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_천조각몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천 조각 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천 조각을 열심히 꼬매서 만든 몸이에요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>slimebody</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_슬라임몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_슬라임몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임 몸(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>말랑거리고 살짝 투명한 슬라임같습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leaffeeler</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_나뭇잎더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_나뭇잎더듬이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나뭇잎 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나뭇잎 형태로 변한 더듬이입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commoneyes10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈10]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈10정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>심술난 얼굴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>심술이 잔뜩난 얼굴이네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mushroomshell01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mushroomshell02</t>
+  </si>
+  <si>
+    <t>[일반_버섯껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_버섯껍질02]</t>
+  </si>
+  <si>
+    <t>거대버섯 껍질(빨간색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대버섯 껍질(보라색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대한 버섯이 등에 자라났습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_버섯껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈11]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commoneyes11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈11정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>웃는 얼굴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>살짝 웃음기를 띤 얼굴입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3442,7 +3612,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3501,6 +3671,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4739,16 +4912,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8799056C-300F-4910-A643-17063CC9919B}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="17.625" customWidth="1"/>
     <col min="4" max="5" width="18.375" customWidth="1"/>
     <col min="6" max="6" width="39.75" customWidth="1"/>
     <col min="7" max="7" width="39.875" customWidth="1"/>
+    <col min="8" max="8" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4770,8 +4944,11 @@
       <c r="G1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -4793,8 +4970,11 @@
       <c r="G2" s="7" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -4816,8 +4996,11 @@
       <c r="G3" s="8" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -4839,8 +5022,11 @@
       <c r="G4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>84</v>
       </c>
@@ -4862,8 +5048,11 @@
       <c r="G5" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>609</v>
       </c>
@@ -4884,6 +5073,9 @@
       </c>
       <c r="G6" t="s">
         <v>612</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6860,7 +7052,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B237"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -8761,6 +8953,134 @@
       </c>
       <c r="B237" s="10" t="s">
         <v>855</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A238" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A239" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A240" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A241" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="B241" s="10" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A242" s="11" t="s">
+        <v>868</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A243" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="B243" s="10" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A244" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A245" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="B245" s="10" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A246" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A247" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A248" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A249" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A252" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A253" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>898</v>
       </c>
     </row>
   </sheetData>
@@ -8850,18 +9170,20 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB314148-9221-49F7-832E-5D289BE3A143}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="67.625" customWidth="1"/>
+    <col min="5" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="14.625" customWidth="1"/>
+    <col min="11" max="11" width="67.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -8880,11 +9202,23 @@
       <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -8903,11 +9237,23 @@
       <c r="F2" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>486</v>
       </c>
@@ -8926,11 +9272,23 @@
       <c r="F3" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="K3" s="6" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5</v>
       </c>
@@ -8948,6 +9306,18 @@
       </c>
       <c r="F4">
         <v>1600</v>
+      </c>
+      <c r="G4">
+        <v>1800</v>
+      </c>
+      <c r="H4">
+        <v>0.5</v>
+      </c>
+      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9470,7 +9840,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -12090,6 +12460,254 @@
         <v>5</v>
       </c>
     </row>
+    <row r="71" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>866</v>
+      </c>
+      <c r="G71" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" s="11">
+        <v>7</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>868</v>
+      </c>
+      <c r="K71" t="s">
+        <v>68</v>
+      </c>
+      <c r="L71">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G72" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>871</v>
+      </c>
+      <c r="I72" s="11">
+        <v>7</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="K72" t="s">
+        <v>68</v>
+      </c>
+      <c r="L72">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>876</v>
+      </c>
+      <c r="G73" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" s="11">
+        <v>10</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="K73" t="s">
+        <v>68</v>
+      </c>
+      <c r="L73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>881</v>
+      </c>
+      <c r="G74" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" s="11">
+        <v>10</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="K74" t="s">
+        <v>68</v>
+      </c>
+      <c r="L74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>888</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>886</v>
+      </c>
+      <c r="G75" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" s="11">
+        <v>10</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="K75" t="s">
+        <v>68</v>
+      </c>
+      <c r="L75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>889</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="20" t="s">
+        <v>887</v>
+      </c>
+      <c r="G76" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" s="11">
+        <v>10</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>893</v>
+      </c>
+      <c r="K76" t="s">
+        <v>68</v>
+      </c>
+      <c r="L76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>894</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" s="20" t="s">
+        <v>895</v>
+      </c>
+      <c r="G77" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" s="11">
+        <v>10</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>896</v>
+      </c>
+      <c r="K77" t="s">
+        <v>68</v>
+      </c>
+      <c r="L77">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12099,7 +12717,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2444F32-CF16-41C0-B4D3-AE1758A9A6E6}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -12113,9 +12731,10 @@
     <col min="12" max="12" width="20.5" customWidth="1"/>
     <col min="13" max="13" width="16.125" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="15" max="15" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -12158,8 +12777,11 @@
       <c r="N1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -12202,8 +12824,11 @@
       <c r="N2" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -12246,8 +12871,11 @@
       <c r="N3" s="8" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -12287,8 +12915,11 @@
       <c r="N4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -12328,8 +12959,11 @@
       <c r="N5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -12369,8 +13003,11 @@
       <c r="N6">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -12413,8 +13050,11 @@
       <c r="N7">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>732</v>
       </c>
@@ -12454,8 +13094,11 @@
       <c r="N8">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>746</v>
       </c>
@@ -12495,8 +13138,11 @@
       <c r="N9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>748</v>
       </c>
@@ -12536,8 +13182,11 @@
       <c r="N10">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>754</v>
       </c>
@@ -12577,8 +13226,11 @@
       <c r="N11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>759</v>
       </c>
@@ -12618,8 +13270,11 @@
       <c r="N12">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>761</v>
       </c>
@@ -12659,8 +13314,11 @@
       <c r="N13">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>769</v>
       </c>
@@ -12700,8 +13358,11 @@
       <c r="N14">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>774</v>
       </c>
@@ -12740,6 +13401,9 @@
       </c>
       <c r="N15">
         <v>30</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AE01DA-9114-4BAF-B1B6-DC30F7A4E463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B81DE9E-BD69-459C-BF66-A8EF1E7CC65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="908">
   <si>
     <t>ALL</t>
   </si>
@@ -3410,6 +3410,42 @@
   </si>
   <si>
     <t>살짝 웃음기를 띤 얼굴입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimFps</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullabledouble</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_달팽이_초롱눈]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epiceyes02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_달팽이_초롱눈정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초롱초롱한 눈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상대를 방심시킬만큼 초롱초롱합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에픽 알</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에픽 알. 온기가 느껴집니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3612,7 +3648,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3671,9 +3707,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7052,7 +7085,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -9081,6 +9114,38 @@
       </c>
       <c r="B253" s="10" t="s">
         <v>898</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A254" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A255" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="B255" s="10" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>609</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>611</v>
+      </c>
+      <c r="B257" t="s">
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -9840,7 +9905,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -9855,9 +9920,10 @@
     <col min="10" max="10" width="52.125" customWidth="1"/>
     <col min="11" max="11" width="10.25" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.125" customWidth="1"/>
+    <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -9894,8 +9960,11 @@
       <c r="L1" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>23</v>
       </c>
@@ -9932,8 +10001,11 @@
       <c r="L2" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M2" s="7" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
         <v>27</v>
       </c>
@@ -9970,8 +10042,11 @@
       <c r="L3" s="8" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M3" s="8" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>185</v>
       </c>
@@ -10009,7 +10084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>186</v>
       </c>
@@ -10047,7 +10122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>187</v>
       </c>
@@ -10085,7 +10160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>207</v>
       </c>
@@ -10123,7 +10198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
         <v>208</v>
       </c>
@@ -10161,7 +10236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>209</v>
       </c>
@@ -10199,7 +10274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
         <v>210</v>
       </c>
@@ -10237,7 +10312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
         <v>212</v>
       </c>
@@ -10275,7 +10350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
         <v>213</v>
       </c>
@@ -10313,7 +10388,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
         <v>214</v>
       </c>
@@ -10351,7 +10426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>215</v>
       </c>
@@ -10389,7 +10464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
         <v>216</v>
       </c>
@@ -10427,7 +10502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>217</v>
       </c>
@@ -12244,7 +12319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
         <v>779</v>
       </c>
@@ -12282,7 +12357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
         <v>784</v>
       </c>
@@ -12320,7 +12395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
         <v>800</v>
       </c>
@@ -12355,7 +12430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
         <v>805</v>
       </c>
@@ -12390,7 +12465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
         <v>815</v>
       </c>
@@ -12425,7 +12500,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
         <v>820</v>
       </c>
@@ -12460,7 +12535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="11" t="s">
         <v>867</v>
       </c>
@@ -12495,7 +12570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="11" t="s">
         <v>872</v>
       </c>
@@ -12533,7 +12608,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
         <v>877</v>
       </c>
@@ -12549,7 +12624,7 @@
       <c r="E73" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="20" t="s">
+      <c r="F73" s="19" t="s">
         <v>876</v>
       </c>
       <c r="G73" s="11" t="b">
@@ -12568,7 +12643,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="11" t="s">
         <v>882</v>
       </c>
@@ -12584,7 +12659,7 @@
       <c r="E74" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F74" s="20" t="s">
+      <c r="F74" s="19" t="s">
         <v>881</v>
       </c>
       <c r="G74" s="11" t="b">
@@ -12603,7 +12678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="11" t="s">
         <v>888</v>
       </c>
@@ -12619,7 +12694,7 @@
       <c r="E75" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F75" s="20" t="s">
+      <c r="F75" s="19" t="s">
         <v>886</v>
       </c>
       <c r="G75" s="11" t="b">
@@ -12638,7 +12713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="11" t="s">
         <v>889</v>
       </c>
@@ -12654,7 +12729,7 @@
       <c r="E76" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F76" s="20" t="s">
+      <c r="F76" s="19" t="s">
         <v>887</v>
       </c>
       <c r="G76" s="11" t="b">
@@ -12673,7 +12748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="11" t="s">
         <v>894</v>
       </c>
@@ -12689,7 +12764,7 @@
       <c r="E77" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F77" s="20" t="s">
+      <c r="F77" s="19" t="s">
         <v>895</v>
       </c>
       <c r="G77" s="11" t="b">
@@ -12706,6 +12781,44 @@
       </c>
       <c r="L77">
         <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>901</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>902</v>
+      </c>
+      <c r="G78" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="11">
+        <v>7</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>903</v>
+      </c>
+      <c r="K78" t="s">
+        <v>68</v>
+      </c>
+      <c r="L78">
+        <v>7</v>
+      </c>
+      <c r="M78">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B81DE9E-BD69-459C-BF66-A8EF1E7CC65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D97C85C-93A9-4ABE-BC95-55EE2EC5E283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="15" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2185" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="934">
   <si>
     <t>ALL</t>
   </si>
@@ -3446,6 +3446,108 @@
   </si>
   <si>
     <t>에픽 알. 온기가 느껴집니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicshell02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_보석껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicshell02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_보석껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>puddingshell_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>puddingshell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_푸딩껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_푸딩껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보석 껍질(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸딩 껍질(분홍색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>파란색의 빛나는 보석모양의 껍질입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>말랑말랑 뽀잉뽀잉 푸딩 모양의 껍질입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_크로아상껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breadshell01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_크로아상껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breadshell02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_롤빵껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>breadshell02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_롤빵껍질01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_롤빵껍질02]</t>
+  </si>
+  <si>
+    <t>breadshell02_c02</t>
+  </si>
+  <si>
+    <t>롤케이크 껍질(블루베리)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>롤케이크 껍질(딸기)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>맛있는 크림이 들어있는 롤케이크 껍질입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>크루아상 껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>프랑스출신 달팽이인가봐요.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -7085,7 +7187,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -9146,6 +9248,78 @@
       </c>
       <c r="B257" t="s">
         <v>907</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A258" s="11" t="s">
+        <v>909</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A259" s="11" t="s">
+        <v>914</v>
+      </c>
+      <c r="B259" s="10" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A260" s="11" t="s">
+        <v>911</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A261" s="11" t="s">
+        <v>915</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A262" s="11" t="s">
+        <v>924</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A263" s="11" t="s">
+        <v>927</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A264" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A265" s="11" t="s">
+        <v>920</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A266" s="11" t="s">
+        <v>922</v>
+      </c>
+      <c r="B266" s="10" t="s">
+        <v>933</v>
       </c>
     </row>
   </sheetData>
@@ -9905,7 +10079,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -12819,6 +12993,193 @@
       </c>
       <c r="M78">
         <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="11" t="s">
+        <v>909</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>909</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>908</v>
+      </c>
+      <c r="G79" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>910</v>
+      </c>
+      <c r="I79" s="11">
+        <v>5</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>911</v>
+      </c>
+      <c r="K79" t="s">
+        <v>68</v>
+      </c>
+      <c r="L79">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="11" t="s">
+        <v>914</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>914</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>913</v>
+      </c>
+      <c r="G80" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>912</v>
+      </c>
+      <c r="I80" s="11">
+        <v>7</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>915</v>
+      </c>
+      <c r="K80" t="s">
+        <v>68</v>
+      </c>
+      <c r="L80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
+        <v>920</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>920</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>921</v>
+      </c>
+      <c r="G81" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" s="11">
+        <v>10</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>922</v>
+      </c>
+      <c r="K81" t="s">
+        <v>68</v>
+      </c>
+      <c r="L81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="11" t="s">
+        <v>924</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>924</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>923</v>
+      </c>
+      <c r="G82" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="11" t="s">
+        <v>925</v>
+      </c>
+      <c r="I82" s="11">
+        <v>7</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="K82" t="s">
+        <v>68</v>
+      </c>
+      <c r="L82">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="11" t="s">
+        <v>927</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>927</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>923</v>
+      </c>
+      <c r="G83" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>928</v>
+      </c>
+      <c r="I83" s="11">
+        <v>7</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>926</v>
+      </c>
+      <c r="K83" t="s">
+        <v>68</v>
+      </c>
+      <c r="L83">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F081B278-BB51-4356-BCAA-A31C54378DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F75C552-1A4E-41A7-A9F4-8DBFAD0BBD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="1" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="14" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="942">
   <si>
     <t>ALL</t>
   </si>
@@ -3573,6 +3573,22 @@
   </si>
   <si>
     <t>[에픽껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_달팽이판매]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}를 보냈습니다. 바이바이!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[안내_알부화시작]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알을 부화기에 넣었습니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6994,7 +7010,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -9127,6 +9143,22 @@
       </c>
       <c r="B266" s="8" t="s">
         <v>920</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A267" s="9" t="s">
+        <v>938</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A268" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>941</v>
       </c>
     </row>
   </sheetData>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F75C552-1A4E-41A7-A9F4-8DBFAD0BBD9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62383BE-C59D-4B98-9334-ACD78E558532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="14" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="1" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="960">
   <si>
     <t>ALL</t>
   </si>
@@ -1111,24 +1111,6 @@
     <t>명주 달팽이의 껍질.</t>
   </si>
   <si>
-    <t>아프리카 왕달팽이의 껍질. (금와)</t>
-  </si>
-  <si>
-    <t>돌맹이를 깎아 만든 껍질. 농담이다.</t>
-  </si>
-  <si>
-    <t>나쵸칩에 맛들린 달팽이의 일탈 껍질.</t>
-  </si>
-  <si>
-    <t>갈색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>파란색의 민무늬 껍질.</t>
-  </si>
-  <si>
-    <t>주황색의 민무늬 껍질.</t>
-  </si>
-  <si>
     <t>당근이 너무 좋아서 집으로 삼기로 했다.</t>
   </si>
   <si>
@@ -1201,24 +1183,6 @@
     <t>[일반_명주달팽이껍질정보]</t>
   </si>
   <si>
-    <t>[일반_긴껍질01정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질02정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질03정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질04정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질05정보]</t>
-  </si>
-  <si>
-    <t>[일반_긴껍질06정보]</t>
-  </si>
-  <si>
     <t>[레어_당근껍질정보]</t>
   </si>
   <si>
@@ -1292,24 +1256,6 @@
   </si>
   <si>
     <t>명주달팽이껍질</t>
-  </si>
-  <si>
-    <t>긴껍질01</t>
-  </si>
-  <si>
-    <t>긴껍질02</t>
-  </si>
-  <si>
-    <t>긴껍질03</t>
-  </si>
-  <si>
-    <t>긴껍질04</t>
-  </si>
-  <si>
-    <t>긴껍질05</t>
-  </si>
-  <si>
-    <t>긴껍질06</t>
   </si>
   <si>
     <t>뱅글더듬이</t>
@@ -3589,6 +3535,146 @@
   </si>
   <si>
     <t>알을 부화기에 넣었습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectPath</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>spark01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_햄버거껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hamburgershell</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_햄버거껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>햄버거 껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인이 먹던 햄버거를 등에 이고 도망가고 있습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_슬라임몸2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>slimebody2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>슬라임 몸(분홍색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_푸딩껍질2]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>puddingshell_c02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸딩 껍질(노란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_긴껍질07]</t>
+  </si>
+  <si>
+    <t>commonshell02_c07</t>
+  </si>
+  <si>
+    <t>아름다운 고동모양의 껍질입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>줄무늬 고동껍질(보라색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고동껍질(보라색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고동껍질(초록색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>줄무늬 고동껍질(주황색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고동껍질(갈색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고동껍질(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고동껍질(구리색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_긴껍질정보]</t>
+  </si>
+  <si>
+    <t>[일반_긴껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lavabody</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lavabody_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암몸01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암몸02]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lavabody_c02</t>
+  </si>
+  <si>
+    <t>[에픽_용암몸02정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용암 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸이 너무 뜨거웠던걸까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸이 너무 차가웠던걸까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼음 몸</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4519,7 +4605,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>231</v>
@@ -4598,7 +4684,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="F8" s="11">
         <v>100</v>
@@ -4618,7 +4704,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="F9" s="11">
         <v>200</v>
@@ -4641,7 +4727,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="F10" s="11">
         <v>400</v>
@@ -4664,7 +4750,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="F11" s="11">
         <v>300</v>
@@ -4704,10 +4790,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>76</v>
@@ -4724,10 +4810,10 @@
         <v>2</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>800</v>
+        <v>782</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>77</v>
@@ -4744,10 +4830,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>78</v>
@@ -4764,10 +4850,10 @@
         <v>4</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>79</v>
@@ -4912,7 +4998,7 @@
         <v>110</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -4923,7 +5009,7 @@
         <v>251</v>
       </c>
       <c r="H25" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -4931,7 +5017,7 @@
         <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -4942,49 +5028,49 @@
         <v>255</v>
       </c>
       <c r="H26" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B27" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B28" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B29" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -5159,70 +5245,70 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="B7" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="C7" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D7" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="E7" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B8" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C8" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="D8" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="E8" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="B9" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="C9" t="s">
         <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="E9" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="B10" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="C10" t="s">
         <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
       <c r="E10" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -5343,7 +5429,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>98</v>
@@ -5366,7 +5452,7 @@
         <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
@@ -5404,7 +5490,7 @@
         <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="C5" t="s">
         <v>50</v>
@@ -5595,7 +5681,7 @@
         <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="C10" t="s">
         <v>73</v>
@@ -5634,7 +5720,7 @@
         <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="C11" t="s">
         <v>50</v>
@@ -5672,7 +5758,7 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
@@ -5711,7 +5797,7 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
@@ -5749,7 +5835,7 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
@@ -5787,7 +5873,7 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="C15" t="s">
         <v>73</v>
@@ -5903,10 +5989,10 @@
         <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="C18" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -6089,7 +6175,7 @@
         <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
@@ -6128,7 +6214,7 @@
         <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C24" t="s">
         <v>50</v>
@@ -6797,42 +6883,42 @@
         <v>202</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="B4" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="C4" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="M4" t="s">
         <v>67</v>
@@ -6849,25 +6935,25 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="B5" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="C5" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="M5" t="s">
         <v>67</v>
@@ -6884,28 +6970,28 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="B6" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="C6" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="D6" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="M6" t="s">
         <v>67</v>
@@ -6922,25 +7008,25 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="B7" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="C7" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="D7" t="s">
         <v>148</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>622</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>640</v>
-      </c>
       <c r="I7" s="9" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="M7" t="s">
         <v>67</v>
@@ -6957,28 +7043,28 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="B8" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="C8" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="M8" t="s">
         <v>67</v>
@@ -7010,7 +7096,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B272"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -7083,34 +7169,34 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="B9" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="B10" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="B11" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -7126,7 +7212,7 @@
         <v>274</v>
       </c>
       <c r="B14" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -7142,7 +7228,7 @@
         <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -7150,7 +7236,7 @@
         <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -7174,7 +7260,7 @@
         <v>280</v>
       </c>
       <c r="B20" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -7182,7 +7268,7 @@
         <v>281</v>
       </c>
       <c r="B21" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -7190,7 +7276,7 @@
         <v>282</v>
       </c>
       <c r="B22" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -7198,7 +7284,7 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -7206,7 +7292,7 @@
         <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -7214,12 +7300,12 @@
         <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B26" t="s">
         <v>283</v>
@@ -7227,7 +7313,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B27" t="s">
         <v>284</v>
@@ -7235,23 +7321,23 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B28" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s">
         <v>285</v>
@@ -7259,15 +7345,15 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s">
         <v>286</v>
@@ -7275,7 +7361,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s">
         <v>287</v>
@@ -7283,7 +7369,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s">
         <v>288</v>
@@ -7291,7 +7377,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s">
         <v>289</v>
@@ -7299,7 +7385,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s">
         <v>290</v>
@@ -7307,7 +7393,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s">
         <v>291</v>
@@ -7315,7 +7401,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s">
         <v>292</v>
@@ -7323,7 +7409,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s">
         <v>293</v>
@@ -7331,63 +7417,63 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s">
-        <v>294</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>299</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B47" t="s">
         <v>300</v>
@@ -7395,7 +7481,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B48" t="s">
         <v>301</v>
@@ -7403,7 +7489,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s">
         <v>302</v>
@@ -7411,7 +7497,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s">
         <v>303</v>
@@ -7419,535 +7505,535 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="B51" t="s">
-        <v>304</v>
+        <v>182</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="B52" t="s">
-        <v>305</v>
+        <v>183</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
-        <v>337</v>
-      </c>
-      <c r="B53" t="s">
-        <v>306</v>
+        <v>184</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="B54" t="s">
-        <v>307</v>
+        <v>203</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="B55" t="s">
-        <v>308</v>
+        <v>204</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="B56" t="s">
-        <v>309</v>
+        <v>205</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>184</v>
+        <v>482</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>343</v>
+        <v>524</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>344</v>
+        <v>209</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>345</v>
+        <v>210</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>945</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>346</v>
+        <v>211</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>347</v>
+        <v>212</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>943</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>348</v>
+        <v>213</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>542</v>
+        <v>214</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>349</v>
+        <v>525</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>185</v>
+        <v>518</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>365</v>
+        <v>527</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>536</v>
+        <v>199</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>544</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>366</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>367</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>368</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>369</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>545</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>356</v>
+        <v>530</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="9" t="s">
-        <v>233</v>
+      <c r="A86" t="s">
+        <v>529</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>357</v>
+        <v>531</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>234</v>
+        <v>353</v>
       </c>
       <c r="B87" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>354</v>
+      </c>
+      <c r="B88" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>356</v>
+      </c>
+      <c r="B89" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="B88" s="9" t="s">
+      <c r="B90" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="B89" s="9" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>548</v>
+      <c r="B91" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>547</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>549</v>
+        <v>362</v>
+      </c>
+      <c r="B92" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>187</v>
+      <c r="A93" t="s">
+        <v>364</v>
+      </c>
+      <c r="B93" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B94" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B95" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B96" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B97" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="B98" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B99" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B100" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B101" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B102" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B103" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="B104" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="B105" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="B106" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="B107" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="B108" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B109" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="B110" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="B111" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="B112" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="B113" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="B114" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="B115" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B116" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B117" t="s">
         <v>486</v>
@@ -7955,218 +8041,218 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B118" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B119" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B120" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>491</v>
-      </c>
-      <c r="B121" t="s">
-        <v>492</v>
+        <v>494</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B122" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>503</v>
-      </c>
-      <c r="B123" t="s">
-        <v>504</v>
+        <v>498</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B124" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>507</v>
-      </c>
-      <c r="B125" t="s">
-        <v>508</v>
+        <v>502</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="B126" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="B128" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="B130" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>521</v>
-      </c>
-      <c r="B132" t="s">
-        <v>530</v>
+        <v>543</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>523</v>
+      <c r="A133" s="9" t="s">
+        <v>560</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>524</v>
-      </c>
-      <c r="B134" t="s">
-        <v>525</v>
+      <c r="A134" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>526</v>
+      <c r="A135" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>528</v>
-      </c>
-      <c r="B136" t="s">
-        <v>529</v>
+      <c r="A136" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>560</v>
+      <c r="A137" s="9" t="s">
+        <v>567</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" ht="33" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>561</v>
+        <v>574</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A138" s="9" t="s">
+        <v>568</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" s="9" t="s">
-        <v>571</v>
+      <c r="A142" t="s">
+        <v>584</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
@@ -8174,87 +8260,87 @@
         <v>590</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>602</v>
+      <c r="A148" s="9" t="s">
+        <v>599</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
@@ -8262,7 +8348,7 @@
         <v>622</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
@@ -8270,143 +8356,143 @@
         <v>623</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>639</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>641</v>
+      </c>
+      <c r="B161" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="B159" s="8" t="s">
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160" s="9" t="s">
+      <c r="B162" s="8" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>644</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
         <v>647</v>
       </c>
-      <c r="B160" s="8" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="9" t="s">
+      <c r="B164" s="8" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
         <v>648</v>
       </c>
-      <c r="B161" s="8" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="B162" s="8" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="B163" s="8" t="s">
+      <c r="B165" s="8" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="9" t="s">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A167" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="B167" s="8" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A168" s="9" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="B165" s="8" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
+      <c r="B168" s="8" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A169" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="B166" s="8" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" ht="33" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
+      <c r="B169" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="B167" s="8" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A170" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="B168" s="8" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" ht="33" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
+      <c r="B170" s="8" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A171" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="B169" s="8" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>665</v>
-      </c>
-      <c r="B170" s="8" t="s">
+      <c r="B171" s="8" t="s">
         <v>667</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" ht="33" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>666</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
@@ -8414,7 +8500,7 @@
         <v>675</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
@@ -8422,111 +8508,111 @@
         <v>679</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>685</v>
+        <v>761</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B179" s="8" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>686</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="9" t="s">
+      <c r="B181" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="B180" s="8" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="B181" s="8" t="s">
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="9" t="s">
-        <v>697</v>
-      </c>
       <c r="B182" s="8" t="s">
-        <v>700</v>
+        <v>709</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="9" t="s">
-        <v>691</v>
+      <c r="A183" t="s">
+        <v>704</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>779</v>
+        <v>710</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="9" t="s">
-        <v>694</v>
+      <c r="A184" t="s">
+        <v>705</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="9" t="s">
-        <v>698</v>
+      <c r="A185" t="s">
+        <v>706</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>702</v>
+        <v>711</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
@@ -8534,7 +8620,7 @@
         <v>723</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
@@ -8542,164 +8628,164 @@
         <v>724</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
+        <v>728</v>
+      </c>
+      <c r="B194" s="8" t="s">
         <v>735</v>
-      </c>
-      <c r="B194" s="8" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
+        <v>729</v>
+      </c>
+      <c r="B195" s="8" t="s">
         <v>736</v>
-      </c>
-      <c r="B195" s="8" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="B199" s="8" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A200" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="B200" s="8" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>746</v>
-      </c>
-      <c r="B200" s="8" t="s">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A201" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A202" s="9" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>747</v>
-      </c>
-      <c r="B201" s="8" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
+      <c r="B202" s="8" t="s">
         <v>756</v>
       </c>
-      <c r="B202" s="8" t="s">
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A203" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A204" s="9" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
+      <c r="B204" s="8" t="s">
         <v>757</v>
       </c>
-      <c r="B203" s="8" t="s">
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A205" s="9" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>761</v>
-      </c>
-      <c r="B204" s="8" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>762</v>
-      </c>
       <c r="B205" s="8" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="B206" s="8" t="s">
         <v>766</v>
-      </c>
-      <c r="B206" s="8" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
+        <v>767</v>
+      </c>
+      <c r="B207" s="8" t="s">
         <v>768</v>
-      </c>
-      <c r="B207" s="8" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="B209" s="8" t="s">
         <v>773</v>
-      </c>
-      <c r="B209" s="8" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B211" s="8" t="s">
         <v>778</v>
@@ -8707,47 +8793,47 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="9" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="9" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="9" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B217" s="8" t="s">
         <v>796</v>
@@ -8755,130 +8841,130 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
@@ -8891,7 +8977,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B235" s="8" t="s">
         <v>838</v>
@@ -8899,10 +8985,10 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
+        <v>837</v>
+      </c>
+      <c r="B236" s="8" t="s">
         <v>839</v>
-      </c>
-      <c r="B236" s="8" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
@@ -8910,12 +8996,12 @@
         <v>841</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B238" s="8" t="s">
         <v>844</v>
@@ -8923,74 +9009,74 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="B243" s="8" t="s">
         <v>859</v>
-      </c>
-      <c r="B243" s="8" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
+        <v>858</v>
+      </c>
+      <c r="B244" s="8" t="s">
         <v>860</v>
-      </c>
-      <c r="B244" s="8" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
@@ -8998,39 +9084,39 @@
         <v>870</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>578</v>
+      </c>
+      <c r="B250" s="8" t="s">
         <v>875</v>
       </c>
-      <c r="B249" s="8" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A250" s="9" t="s">
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>580</v>
+      </c>
+      <c r="B251" t="s">
         <v>876</v>
-      </c>
-      <c r="B250" s="8" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A251" s="9" t="s">
-        <v>880</v>
-      </c>
-      <c r="B251" s="8" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
@@ -9038,127 +9124,159 @@
         <v>883</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="9" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="B255" s="8" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>596</v>
+      <c r="A256" s="9" t="s">
+        <v>893</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>598</v>
-      </c>
-      <c r="B257" t="s">
-        <v>894</v>
+      <c r="A257" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="B259" s="8" t="s">
         <v>901</v>
-      </c>
-      <c r="B259" s="8" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="s">
-        <v>902</v>
+        <v>920</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>917</v>
+        <v>923</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>916</v>
+        <v>929</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
       <c r="B264" s="8" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
-        <v>907</v>
+        <v>931</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>919</v>
+        <v>933</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="s">
-        <v>909</v>
+        <v>934</v>
       </c>
       <c r="B266" s="8" t="s">
-        <v>920</v>
+        <v>936</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>941</v>
+        <v>939</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A269" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A270" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A271" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A272" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>958</v>
       </c>
     </row>
   </sheetData>
@@ -9200,7 +9318,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -9217,10 +9335,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>63</v>
@@ -9231,10 +9349,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="B4" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -9339,40 +9457,40 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>849</v>
+        <v>831</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>847</v>
+        <v>829</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>848</v>
+        <v>830</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>850</v>
+        <v>832</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -9418,7 +9536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -9436,9 +9554,10 @@
     <col min="13" max="13" width="11.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.625" customWidth="1"/>
     <col min="15" max="15" width="14.5" customWidth="1"/>
+    <col min="16" max="16" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -9484,8 +9603,11 @@
       <c r="O1" s="13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -9523,16 +9645,19 @@
         <v>19</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>887</v>
+        <v>869</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>904</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
@@ -9570,16 +9695,19 @@
         <v>105</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>455</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>182</v>
       </c>
@@ -9608,7 +9736,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="K4" t="s">
         <v>67</v>
@@ -9617,13 +9745,13 @@
         <v>5</v>
       </c>
       <c r="N4" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>183</v>
       </c>
@@ -9652,7 +9780,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="K5" t="s">
         <v>67</v>
@@ -9661,13 +9789,13 @@
         <v>5</v>
       </c>
       <c r="N5" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>184</v>
       </c>
@@ -9696,7 +9824,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K6" t="s">
         <v>67</v>
@@ -9705,13 +9833,13 @@
         <v>5</v>
       </c>
       <c r="N6" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>203</v>
       </c>
@@ -9740,7 +9868,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="K7" t="s">
         <v>67</v>
@@ -9749,13 +9877,13 @@
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>204</v>
       </c>
@@ -9784,7 +9912,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="K8" t="s">
         <v>67</v>
@@ -9793,13 +9921,13 @@
         <v>5</v>
       </c>
       <c r="N8" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>205</v>
       </c>
@@ -9828,7 +9956,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="K9" t="s">
         <v>67</v>
@@ -9837,13 +9965,13 @@
         <v>5</v>
       </c>
       <c r="N9" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>206</v>
       </c>
@@ -9872,7 +10000,7 @@
         <v>10</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="K10" t="s">
         <v>67</v>
@@ -9881,13 +10009,13 @@
         <v>5</v>
       </c>
       <c r="N10" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>208</v>
       </c>
@@ -9916,7 +10044,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="K11" t="s">
         <v>67</v>
@@ -9925,13 +10053,13 @@
         <v>5</v>
       </c>
       <c r="N11" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>209</v>
       </c>
@@ -9960,7 +10088,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>318</v>
+        <v>947</v>
       </c>
       <c r="K12" t="s">
         <v>67</v>
@@ -9969,13 +10097,13 @@
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="O12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>210</v>
       </c>
@@ -10004,7 +10132,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>319</v>
+        <v>947</v>
       </c>
       <c r="K13" t="s">
         <v>67</v>
@@ -10013,13 +10141,13 @@
         <v>5</v>
       </c>
       <c r="N13" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="O13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>211</v>
       </c>
@@ -10048,7 +10176,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>320</v>
+        <v>947</v>
       </c>
       <c r="K14" t="s">
         <v>67</v>
@@ -10057,13 +10185,13 @@
         <v>5</v>
       </c>
       <c r="N14" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="O14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>212</v>
       </c>
@@ -10092,7 +10220,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>321</v>
+        <v>947</v>
       </c>
       <c r="K15" t="s">
         <v>67</v>
@@ -10101,13 +10229,13 @@
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="O15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>213</v>
       </c>
@@ -10136,7 +10264,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>322</v>
+        <v>947</v>
       </c>
       <c r="K16" t="s">
         <v>67</v>
@@ -10145,7 +10273,7 @@
         <v>5</v>
       </c>
       <c r="N16" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -10180,7 +10308,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>323</v>
+        <v>947</v>
       </c>
       <c r="K17" t="s">
         <v>67</v>
@@ -10189,7 +10317,7 @@
         <v>5</v>
       </c>
       <c r="N17" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -10197,43 +10325,43 @@
     </row>
     <row r="18" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>185</v>
+        <v>937</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>185</v>
+        <v>937</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="G18" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>181</v>
+        <v>938</v>
       </c>
       <c r="I18" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>324</v>
+        <v>947</v>
       </c>
       <c r="K18" t="s">
         <v>67</v>
       </c>
       <c r="L18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N18" t="s">
-        <v>925</v>
+        <v>906</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -10241,10 +10369,10 @@
     </row>
     <row r="19" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>497</v>
+        <v>185</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>497</v>
+        <v>185</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>225</v>
@@ -10256,19 +10384,19 @@
         <v>11</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>498</v>
+        <v>188</v>
       </c>
       <c r="G19" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>499</v>
+        <v>181</v>
       </c>
       <c r="I19" s="9">
         <v>7</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>500</v>
+        <v>312</v>
       </c>
       <c r="K19" t="s">
         <v>67</v>
@@ -10277,7 +10405,7 @@
         <v>10</v>
       </c>
       <c r="N19" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -10285,43 +10413,43 @@
     </row>
     <row r="20" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>585</v>
+        <v>479</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>585</v>
+        <v>479</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>574</v>
+        <v>225</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>575</v>
+        <v>148</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>587</v>
+        <v>480</v>
       </c>
       <c r="G20" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>588</v>
+        <v>481</v>
       </c>
       <c r="I20" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>590</v>
+        <v>482</v>
       </c>
       <c r="K20" t="s">
         <v>67</v>
       </c>
       <c r="L20">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N20" t="s">
-        <v>926</v>
+        <v>907</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -10329,34 +10457,34 @@
     </row>
     <row r="21" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="G21" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="I21" s="9">
         <v>5</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="K21" t="s">
         <v>67</v>
@@ -10365,7 +10493,7 @@
         <v>20</v>
       </c>
       <c r="N21" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -10373,41 +10501,43 @@
     </row>
     <row r="22" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>631</v>
+        <v>568</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>631</v>
+        <v>568</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>224</v>
+        <v>556</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>50</v>
+        <v>557</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>632</v>
+        <v>569</v>
       </c>
       <c r="G22" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>571</v>
+      </c>
       <c r="I22" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>633</v>
+        <v>572</v>
       </c>
       <c r="K22" t="s">
         <v>67</v>
       </c>
       <c r="L22">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N22" t="s">
-        <v>923</v>
+        <v>908</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -10415,41 +10545,41 @@
     </row>
     <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>647</v>
+        <v>613</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>647</v>
+        <v>613</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>644</v>
+        <v>614</v>
       </c>
       <c r="G23" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>648</v>
+        <v>615</v>
       </c>
       <c r="K23" t="s">
         <v>67</v>
       </c>
       <c r="L23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N23" t="s">
-        <v>927</v>
+        <v>905</v>
       </c>
       <c r="O23">
         <v>5</v>
@@ -10457,43 +10587,41 @@
     </row>
     <row r="24" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>159</v>
+        <v>629</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>159</v>
+        <v>629</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>157</v>
+        <v>626</v>
       </c>
       <c r="G24" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>164</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H24" s="9"/>
       <c r="I24" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>325</v>
+        <v>630</v>
       </c>
       <c r="K24" t="s">
         <v>67</v>
       </c>
       <c r="L24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N24" t="s">
-        <v>928</v>
+        <v>909</v>
       </c>
       <c r="O24">
         <v>5</v>
@@ -10501,10 +10629,10 @@
     </row>
     <row r="25" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>224</v>
@@ -10522,13 +10650,13 @@
         <v>1</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I25" s="9">
         <v>10</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="K25" t="s">
         <v>67</v>
@@ -10537,7 +10665,7 @@
         <v>5</v>
       </c>
       <c r="N25" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O25">
         <v>5</v>
@@ -10545,10 +10673,10 @@
     </row>
     <row r="26" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>224</v>
@@ -10566,13 +10694,13 @@
         <v>1</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I26" s="9">
         <v>10</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="K26" t="s">
         <v>67</v>
@@ -10581,7 +10709,7 @@
         <v>5</v>
       </c>
       <c r="N26" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O26">
         <v>5</v>
@@ -10589,10 +10717,10 @@
     </row>
     <row r="27" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>423</v>
+        <v>230</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>423</v>
+        <v>230</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>224</v>
@@ -10610,13 +10738,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>419</v>
+        <v>166</v>
       </c>
       <c r="I27" s="9">
         <v>10</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>426</v>
+        <v>315</v>
       </c>
       <c r="K27" t="s">
         <v>67</v>
@@ -10625,7 +10753,7 @@
         <v>5</v>
       </c>
       <c r="N27" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O27">
         <v>5</v>
@@ -10633,10 +10761,10 @@
     </row>
     <row r="28" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>224</v>
@@ -10654,13 +10782,13 @@
         <v>1</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="I28" s="9">
         <v>10</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="K28" t="s">
         <v>67</v>
@@ -10669,7 +10797,7 @@
         <v>5</v>
       </c>
       <c r="N28" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O28">
         <v>5</v>
@@ -10677,10 +10805,10 @@
     </row>
     <row r="29" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>224</v>
@@ -10698,13 +10826,13 @@
         <v>1</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="I29" s="9">
         <v>10</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="K29" t="s">
         <v>67</v>
@@ -10713,7 +10841,7 @@
         <v>5</v>
       </c>
       <c r="N29" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O29">
         <v>5</v>
@@ -10721,10 +10849,10 @@
     </row>
     <row r="30" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>634</v>
+        <v>407</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>634</v>
+        <v>407</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>224</v>
@@ -10742,13 +10870,13 @@
         <v>1</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>636</v>
+        <v>403</v>
       </c>
       <c r="I30" s="9">
         <v>10</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>635</v>
+        <v>410</v>
       </c>
       <c r="K30" t="s">
         <v>67</v>
@@ -10757,7 +10885,7 @@
         <v>5</v>
       </c>
       <c r="N30" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -10765,10 +10893,10 @@
     </row>
     <row r="31" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>224</v>
@@ -10786,13 +10914,13 @@
         <v>1</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="I31" s="9">
         <v>10</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="K31" t="s">
         <v>67</v>
@@ -10801,7 +10929,7 @@
         <v>5</v>
       </c>
       <c r="N31" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O31">
         <v>5</v>
@@ -10809,10 +10937,10 @@
     </row>
     <row r="32" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>235</v>
+        <v>583</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>235</v>
+        <v>583</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>224</v>
@@ -10824,19 +10952,19 @@
         <v>13</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>236</v>
+        <v>157</v>
       </c>
       <c r="G32" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>237</v>
+        <v>582</v>
       </c>
       <c r="I32" s="9">
         <v>10</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>328</v>
+        <v>585</v>
       </c>
       <c r="K32" t="s">
         <v>67</v>
@@ -10845,7 +10973,7 @@
         <v>5</v>
       </c>
       <c r="N32" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O32">
         <v>5</v>
@@ -10853,10 +10981,10 @@
     </row>
     <row r="33" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>628</v>
+        <v>235</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>628</v>
+        <v>235</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>224</v>
@@ -10868,17 +10996,19 @@
         <v>13</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>629</v>
+        <v>236</v>
       </c>
       <c r="G33" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>237</v>
+      </c>
       <c r="I33" s="9">
         <v>10</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>630</v>
+        <v>316</v>
       </c>
       <c r="K33" t="s">
         <v>67</v>
@@ -10887,7 +11017,7 @@
         <v>5</v>
       </c>
       <c r="N33" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -10895,10 +11025,10 @@
     </row>
     <row r="34" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>257</v>
+        <v>610</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>257</v>
+        <v>610</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>224</v>
@@ -10910,19 +11040,17 @@
         <v>13</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>258</v>
+        <v>611</v>
       </c>
       <c r="G34" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H34" s="9"/>
       <c r="I34" s="9">
         <v>10</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>329</v>
+        <v>612</v>
       </c>
       <c r="K34" t="s">
         <v>67</v>
@@ -10931,7 +11059,7 @@
         <v>5</v>
       </c>
       <c r="N34" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O34">
         <v>5</v>
@@ -10939,10 +11067,10 @@
     </row>
     <row r="35" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>429</v>
+        <v>257</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>429</v>
+        <v>257</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>224</v>
@@ -10960,13 +11088,13 @@
         <v>1</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>422</v>
+        <v>259</v>
       </c>
       <c r="I35" s="9">
         <v>10</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>430</v>
+        <v>317</v>
       </c>
       <c r="K35" t="s">
         <v>67</v>
@@ -10975,7 +11103,7 @@
         <v>5</v>
       </c>
       <c r="N35" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="O35">
         <v>5</v>
@@ -10983,43 +11111,43 @@
     </row>
     <row r="36" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>438</v>
+        <v>258</v>
       </c>
       <c r="G36" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c r="I36" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>440</v>
+        <v>412</v>
       </c>
       <c r="K36" t="s">
         <v>67</v>
       </c>
       <c r="L36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N36" t="s">
-        <v>929</v>
+        <v>910</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -11027,43 +11155,43 @@
     </row>
     <row r="37" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>533</v>
+        <v>419</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>533</v>
+        <v>419</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>534</v>
+        <v>420</v>
       </c>
       <c r="G37" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>535</v>
+        <v>421</v>
       </c>
       <c r="I37" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>536</v>
+        <v>422</v>
       </c>
       <c r="K37" t="s">
         <v>67</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N37" t="s">
-        <v>928</v>
+        <v>911</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -11071,41 +11199,43 @@
     </row>
     <row r="38" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>578</v>
+        <v>515</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>578</v>
+        <v>515</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>574</v>
+        <v>224</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>575</v>
+        <v>50</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>579</v>
+        <v>516</v>
       </c>
       <c r="G38" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>517</v>
+      </c>
       <c r="I38" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>580</v>
+        <v>518</v>
       </c>
       <c r="K38" t="s">
         <v>67</v>
       </c>
       <c r="L38">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N38" t="s">
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="O38">
         <v>5</v>
@@ -11113,43 +11243,41 @@
     </row>
     <row r="39" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>653</v>
+        <v>560</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>653</v>
+        <v>560</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>225</v>
+        <v>556</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>148</v>
+        <v>557</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="17" t="s">
-        <v>651</v>
+      <c r="F39" s="10" t="s">
+        <v>561</v>
       </c>
       <c r="G39" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>652</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H39" s="9"/>
       <c r="I39" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>654</v>
+        <v>562</v>
       </c>
       <c r="K39" t="s">
         <v>67</v>
       </c>
       <c r="L39">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N39" t="s">
-        <v>929</v>
+        <v>912</v>
       </c>
       <c r="O39">
         <v>5</v>
@@ -11157,41 +11285,43 @@
     </row>
     <row r="40" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>160</v>
+        <v>635</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>160</v>
+        <v>635</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>158</v>
+        <v>13</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>633</v>
       </c>
       <c r="G40" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>634</v>
+      </c>
       <c r="I40" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>330</v>
+        <v>636</v>
       </c>
       <c r="K40" t="s">
         <v>67</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N40" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="O40">
         <v>5</v>
@@ -11199,10 +11329,10 @@
     </row>
     <row r="41" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>224</v>
@@ -11214,7 +11344,7 @@
         <v>14</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="G41" s="9" t="b">
         <v>0</v>
@@ -11224,7 +11354,7 @@
         <v>10</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="K41" t="s">
         <v>67</v>
@@ -11233,7 +11363,7 @@
         <v>5</v>
       </c>
       <c r="N41" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="O41">
         <v>5</v>
@@ -11241,10 +11371,10 @@
     </row>
     <row r="42" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>224</v>
@@ -11256,7 +11386,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G42" s="9" t="b">
         <v>0</v>
@@ -11266,7 +11396,7 @@
         <v>10</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="K42" t="s">
         <v>67</v>
@@ -11275,7 +11405,7 @@
         <v>5</v>
       </c>
       <c r="N42" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -11283,10 +11413,10 @@
     </row>
     <row r="43" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>224</v>
@@ -11298,7 +11428,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G43" s="9" t="b">
         <v>0</v>
@@ -11308,7 +11438,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="K43" t="s">
         <v>67</v>
@@ -11317,7 +11447,7 @@
         <v>5</v>
       </c>
       <c r="N43" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="O43">
         <v>5</v>
@@ -11325,10 +11455,10 @@
     </row>
     <row r="44" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>431</v>
+        <v>219</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>431</v>
+        <v>219</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>224</v>
@@ -11340,7 +11470,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>432</v>
+        <v>222</v>
       </c>
       <c r="G44" s="9" t="b">
         <v>0</v>
@@ -11350,7 +11480,7 @@
         <v>10</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>433</v>
+        <v>321</v>
       </c>
       <c r="K44" t="s">
         <v>67</v>
@@ -11359,18 +11489,18 @@
         <v>5</v>
       </c>
       <c r="N44" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="O44">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>617</v>
+        <v>413</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>617</v>
+        <v>413</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>224</v>
@@ -11381,8 +11511,8 @@
       <c r="E45" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F45" s="17" t="s">
-        <v>616</v>
+      <c r="F45" s="10" t="s">
+        <v>414</v>
       </c>
       <c r="G45" s="9" t="b">
         <v>0</v>
@@ -11392,7 +11522,7 @@
         <v>10</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>618</v>
+        <v>415</v>
       </c>
       <c r="K45" t="s">
         <v>67</v>
@@ -11401,7 +11531,7 @@
         <v>5</v>
       </c>
       <c r="N45" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="O45">
         <v>5</v>
@@ -11409,10 +11539,10 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>637</v>
+        <v>599</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>637</v>
+        <v>599</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>224</v>
@@ -11424,7 +11554,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="G46" s="9" t="b">
         <v>0</v>
@@ -11434,7 +11564,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>638</v>
+        <v>600</v>
       </c>
       <c r="K46" t="s">
         <v>67</v>
@@ -11443,18 +11573,18 @@
         <v>5</v>
       </c>
       <c r="N46" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="O46">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>674</v>
+        <v>619</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>674</v>
+        <v>619</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>224</v>
@@ -11466,7 +11596,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="G47" s="9" t="b">
         <v>0</v>
@@ -11476,7 +11606,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>675</v>
+        <v>620</v>
       </c>
       <c r="K47" t="s">
         <v>67</v>
@@ -11485,7 +11615,7 @@
         <v>5</v>
       </c>
       <c r="N47" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="O47">
         <v>5</v>
@@ -11493,96 +11623,94 @@
     </row>
     <row r="48" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>573</v>
+        <v>656</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>573</v>
+        <v>656</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>574</v>
+        <v>224</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>575</v>
+        <v>50</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F48" s="10" t="s">
-        <v>576</v>
+      <c r="F48" s="17" t="s">
+        <v>598</v>
       </c>
       <c r="G48" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>577</v>
+        <v>657</v>
       </c>
       <c r="K48" t="s">
         <v>67</v>
       </c>
       <c r="L48">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N48" t="s">
-        <v>932</v>
+        <v>913</v>
       </c>
       <c r="O48">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>167</v>
+        <v>555</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>167</v>
+        <v>555</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>224</v>
+        <v>556</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>50</v>
+        <v>557</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>168</v>
+        <v>558</v>
       </c>
       <c r="G49" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>195</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H49" s="9"/>
       <c r="I49" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="K49" t="s">
         <v>67</v>
       </c>
       <c r="L49">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N49" t="s">
-        <v>933</v>
+        <v>914</v>
       </c>
       <c r="O49">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>468</v>
+        <v>167</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>468</v>
+        <v>167</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>224</v>
@@ -11594,19 +11722,19 @@
         <v>152</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="G50" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="I50" s="9">
         <v>10</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="K50" t="s">
         <v>67</v>
@@ -11615,18 +11743,18 @@
         <v>5</v>
       </c>
       <c r="N50" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="O50">
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>224</v>
@@ -11644,13 +11772,13 @@
         <v>1</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>470</v>
+        <v>161</v>
       </c>
       <c r="I51" s="9">
         <v>10</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="K51" t="s">
         <v>67</v>
@@ -11659,18 +11787,18 @@
         <v>5</v>
       </c>
       <c r="N51" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="O51">
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>263</v>
+        <v>451</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>263</v>
+        <v>451</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>224</v>
@@ -11682,19 +11810,19 @@
         <v>152</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G52" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>162</v>
+        <v>452</v>
       </c>
       <c r="I52" s="9">
         <v>10</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="K52" t="s">
         <v>67</v>
@@ -11703,18 +11831,18 @@
         <v>5</v>
       </c>
       <c r="N52" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="O52">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>224</v>
@@ -11726,19 +11854,19 @@
         <v>152</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G53" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I53" s="9">
         <v>10</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>337</v>
+        <v>453</v>
       </c>
       <c r="K53" t="s">
         <v>67</v>
@@ -11747,102 +11875,104 @@
         <v>5</v>
       </c>
       <c r="N53" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="O53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>572</v>
+        <v>233</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>572</v>
+        <v>233</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>574</v>
+        <v>224</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>575</v>
+        <v>50</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>152</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>570</v>
+        <v>196</v>
       </c>
       <c r="G54" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>163</v>
+      </c>
       <c r="I54" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>571</v>
+        <v>325</v>
       </c>
       <c r="K54" t="s">
         <v>67</v>
       </c>
       <c r="L54">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N54" t="s">
-        <v>934</v>
+        <v>915</v>
       </c>
       <c r="O54">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>640</v>
+        <v>554</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>640</v>
+        <v>554</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>224</v>
+        <v>556</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>50</v>
+        <v>557</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F55" s="17" t="s">
-        <v>639</v>
+      <c r="F55" s="10" t="s">
+        <v>552</v>
       </c>
       <c r="G55" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="9"/>
       <c r="I55" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>641</v>
+        <v>553</v>
       </c>
       <c r="K55" t="s">
         <v>67</v>
       </c>
       <c r="L55">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N55" t="s">
-        <v>933</v>
+        <v>916</v>
       </c>
       <c r="O55">
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>224</v>
@@ -11853,8 +11983,8 @@
       <c r="E56" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F56" t="s">
-        <v>606</v>
+      <c r="F56" s="17" t="s">
+        <v>621</v>
       </c>
       <c r="G56" s="9" t="b">
         <v>0</v>
@@ -11864,27 +11994,27 @@
         <v>10</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="K56" t="s">
         <v>67</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N56" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="O56">
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>224</v>
@@ -11893,10 +12023,10 @@
         <v>50</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>611</v>
+        <v>152</v>
+      </c>
+      <c r="F57" t="s">
+        <v>588</v>
       </c>
       <c r="G57" s="9" t="b">
         <v>0</v>
@@ -11906,7 +12036,7 @@
         <v>10</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="K57" t="s">
         <v>67</v>
@@ -11915,60 +12045,60 @@
         <v>6</v>
       </c>
       <c r="N57" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="O57">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
       <c r="G58" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
       <c r="K58" t="s">
         <v>67</v>
       </c>
       <c r="L58">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N58" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="O58">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>225</v>
@@ -11977,10 +12107,10 @@
         <v>148</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="G59" s="9" t="b">
         <v>0</v>
@@ -11990,27 +12120,30 @@
         <v>7</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="K59" t="s">
         <v>67</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N59" t="s">
-        <v>935</v>
+        <v>907</v>
       </c>
       <c r="O59">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P59" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>679</v>
+        <v>652</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>679</v>
+        <v>652</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>225</v>
@@ -12019,10 +12152,10 @@
         <v>148</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>678</v>
+        <v>651</v>
       </c>
       <c r="G60" s="9" t="b">
         <v>0</v>
@@ -12032,7 +12165,7 @@
         <v>7</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>680</v>
+        <v>653</v>
       </c>
       <c r="K60" t="s">
         <v>67</v>
@@ -12041,18 +12174,18 @@
         <v>6</v>
       </c>
       <c r="N60" t="s">
-        <v>936</v>
+        <v>917</v>
       </c>
       <c r="O60">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>225</v>
@@ -12064,7 +12197,7 @@
         <v>14</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>683</v>
+        <v>660</v>
       </c>
       <c r="G61" s="9" t="b">
         <v>0</v>
@@ -12074,7 +12207,7 @@
         <v>7</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>682</v>
+        <v>662</v>
       </c>
       <c r="K61" t="s">
         <v>67</v>
@@ -12083,18 +12216,18 @@
         <v>6</v>
       </c>
       <c r="N61" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="O61">
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>225</v>
@@ -12103,22 +12236,20 @@
         <v>148</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>688</v>
+        <v>665</v>
       </c>
       <c r="G62" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>690</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H62" s="9"/>
       <c r="I62" s="9">
         <v>7</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>691</v>
+        <v>664</v>
       </c>
       <c r="K62" t="s">
         <v>67</v>
@@ -12127,18 +12258,18 @@
         <v>6</v>
       </c>
       <c r="N62" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="O62">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>693</v>
+        <v>671</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>693</v>
+        <v>671</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>225</v>
@@ -12147,22 +12278,22 @@
         <v>148</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>692</v>
+        <v>670</v>
       </c>
       <c r="G63" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H63" t="s">
-        <v>695</v>
+      <c r="H63" s="9" t="s">
+        <v>672</v>
       </c>
       <c r="I63" s="9">
         <v>7</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="K63" t="s">
         <v>67</v>
@@ -12171,18 +12302,18 @@
         <v>6</v>
       </c>
       <c r="N63" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="O63">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>225</v>
@@ -12191,19 +12322,22 @@
         <v>148</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>696</v>
+        <v>674</v>
       </c>
       <c r="G64" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>677</v>
       </c>
       <c r="I64" s="9">
         <v>7</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>698</v>
+        <v>676</v>
       </c>
       <c r="K64" t="s">
         <v>67</v>
@@ -12212,7 +12346,7 @@
         <v>6</v>
       </c>
       <c r="N64" t="s">
-        <v>935</v>
+        <v>907</v>
       </c>
       <c r="O64">
         <v>5</v>
@@ -12220,10 +12354,10 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>766</v>
+        <v>679</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>766</v>
+        <v>679</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>225</v>
@@ -12232,22 +12366,19 @@
         <v>148</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" t="s">
-        <v>765</v>
+        <v>152</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>678</v>
       </c>
       <c r="G65" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="I65" s="9">
         <v>7</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>768</v>
+        <v>680</v>
       </c>
       <c r="K65" t="s">
         <v>67</v>
@@ -12256,7 +12387,7 @@
         <v>6</v>
       </c>
       <c r="N65" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="O65">
         <v>5</v>
@@ -12264,10 +12395,10 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>771</v>
+        <v>748</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>771</v>
+        <v>748</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>225</v>
@@ -12279,19 +12410,19 @@
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="G66" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>772</v>
+        <v>749</v>
       </c>
       <c r="I66" s="9">
         <v>7</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>773</v>
+        <v>750</v>
       </c>
       <c r="K66" t="s">
         <v>67</v>
@@ -12300,7 +12431,7 @@
         <v>6</v>
       </c>
       <c r="N66" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="O66">
         <v>5</v>
@@ -12308,10 +12439,10 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>787</v>
+        <v>753</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>787</v>
+        <v>753</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>225</v>
@@ -12322,17 +12453,20 @@
       <c r="E67" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F67" s="17" t="s">
-        <v>788</v>
+      <c r="F67" t="s">
+        <v>747</v>
       </c>
       <c r="G67" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>754</v>
       </c>
       <c r="I67" s="9">
         <v>7</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>789</v>
+        <v>755</v>
       </c>
       <c r="K67" t="s">
         <v>67</v>
@@ -12341,7 +12475,7 @@
         <v>6</v>
       </c>
       <c r="N67" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="O67">
         <v>5</v>
@@ -12349,10 +12483,10 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>792</v>
+        <v>769</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>225</v>
@@ -12364,7 +12498,7 @@
         <v>11</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>794</v>
+        <v>770</v>
       </c>
       <c r="G68" s="9" t="b">
         <v>0</v>
@@ -12373,7 +12507,7 @@
         <v>7</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>793</v>
+        <v>771</v>
       </c>
       <c r="K68" t="s">
         <v>67</v>
@@ -12382,7 +12516,7 @@
         <v>6</v>
       </c>
       <c r="N68" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="O68">
         <v>5</v>
@@ -12390,40 +12524,40 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>802</v>
+        <v>774</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>802</v>
+        <v>774</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>803</v>
+        <v>776</v>
       </c>
       <c r="G69" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I69" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>804</v>
+        <v>775</v>
       </c>
       <c r="K69" t="s">
         <v>67</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N69" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="O69">
         <v>5</v>
@@ -12431,10 +12565,10 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>224</v>
@@ -12446,7 +12580,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>808</v>
+        <v>785</v>
       </c>
       <c r="G70" s="9" t="b">
         <v>0</v>
@@ -12455,7 +12589,7 @@
         <v>10</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="K70" t="s">
         <v>67</v>
@@ -12464,48 +12598,48 @@
         <v>5</v>
       </c>
       <c r="N70" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="O70">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>854</v>
+        <v>789</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>854</v>
+        <v>789</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>853</v>
+        <v>790</v>
       </c>
       <c r="G71" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I71" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>855</v>
+        <v>791</v>
       </c>
       <c r="K71" t="s">
         <v>67</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N71" t="s">
-        <v>929</v>
+        <v>905</v>
       </c>
       <c r="O71">
         <v>5</v>
@@ -12513,10 +12647,10 @@
     </row>
     <row r="72" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>225</v>
@@ -12527,20 +12661,17 @@
       <c r="E72" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>157</v>
+      <c r="F72" s="17" t="s">
+        <v>835</v>
       </c>
       <c r="G72" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
-        <v>858</v>
+        <v>0</v>
       </c>
       <c r="I72" s="9">
         <v>7</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
       <c r="K72" t="s">
         <v>67</v>
@@ -12549,89 +12680,95 @@
         <v>6</v>
       </c>
       <c r="N72" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="O72">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>863</v>
+        <v>13</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="G73" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>840</v>
       </c>
       <c r="I73" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>865</v>
+        <v>842</v>
       </c>
       <c r="K73" t="s">
         <v>67</v>
       </c>
       <c r="L73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N73" t="s">
-        <v>933</v>
+        <v>911</v>
       </c>
       <c r="O73">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
-        <v>869</v>
+        <v>931</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>869</v>
+        <v>931</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F74" s="17" t="s">
-        <v>868</v>
+        <v>13</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="G74" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>932</v>
       </c>
       <c r="I74" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>870</v>
+        <v>842</v>
       </c>
       <c r="K74" t="s">
         <v>67</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N74" t="s">
-        <v>931</v>
+        <v>911</v>
       </c>
       <c r="O74">
         <v>5</v>
@@ -12639,10 +12776,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>875</v>
+        <v>846</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>875</v>
+        <v>846</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>224</v>
@@ -12651,10 +12788,10 @@
         <v>50</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>873</v>
+        <v>845</v>
       </c>
       <c r="G75" s="9" t="b">
         <v>0</v>
@@ -12663,7 +12800,7 @@
         <v>10</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>880</v>
+        <v>847</v>
       </c>
       <c r="K75" t="s">
         <v>67</v>
@@ -12672,7 +12809,7 @@
         <v>5</v>
       </c>
       <c r="N75" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="O75">
         <v>5</v>
@@ -12680,10 +12817,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>876</v>
+        <v>851</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>876</v>
+        <v>851</v>
       </c>
       <c r="C76" s="9" t="s">
         <v>224</v>
@@ -12692,10 +12829,10 @@
         <v>50</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>874</v>
+        <v>850</v>
       </c>
       <c r="G76" s="9" t="b">
         <v>0</v>
@@ -12704,7 +12841,7 @@
         <v>10</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>880</v>
+        <v>852</v>
       </c>
       <c r="K76" t="s">
         <v>67</v>
@@ -12713,7 +12850,7 @@
         <v>5</v>
       </c>
       <c r="N76" t="s">
-        <v>923</v>
+        <v>913</v>
       </c>
       <c r="O76">
         <v>5</v>
@@ -12721,10 +12858,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>881</v>
+        <v>857</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>881</v>
+        <v>857</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>224</v>
@@ -12733,10 +12870,10 @@
         <v>50</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>882</v>
+        <v>855</v>
       </c>
       <c r="G77" s="9" t="b">
         <v>0</v>
@@ -12745,7 +12882,7 @@
         <v>10</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>883</v>
+        <v>862</v>
       </c>
       <c r="K77" t="s">
         <v>67</v>
@@ -12754,7 +12891,7 @@
         <v>5</v>
       </c>
       <c r="N77" t="s">
-        <v>931</v>
+        <v>905</v>
       </c>
       <c r="O77">
         <v>5</v>
@@ -12762,43 +12899,40 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>888</v>
+        <v>858</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>888</v>
+        <v>858</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>889</v>
+        <v>856</v>
       </c>
       <c r="G78" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I78" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>890</v>
+        <v>862</v>
       </c>
       <c r="K78" t="s">
         <v>67</v>
       </c>
       <c r="L78">
-        <v>7</v>
-      </c>
-      <c r="M78">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N78" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="O78">
         <v>5</v>
@@ -12806,43 +12940,40 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>896</v>
+        <v>863</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>896</v>
+        <v>863</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>574</v>
+        <v>224</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>575</v>
+        <v>50</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>895</v>
+        <v>864</v>
       </c>
       <c r="G79" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>897</v>
+        <v>0</v>
       </c>
       <c r="I79" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="K79" t="s">
         <v>67</v>
       </c>
       <c r="L79">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N79" t="s">
-        <v>937</v>
+        <v>913</v>
       </c>
       <c r="O79">
         <v>5</v>
@@ -12850,10 +12981,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>901</v>
+        <v>870</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>901</v>
+        <v>870</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>225</v>
@@ -12862,31 +12993,31 @@
         <v>148</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>900</v>
+        <v>871</v>
       </c>
       <c r="G80" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80" t="s">
-        <v>899</v>
+        <v>0</v>
       </c>
       <c r="I80" s="9">
         <v>7</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>902</v>
+        <v>872</v>
       </c>
       <c r="K80" t="s">
         <v>67</v>
       </c>
       <c r="L80">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="M80">
+        <v>14</v>
       </c>
       <c r="N80" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="O80">
         <v>5</v>
@@ -12894,40 +13025,43 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
-        <v>907</v>
+        <v>878</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>907</v>
+        <v>878</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>224</v>
+        <v>556</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>50</v>
+        <v>557</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>908</v>
+        <v>877</v>
       </c>
       <c r="G81" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>879</v>
       </c>
       <c r="I81" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>909</v>
+        <v>880</v>
       </c>
       <c r="K81" t="s">
         <v>67</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N81" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="O81">
         <v>5</v>
@@ -12935,10 +13069,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>911</v>
+        <v>883</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>911</v>
+        <v>883</v>
       </c>
       <c r="C82" s="9" t="s">
         <v>225</v>
@@ -12950,28 +13084,28 @@
         <v>11</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>910</v>
+        <v>882</v>
       </c>
       <c r="G82" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H82" s="9" t="s">
-        <v>912</v>
+      <c r="H82" t="s">
+        <v>881</v>
       </c>
       <c r="I82" s="9">
         <v>7</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>913</v>
+        <v>884</v>
       </c>
       <c r="K82" t="s">
         <v>67</v>
       </c>
       <c r="L82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N82" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
       <c r="O82">
         <v>5</v>
@@ -12979,10 +13113,10 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="C83" s="9" t="s">
         <v>225</v>
@@ -12994,30 +13128,288 @@
         <v>11</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>910</v>
+        <v>882</v>
       </c>
       <c r="G83" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H83" s="9" t="s">
-        <v>915</v>
+      <c r="H83" t="s">
+        <v>935</v>
       </c>
       <c r="I83" s="9">
         <v>7</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>913</v>
+        <v>884</v>
       </c>
       <c r="K83" t="s">
         <v>67</v>
       </c>
       <c r="L83">
+        <v>6</v>
+      </c>
+      <c r="N83" t="s">
+        <v>907</v>
+      </c>
+      <c r="O83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A84" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="17" t="s">
+        <v>890</v>
+      </c>
+      <c r="G84" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" s="9">
+        <v>10</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="K84" t="s">
+        <v>67</v>
+      </c>
+      <c r="L84">
+        <v>5</v>
+      </c>
+      <c r="N84" t="s">
+        <v>905</v>
+      </c>
+      <c r="O84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>893</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>892</v>
+      </c>
+      <c r="G85" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="I85" s="9">
         <v>7</v>
       </c>
-      <c r="N83" t="s">
+      <c r="J85" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="K85" t="s">
+        <v>67</v>
+      </c>
+      <c r="L85">
+        <v>7</v>
+      </c>
+      <c r="N85" t="s">
+        <v>909</v>
+      </c>
+      <c r="O85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>892</v>
+      </c>
+      <c r="G86" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="I86" s="9">
+        <v>7</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="K86" t="s">
+        <v>67</v>
+      </c>
+      <c r="L86">
+        <v>7</v>
+      </c>
+      <c r="N86" t="s">
+        <v>909</v>
+      </c>
+      <c r="O86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="17" t="s">
         <v>927</v>
       </c>
-      <c r="O83">
+      <c r="G87" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" s="9">
+        <v>7</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>928</v>
+      </c>
+      <c r="K87" t="s">
+        <v>67</v>
+      </c>
+      <c r="L87">
+        <v>7</v>
+      </c>
+      <c r="N87" t="s">
+        <v>909</v>
+      </c>
+      <c r="O87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="G88" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>951</v>
+      </c>
+      <c r="I88" s="9">
+        <v>5</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="K88" t="s">
+        <v>67</v>
+      </c>
+      <c r="L88">
+        <v>20</v>
+      </c>
+      <c r="N88" t="s">
+        <v>912</v>
+      </c>
+      <c r="O88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>950</v>
+      </c>
+      <c r="G89" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>954</v>
+      </c>
+      <c r="I89" s="9">
+        <v>5</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>955</v>
+      </c>
+      <c r="K89" t="s">
+        <v>67</v>
+      </c>
+      <c r="L89">
+        <v>20</v>
+      </c>
+      <c r="N89" t="s">
+        <v>912</v>
+      </c>
+      <c r="O89">
         <v>5</v>
       </c>
     </row>
@@ -13109,7 +13501,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>19</v>
@@ -13165,7 +13557,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>65</v>
@@ -13177,16 +13569,16 @@
         <v>4</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>268</v>
@@ -13215,16 +13607,16 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="J4" t="s">
         <v>241</v>
       </c>
       <c r="K4" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="L4" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -13259,16 +13651,16 @@
         <v>2.5</v>
       </c>
       <c r="I5" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="J5" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="K5" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="L5" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -13303,16 +13695,16 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="J6" t="s">
         <v>265</v>
       </c>
       <c r="K6" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="L6" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -13350,16 +13742,16 @@
         <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="J7" t="s">
         <v>266</v>
       </c>
       <c r="K7" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="L7" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -13373,13 +13765,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -13394,16 +13786,16 @@
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="J8" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="K8" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="L8" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -13417,13 +13809,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="D9" t="s">
         <v>50</v>
@@ -13438,16 +13830,16 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="J9" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="K9" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="L9" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -13461,13 +13853,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -13482,16 +13874,16 @@
         <v>3</v>
       </c>
       <c r="I10" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="J10" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="K10" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="L10" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -13505,13 +13897,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -13526,16 +13918,16 @@
         <v>3</v>
       </c>
       <c r="I11" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="J11" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="K11" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="L11" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -13549,13 +13941,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -13570,16 +13962,16 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="J12" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="K12" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="L12" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -13593,13 +13985,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="D13" t="s">
         <v>148</v>
@@ -13614,16 +14006,16 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="J13" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="K13" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="L13" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="M13">
         <v>3</v>
@@ -13637,13 +14029,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="D14" t="s">
         <v>148</v>
@@ -13658,16 +14050,16 @@
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>757</v>
+        <v>739</v>
       </c>
       <c r="J14" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="K14" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="L14" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="M14">
         <v>3</v>
@@ -13681,13 +14073,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="D15" t="s">
         <v>148</v>
@@ -13702,16 +14094,16 @@
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="J15" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="K15" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="L15" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="M15">
         <v>3</v>
@@ -13858,7 +14250,7 @@
         <v>101</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -14696,16 +15088,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>780</v>
+        <v>762</v>
       </c>
       <c r="B5" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
     </row>
   </sheetData>
@@ -15027,7 +15419,7 @@
         <v>269</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>80</v>
@@ -15099,25 +15491,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="B6" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="C6">
         <v>600</v>
       </c>
       <c r="D6" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E6" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="F6" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="G6" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="H6">
         <v>1</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62383BE-C59D-4B98-9334-ACD78E558532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A47EF9D-9139-4AAB-8082-1B6455561D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="1" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="10" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="960">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="962">
   <si>
     <t>ALL</t>
   </si>
@@ -660,9 +660,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>commonfeeler02_c01</t>
-  </si>
-  <si>
     <t>commonfeeler03_c01</t>
   </si>
   <si>
@@ -1276,12 +1273,6 @@
     <t>고양이더듬이02</t>
   </si>
   <si>
-    <t>일반달팽이_몸01</t>
-  </si>
-  <si>
-    <t>일반달팽이_몸02</t>
-  </si>
-  <si>
     <t>일반달팽이_몸03</t>
   </si>
   <si>
@@ -1661,13 +1652,6 @@
   </si>
   <si>
     <t>[일반_오목더듬이01]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[일반_오목더듬이02]</t>
-  </si>
-  <si>
-    <t>commonfeeler02_c02</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3675,6 +3659,34 @@
   </si>
   <si>
     <t>얼음 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸른색의 아름다운 몸입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바다가 생각나는 멋진 몸입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>etc02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[낫]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[낫정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>낫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>열심히 농사 마무리하고 왔다네요.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4582,10 +4594,10 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>9</v>
@@ -4605,13 +4617,13 @@
         <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>10</v>
@@ -4684,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F8" s="11">
         <v>100</v>
@@ -4704,13 +4716,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="F9" s="11">
         <v>200</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>57</v>
@@ -4727,13 +4739,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="F10" s="11">
         <v>400</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>58</v>
@@ -4750,13 +4762,13 @@
         <v>4</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F11" s="11">
         <v>300</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>154</v>
@@ -4790,10 +4802,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>76</v>
@@ -4810,10 +4822,10 @@
         <v>2</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>77</v>
@@ -4830,10 +4842,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>78</v>
@@ -4850,10 +4862,10 @@
         <v>4</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>79</v>
@@ -4998,7 +5010,7 @@
         <v>110</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -5009,7 +5021,7 @@
         <v>251</v>
       </c>
       <c r="H25" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -5017,7 +5029,7 @@
         <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -5028,49 +5040,49 @@
         <v>255</v>
       </c>
       <c r="H26" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B27" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B28" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B29" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -5131,7 +5143,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -5180,7 +5192,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>110</v>
@@ -5189,7 +5201,7 @@
         <v>117</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5206,7 +5218,7 @@
         <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5223,7 +5235,7 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5240,75 +5252,92 @@
         <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B8" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C8" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E8" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B9" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C9" t="s">
         <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="E9" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="B10" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C10" t="s">
         <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="E10" t="s">
-        <v>706</v>
+        <v>701</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>958</v>
+      </c>
+      <c r="B11" t="s">
+        <v>958</v>
+      </c>
+      <c r="C11" t="s">
+        <v>436</v>
+      </c>
+      <c r="D11" t="s">
+        <v>957</v>
+      </c>
+      <c r="E11" t="s">
+        <v>959</v>
       </c>
     </row>
   </sheetData>
@@ -5319,7 +5348,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E79052-7558-4F08-8689-6E3AEA3B2BB4}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
@@ -5429,7 +5458,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>98</v>
@@ -5452,7 +5481,7 @@
         <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
@@ -5490,7 +5519,7 @@
         <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C5" t="s">
         <v>50</v>
@@ -5681,7 +5710,7 @@
         <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="C10" t="s">
         <v>73</v>
@@ -5720,7 +5749,7 @@
         <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="C11" t="s">
         <v>50</v>
@@ -5758,7 +5787,7 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
@@ -5797,7 +5826,7 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
@@ -5835,7 +5864,7 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
@@ -5873,7 +5902,7 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C15" t="s">
         <v>73</v>
@@ -5989,10 +6018,10 @@
         <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C18" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -6109,10 +6138,10 @@
         <v>68</v>
       </c>
       <c r="F21">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G21" s="12">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>99</v>
@@ -6128,7 +6157,7 @@
       </c>
       <c r="L21">
         <f t="shared" si="4"/>
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -6148,10 +6177,10 @@
         <v>68</v>
       </c>
       <c r="F22">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G22" s="12">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>99</v>
@@ -6167,7 +6196,7 @@
       </c>
       <c r="L22">
         <f t="shared" si="4"/>
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -6175,7 +6204,7 @@
         <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
@@ -6187,10 +6216,10 @@
         <v>67</v>
       </c>
       <c r="F23">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G23" s="12">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>99</v>
@@ -6206,7 +6235,7 @@
       </c>
       <c r="L23">
         <f t="shared" ref="L23:L24" si="5">F23/2</f>
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -6214,7 +6243,7 @@
         <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C24" t="s">
         <v>50</v>
@@ -6226,10 +6255,10 @@
         <v>67</v>
       </c>
       <c r="F24">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12">
-        <v>350</v>
+        <v>70</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>99</v>
@@ -6245,7 +6274,46 @@
       </c>
       <c r="L24">
         <f t="shared" si="5"/>
-        <v>250</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>958</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="G25" s="12">
+        <v>70</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25">
+        <f t="shared" ref="L25" si="6">F25/2</f>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -6301,7 +6369,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>23</v>
@@ -6806,25 +6874,25 @@
         <v>22</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>69</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>69</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>69</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>69</v>
@@ -6850,75 +6918,75 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>80</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>194</v>
-      </c>
       <c r="K3" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="M3" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>546</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C4" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="M4" t="s">
         <v>67</v>
@@ -6935,25 +7003,25 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B5" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C5" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>589</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>594</v>
       </c>
       <c r="M5" t="s">
         <v>67</v>
@@ -6970,28 +7038,28 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B6" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C6" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="D6" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="M6" t="s">
         <v>67</v>
@@ -7008,25 +7076,25 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B7" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="C7" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="D7" t="s">
         <v>148</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="M7" t="s">
         <v>67</v>
@@ -7043,28 +7111,28 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B8" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="C8" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="M8" t="s">
         <v>67</v>
@@ -7096,7 +7164,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B272"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -7124,15 +7192,15 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" t="s">
         <v>261</v>
-      </c>
-      <c r="B4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -7169,39 +7237,39 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B9" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B10" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B11" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
@@ -7209,10 +7277,10 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -7220,23 +7288,23 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B16" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -7244,7 +7312,7 @@
         <v>82</v>
       </c>
       <c r="B18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -7252,31 +7320,31 @@
         <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B20" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B21" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B22" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -7284,7 +7352,7 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -7292,7 +7360,7 @@
         <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -7300,124 +7368,124 @@
         <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B26" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B40" t="s">
         <v>155</v>
@@ -7425,210 +7493,210 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B44" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B45" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -7636,47 +7704,47 @@
         <v>159</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>343</v>
+        <v>956</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>344</v>
+        <v>955</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -7684,1599 +7752,1615 @@
         <v>160</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B88" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B89" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B90" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B91" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B92" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B94" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B95" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B96" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B97" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B99" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B100" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
+        <v>394</v>
+      </c>
+      <c r="B101" t="s">
         <v>397</v>
-      </c>
-      <c r="B101" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B102" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B103" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B104" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B105" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B106" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B107" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B108" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B109" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B110" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
+        <v>458</v>
+      </c>
+      <c r="B111" t="s">
         <v>463</v>
-      </c>
-      <c r="B111" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B112" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B113" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B114" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B115" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B116" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B117" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B118" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B119" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B120" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B122" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B124" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B126" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B128" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B130" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B170" s="8" t="s">
         <v>661</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="B171" s="8" t="s">
         <v>662</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="B172" s="8" t="s">
         <v>663</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="B173" s="8" t="s">
         <v>664</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
+        <v>701</v>
+      </c>
+      <c r="B185" s="8" t="s">
         <v>706</v>
-      </c>
-      <c r="B185" s="8" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="9" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="9" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="9" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="9" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="B234" s="8" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="9" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="9" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B251" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="9" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="B255" s="8" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="9" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="9" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="B258" s="8" t="s">
         <v>895</v>
-      </c>
-      <c r="B258" s="8" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="9" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B264" s="8" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B266" s="8" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="9" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="B271" s="8" t="s">
         <v>952</v>
-      </c>
-      <c r="B271" s="8" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="9" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B272" s="8" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
         <v>958</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>959</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -9318,7 +9402,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -9335,10 +9419,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>63</v>
@@ -9349,10 +9433,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -9422,34 +9506,34 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>9</v>
@@ -9457,40 +9541,40 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>461</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -9536,7 +9620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -9621,7 +9705,7 @@
         <v>150</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>24</v>
@@ -9630,7 +9714,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>23</v>
@@ -9645,13 +9729,13 @@
         <v>19</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>3</v>
@@ -9662,10 +9746,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>80</v>
@@ -9686,7 +9770,7 @@
         <v>146</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>104</v>
@@ -9695,27 +9779,27 @@
         <v>105</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>50</v>
@@ -9730,13 +9814,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I4" s="9">
         <v>10</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K4" t="s">
         <v>67</v>
@@ -9745,7 +9829,7 @@
         <v>5</v>
       </c>
       <c r="N4" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -9753,13 +9837,13 @@
     </row>
     <row r="5" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>50</v>
@@ -9774,13 +9858,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I5" s="9">
         <v>10</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K5" t="s">
         <v>67</v>
@@ -9789,7 +9873,7 @@
         <v>5</v>
       </c>
       <c r="N5" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -9797,13 +9881,13 @@
     </row>
     <row r="6" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>50</v>
@@ -9818,13 +9902,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I6" s="9">
         <v>10</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K6" t="s">
         <v>67</v>
@@ -9833,7 +9917,7 @@
         <v>5</v>
       </c>
       <c r="N6" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -9841,13 +9925,13 @@
     </row>
     <row r="7" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>50</v>
@@ -9862,13 +9946,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I7" s="9">
         <v>10</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K7" t="s">
         <v>67</v>
@@ -9877,7 +9961,7 @@
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -9885,13 +9969,13 @@
     </row>
     <row r="8" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>50</v>
@@ -9906,13 +9990,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I8" s="9">
         <v>10</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K8" t="s">
         <v>67</v>
@@ -9921,7 +10005,7 @@
         <v>5</v>
       </c>
       <c r="N8" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -9929,13 +10013,13 @@
     </row>
     <row r="9" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>50</v>
@@ -9950,13 +10034,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I9" s="9">
         <v>10</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K9" t="s">
         <v>67</v>
@@ -9965,7 +10049,7 @@
         <v>5</v>
       </c>
       <c r="N9" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -9973,13 +10057,13 @@
     </row>
     <row r="10" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>50</v>
@@ -9994,13 +10078,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I10" s="9">
         <v>10</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K10" t="s">
         <v>67</v>
@@ -10009,7 +10093,7 @@
         <v>5</v>
       </c>
       <c r="N10" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -10017,13 +10101,13 @@
     </row>
     <row r="11" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>50</v>
@@ -10038,13 +10122,13 @@
         <v>1</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I11" s="9">
         <v>10</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K11" t="s">
         <v>67</v>
@@ -10053,7 +10137,7 @@
         <v>5</v>
       </c>
       <c r="N11" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O11">
         <v>5</v>
@@ -10061,13 +10145,13 @@
     </row>
     <row r="12" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>50</v>
@@ -10076,19 +10160,19 @@
         <v>11</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I12" s="9">
         <v>10</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K12" t="s">
         <v>67</v>
@@ -10097,7 +10181,7 @@
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -10105,13 +10189,13 @@
     </row>
     <row r="13" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>50</v>
@@ -10120,19 +10204,19 @@
         <v>11</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I13" s="9">
         <v>10</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K13" t="s">
         <v>67</v>
@@ -10141,7 +10225,7 @@
         <v>5</v>
       </c>
       <c r="N13" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -10149,13 +10233,13 @@
     </row>
     <row r="14" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>50</v>
@@ -10164,19 +10248,19 @@
         <v>11</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G14" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I14" s="9">
         <v>10</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K14" t="s">
         <v>67</v>
@@ -10185,7 +10269,7 @@
         <v>5</v>
       </c>
       <c r="N14" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -10193,13 +10277,13 @@
     </row>
     <row r="15" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>50</v>
@@ -10208,19 +10292,19 @@
         <v>11</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G15" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I15" s="9">
         <v>10</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K15" t="s">
         <v>67</v>
@@ -10229,7 +10313,7 @@
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -10237,13 +10321,13 @@
     </row>
     <row r="16" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>50</v>
@@ -10252,19 +10336,19 @@
         <v>11</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G16" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I16" s="9">
         <v>10</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K16" t="s">
         <v>67</v>
@@ -10273,7 +10357,7 @@
         <v>5</v>
       </c>
       <c r="N16" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -10281,13 +10365,13 @@
     </row>
     <row r="17" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>50</v>
@@ -10296,19 +10380,19 @@
         <v>11</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G17" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I17" s="9">
         <v>10</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K17" t="s">
         <v>67</v>
@@ -10317,7 +10401,7 @@
         <v>5</v>
       </c>
       <c r="N17" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -10325,13 +10409,13 @@
     </row>
     <row r="18" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>50</v>
@@ -10340,19 +10424,19 @@
         <v>11</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G18" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="I18" s="9">
         <v>10</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="K18" t="s">
         <v>67</v>
@@ -10361,7 +10445,7 @@
         <v>5</v>
       </c>
       <c r="N18" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -10369,13 +10453,13 @@
     </row>
     <row r="19" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>148</v>
@@ -10384,19 +10468,19 @@
         <v>11</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I19" s="9">
         <v>7</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K19" t="s">
         <v>67</v>
@@ -10405,7 +10489,7 @@
         <v>10</v>
       </c>
       <c r="N19" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -10413,13 +10497,13 @@
     </row>
     <row r="20" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>148</v>
@@ -10428,19 +10512,19 @@
         <v>11</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="G20" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="I20" s="9">
         <v>7</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="K20" t="s">
         <v>67</v>
@@ -10449,7 +10533,7 @@
         <v>10</v>
       </c>
       <c r="N20" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="O20">
         <v>5</v>
@@ -10457,34 +10541,34 @@
     </row>
     <row r="21" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G21" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="I21" s="9">
         <v>5</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="K21" t="s">
         <v>67</v>
@@ -10493,7 +10577,7 @@
         <v>20</v>
       </c>
       <c r="N21" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -10501,34 +10585,34 @@
     </row>
     <row r="22" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G22" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="I22" s="9">
         <v>5</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="K22" t="s">
         <v>67</v>
@@ -10537,7 +10621,7 @@
         <v>20</v>
       </c>
       <c r="N22" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -10545,13 +10629,13 @@
     </row>
     <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>50</v>
@@ -10560,7 +10644,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="G23" s="9" t="b">
         <v>0</v>
@@ -10570,7 +10654,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="K23" t="s">
         <v>67</v>
@@ -10579,7 +10663,7 @@
         <v>5</v>
       </c>
       <c r="N23" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O23">
         <v>5</v>
@@ -10587,13 +10671,13 @@
     </row>
     <row r="24" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>148</v>
@@ -10602,7 +10686,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="G24" s="9" t="b">
         <v>0</v>
@@ -10612,7 +10696,7 @@
         <v>7</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="K24" t="s">
         <v>67</v>
@@ -10621,7 +10705,7 @@
         <v>10</v>
       </c>
       <c r="N24" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="O24">
         <v>5</v>
@@ -10635,7 +10719,7 @@
         <v>159</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>50</v>
@@ -10650,13 +10734,13 @@
         <v>1</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I25" s="9">
         <v>10</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K25" t="s">
         <v>67</v>
@@ -10665,7 +10749,7 @@
         <v>5</v>
       </c>
       <c r="N25" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O25">
         <v>5</v>
@@ -10673,13 +10757,13 @@
     </row>
     <row r="26" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>50</v>
@@ -10694,13 +10778,13 @@
         <v>1</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I26" s="9">
         <v>10</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K26" t="s">
         <v>67</v>
@@ -10709,7 +10793,7 @@
         <v>5</v>
       </c>
       <c r="N26" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O26">
         <v>5</v>
@@ -10717,13 +10801,13 @@
     </row>
     <row r="27" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>50</v>
@@ -10738,13 +10822,13 @@
         <v>1</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I27" s="9">
         <v>10</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K27" t="s">
         <v>67</v>
@@ -10753,7 +10837,7 @@
         <v>5</v>
       </c>
       <c r="N27" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O27">
         <v>5</v>
@@ -10761,13 +10845,13 @@
     </row>
     <row r="28" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>50</v>
@@ -10782,13 +10866,13 @@
         <v>1</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="I28" s="9">
         <v>10</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="K28" t="s">
         <v>67</v>
@@ -10797,7 +10881,7 @@
         <v>5</v>
       </c>
       <c r="N28" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O28">
         <v>5</v>
@@ -10805,13 +10889,13 @@
     </row>
     <row r="29" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>50</v>
@@ -10826,13 +10910,13 @@
         <v>1</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="I29" s="9">
         <v>10</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="K29" t="s">
         <v>67</v>
@@ -10841,7 +10925,7 @@
         <v>5</v>
       </c>
       <c r="N29" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O29">
         <v>5</v>
@@ -10849,13 +10933,13 @@
     </row>
     <row r="30" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>50</v>
@@ -10870,13 +10954,13 @@
         <v>1</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="I30" s="9">
         <v>10</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="K30" t="s">
         <v>67</v>
@@ -10885,7 +10969,7 @@
         <v>5</v>
       </c>
       <c r="N30" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -10893,13 +10977,13 @@
     </row>
     <row r="31" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>50</v>
@@ -10914,13 +10998,13 @@
         <v>1</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="I31" s="9">
         <v>10</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="K31" t="s">
         <v>67</v>
@@ -10929,7 +11013,7 @@
         <v>5</v>
       </c>
       <c r="N31" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O31">
         <v>5</v>
@@ -10937,13 +11021,13 @@
     </row>
     <row r="32" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>50</v>
@@ -10958,13 +11042,13 @@
         <v>1</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="I32" s="9">
         <v>10</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="K32" t="s">
         <v>67</v>
@@ -10973,7 +11057,7 @@
         <v>5</v>
       </c>
       <c r="N32" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O32">
         <v>5</v>
@@ -10981,13 +11065,13 @@
     </row>
     <row r="33" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>50</v>
@@ -10996,19 +11080,19 @@
         <v>13</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G33" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I33" s="9">
         <v>10</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K33" t="s">
         <v>67</v>
@@ -11017,7 +11101,7 @@
         <v>5</v>
       </c>
       <c r="N33" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -11025,13 +11109,13 @@
     </row>
     <row r="34" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>50</v>
@@ -11040,7 +11124,7 @@
         <v>13</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="G34" s="9" t="b">
         <v>0</v>
@@ -11050,7 +11134,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="K34" t="s">
         <v>67</v>
@@ -11059,7 +11143,7 @@
         <v>5</v>
       </c>
       <c r="N34" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O34">
         <v>5</v>
@@ -11067,13 +11151,13 @@
     </row>
     <row r="35" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>50</v>
@@ -11082,19 +11166,19 @@
         <v>13</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G35" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I35" s="9">
         <v>10</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K35" t="s">
         <v>67</v>
@@ -11103,7 +11187,7 @@
         <v>5</v>
       </c>
       <c r="N35" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O35">
         <v>5</v>
@@ -11111,13 +11195,13 @@
     </row>
     <row r="36" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>50</v>
@@ -11126,19 +11210,19 @@
         <v>13</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G36" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="I36" s="9">
         <v>10</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="K36" t="s">
         <v>67</v>
@@ -11147,7 +11231,7 @@
         <v>5</v>
       </c>
       <c r="N36" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -11155,13 +11239,13 @@
     </row>
     <row r="37" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>148</v>
@@ -11170,19 +11254,19 @@
         <v>13</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G37" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="I37" s="9">
         <v>7</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="K37" t="s">
         <v>67</v>
@@ -11191,7 +11275,7 @@
         <v>10</v>
       </c>
       <c r="N37" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -11199,13 +11283,13 @@
     </row>
     <row r="38" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>50</v>
@@ -11214,19 +11298,19 @@
         <v>13</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G38" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="I38" s="9">
         <v>10</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="K38" t="s">
         <v>67</v>
@@ -11235,7 +11319,7 @@
         <v>5</v>
       </c>
       <c r="N38" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O38">
         <v>5</v>
@@ -11243,22 +11327,22 @@
     </row>
     <row r="39" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="G39" s="9" t="b">
         <v>0</v>
@@ -11268,7 +11352,7 @@
         <v>5</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="K39" t="s">
         <v>67</v>
@@ -11277,7 +11361,7 @@
         <v>20</v>
       </c>
       <c r="N39" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="O39">
         <v>5</v>
@@ -11285,13 +11369,13 @@
     </row>
     <row r="40" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>148</v>
@@ -11300,19 +11384,19 @@
         <v>13</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G40" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="I40" s="9">
         <v>7</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="K40" t="s">
         <v>67</v>
@@ -11321,7 +11405,7 @@
         <v>10</v>
       </c>
       <c r="N40" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="O40">
         <v>5</v>
@@ -11335,7 +11419,7 @@
         <v>160</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>50</v>
@@ -11354,7 +11438,7 @@
         <v>10</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K41" t="s">
         <v>67</v>
@@ -11363,7 +11447,7 @@
         <v>5</v>
       </c>
       <c r="N41" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O41">
         <v>5</v>
@@ -11371,13 +11455,13 @@
     </row>
     <row r="42" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>50</v>
@@ -11386,7 +11470,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G42" s="9" t="b">
         <v>0</v>
@@ -11396,7 +11480,7 @@
         <v>10</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="K42" t="s">
         <v>67</v>
@@ -11405,7 +11489,7 @@
         <v>5</v>
       </c>
       <c r="N42" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -11413,13 +11497,13 @@
     </row>
     <row r="43" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>50</v>
@@ -11428,7 +11512,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G43" s="9" t="b">
         <v>0</v>
@@ -11438,7 +11522,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K43" t="s">
         <v>67</v>
@@ -11447,7 +11531,7 @@
         <v>5</v>
       </c>
       <c r="N43" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O43">
         <v>5</v>
@@ -11455,13 +11539,13 @@
     </row>
     <row r="44" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>50</v>
@@ -11470,7 +11554,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G44" s="9" t="b">
         <v>0</v>
@@ -11480,7 +11564,7 @@
         <v>10</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K44" t="s">
         <v>67</v>
@@ -11489,7 +11573,7 @@
         <v>5</v>
       </c>
       <c r="N44" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O44">
         <v>5</v>
@@ -11497,13 +11581,13 @@
     </row>
     <row r="45" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>50</v>
@@ -11512,7 +11596,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G45" s="9" t="b">
         <v>0</v>
@@ -11522,7 +11606,7 @@
         <v>10</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="K45" t="s">
         <v>67</v>
@@ -11531,7 +11615,7 @@
         <v>5</v>
       </c>
       <c r="N45" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O45">
         <v>5</v>
@@ -11539,13 +11623,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>50</v>
@@ -11554,7 +11638,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G46" s="9" t="b">
         <v>0</v>
@@ -11564,7 +11648,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="K46" t="s">
         <v>67</v>
@@ -11573,7 +11657,7 @@
         <v>5</v>
       </c>
       <c r="N46" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O46">
         <v>5</v>
@@ -11581,13 +11665,13 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>50</v>
@@ -11596,7 +11680,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G47" s="9" t="b">
         <v>0</v>
@@ -11606,7 +11690,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="K47" t="s">
         <v>67</v>
@@ -11615,7 +11699,7 @@
         <v>5</v>
       </c>
       <c r="N47" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O47">
         <v>5</v>
@@ -11623,13 +11707,13 @@
     </row>
     <row r="48" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>50</v>
@@ -11638,7 +11722,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G48" s="9" t="b">
         <v>0</v>
@@ -11648,7 +11732,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="K48" t="s">
         <v>67</v>
@@ -11657,7 +11741,7 @@
         <v>5</v>
       </c>
       <c r="N48" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O48">
         <v>5</v>
@@ -11665,22 +11749,22 @@
     </row>
     <row r="49" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="G49" s="9" t="b">
         <v>0</v>
@@ -11690,7 +11774,7 @@
         <v>5</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="K49" t="s">
         <v>67</v>
@@ -11699,7 +11783,7 @@
         <v>20</v>
       </c>
       <c r="N49" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="O49">
         <v>5</v>
@@ -11707,13 +11791,13 @@
     </row>
     <row r="50" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>50</v>
@@ -11722,19 +11806,19 @@
         <v>152</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G50" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I50" s="9">
         <v>10</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="K50" t="s">
         <v>67</v>
@@ -11743,7 +11827,7 @@
         <v>5</v>
       </c>
       <c r="N50" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="O50">
         <v>5</v>
@@ -11751,13 +11835,13 @@
     </row>
     <row r="51" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>50</v>
@@ -11766,19 +11850,17 @@
         <v>152</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G51" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>161</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H51" s="9"/>
       <c r="I51" s="9">
         <v>10</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="K51" t="s">
         <v>67</v>
@@ -11787,7 +11869,7 @@
         <v>5</v>
       </c>
       <c r="N51" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="O51">
         <v>5</v>
@@ -11795,13 +11877,13 @@
     </row>
     <row r="52" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>451</v>
+        <v>262</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>50</v>
@@ -11816,13 +11898,13 @@
         <v>1</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>452</v>
+        <v>161</v>
       </c>
       <c r="I52" s="9">
         <v>10</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="K52" t="s">
         <v>67</v>
@@ -11831,7 +11913,7 @@
         <v>5</v>
       </c>
       <c r="N52" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="O52">
         <v>5</v>
@@ -11839,13 +11921,13 @@
     </row>
     <row r="53" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>50</v>
@@ -11854,7 +11936,7 @@
         <v>152</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G53" s="9" t="b">
         <v>1</v>
@@ -11866,7 +11948,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>453</v>
+        <v>324</v>
       </c>
       <c r="K53" t="s">
         <v>67</v>
@@ -11875,7 +11957,7 @@
         <v>5</v>
       </c>
       <c r="N53" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="O53">
         <v>5</v>
@@ -11883,85 +11965,83 @@
     </row>
     <row r="54" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>233</v>
+        <v>549</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>233</v>
+        <v>549</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>224</v>
+        <v>551</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>50</v>
+        <v>552</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>152</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>196</v>
+        <v>547</v>
       </c>
       <c r="G54" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>163</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H54" s="9"/>
       <c r="I54" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>325</v>
+        <v>548</v>
       </c>
       <c r="K54" t="s">
         <v>67</v>
       </c>
       <c r="L54">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N54" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="O54">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
-        <v>554</v>
+        <v>617</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>554</v>
+        <v>617</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>556</v>
+        <v>223</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>557</v>
+        <v>50</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>552</v>
+      <c r="F55" s="17" t="s">
+        <v>616</v>
       </c>
       <c r="G55" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="9"/>
       <c r="I55" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>553</v>
+        <v>618</v>
       </c>
       <c r="K55" t="s">
         <v>67</v>
       </c>
       <c r="L55">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N55" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="O55">
         <v>5</v>
@@ -11969,13 +12049,13 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
-        <v>622</v>
+        <v>584</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>622</v>
+        <v>584</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>50</v>
@@ -11983,8 +12063,8 @@
       <c r="E56" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F56" s="17" t="s">
-        <v>621</v>
+      <c r="F56" t="s">
+        <v>583</v>
       </c>
       <c r="G56" s="9" t="b">
         <v>0</v>
@@ -11994,16 +12074,16 @@
         <v>10</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>623</v>
+        <v>585</v>
       </c>
       <c r="K56" t="s">
         <v>67</v>
       </c>
       <c r="L56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N56" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="O56">
         <v>5</v>
@@ -12017,15 +12097,15 @@
         <v>589</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="17" t="s">
         <v>588</v>
       </c>
       <c r="G57" s="9" t="b">
@@ -12045,7 +12125,7 @@
         <v>6</v>
       </c>
       <c r="N57" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="O57">
         <v>5</v>
@@ -12053,64 +12133,67 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>224</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="G58" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="K58" t="s">
         <v>67</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N58" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="O58">
         <v>5</v>
+      </c>
+      <c r="P58" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>604</v>
+        <v>647</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>604</v>
+        <v>647</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>603</v>
+        <v>646</v>
       </c>
       <c r="G59" s="9" t="b">
         <v>0</v>
@@ -12120,42 +12203,39 @@
         <v>7</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>605</v>
+        <v>648</v>
       </c>
       <c r="K59" t="s">
         <v>67</v>
       </c>
       <c r="L59">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N59" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="O59">
         <v>5</v>
-      </c>
-      <c r="P59" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G60" s="9" t="b">
         <v>0</v>
@@ -12165,7 +12245,7 @@
         <v>7</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K60" t="s">
         <v>67</v>
@@ -12174,7 +12254,7 @@
         <v>6</v>
       </c>
       <c r="N60" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="O60">
         <v>5</v>
@@ -12182,13 +12262,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>148</v>
@@ -12207,7 +12287,7 @@
         <v>7</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="K61" t="s">
         <v>67</v>
@@ -12216,7 +12296,7 @@
         <v>6</v>
       </c>
       <c r="N61" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="O61">
         <v>5</v>
@@ -12224,32 +12304,34 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F62" s="17" t="s">
         <v>665</v>
       </c>
       <c r="G62" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>667</v>
+      </c>
       <c r="I62" s="9">
         <v>7</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="K62" t="s">
         <v>67</v>
@@ -12258,7 +12340,7 @@
         <v>6</v>
       </c>
       <c r="N62" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
       <c r="O62">
         <v>5</v>
@@ -12266,34 +12348,34 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G63" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H63" s="9" t="s">
+      <c r="H63" t="s">
         <v>672</v>
       </c>
       <c r="I63" s="9">
         <v>7</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K63" t="s">
         <v>67</v>
@@ -12302,7 +12384,7 @@
         <v>6</v>
       </c>
       <c r="N63" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="O63">
         <v>5</v>
@@ -12310,34 +12392,31 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G64" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9">
         <v>7</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="K64" t="s">
         <v>67</v>
@@ -12346,7 +12425,7 @@
         <v>6</v>
       </c>
       <c r="N64" t="s">
-        <v>907</v>
+        <v>912</v>
       </c>
       <c r="O64">
         <v>5</v>
@@ -12354,31 +12433,34 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>679</v>
+        <v>743</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>679</v>
+        <v>743</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>148</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F65" s="17" t="s">
-        <v>678</v>
+        <v>11</v>
+      </c>
+      <c r="F65" t="s">
+        <v>742</v>
       </c>
       <c r="G65" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>744</v>
       </c>
       <c r="I65" s="9">
         <v>7</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>680</v>
+        <v>745</v>
       </c>
       <c r="K65" t="s">
         <v>67</v>
@@ -12387,7 +12469,7 @@
         <v>6</v>
       </c>
       <c r="N65" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="O65">
         <v>5</v>
@@ -12401,7 +12483,7 @@
         <v>748</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>148</v>
@@ -12410,7 +12492,7 @@
         <v>11</v>
       </c>
       <c r="F66" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="G66" s="9" t="b">
         <v>1</v>
@@ -12431,7 +12513,7 @@
         <v>6</v>
       </c>
       <c r="N66" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="O66">
         <v>5</v>
@@ -12439,13 +12521,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>148</v>
@@ -12453,20 +12535,17 @@
       <c r="E67" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F67" t="s">
-        <v>747</v>
+      <c r="F67" s="17" t="s">
+        <v>765</v>
       </c>
       <c r="G67" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>754</v>
+        <v>0</v>
       </c>
       <c r="I67" s="9">
         <v>7</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="K67" t="s">
         <v>67</v>
@@ -12475,7 +12554,7 @@
         <v>6</v>
       </c>
       <c r="N67" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="O67">
         <v>5</v>
@@ -12489,7 +12568,7 @@
         <v>769</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>148</v>
@@ -12498,7 +12577,7 @@
         <v>11</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="G68" s="9" t="b">
         <v>0</v>
@@ -12507,7 +12586,7 @@
         <v>7</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K68" t="s">
         <v>67</v>
@@ -12516,7 +12595,7 @@
         <v>6</v>
       </c>
       <c r="N68" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="O68">
         <v>5</v>
@@ -12524,40 +12603,40 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="G69" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I69" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="K69" t="s">
         <v>67</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N69" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="O69">
         <v>5</v>
@@ -12571,7 +12650,7 @@
         <v>784</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>50</v>
@@ -12598,48 +12677,48 @@
         <v>5</v>
       </c>
       <c r="N70" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O70">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
-        <v>789</v>
+        <v>831</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>789</v>
+        <v>831</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>224</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>790</v>
+        <v>830</v>
       </c>
       <c r="G71" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I71" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>791</v>
+        <v>832</v>
       </c>
       <c r="K71" t="s">
         <v>67</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N71" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="O71">
         <v>5</v>
@@ -12653,7 +12732,7 @@
         <v>836</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>148</v>
@@ -12661,11 +12740,14 @@
       <c r="E72" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G72" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
         <v>835</v>
-      </c>
-      <c r="G72" s="9" t="b">
-        <v>0</v>
       </c>
       <c r="I72" s="9">
         <v>7</v>
@@ -12680,7 +12762,7 @@
         <v>6</v>
       </c>
       <c r="N72" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="O72">
         <v>5</v>
@@ -12688,13 +12770,13 @@
     </row>
     <row r="73" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
-        <v>841</v>
+        <v>926</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>841</v>
+        <v>926</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>148</v>
@@ -12709,13 +12791,13 @@
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>840</v>
+        <v>927</v>
       </c>
       <c r="I73" s="9">
         <v>7</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="K73" t="s">
         <v>67</v>
@@ -12724,39 +12806,36 @@
         <v>6</v>
       </c>
       <c r="N73" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="O73">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
-        <v>931</v>
+        <v>841</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>931</v>
+        <v>841</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>157</v>
+        <v>152</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>840</v>
       </c>
       <c r="G74" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" t="s">
-        <v>932</v>
+        <v>0</v>
       </c>
       <c r="I74" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J74" s="9" t="s">
         <v>842</v>
@@ -12765,10 +12844,10 @@
         <v>67</v>
       </c>
       <c r="L74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N74" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="O74">
         <v>5</v>
@@ -12782,13 +12861,13 @@
         <v>846</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>845</v>
@@ -12809,7 +12888,7 @@
         <v>5</v>
       </c>
       <c r="N75" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="O75">
         <v>5</v>
@@ -12817,19 +12896,19 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>850</v>
@@ -12841,7 +12920,7 @@
         <v>10</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="K76" t="s">
         <v>67</v>
@@ -12850,7 +12929,7 @@
         <v>5</v>
       </c>
       <c r="N76" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
       <c r="O76">
         <v>5</v>
@@ -12858,13 +12937,13 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>50</v>
@@ -12873,7 +12952,7 @@
         <v>11</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="G77" s="9" t="b">
         <v>0</v>
@@ -12882,7 +12961,7 @@
         <v>10</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="K77" t="s">
         <v>67</v>
@@ -12891,7 +12970,7 @@
         <v>5</v>
       </c>
       <c r="N77" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="O77">
         <v>5</v>
@@ -12905,16 +12984,16 @@
         <v>858</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D78" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="G78" s="9" t="b">
         <v>0</v>
@@ -12923,7 +13002,7 @@
         <v>10</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="K78" t="s">
         <v>67</v>
@@ -12932,7 +13011,7 @@
         <v>5</v>
       </c>
       <c r="N78" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="O78">
         <v>5</v>
@@ -12940,37 +13019,40 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C79" s="9" t="s">
         <v>224</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="G79" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I79" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="K79" t="s">
         <v>67</v>
       </c>
       <c r="L79">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="M79">
+        <v>14</v>
       </c>
       <c r="N79" t="s">
         <v>913</v>
@@ -12981,43 +13063,43 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>225</v>
+        <v>551</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>148</v>
+        <v>552</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G80" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>874</v>
       </c>
       <c r="I80" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="K80" t="s">
         <v>67</v>
       </c>
       <c r="L80">
-        <v>7</v>
-      </c>
-      <c r="M80">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N80" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="O80">
         <v>5</v>
@@ -13031,10 +13113,10 @@
         <v>878</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>556</v>
+        <v>224</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>557</v>
+        <v>148</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>11</v>
@@ -13045,23 +13127,23 @@
       <c r="G81" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="H81" t="s">
+        <v>876</v>
+      </c>
+      <c r="I81" s="9">
+        <v>7</v>
+      </c>
+      <c r="J81" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="I81" s="9">
-        <v>5</v>
-      </c>
-      <c r="J81" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="K81" t="s">
         <v>67</v>
       </c>
       <c r="L81">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N81" t="s">
-        <v>919</v>
+        <v>902</v>
       </c>
       <c r="O81">
         <v>5</v>
@@ -13069,13 +13151,13 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>883</v>
+        <v>929</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>883</v>
+        <v>929</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>148</v>
@@ -13084,19 +13166,19 @@
         <v>11</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G82" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>881</v>
+        <v>930</v>
       </c>
       <c r="I82" s="9">
         <v>7</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="K82" t="s">
         <v>67</v>
@@ -13105,7 +13187,7 @@
         <v>6</v>
       </c>
       <c r="N82" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="O82">
         <v>5</v>
@@ -13113,43 +13195,40 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>934</v>
+        <v>884</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>934</v>
+        <v>884</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="G83" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H83" t="s">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="I83" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="K83" t="s">
         <v>67</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N83" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="O83">
         <v>5</v>
@@ -13157,40 +13236,43 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>224</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F84" s="17" t="s">
+        <v>887</v>
+      </c>
+      <c r="G84" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>889</v>
+      </c>
+      <c r="I84" s="9">
+        <v>7</v>
+      </c>
+      <c r="J84" s="9" t="s">
         <v>890</v>
-      </c>
-      <c r="G84" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" s="9">
-        <v>10</v>
-      </c>
-      <c r="J84" s="9" t="s">
-        <v>891</v>
       </c>
       <c r="K84" t="s">
         <v>67</v>
       </c>
       <c r="L84">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N84" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="O84">
         <v>5</v>
@@ -13198,13 +13280,13 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>148</v>
@@ -13213,19 +13295,19 @@
         <v>11</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="G85" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="I85" s="9">
         <v>7</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="K85" t="s">
         <v>67</v>
@@ -13234,7 +13316,7 @@
         <v>7</v>
       </c>
       <c r="N85" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="O85">
         <v>5</v>
@@ -13242,13 +13324,13 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>896</v>
+        <v>921</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>896</v>
+        <v>921</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>148</v>
@@ -13257,19 +13339,16 @@
         <v>11</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>892</v>
+        <v>922</v>
       </c>
       <c r="G86" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>897</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9">
         <v>7</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>895</v>
+        <v>923</v>
       </c>
       <c r="K86" t="s">
         <v>67</v>
@@ -13278,7 +13357,7 @@
         <v>7</v>
       </c>
       <c r="N86" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="O86">
         <v>5</v>
@@ -13286,40 +13365,43 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>926</v>
+        <v>944</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>225</v>
+        <v>551</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>148</v>
+        <v>552</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F87" s="17" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="G87" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>946</v>
       </c>
       <c r="I87" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>928</v>
+        <v>947</v>
       </c>
       <c r="K87" t="s">
         <v>67</v>
       </c>
       <c r="L87">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N87" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="O87">
         <v>5</v>
@@ -13327,34 +13409,34 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F88" s="17" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="G88" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="I88" s="9">
         <v>5</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="K88" t="s">
         <v>67</v>
@@ -13363,53 +13445,9 @@
         <v>20</v>
       </c>
       <c r="N88" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="O88">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A89" s="9" t="s">
-        <v>953</v>
-      </c>
-      <c r="B89" s="9" t="s">
-        <v>953</v>
-      </c>
-      <c r="C89" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="17" t="s">
-        <v>950</v>
-      </c>
-      <c r="G89" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>954</v>
-      </c>
-      <c r="I89" s="9">
-        <v>5</v>
-      </c>
-      <c r="J89" s="9" t="s">
-        <v>955</v>
-      </c>
-      <c r="K89" t="s">
-        <v>67</v>
-      </c>
-      <c r="L89">
-        <v>20</v>
-      </c>
-      <c r="N89" t="s">
-        <v>912</v>
-      </c>
-      <c r="O89">
         <v>5</v>
       </c>
     </row>
@@ -13501,7 +13539,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>19</v>
@@ -13545,7 +13583,7 @@
         <v>29</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>72</v>
@@ -13557,31 +13595,31 @@
         <v>36</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>65</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="L3" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>694</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>698</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>699</v>
-      </c>
       <c r="O3" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -13592,7 +13630,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
@@ -13607,16 +13645,16 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="J4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K4" t="s">
+        <v>685</v>
+      </c>
+      <c r="L4" t="s">
         <v>690</v>
-      </c>
-      <c r="L4" t="s">
-        <v>695</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -13636,7 +13674,7 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
@@ -13651,16 +13689,16 @@
         <v>2.5</v>
       </c>
       <c r="I5" t="s">
+        <v>421</v>
+      </c>
+      <c r="J5" t="s">
         <v>424</v>
       </c>
-      <c r="J5" t="s">
-        <v>427</v>
-      </c>
       <c r="K5" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="L5" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -13695,16 +13733,16 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K6" t="s">
+        <v>685</v>
+      </c>
+      <c r="L6" t="s">
         <v>690</v>
-      </c>
-      <c r="L6" t="s">
-        <v>695</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -13742,16 +13780,16 @@
         <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K7" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="L7" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -13765,13 +13803,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -13786,16 +13824,16 @@
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="J8" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="K8" t="s">
+        <v>685</v>
+      </c>
+      <c r="L8" t="s">
         <v>690</v>
-      </c>
-      <c r="L8" t="s">
-        <v>695</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -13809,13 +13847,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D9" t="s">
         <v>50</v>
@@ -13830,16 +13868,16 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="J9" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="K9" t="s">
+        <v>685</v>
+      </c>
+      <c r="L9" t="s">
         <v>690</v>
-      </c>
-      <c r="L9" t="s">
-        <v>695</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -13853,13 +13891,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -13874,16 +13912,16 @@
         <v>3</v>
       </c>
       <c r="I10" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="J10" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="K10" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="L10" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -13897,13 +13935,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -13918,16 +13956,16 @@
         <v>3</v>
       </c>
       <c r="I11" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="J11" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="K11" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="L11" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -13941,13 +13979,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -13962,16 +14000,16 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="J12" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="K12" t="s">
+        <v>685</v>
+      </c>
+      <c r="L12" t="s">
         <v>690</v>
-      </c>
-      <c r="L12" t="s">
-        <v>695</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -13985,13 +14023,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="D13" t="s">
         <v>148</v>
@@ -14006,16 +14044,16 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="J13" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="K13" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="L13" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="M13">
         <v>3</v>
@@ -14029,13 +14067,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="D14" t="s">
         <v>148</v>
@@ -14050,16 +14088,16 @@
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="J14" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="K14" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="L14" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="M14">
         <v>3</v>
@@ -14073,13 +14111,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="D15" t="s">
         <v>148</v>
@@ -14094,16 +14132,16 @@
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="J15" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K15" t="s">
+        <v>685</v>
+      </c>
+      <c r="L15" t="s">
         <v>690</v>
-      </c>
-      <c r="L15" t="s">
-        <v>695</v>
       </c>
       <c r="M15">
         <v>3</v>
@@ -14220,7 +14258,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -14232,25 +14270,25 @@
         <v>42</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="K3" s="6" t="s">
         <v>101</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -15052,7 +15090,7 @@
         <v>24</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>9</v>
@@ -15066,7 +15104,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
@@ -15074,30 +15112,30 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B5" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -15142,18 +15180,18 @@
         <v>19</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>65</v>
@@ -15226,7 +15264,7 @@
         <v>43</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>24</v>
@@ -15249,7 +15287,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -15266,7 +15304,7 @@
         <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -15318,10 +15356,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
@@ -15335,10 +15373,10 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -15416,10 +15454,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>80</v>
@@ -15428,13 +15466,13 @@
         <v>4</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>95</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -15454,10 +15492,10 @@
         <v>147</v>
       </c>
       <c r="F4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -15480,10 +15518,10 @@
         <v>149</v>
       </c>
       <c r="F5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -15491,25 +15529,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B6" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C6">
         <v>600</v>
       </c>
       <c r="D6" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E6" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="F6" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="G6" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="H6">
         <v>1</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A47EF9D-9139-4AAB-8082-1B6455561D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADCF035-4588-4478-8679-65DB0AF4C206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="2" activeTab="10" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="17" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="LanguageData" sheetId="18" r:id="rId15"/>
     <sheet name="UnlockData" sheetId="19" r:id="rId16"/>
     <sheet name="GameConfig" sheetId="20" r:id="rId17"/>
+    <sheet name="ContentsGuide" sheetId="21" r:id="rId18"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="962">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="988">
   <si>
     <t>ALL</t>
   </si>
@@ -3686,7 +3687,114 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>열심히 농사 마무리하고 왔다네요.</t>
+    <t>[짝꿍슬롯]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짝꿍 슬롯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[짝꿍슬롯정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>배치하기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[배치하기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[짝꿍안내]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MateSlotLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짝꿍 비우기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[짝꿍비우기]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짝꿍 달팽이로 배치된 달팽이입니다.
+메인 달팽이로 옮길까요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[짝꿍배치변경]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}살 이상의 달팽이를 짝꿍 슬롯에 배치할 수 있습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}살 이상의 달팽이가 없어요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확의 계절이 왔습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainTitleId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubTitleId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짝꿍 달팽이란?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[짝꿍달팽이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>짝꿍 달팽이 자리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[짝꿍달팽이자리]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[짝꿍달팽이자리정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 달팽이와 짝을 만들어줄 수 있는 자리입니다.
+- 짝꿍 달팽이는 특정 나이 이상의 달팽이만 배치할 수 있습니다.
+- 짝꿍 달팽이는 옮기거나 만질수는 있지만, 성장하거나 밥을 먹을 수는 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알발견]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[알발견정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>알 발견?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 짝꿍 달팽이와 내 달팽이가 놀다보면, 둘 사이의 알이 발견되기도 한답니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroupId</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3874,7 +3982,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3928,6 +4036,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7164,7 +7281,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:C285"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -9347,7 +9464,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>958</v>
       </c>
@@ -9355,12 +9472,101 @@
         <v>960</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>959</v>
       </c>
       <c r="B274" s="8" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="9" t="s">
         <v>961</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="9" t="s">
+        <v>963</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="9" t="s">
+        <v>965</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="9" t="s">
+        <v>966</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" ht="33" x14ac:dyDescent="0.3">
+      <c r="A280" s="9" t="s">
+        <v>971</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="C281" s="8"/>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" s="9" t="s">
+        <v>980</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A283" s="9" t="s">
+        <v>981</v>
+      </c>
+      <c r="B283" s="18" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B284" s="8" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="9" t="s">
+        <v>984</v>
+      </c>
+      <c r="B285" s="19" t="s">
+        <v>986</v>
       </c>
     </row>
   </sheetData>
@@ -9450,7 +9656,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB314148-9221-49F7-832E-5D289BE3A143}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
@@ -9459,11 +9665,11 @@
     <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
     <col min="5" max="8" width="14.625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="11" width="14.625" customWidth="1"/>
-    <col min="12" max="12" width="67.625" customWidth="1"/>
+    <col min="10" max="12" width="14.625" customWidth="1"/>
+    <col min="13" max="13" width="67.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -9497,11 +9703,14 @@
       <c r="K1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -9535,11 +9744,14 @@
       <c r="K2" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>450</v>
       </c>
@@ -9573,11 +9785,14 @@
       <c r="K3" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5</v>
       </c>
@@ -9611,6 +9826,97 @@
       <c r="K4">
         <v>5</v>
       </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56E74C4-84B7-4A19-9C4F-34E06C7B143D}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.625" customWidth="1"/>
+    <col min="2" max="2" width="25.375" customWidth="1"/>
+    <col min="3" max="3" width="24.875" customWidth="1"/>
+    <col min="4" max="4" width="61.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>976</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>978</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>980</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>978</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -15060,15 +15366,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE7402E-9381-444B-A1AD-921D46BBAC61}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="23.875" customWidth="1"/>
+    <col min="2" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="23.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -15078,11 +15384,14 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -15092,11 +15401,14 @@
       <c r="C2" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
@@ -15106,11 +15418,14 @@
       <c r="C3" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>255</v>
       </c>
@@ -15120,11 +15435,14 @@
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>757</v>
       </c>
@@ -15134,7 +15452,10 @@
       <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
         <v>759</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADCF035-4588-4478-8679-65DB0AF4C206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCEB8F5-3826-4522-BF6E-CD86A3A247B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="17" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="16" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -3982,7 +3982,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4041,9 +4041,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9803,7 +9800,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -9838,7 +9835,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56E74C4-84B7-4A19-9C4F-34E06C7B143D}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" customWidth="1"/>
@@ -9914,9 +9911,6 @@
       <c r="D5" s="9" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCEB8F5-3826-4522-BF6E-CD86A3A247B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAD289F-72C6-43A2-BB16-D4A9FFCB41EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="3" activeTab="16" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="14" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="1073">
   <si>
     <t>ALL</t>
   </si>
@@ -1112,19 +1112,7 @@
     <t>당근이 너무 좋아서 집으로 삼기로 했다.</t>
   </si>
   <si>
-    <t>연두색의 몸.</t>
-  </si>
-  <si>
-    <t>분홍색의 몸.</t>
-  </si>
-  <si>
     <t>갈색의 몸.</t>
-  </si>
-  <si>
-    <t>느려졌지만, 행복해보인다.</t>
-  </si>
-  <si>
-    <t>주인을 안아주고 싶어서 손이 돋아났다.</t>
   </si>
   <si>
     <t>웃는 달팽이의 눈.</t>
@@ -3660,14 +3648,6 @@
   </si>
   <si>
     <t>얼음 몸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>푸른색의 아름다운 몸입니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>바다가 생각나는 멋진 몸입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3795,6 +3775,362 @@
   </si>
   <si>
     <t>GroupId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[확률]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>확률</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[등장확률]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0} 등장 확률</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[얼굴]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼굴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[달팽이도감]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>달팽이 도감</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바다가 생각나는 멋진 몸입니다.</t>
+  </si>
+  <si>
+    <t>바다토끼 몸(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하늘 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_몸02]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>푸른색의 하늘이 생각나는 몸입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>느려졌지만, 행복해보이네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인을 안아주고 싶어서 손이 돋아났습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_포션껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_포션껍질01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>posionshell01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_포션껍질02]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>posionshell02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_포션껍질02정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물약 껍질(HP)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물약 껍질(MP)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜인지 보기만해도 Hp가 차는 기분입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜인지 보기만해도 Mp가 차는 기분입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareeyes03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_파란눈]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_파란눈정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>맑은 눈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>맑고 동그란 눈입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_뿔더듬이]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rarefeeler02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_뿔더듬이정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뿔 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>나뭇가지같이 생긴 뿔이 돋아났습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_우파루파몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody03_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_우파루파몸01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_우파루파몸02]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody03_c02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수속성 몸(분홍)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수속성 몸(파랑)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물을 너무 좋아해서 일까요? 물에서 숨을 쉴 수 있게 되었습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[외형도감]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>외형 도감</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[외형도감안내]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수집한 외형을 확인할 수 있습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicfeeler02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암더듬이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암더듬이02]</t>
+  </si>
+  <si>
+    <t>epicfeeler02_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicfeeler02_c02</t>
+  </si>
+  <si>
+    <t>[에픽_용암더듬이01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암더듬이02정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>용암 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼음 더듬이</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뜨거운 음식을 많이 먹다보니 변해있었습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차가운 음식을 많이 먹다보니 변해있었습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicshell03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암껍질02]</t>
+  </si>
+  <si>
+    <t>epicshell03_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicshell03_c02</t>
+  </si>
+  <si>
+    <t>[에픽_용암껍질01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용암껍질02정보]</t>
+  </si>
+  <si>
+    <t>rareshell04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_꼬깔껍질]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_꼬깔껍질정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>라바콘 껍질</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공사장 근처에서 기념품을 가져왔습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_바나나몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_바나나몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바나나 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>바나나만 먹던 달팽이는… 몸이 바나나로 변했습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commoneyes07</t>
+  </si>
+  <si>
+    <t>commoneyes08</t>
+  </si>
+  <si>
+    <t>하품하는 얼굴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>후아암… 꽤나 지루해보이네요.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody01_c08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_핑크몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_핑크몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분홍색 점박이 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>등에 분홍색의 작은 점박이가 있는 몸입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4731,7 +5067,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>230</v>
@@ -4810,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F8" s="11">
         <v>100</v>
@@ -4830,7 +5166,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F9" s="11">
         <v>200</v>
@@ -4853,7 +5189,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F10" s="11">
         <v>400</v>
@@ -4876,7 +5212,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F11" s="11">
         <v>300</v>
@@ -4916,10 +5252,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>76</v>
@@ -4936,10 +5272,10 @@
         <v>2</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>77</v>
@@ -4956,10 +5292,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>78</v>
@@ -4976,10 +5312,10 @@
         <v>4</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>79</v>
@@ -5124,7 +5460,7 @@
         <v>110</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -5135,7 +5471,7 @@
         <v>251</v>
       </c>
       <c r="H25" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -5143,7 +5479,7 @@
         <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -5154,49 +5490,49 @@
         <v>255</v>
       </c>
       <c r="H26" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B27" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>367</v>
+      </c>
+      <c r="B28" t="s">
         <v>371</v>
-      </c>
-      <c r="B28" t="s">
-        <v>375</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B29" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -5371,87 +5707,87 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B7" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C7" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D7" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E7" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B8" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C8" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="D8" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E8" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B9" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C9" t="s">
         <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E9" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B10" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C10" t="s">
         <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="E10" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B11" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="C11" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D11" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="E11" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
     </row>
   </sheetData>
@@ -5572,7 +5908,7 @@
         <v>64</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>98</v>
@@ -5595,7 +5931,7 @@
         <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
@@ -5633,7 +5969,7 @@
         <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C5" t="s">
         <v>50</v>
@@ -5824,7 +6160,7 @@
         <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C10" t="s">
         <v>73</v>
@@ -5863,7 +6199,7 @@
         <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C11" t="s">
         <v>50</v>
@@ -5901,7 +6237,7 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
@@ -5940,7 +6276,7 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C13" t="s">
         <v>73</v>
@@ -5978,7 +6314,7 @@
         <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C14" t="s">
         <v>73</v>
@@ -6016,7 +6352,7 @@
         <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C15" t="s">
         <v>73</v>
@@ -6132,10 +6468,10 @@
         <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C18" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -6318,7 +6654,7 @@
         <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
@@ -6357,7 +6693,7 @@
         <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C24" t="s">
         <v>50</v>
@@ -6396,7 +6732,7 @@
         <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="C25" t="s">
         <v>50</v>
@@ -7065,42 +7401,42 @@
         <v>201</v>
       </c>
       <c r="M3" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>542</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>543</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B4" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C4" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="M4" t="s">
         <v>67</v>
@@ -7117,25 +7453,25 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B5" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C5" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="M5" t="s">
         <v>67</v>
@@ -7152,28 +7488,28 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B6" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C6" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D6" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="M6" t="s">
         <v>67</v>
@@ -7190,25 +7526,25 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B7" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C7" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D7" t="s">
         <v>148</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="M7" t="s">
         <v>67</v>
@@ -7225,28 +7561,28 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B8" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C8" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="I8" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>674</v>
-      </c>
       <c r="K8" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="M8" t="s">
         <v>67</v>
@@ -7278,7 +7614,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C317"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -7351,34 +7687,34 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B9" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B10" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B11" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -7394,7 +7730,7 @@
         <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -7410,7 +7746,7 @@
         <v>275</v>
       </c>
       <c r="B16" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -7418,7 +7754,7 @@
         <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -7442,7 +7778,7 @@
         <v>279</v>
       </c>
       <c r="B20" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -7450,7 +7786,7 @@
         <v>280</v>
       </c>
       <c r="B21" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -7458,7 +7794,7 @@
         <v>281</v>
       </c>
       <c r="B22" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -7466,7 +7802,7 @@
         <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -7474,7 +7810,7 @@
         <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -7482,12 +7818,12 @@
         <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B26" t="s">
         <v>282</v>
@@ -7495,7 +7831,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B27" t="s">
         <v>283</v>
@@ -7503,23 +7839,23 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s">
         <v>284</v>
@@ -7527,15 +7863,15 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s">
         <v>285</v>
@@ -7543,7 +7879,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s">
         <v>286</v>
@@ -7551,7 +7887,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s">
         <v>287</v>
@@ -7559,47 +7895,47 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s">
-        <v>288</v>
+        <v>996</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s">
-        <v>289</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s">
-        <v>291</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s">
-        <v>292</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s">
         <v>155</v>
@@ -7607,82 +7943,82 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B47" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -7690,7 +8026,7 @@
         <v>181</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -7698,7 +8034,7 @@
         <v>182</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -7706,7 +8042,7 @@
         <v>183</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -7714,7 +8050,7 @@
         <v>202</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -7722,7 +8058,7 @@
         <v>203</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -7730,7 +8066,7 @@
         <v>204</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -7738,7 +8074,7 @@
         <v>205</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -7746,15 +8082,15 @@
         <v>207</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -7762,7 +8098,7 @@
         <v>208</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -7770,7 +8106,7 @@
         <v>209</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -7778,7 +8114,7 @@
         <v>210</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -7786,7 +8122,7 @@
         <v>211</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -7794,7 +8130,7 @@
         <v>212</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -7802,7 +8138,7 @@
         <v>213</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -7810,7 +8146,7 @@
         <v>184</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -7818,15 +8154,15 @@
         <v>159</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>956</v>
+        <v>997</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>228</v>
+        <v>999</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>955</v>
+        <v>998</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -7834,7 +8170,7 @@
         <v>229</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -7842,7 +8178,7 @@
         <v>234</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -7850,15 +8186,15 @@
         <v>256</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -7866,7 +8202,7 @@
         <v>160</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -7874,7 +8210,7 @@
         <v>216</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -7882,7 +8218,7 @@
         <v>217</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -7890,7 +8226,7 @@
         <v>218</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -7898,7 +8234,7 @@
         <v>166</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -7906,7 +8242,7 @@
         <v>198</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -7914,7 +8250,7 @@
         <v>199</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -7922,7 +8258,7 @@
         <v>232</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -7930,7 +8266,7 @@
         <v>233</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -7938,7 +8274,7 @@
         <v>262</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -7946,7 +8282,7 @@
         <v>263</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -7954,28 +8290,28 @@
         <v>185</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B87" s="9" t="s">
         <v>186</v>
@@ -7983,1587 +8319,1843 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B88" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B89" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B90" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B91" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B92" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B93" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B94" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B95" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B97" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B98" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B99" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B100" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B101" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B102" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B103" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>423</v>
+      </c>
+      <c r="B104" t="s">
         <v>427</v>
-      </c>
-      <c r="B104" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
+        <v>424</v>
+      </c>
+      <c r="B105" t="s">
         <v>428</v>
-      </c>
-      <c r="B105" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
+        <v>425</v>
+      </c>
+      <c r="B106" t="s">
         <v>429</v>
-      </c>
-      <c r="B106" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
+        <v>426</v>
+      </c>
+      <c r="B107" t="s">
         <v>430</v>
-      </c>
-      <c r="B107" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B108" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B109" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B110" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B111" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B112" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B113" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B114" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B115" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B116" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B117" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B118" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B119" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B120" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B122" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B124" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B126" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B128" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B130" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="B143" s="8" t="s">
         <v>578</v>
-      </c>
-      <c r="B143" s="8" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="33" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B179" s="8" t="s">
         <v>675</v>
-      </c>
-      <c r="B179" s="8" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B200" s="8" t="s">
         <v>743</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="9" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="B213" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="B213" s="8" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="9" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B234" s="8" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="9" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="9" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B251" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="B255" s="8" t="s">
         <v>879</v>
-      </c>
-      <c r="B255" s="8" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="9" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="9" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="9" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="9" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B264" s="8" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B266" s="8" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="9" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="9" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" s="9" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" s="9" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" s="9" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" s="9" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="33" x14ac:dyDescent="0.3">
       <c r="A280" s="9" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="B280" s="8" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" s="9" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="B281" s="8" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="C281" s="8"/>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" s="9" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A283" s="9" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="B283" s="18" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" s="9" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" s="9" t="s">
+        <v>978</v>
+      </c>
+      <c r="B285" s="19" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="9" t="s">
+        <v>982</v>
+      </c>
+      <c r="B286" s="8" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="9" t="s">
         <v>984</v>
       </c>
-      <c r="B285" s="19" t="s">
+      <c r="B287" s="8" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" s="9" t="s">
         <v>986</v>
+      </c>
+      <c r="B288" s="8" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A289" s="9" t="s">
+        <v>987</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A290" s="9" t="s">
+        <v>988</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A291" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A292" s="9" t="s">
+        <v>994</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A293" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A294" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A295" s="9" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A296" s="9" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A297" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A298" s="9" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A299" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A300" s="9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A301" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B301" s="8" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A302" s="9" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B302" s="8" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="A303" s="9" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A304" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A305" s="9" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B305" s="8" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A306" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B306" s="8" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A307" s="9" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B307" s="8" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A308" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B308" s="8" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A309" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A310" s="9" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B310" s="8" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A311" s="9" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B311" s="8" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A312" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B312" s="8" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A313" s="9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A314" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="B314" s="8" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A315" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="B315" s="8" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A316" s="9" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B316" s="8" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A317" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B317" s="8" t="s">
+        <v>1072</v>
       </c>
     </row>
   </sheetData>
@@ -9605,7 +10197,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -9622,10 +10214,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>63</v>
@@ -9636,10 +10228,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B4" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -9750,43 +10342,43 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="E3" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>456</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -9874,13 +10466,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>271</v>
@@ -9888,28 +10480,28 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
   </sheetData>
@@ -9920,7 +10512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -9939,9 +10531,15 @@
     <col min="14" max="14" width="14.625" customWidth="1"/>
     <col min="15" max="15" width="14.5" customWidth="1"/>
     <col min="16" max="16" width="18.875" customWidth="1"/>
+    <col min="17" max="17" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -9990,8 +10588,26 @@
       <c r="P1" s="5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -10029,19 +10645,37 @@
         <v>19</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>26</v>
       </c>
@@ -10079,19 +10713,37 @@
         <v>105</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>915</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>181</v>
       </c>
@@ -10120,7 +10772,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="K4" t="s">
         <v>67</v>
@@ -10129,13 +10781,19 @@
         <v>5</v>
       </c>
       <c r="N4" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q4" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>182</v>
       </c>
@@ -10164,7 +10822,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="K5" t="s">
         <v>67</v>
@@ -10173,13 +10831,19 @@
         <v>5</v>
       </c>
       <c r="N5" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q5" t="s">
+        <v>67</v>
+      </c>
+      <c r="R5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>183</v>
       </c>
@@ -10208,7 +10872,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="K6" t="s">
         <v>67</v>
@@ -10217,13 +10881,19 @@
         <v>5</v>
       </c>
       <c r="N6" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>202</v>
       </c>
@@ -10252,7 +10922,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K7" t="s">
         <v>67</v>
@@ -10261,13 +10931,19 @@
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>203</v>
       </c>
@@ -10296,7 +10972,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="K8" t="s">
         <v>67</v>
@@ -10305,13 +10981,19 @@
         <v>5</v>
       </c>
       <c r="N8" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q8" t="s">
+        <v>67</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>204</v>
       </c>
@@ -10340,7 +11022,7 @@
         <v>10</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K9" t="s">
         <v>67</v>
@@ -10349,13 +11031,19 @@
         <v>5</v>
       </c>
       <c r="N9" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q9" t="s">
+        <v>67</v>
+      </c>
+      <c r="R9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>205</v>
       </c>
@@ -10384,7 +11072,7 @@
         <v>10</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K10" t="s">
         <v>67</v>
@@ -10393,13 +11081,19 @@
         <v>5</v>
       </c>
       <c r="N10" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q10" t="s">
+        <v>67</v>
+      </c>
+      <c r="R10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>207</v>
       </c>
@@ -10428,7 +11122,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K11" t="s">
         <v>67</v>
@@ -10437,13 +11131,19 @@
         <v>5</v>
       </c>
       <c r="N11" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q11" t="s">
+        <v>67</v>
+      </c>
+      <c r="R11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>208</v>
       </c>
@@ -10472,7 +11172,7 @@
         <v>10</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="K12" t="s">
         <v>67</v>
@@ -10481,13 +11181,19 @@
         <v>5</v>
       </c>
       <c r="N12" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="O12">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>209</v>
       </c>
@@ -10516,7 +11222,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="K13" t="s">
         <v>67</v>
@@ -10525,13 +11231,19 @@
         <v>5</v>
       </c>
       <c r="N13" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="O13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q13" t="s">
+        <v>67</v>
+      </c>
+      <c r="R13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>210</v>
       </c>
@@ -10560,7 +11272,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="K14" t="s">
         <v>67</v>
@@ -10569,13 +11281,19 @@
         <v>5</v>
       </c>
       <c r="N14" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="O14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q14" t="s">
+        <v>67</v>
+      </c>
+      <c r="R14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>211</v>
       </c>
@@ -10604,7 +11322,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="K15" t="s">
         <v>67</v>
@@ -10613,13 +11331,19 @@
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="O15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q15" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>212</v>
       </c>
@@ -10648,7 +11372,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="K16" t="s">
         <v>67</v>
@@ -10657,13 +11381,19 @@
         <v>5</v>
       </c>
       <c r="N16" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="O16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q16" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>213</v>
       </c>
@@ -10692,7 +11422,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="K17" t="s">
         <v>67</v>
@@ -10701,18 +11431,24 @@
         <v>5</v>
       </c>
       <c r="N17" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="O17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q17" t="s">
+        <v>67</v>
+      </c>
+      <c r="R17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>223</v>
@@ -10730,13 +11466,13 @@
         <v>1</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="I18" s="9">
         <v>10</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="K18" t="s">
         <v>67</v>
@@ -10745,13 +11481,19 @@
         <v>5</v>
       </c>
       <c r="N18" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="O18">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q18" t="s">
+        <v>67</v>
+      </c>
+      <c r="R18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>184</v>
       </c>
@@ -10780,7 +11522,7 @@
         <v>7</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="K19" t="s">
         <v>67</v>
@@ -10789,18 +11531,24 @@
         <v>10</v>
       </c>
       <c r="N19" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="O19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q19" t="s">
+        <v>67</v>
+      </c>
+      <c r="R19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>224</v>
@@ -10812,19 +11560,19 @@
         <v>11</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="G20" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="I20" s="9">
         <v>7</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="K20" t="s">
         <v>67</v>
@@ -10833,42 +11581,48 @@
         <v>10</v>
       </c>
       <c r="N20" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="O20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q20" t="s">
+        <v>67</v>
+      </c>
+      <c r="R20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="G21" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="I21" s="9">
         <v>5</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="K21" t="s">
         <v>67</v>
@@ -10877,42 +11631,48 @@
         <v>20</v>
       </c>
       <c r="N21" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="O21">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q21" t="s">
+        <v>67</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="G22" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="I22" s="9">
         <v>5</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="K22" t="s">
         <v>67</v>
@@ -10921,18 +11681,24 @@
         <v>20</v>
       </c>
       <c r="N22" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="O22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q22" t="s">
+        <v>67</v>
+      </c>
+      <c r="R22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>223</v>
@@ -10944,7 +11710,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G23" s="9" t="b">
         <v>0</v>
@@ -10954,7 +11720,7 @@
         <v>10</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="K23" t="s">
         <v>67</v>
@@ -10963,18 +11729,24 @@
         <v>5</v>
       </c>
       <c r="N23" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>224</v>
@@ -10986,7 +11758,7 @@
         <v>11</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G24" s="9" t="b">
         <v>0</v>
@@ -10996,7 +11768,7 @@
         <v>7</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="K24" t="s">
         <v>67</v>
@@ -11005,13 +11777,19 @@
         <v>10</v>
       </c>
       <c r="N24" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="O24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q24" t="s">
+        <v>67</v>
+      </c>
+      <c r="R24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>159</v>
       </c>
@@ -11040,7 +11818,7 @@
         <v>10</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="K25" t="s">
         <v>67</v>
@@ -11049,13 +11827,19 @@
         <v>5</v>
       </c>
       <c r="N25" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q25" t="s">
+        <v>67</v>
+      </c>
+      <c r="R25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>228</v>
       </c>
@@ -11084,7 +11868,7 @@
         <v>10</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K26" t="s">
         <v>67</v>
@@ -11093,13 +11877,19 @@
         <v>5</v>
       </c>
       <c r="N26" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q26" t="s">
+        <v>67</v>
+      </c>
+      <c r="R26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>229</v>
       </c>
@@ -11128,7 +11918,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K27" t="s">
         <v>67</v>
@@ -11137,18 +11927,24 @@
         <v>5</v>
       </c>
       <c r="N27" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O27">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q27" t="s">
+        <v>67</v>
+      </c>
+      <c r="R27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>223</v>
@@ -11166,13 +11962,13 @@
         <v>1</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="I28" s="9">
         <v>10</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="K28" t="s">
         <v>67</v>
@@ -11181,18 +11977,24 @@
         <v>5</v>
       </c>
       <c r="N28" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O28">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q28" t="s">
+        <v>67</v>
+      </c>
+      <c r="R28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>223</v>
@@ -11210,13 +12012,13 @@
         <v>1</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I29" s="9">
         <v>10</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="K29" t="s">
         <v>67</v>
@@ -11225,18 +12027,24 @@
         <v>5</v>
       </c>
       <c r="N29" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O29">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q29" t="s">
+        <v>67</v>
+      </c>
+      <c r="R29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>223</v>
@@ -11254,13 +12062,13 @@
         <v>1</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I30" s="9">
         <v>10</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="K30" t="s">
         <v>67</v>
@@ -11269,18 +12077,24 @@
         <v>5</v>
       </c>
       <c r="N30" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O30">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q30" t="s">
+        <v>67</v>
+      </c>
+      <c r="R30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>223</v>
@@ -11298,13 +12112,13 @@
         <v>1</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="I31" s="9">
         <v>10</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="K31" t="s">
         <v>67</v>
@@ -11313,18 +12127,24 @@
         <v>5</v>
       </c>
       <c r="N31" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O31">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q31" t="s">
+        <v>67</v>
+      </c>
+      <c r="R31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>223</v>
@@ -11342,13 +12162,13 @@
         <v>1</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="I32" s="9">
         <v>10</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="K32" t="s">
         <v>67</v>
@@ -11357,18 +12177,24 @@
         <v>5</v>
       </c>
       <c r="N32" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O32">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q32" t="s">
+        <v>67</v>
+      </c>
+      <c r="R32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>234</v>
+        <v>1069</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>234</v>
+        <v>1069</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>223</v>
@@ -11380,19 +12206,19 @@
         <v>13</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="G33" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>236</v>
+        <v>1068</v>
       </c>
       <c r="I33" s="9">
         <v>10</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>315</v>
+        <v>1070</v>
       </c>
       <c r="K33" t="s">
         <v>67</v>
@@ -11401,18 +12227,24 @@
         <v>5</v>
       </c>
       <c r="N33" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O33">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q33" t="s">
+        <v>67</v>
+      </c>
+      <c r="R33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>605</v>
+        <v>234</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>605</v>
+        <v>234</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>223</v>
@@ -11424,17 +12256,19 @@
         <v>13</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>606</v>
+        <v>235</v>
       </c>
       <c r="G34" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>236</v>
+      </c>
       <c r="I34" s="9">
         <v>10</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>607</v>
+        <v>311</v>
       </c>
       <c r="K34" t="s">
         <v>67</v>
@@ -11443,18 +12277,24 @@
         <v>5</v>
       </c>
       <c r="N34" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O34">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q34" t="s">
+        <v>67</v>
+      </c>
+      <c r="R34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>223</v>
@@ -11466,19 +12306,17 @@
         <v>13</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>257</v>
+        <v>602</v>
       </c>
       <c r="G35" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>258</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H35" s="9"/>
       <c r="I35" s="9">
         <v>10</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>316</v>
+        <v>603</v>
       </c>
       <c r="K35" t="s">
         <v>67</v>
@@ -11487,18 +12325,24 @@
         <v>5</v>
       </c>
       <c r="N35" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O35">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q35" t="s">
+        <v>67</v>
+      </c>
+      <c r="R35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>408</v>
+        <v>256</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>408</v>
+        <v>256</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>223</v>
@@ -11516,13 +12360,13 @@
         <v>1</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>401</v>
+        <v>258</v>
       </c>
       <c r="I36" s="9">
         <v>10</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>409</v>
+        <v>312</v>
       </c>
       <c r="K36" t="s">
         <v>67</v>
@@ -11531,234 +12375,272 @@
         <v>5</v>
       </c>
       <c r="N36" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O36">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q36" t="s">
+        <v>67</v>
+      </c>
+      <c r="R36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>417</v>
+        <v>257</v>
       </c>
       <c r="G37" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="I37" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="K37" t="s">
         <v>67</v>
       </c>
       <c r="L37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N37" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="O37">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q37" t="s">
+        <v>67</v>
+      </c>
+      <c r="R37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>510</v>
+        <v>412</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>510</v>
+        <v>412</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>511</v>
+        <v>413</v>
       </c>
       <c r="G38" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>512</v>
+        <v>414</v>
       </c>
       <c r="I38" s="9">
+        <v>7</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="K38" t="s">
+        <v>67</v>
+      </c>
+      <c r="L38">
         <v>10</v>
       </c>
-      <c r="J38" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="K38" t="s">
-        <v>67</v>
-      </c>
-      <c r="L38">
-        <v>5</v>
-      </c>
       <c r="N38" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="O38">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q38" t="s">
+        <v>67</v>
+      </c>
+      <c r="R38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>551</v>
+        <v>223</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>552</v>
+        <v>50</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>556</v>
+        <v>507</v>
       </c>
       <c r="G39" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>508</v>
+      </c>
       <c r="I39" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>557</v>
+        <v>509</v>
       </c>
       <c r="K39" t="s">
         <v>67</v>
       </c>
       <c r="L39">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N39" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="O39">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q39" t="s">
+        <v>67</v>
+      </c>
+      <c r="R39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>630</v>
+        <v>551</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>630</v>
+        <v>551</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>224</v>
+        <v>547</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>148</v>
+        <v>548</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="17" t="s">
-        <v>628</v>
+      <c r="F40" s="10" t="s">
+        <v>552</v>
       </c>
       <c r="G40" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9">
+        <v>5</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="K40" t="s">
+        <v>67</v>
+      </c>
+      <c r="L40">
+        <v>20</v>
+      </c>
+      <c r="N40" t="s">
+        <v>903</v>
+      </c>
+      <c r="O40">
+        <v>5</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>67</v>
+      </c>
+      <c r="R40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="G41" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H40" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="I40" s="9">
+      <c r="H41" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="I41" s="9">
         <v>7</v>
       </c>
-      <c r="J40" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="K40" t="s">
-        <v>67</v>
-      </c>
-      <c r="L40">
+      <c r="J41" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="K41" t="s">
+        <v>67</v>
+      </c>
+      <c r="L41">
         <v>10</v>
       </c>
-      <c r="N40" t="s">
-        <v>906</v>
-      </c>
-      <c r="O40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="9" t="s">
+      <c r="N41" t="s">
+        <v>902</v>
+      </c>
+      <c r="O41">
+        <v>5</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>67</v>
+      </c>
+      <c r="R41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B42" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="G41" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9">
-        <v>10</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="K41" t="s">
-        <v>67</v>
-      </c>
-      <c r="L41">
-        <v>5</v>
-      </c>
-      <c r="N41" t="s">
-        <v>908</v>
-      </c>
-      <c r="O41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>216</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>223</v>
@@ -11770,7 +12652,7 @@
         <v>14</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
       <c r="G42" s="9" t="b">
         <v>0</v>
@@ -11780,7 +12662,7 @@
         <v>10</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="K42" t="s">
         <v>67</v>
@@ -11789,18 +12671,24 @@
         <v>5</v>
       </c>
       <c r="N42" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="O42">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q42" t="s">
+        <v>67</v>
+      </c>
+      <c r="R42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>223</v>
@@ -11812,7 +12700,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G43" s="9" t="b">
         <v>0</v>
@@ -11822,7 +12710,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="K43" t="s">
         <v>67</v>
@@ -11831,18 +12719,24 @@
         <v>5</v>
       </c>
       <c r="N43" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="O43">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q43" t="s">
+        <v>67</v>
+      </c>
+      <c r="R43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>223</v>
@@ -11854,7 +12748,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G44" s="9" t="b">
         <v>0</v>
@@ -11864,7 +12758,7 @@
         <v>10</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K44" t="s">
         <v>67</v>
@@ -11873,18 +12767,24 @@
         <v>5</v>
       </c>
       <c r="N44" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="O44">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q44" t="s">
+        <v>67</v>
+      </c>
+      <c r="R44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>410</v>
+        <v>218</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>410</v>
+        <v>218</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>223</v>
@@ -11896,7 +12796,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>411</v>
+        <v>221</v>
       </c>
       <c r="G45" s="9" t="b">
         <v>0</v>
@@ -11906,7 +12806,7 @@
         <v>10</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>412</v>
+        <v>316</v>
       </c>
       <c r="K45" t="s">
         <v>67</v>
@@ -11915,18 +12815,24 @@
         <v>5</v>
       </c>
       <c r="N45" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="O45">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q45" t="s">
+        <v>67</v>
+      </c>
+      <c r="R45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>594</v>
+        <v>406</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>223</v>
@@ -11937,8 +12843,8 @@
       <c r="E46" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F46" s="17" t="s">
-        <v>593</v>
+      <c r="F46" s="10" t="s">
+        <v>407</v>
       </c>
       <c r="G46" s="9" t="b">
         <v>0</v>
@@ -11948,7 +12854,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>595</v>
+        <v>408</v>
       </c>
       <c r="K46" t="s">
         <v>67</v>
@@ -11957,18 +12863,24 @@
         <v>5</v>
       </c>
       <c r="N46" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="O46">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q46" t="s">
+        <v>67</v>
+      </c>
+      <c r="R46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>223</v>
@@ -11980,7 +12892,7 @@
         <v>14</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G47" s="9" t="b">
         <v>0</v>
@@ -11990,7 +12902,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
       <c r="K47" t="s">
         <v>67</v>
@@ -11999,18 +12911,24 @@
         <v>5</v>
       </c>
       <c r="N47" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="O47">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q47" t="s">
+        <v>67</v>
+      </c>
+      <c r="R47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>223</v>
@@ -12022,7 +12940,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>593</v>
+        <v>1064</v>
       </c>
       <c r="G48" s="9" t="b">
         <v>0</v>
@@ -12032,7 +12950,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>652</v>
+        <v>611</v>
       </c>
       <c r="K48" t="s">
         <v>67</v>
@@ -12041,60 +12959,72 @@
         <v>5</v>
       </c>
       <c r="N48" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="O48">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q48" t="s">
+        <v>67</v>
+      </c>
+      <c r="R48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>550</v>
+        <v>647</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>550</v>
+        <v>647</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>551</v>
+        <v>223</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>552</v>
+        <v>50</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>553</v>
+      <c r="F49" s="17" t="s">
+        <v>1065</v>
       </c>
       <c r="G49" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>554</v>
+        <v>648</v>
       </c>
       <c r="K49" t="s">
         <v>67</v>
       </c>
       <c r="L49">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N49" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="O49">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q49" t="s">
+        <v>67</v>
+      </c>
+      <c r="R49">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>166</v>
+        <v>854</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>166</v>
+        <v>854</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>223</v>
@@ -12103,22 +13033,20 @@
         <v>50</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>167</v>
+        <v>14</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>855</v>
       </c>
       <c r="G50" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>194</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H50" s="9"/>
       <c r="I50" s="9">
         <v>10</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>523</v>
+        <v>856</v>
       </c>
       <c r="K50" t="s">
         <v>67</v>
@@ -12127,60 +13055,72 @@
         <v>5</v>
       </c>
       <c r="N50" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="O50">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q50" t="s">
+        <v>67</v>
+      </c>
+      <c r="R50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>447</v>
+        <v>546</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>447</v>
+        <v>546</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>223</v>
+        <v>547</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>50</v>
+        <v>548</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>196</v>
+        <v>549</v>
       </c>
       <c r="G51" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>449</v>
+        <v>550</v>
       </c>
       <c r="K51" t="s">
         <v>67</v>
       </c>
       <c r="L51">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N51" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O51">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q51" t="s">
+        <v>67</v>
+      </c>
+      <c r="R51">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>262</v>
+        <v>166</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>262</v>
+        <v>166</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>223</v>
@@ -12192,19 +13132,19 @@
         <v>152</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="G52" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="I52" s="9">
         <v>10</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>448</v>
+        <v>519</v>
       </c>
       <c r="K52" t="s">
         <v>67</v>
@@ -12213,18 +13153,24 @@
         <v>5</v>
       </c>
       <c r="N52" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="O52">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q52" t="s">
+        <v>67</v>
+      </c>
+      <c r="R52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>232</v>
+        <v>443</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>232</v>
+        <v>443</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>223</v>
@@ -12236,19 +13182,17 @@
         <v>152</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G53" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>162</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H53" s="9"/>
       <c r="I53" s="9">
         <v>10</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="K53" t="s">
         <v>67</v>
@@ -12257,60 +13201,74 @@
         <v>5</v>
       </c>
       <c r="N53" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="O53">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q53" t="s">
+        <v>67</v>
+      </c>
+      <c r="R53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>549</v>
+        <v>262</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>549</v>
+        <v>262</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>551</v>
+        <v>223</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>552</v>
+        <v>50</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>152</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>547</v>
+        <v>197</v>
       </c>
       <c r="G54" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>161</v>
+      </c>
       <c r="I54" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>548</v>
+        <v>444</v>
       </c>
       <c r="K54" t="s">
         <v>67</v>
       </c>
       <c r="L54">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N54" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="O54">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q54" t="s">
+        <v>67</v>
+      </c>
+      <c r="R54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>617</v>
+        <v>232</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>617</v>
+        <v>232</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>223</v>
@@ -12321,18 +13279,20 @@
       <c r="E55" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F55" s="17" t="s">
-        <v>616</v>
+      <c r="F55" s="10" t="s">
+        <v>195</v>
       </c>
       <c r="G55" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>162</v>
+      </c>
       <c r="I55" s="9">
         <v>10</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>618</v>
+        <v>320</v>
       </c>
       <c r="K55" t="s">
         <v>67</v>
@@ -12341,60 +13301,72 @@
         <v>5</v>
       </c>
       <c r="N55" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="O55">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q55" t="s">
+        <v>67</v>
+      </c>
+      <c r="R55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>223</v>
+        <v>547</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>50</v>
+        <v>548</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F56" t="s">
-        <v>583</v>
+      <c r="F56" s="10" t="s">
+        <v>543</v>
       </c>
       <c r="G56" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="9"/>
       <c r="I56" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>585</v>
+        <v>544</v>
       </c>
       <c r="K56" t="s">
         <v>67</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N56" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="O56">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q56" t="s">
+        <v>67</v>
+      </c>
+      <c r="R56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>223</v>
@@ -12403,10 +13375,10 @@
         <v>50</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="G57" s="9" t="b">
         <v>0</v>
@@ -12416,94 +13388,103 @@
         <v>10</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="K57" t="s">
         <v>67</v>
       </c>
       <c r="L57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N57" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="O57">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q57" t="s">
+        <v>67</v>
+      </c>
+      <c r="R57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>598</v>
+        <v>152</v>
+      </c>
+      <c r="F58" t="s">
+        <v>579</v>
       </c>
       <c r="G58" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="K58" t="s">
         <v>67</v>
       </c>
       <c r="L58">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N58" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="O58">
         <v>5</v>
       </c>
-      <c r="P58" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q58" t="s">
+        <v>67</v>
+      </c>
+      <c r="R58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="G59" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="9"/>
       <c r="I59" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
       <c r="K59" t="s">
         <v>67</v>
@@ -12512,18 +13493,24 @@
         <v>6</v>
       </c>
       <c r="N59" t="s">
-        <v>912</v>
+        <v>896</v>
       </c>
       <c r="O59">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q59" t="s">
+        <v>67</v>
+      </c>
+      <c r="R59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>656</v>
+        <v>595</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>656</v>
+        <v>595</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>224</v>
@@ -12532,10 +13519,10 @@
         <v>148</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>655</v>
+        <v>594</v>
       </c>
       <c r="G60" s="9" t="b">
         <v>0</v>
@@ -12545,27 +13532,36 @@
         <v>7</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>657</v>
+        <v>596</v>
       </c>
       <c r="K60" t="s">
         <v>67</v>
       </c>
       <c r="L60">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N60" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="O60">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P60" t="s">
+        <v>916</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>67</v>
+      </c>
+      <c r="R60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>224</v>
@@ -12574,10 +13570,10 @@
         <v>148</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="G61" s="9" t="b">
         <v>0</v>
@@ -12587,7 +13583,7 @@
         <v>7</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>659</v>
+        <v>644</v>
       </c>
       <c r="K61" t="s">
         <v>67</v>
@@ -12596,18 +13592,24 @@
         <v>6</v>
       </c>
       <c r="N61" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="O61">
         <v>5</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q61" t="s">
+        <v>67</v>
+      </c>
+      <c r="R61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>224</v>
@@ -12616,22 +13618,20 @@
         <v>148</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="G62" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" s="9" t="s">
-        <v>667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H62" s="9"/>
       <c r="I62" s="9">
         <v>7</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="K62" t="s">
         <v>67</v>
@@ -12640,18 +13640,24 @@
         <v>6</v>
       </c>
       <c r="N62" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="O62">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q62" t="s">
+        <v>67</v>
+      </c>
+      <c r="R62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>224</v>
@@ -12660,22 +13666,20 @@
         <v>148</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="G63" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H63" t="s">
-        <v>672</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H63" s="9"/>
       <c r="I63" s="9">
         <v>7</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="K63" t="s">
         <v>67</v>
@@ -12684,18 +13688,24 @@
         <v>6</v>
       </c>
       <c r="N63" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="O63">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q63" t="s">
+        <v>67</v>
+      </c>
+      <c r="R63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>224</v>
@@ -12704,19 +13714,22 @@
         <v>148</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="G64" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>663</v>
       </c>
       <c r="I64" s="9">
         <v>7</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="K64" t="s">
         <v>67</v>
@@ -12725,18 +13738,24 @@
         <v>6</v>
       </c>
       <c r="N64" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="O64">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q64" t="s">
+        <v>67</v>
+      </c>
+      <c r="R64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>743</v>
+        <v>666</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>743</v>
+        <v>666</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>224</v>
@@ -12747,20 +13766,20 @@
       <c r="E65" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F65" t="s">
-        <v>742</v>
+      <c r="F65" s="17" t="s">
+        <v>665</v>
       </c>
       <c r="G65" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H65" s="9" t="s">
-        <v>744</v>
+      <c r="H65" t="s">
+        <v>668</v>
       </c>
       <c r="I65" s="9">
         <v>7</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>745</v>
+        <v>667</v>
       </c>
       <c r="K65" t="s">
         <v>67</v>
@@ -12769,18 +13788,24 @@
         <v>6</v>
       </c>
       <c r="N65" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="O65">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q65" t="s">
+        <v>67</v>
+      </c>
+      <c r="R65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>748</v>
+        <v>670</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>748</v>
+        <v>670</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>224</v>
@@ -12789,22 +13814,19 @@
         <v>148</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" t="s">
-        <v>742</v>
+        <v>152</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>669</v>
       </c>
       <c r="G66" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>749</v>
+        <v>0</v>
       </c>
       <c r="I66" s="9">
         <v>7</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>750</v>
+        <v>671</v>
       </c>
       <c r="K66" t="s">
         <v>67</v>
@@ -12813,18 +13835,24 @@
         <v>6</v>
       </c>
       <c r="N66" t="s">
-        <v>902</v>
+        <v>908</v>
       </c>
       <c r="O66">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q66" t="s">
+        <v>67</v>
+      </c>
+      <c r="R66">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>764</v>
+        <v>739</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>764</v>
+        <v>739</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>224</v>
@@ -12835,17 +13863,20 @@
       <c r="E67" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F67" s="17" t="s">
-        <v>765</v>
+      <c r="F67" t="s">
+        <v>738</v>
       </c>
       <c r="G67" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>740</v>
       </c>
       <c r="I67" s="9">
         <v>7</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>766</v>
+        <v>741</v>
       </c>
       <c r="K67" t="s">
         <v>67</v>
@@ -12854,18 +13885,24 @@
         <v>6</v>
       </c>
       <c r="N67" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="O67">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q67" t="s">
+        <v>67</v>
+      </c>
+      <c r="R67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>769</v>
+        <v>744</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>769</v>
+        <v>744</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>224</v>
@@ -12876,17 +13913,20 @@
       <c r="E68" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F68" s="17" t="s">
-        <v>771</v>
+      <c r="F68" t="s">
+        <v>738</v>
       </c>
       <c r="G68" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>745</v>
       </c>
       <c r="I68" s="9">
         <v>7</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="K68" t="s">
         <v>67</v>
@@ -12895,185 +13935,212 @@
         <v>6</v>
       </c>
       <c r="N68" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="O68">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q68" t="s">
+        <v>67</v>
+      </c>
+      <c r="R68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="G69" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I69" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="K69" t="s">
         <v>67</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N69" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="O69">
         <v>5</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q69" t="s">
+        <v>67</v>
+      </c>
+      <c r="R69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E70" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>785</v>
+        <v>767</v>
       </c>
       <c r="G70" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I70" s="9">
+        <v>7</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="K70" t="s">
+        <v>67</v>
+      </c>
+      <c r="L70">
+        <v>6</v>
+      </c>
+      <c r="N70" t="s">
+        <v>898</v>
+      </c>
+      <c r="O70">
+        <v>5</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>67</v>
+      </c>
+      <c r="R70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A71" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="G71" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" s="9">
         <v>10</v>
       </c>
-      <c r="J70" s="9" t="s">
-        <v>786</v>
-      </c>
-      <c r="K70" t="s">
-        <v>67</v>
-      </c>
-      <c r="L70">
-        <v>5</v>
-      </c>
-      <c r="N70" t="s">
-        <v>900</v>
-      </c>
-      <c r="O70">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="9" t="s">
-        <v>831</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>831</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>830</v>
-      </c>
-      <c r="G71" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71" s="9">
-        <v>7</v>
-      </c>
       <c r="J71" s="9" t="s">
-        <v>832</v>
+        <v>777</v>
       </c>
       <c r="K71" t="s">
         <v>67</v>
       </c>
       <c r="L71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N71" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="O71">
         <v>5</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q71" t="s">
+        <v>67</v>
+      </c>
+      <c r="R71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>836</v>
+        <v>780</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>836</v>
+        <v>780</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>157</v>
+        <v>11</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>781</v>
       </c>
       <c r="G72" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="I72" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>837</v>
+        <v>782</v>
       </c>
       <c r="K72" t="s">
         <v>67</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N72" t="s">
-        <v>906</v>
+        <v>896</v>
       </c>
       <c r="O72">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="Q72" t="s">
+        <v>67</v>
+      </c>
+      <c r="R72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
-        <v>926</v>
+        <v>827</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>926</v>
+        <v>827</v>
       </c>
       <c r="C73" s="9" t="s">
         <v>224</v>
@@ -13084,20 +14151,17 @@
       <c r="E73" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>157</v>
+      <c r="F73" s="17" t="s">
+        <v>826</v>
       </c>
       <c r="G73" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H73" t="s">
-        <v>927</v>
+        <v>0</v>
       </c>
       <c r="I73" s="9">
         <v>7</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="K73" t="s">
         <v>67</v>
@@ -13106,100 +14170,124 @@
         <v>6</v>
       </c>
       <c r="N73" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="O73">
         <v>5</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q73" t="s">
+        <v>67</v>
+      </c>
+      <c r="R73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F74" s="17" t="s">
-        <v>840</v>
+        <v>13</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="G74" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>831</v>
       </c>
       <c r="I74" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="K74" t="s">
         <v>67</v>
       </c>
       <c r="L74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N74" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="O74">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q74" t="s">
+        <v>67</v>
+      </c>
+      <c r="R74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
-        <v>846</v>
+        <v>922</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>846</v>
+        <v>922</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F75" s="17" t="s">
-        <v>845</v>
+        <v>13</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="G75" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>923</v>
       </c>
       <c r="I75" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>847</v>
+        <v>833</v>
       </c>
       <c r="K75" t="s">
         <v>67</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="O75">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q75" t="s">
+        <v>67</v>
+      </c>
+      <c r="R75">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="C76" s="9" t="s">
         <v>223</v>
@@ -13208,10 +14296,10 @@
         <v>50</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="G76" s="9" t="b">
         <v>0</v>
@@ -13220,7 +14308,7 @@
         <v>10</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
       <c r="K76" t="s">
         <v>67</v>
@@ -13229,18 +14317,24 @@
         <v>5</v>
       </c>
       <c r="N76" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="O76">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q76" t="s">
+        <v>67</v>
+      </c>
+      <c r="R76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>223</v>
@@ -13249,10 +14343,10 @@
         <v>50</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="G77" s="9" t="b">
         <v>0</v>
@@ -13261,7 +14355,7 @@
         <v>10</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="K77" t="s">
         <v>67</v>
@@ -13270,18 +14364,24 @@
         <v>5</v>
       </c>
       <c r="N77" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="O77">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q77" t="s">
+        <v>67</v>
+      </c>
+      <c r="R77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>223</v>
@@ -13290,10 +14390,10 @@
         <v>50</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>859</v>
+        <v>846</v>
       </c>
       <c r="G78" s="9" t="b">
         <v>0</v>
@@ -13302,7 +14402,7 @@
         <v>10</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="K78" t="s">
         <v>67</v>
@@ -13311,106 +14411,118 @@
         <v>5</v>
       </c>
       <c r="N78" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
       <c r="O78">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q78" t="s">
+        <v>67</v>
+      </c>
+      <c r="R78">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E79" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="17" t="s">
+        <v>847</v>
+      </c>
+      <c r="G79" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" s="9">
+        <v>10</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="K79" t="s">
+        <v>67</v>
+      </c>
+      <c r="L79">
+        <v>5</v>
+      </c>
+      <c r="N79" t="s">
+        <v>896</v>
+      </c>
+      <c r="O79">
+        <v>5</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>67</v>
+      </c>
+      <c r="R79">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A80" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>854</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E80" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F79" s="17" t="s">
-        <v>866</v>
-      </c>
-      <c r="G79" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79" s="9">
-        <v>7</v>
-      </c>
-      <c r="J79" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="K79" t="s">
-        <v>67</v>
-      </c>
-      <c r="L79">
-        <v>7</v>
-      </c>
-      <c r="M79">
-        <v>14</v>
-      </c>
-      <c r="N79" t="s">
-        <v>913</v>
-      </c>
-      <c r="O79">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A80" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="F80" s="17" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
       <c r="G80" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H80" s="9" t="s">
-        <v>874</v>
+        <v>0</v>
       </c>
       <c r="I80" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>875</v>
+        <v>856</v>
       </c>
       <c r="K80" t="s">
         <v>67</v>
       </c>
       <c r="L80">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N80" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="O80">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q80" t="s">
+        <v>67</v>
+      </c>
+      <c r="R80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
-        <v>878</v>
+        <v>861</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>878</v>
+        <v>861</v>
       </c>
       <c r="C81" s="9" t="s">
         <v>224</v>
@@ -13419,127 +14531,148 @@
         <v>148</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="G81" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81" t="s">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="I81" s="9">
         <v>7</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="K81" t="s">
         <v>67</v>
       </c>
       <c r="L81">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="M81">
+        <v>14</v>
       </c>
       <c r="N81" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="O81">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q81" t="s">
+        <v>67</v>
+      </c>
+      <c r="R81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>929</v>
+        <v>869</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>929</v>
+        <v>869</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>224</v>
+        <v>547</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>148</v>
+        <v>548</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="G82" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H82" t="s">
-        <v>930</v>
+      <c r="H82" s="9" t="s">
+        <v>870</v>
       </c>
       <c r="I82" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="K82" t="s">
         <v>67</v>
       </c>
       <c r="L82">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N82" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="O82">
         <v>5</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q82" t="s">
+        <v>67</v>
+      </c>
+      <c r="R82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="G83" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>872</v>
       </c>
       <c r="I83" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="K83" t="s">
         <v>67</v>
       </c>
       <c r="L83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N83" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="O83">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q83" t="s">
+        <v>67</v>
+      </c>
+      <c r="R83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>888</v>
+        <v>925</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>888</v>
+        <v>925</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>224</v>
@@ -13551,83 +14684,92 @@
         <v>11</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>887</v>
+        <v>873</v>
       </c>
       <c r="G84" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H84" s="9" t="s">
-        <v>889</v>
+      <c r="H84" t="s">
+        <v>926</v>
       </c>
       <c r="I84" s="9">
         <v>7</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="K84" t="s">
         <v>67</v>
       </c>
       <c r="L84">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N84" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="O84">
         <v>5</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q84" t="s">
+        <v>67</v>
+      </c>
+      <c r="R84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="G85" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>892</v>
+        <v>0</v>
       </c>
       <c r="I85" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="K85" t="s">
         <v>67</v>
       </c>
       <c r="L85">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N85" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="O85">
         <v>5</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q85" t="s">
+        <v>67</v>
+      </c>
+      <c r="R85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>921</v>
+        <v>884</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>921</v>
+        <v>884</v>
       </c>
       <c r="C86" s="9" t="s">
         <v>224</v>
@@ -13639,16 +14781,19 @@
         <v>11</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>922</v>
+        <v>883</v>
       </c>
       <c r="G86" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>885</v>
       </c>
       <c r="I86" s="9">
         <v>7</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>923</v>
+        <v>886</v>
       </c>
       <c r="K86" t="s">
         <v>67</v>
@@ -13657,97 +14802,794 @@
         <v>7</v>
       </c>
       <c r="N86" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="O86">
         <v>5</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q86" t="s">
+        <v>67</v>
+      </c>
+      <c r="R86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>944</v>
+        <v>887</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>944</v>
+        <v>887</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>551</v>
+        <v>224</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>552</v>
+        <v>148</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F87" s="17" t="s">
-        <v>945</v>
+        <v>883</v>
       </c>
       <c r="G87" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H87" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="I87" s="9">
+        <v>7</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>886</v>
+      </c>
+      <c r="K87" t="s">
+        <v>67</v>
+      </c>
+      <c r="L87">
+        <v>7</v>
+      </c>
+      <c r="N87" t="s">
+        <v>900</v>
+      </c>
+      <c r="O87">
+        <v>5</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>67</v>
+      </c>
+      <c r="R87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A88" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>918</v>
+      </c>
+      <c r="G88" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" s="9">
+        <v>7</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>919</v>
+      </c>
+      <c r="K88" t="s">
+        <v>67</v>
+      </c>
+      <c r="L88">
+        <v>7</v>
+      </c>
+      <c r="N88" t="s">
+        <v>900</v>
+      </c>
+      <c r="O88">
+        <v>5</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>67</v>
+      </c>
+      <c r="R88">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A89" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>941</v>
+      </c>
+      <c r="G89" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>942</v>
+      </c>
+      <c r="I89" s="9">
+        <v>5</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>943</v>
+      </c>
+      <c r="K89" t="s">
+        <v>67</v>
+      </c>
+      <c r="L89">
+        <v>20</v>
+      </c>
+      <c r="N89" t="s">
+        <v>903</v>
+      </c>
+      <c r="O89">
+        <v>5</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>67</v>
+      </c>
+      <c r="R89">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A90" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>944</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="17" t="s">
+        <v>941</v>
+      </c>
+      <c r="G90" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>945</v>
+      </c>
+      <c r="I90" s="9">
+        <v>5</v>
+      </c>
+      <c r="J90" s="9" t="s">
         <v>946</v>
       </c>
-      <c r="I87" s="9">
-        <v>5</v>
-      </c>
-      <c r="J87" s="9" t="s">
-        <v>947</v>
-      </c>
-      <c r="K87" t="s">
-        <v>67</v>
-      </c>
-      <c r="L87">
+      <c r="K90" t="s">
+        <v>67</v>
+      </c>
+      <c r="L90">
         <v>20</v>
       </c>
-      <c r="N87" t="s">
+      <c r="N90" t="s">
+        <v>903</v>
+      </c>
+      <c r="O90">
+        <v>5</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>67</v>
+      </c>
+      <c r="R90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A91" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G91" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" s="9">
+        <v>5</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>1004</v>
+      </c>
+      <c r="K91" t="s">
+        <v>67</v>
+      </c>
+      <c r="L91">
+        <v>20</v>
+      </c>
+      <c r="N91" t="s">
+        <v>910</v>
+      </c>
+      <c r="O91">
+        <v>5</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>67</v>
+      </c>
+      <c r="R91">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A92" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G92" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I92" s="9">
+        <v>5</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K92" t="s">
+        <v>67</v>
+      </c>
+      <c r="L92">
+        <v>20</v>
+      </c>
+      <c r="N92" t="s">
+        <v>910</v>
+      </c>
+      <c r="O92">
+        <v>5</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>67</v>
+      </c>
+      <c r="R92">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A93" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F93" s="17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G93" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" s="9">
+        <v>7</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K93" t="s">
+        <v>67</v>
+      </c>
+      <c r="L93">
+        <v>7</v>
+      </c>
+      <c r="N93" t="s">
+        <v>909</v>
+      </c>
+      <c r="O93">
+        <v>5</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>67</v>
+      </c>
+      <c r="R93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A94" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F94" s="17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G94" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" s="9">
+        <v>10</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K94" t="s">
+        <v>67</v>
+      </c>
+      <c r="L94">
+        <v>6</v>
+      </c>
+      <c r="N94" t="s">
+        <v>906</v>
+      </c>
+      <c r="O94">
+        <v>5</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>67</v>
+      </c>
+      <c r="R94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A95" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F95" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G95" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I95" s="9">
+        <v>5</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>1026</v>
+      </c>
+      <c r="K95" t="s">
+        <v>67</v>
+      </c>
+      <c r="L95">
+        <v>20</v>
+      </c>
+      <c r="N95" t="s">
+        <v>903</v>
+      </c>
+      <c r="O95">
+        <v>5</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>67</v>
+      </c>
+      <c r="R95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A96" s="9" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G96" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I96" s="9">
+        <v>5</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>1026</v>
+      </c>
+      <c r="K96" t="s">
+        <v>67</v>
+      </c>
+      <c r="L96">
+        <v>20</v>
+      </c>
+      <c r="N96" t="s">
+        <v>903</v>
+      </c>
+      <c r="O96">
+        <v>5</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>67</v>
+      </c>
+      <c r="R96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F97" s="17" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G97" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I97" s="9">
+        <v>5</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K97" t="s">
+        <v>67</v>
+      </c>
+      <c r="L97">
+        <v>20</v>
+      </c>
+      <c r="N97" t="s">
         <v>907</v>
       </c>
-      <c r="O87">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A88" s="9" t="s">
-        <v>948</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>948</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="E88" s="9" t="s">
+      <c r="O97">
+        <v>5</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>67</v>
+      </c>
+      <c r="R97">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A98" s="9" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F98" s="17" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G98" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I98" s="9">
+        <v>5</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K98" t="s">
+        <v>67</v>
+      </c>
+      <c r="L98">
+        <v>20</v>
+      </c>
+      <c r="N98" t="s">
+        <v>907</v>
+      </c>
+      <c r="O98">
+        <v>5</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>67</v>
+      </c>
+      <c r="R98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A99" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G99" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I99" s="9">
+        <v>5</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>1052</v>
+      </c>
+      <c r="K99" t="s">
+        <v>67</v>
+      </c>
+      <c r="L99">
+        <v>20</v>
+      </c>
+      <c r="N99" t="s">
+        <v>910</v>
+      </c>
+      <c r="O99">
+        <v>5</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>67</v>
+      </c>
+      <c r="R99">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A100" s="9" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="17" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G100" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I100" s="9">
+        <v>5</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>1053</v>
+      </c>
+      <c r="K100" t="s">
+        <v>67</v>
+      </c>
+      <c r="L100">
+        <v>20</v>
+      </c>
+      <c r="N100" t="s">
+        <v>910</v>
+      </c>
+      <c r="O100">
+        <v>5</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>67</v>
+      </c>
+      <c r="R100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A101" s="9" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="17" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G101" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" s="9">
+        <v>7</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K101" t="s">
+        <v>67</v>
+      </c>
+      <c r="L101">
+        <v>7</v>
+      </c>
+      <c r="N101" t="s">
+        <v>898</v>
+      </c>
+      <c r="O101">
+        <v>5</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>67</v>
+      </c>
+      <c r="R101">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A102" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E102" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="17" t="s">
-        <v>945</v>
-      </c>
-      <c r="G88" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>949</v>
-      </c>
-      <c r="I88" s="9">
-        <v>5</v>
-      </c>
-      <c r="J88" s="9" t="s">
-        <v>950</v>
-      </c>
-      <c r="K88" t="s">
-        <v>67</v>
-      </c>
-      <c r="L88">
+      <c r="F102" s="17" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G102" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" s="9">
+        <v>5</v>
+      </c>
+      <c r="J102" s="9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="K102" t="s">
+        <v>67</v>
+      </c>
+      <c r="L102">
         <v>20</v>
       </c>
-      <c r="N88" t="s">
-        <v>907</v>
-      </c>
-      <c r="O88">
+      <c r="N102" t="s">
+        <v>903</v>
+      </c>
+      <c r="O102">
+        <v>5</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>67</v>
+      </c>
+      <c r="R102">
         <v>5</v>
       </c>
     </row>
@@ -13839,7 +15681,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>19</v>
@@ -13895,7 +15737,7 @@
         <v>36</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>65</v>
@@ -13907,16 +15749,16 @@
         <v>4</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="L3" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>689</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>693</v>
-      </c>
       <c r="N3" s="6" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>267</v>
@@ -13945,16 +15787,16 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="J4" t="s">
         <v>240</v>
       </c>
       <c r="K4" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="L4" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -13989,16 +15831,16 @@
         <v>2.5</v>
       </c>
       <c r="I5" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="J5" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="K5" t="s">
+        <v>683</v>
+      </c>
+      <c r="L5" t="s">
         <v>687</v>
-      </c>
-      <c r="L5" t="s">
-        <v>691</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -14033,16 +15875,16 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="J6" t="s">
         <v>264</v>
       </c>
       <c r="K6" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="L6" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -14080,16 +15922,16 @@
         <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="J7" t="s">
         <v>265</v>
       </c>
       <c r="K7" t="s">
+        <v>684</v>
+      </c>
+      <c r="L7" t="s">
         <v>688</v>
-      </c>
-      <c r="L7" t="s">
-        <v>692</v>
       </c>
       <c r="M7">
         <v>2</v>
@@ -14103,13 +15945,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -14124,16 +15966,16 @@
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="J8" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="K8" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="L8" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -14147,13 +15989,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D9" t="s">
         <v>50</v>
@@ -14168,16 +16010,16 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="J9" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="K9" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="L9" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M9">
         <v>1</v>
@@ -14191,13 +16033,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -14212,16 +16054,16 @@
         <v>3</v>
       </c>
       <c r="I10" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="J10" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="K10" t="s">
+        <v>683</v>
+      </c>
+      <c r="L10" t="s">
         <v>687</v>
-      </c>
-      <c r="L10" t="s">
-        <v>691</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -14235,13 +16077,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D11" t="s">
         <v>50</v>
@@ -14256,16 +16098,16 @@
         <v>3</v>
       </c>
       <c r="I11" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J11" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="K11" t="s">
+        <v>683</v>
+      </c>
+      <c r="L11" t="s">
         <v>687</v>
-      </c>
-      <c r="L11" t="s">
-        <v>691</v>
       </c>
       <c r="M11">
         <v>1</v>
@@ -14279,13 +16121,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="D12" t="s">
         <v>148</v>
@@ -14300,16 +16142,16 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="J12" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="K12" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="L12" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M12">
         <v>3</v>
@@ -14323,13 +16165,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D13" t="s">
         <v>148</v>
@@ -14344,16 +16186,16 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="J13" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="K13" t="s">
+        <v>683</v>
+      </c>
+      <c r="L13" t="s">
         <v>687</v>
-      </c>
-      <c r="L13" t="s">
-        <v>691</v>
       </c>
       <c r="M13">
         <v>3</v>
@@ -14367,13 +16209,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D14" t="s">
         <v>148</v>
@@ -14388,16 +16230,16 @@
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="J14" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="K14" t="s">
+        <v>684</v>
+      </c>
+      <c r="L14" t="s">
         <v>688</v>
-      </c>
-      <c r="L14" t="s">
-        <v>692</v>
       </c>
       <c r="M14">
         <v>3</v>
@@ -14411,13 +16253,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="D15" t="s">
         <v>148</v>
@@ -14432,16 +16274,16 @@
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="J15" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="K15" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="L15" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M15">
         <v>3</v>
@@ -14588,7 +16430,7 @@
         <v>101</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -15438,10 +17280,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B5" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -15450,7 +17292,7 @@
         <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
     </row>
   </sheetData>
@@ -15772,7 +17614,7 @@
         <v>268</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>80</v>
@@ -15844,25 +17686,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B6" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C6">
         <v>600</v>
       </c>
       <c r="D6" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E6" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="F6" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="H6">
         <v>1</v>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAD289F-72C6-43A2-BB16-D4A9FFCB41EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAFF78E-30B7-4F76-87D6-6AF1C00F8305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" firstSheet="1" activeTab="14" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="1" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
   </bookViews>
   <sheets>
     <sheet name="EnumData" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2855" uniqueCount="1134">
   <si>
     <t>ALL</t>
   </si>
@@ -4131,6 +4131,240 @@
   </si>
   <si>
     <t>등에 분홍색의 작은 점박이가 있는 몸입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_흙색몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반_흙색몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commonbody01_c09</t>
+  </si>
+  <si>
+    <t>흙색 점박이 몸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>배쪽에 흙색의 점박이가 있는 몸입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_동글껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell05_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_동글껍질01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매끈껍질(빨간색)</t>
+  </si>
+  <si>
+    <t>매끈한 껍질에 아름다운 점박이 무늬가 새겨져 있습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_동글껍질02]</t>
+  </si>
+  <si>
+    <t>rareshell05_c02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_동글껍질03]</t>
+  </si>
+  <si>
+    <t>매끈껍질(보라색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매끈껍질(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_동글껍질04]</t>
+  </si>
+  <si>
+    <t>[레어_동글껍질04]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>rareshell05_c03</t>
+  </si>
+  <si>
+    <t>rareshell05_c04</t>
+  </si>
+  <si>
+    <t>[레어_동글껍질04정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매끈한 껍질에 아름다운 줄무늬가 새겨져 있습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용몸]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dragon</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_용몸정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>드래곤 몸(초록색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>세상에서 제일 느린 드래곤이 탄생했습니다!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[리본01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hat03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[리본01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[넥타이01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>etc03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[넥타이01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왕리본(분홍)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>넥타이(빨간색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>kawaii~~♡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>출근 필수 아이템.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[레어_동글껍질05]</t>
+  </si>
+  <si>
+    <t>rareshell05_c05</t>
+  </si>
+  <si>
+    <t>매끈 줄무늬껍질(노란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매끈 줄무늬껍질(보라색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_해골몸01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_해골몸01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_해골몸02]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산성 몸(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산성 몸(주황색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>뭔가 몸 안에서 돌아다니고 있습니다..</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>epicbody06</t>
+  </si>
+  <si>
+    <t>[에픽_하트껍질01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>heart</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>heart_c01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_하트껍질01정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[에픽_하트껍질02]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사랑을 듬뿍받아 집으로 만들었나봐요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하트 껍질(분홍색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>하트 껍질(파란색)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFXR2 Poison Cloud</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈12]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[일반달팽이_눈12정보]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>commoneyes12</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5593,7 +5827,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A30A70E-EA93-48C5-ACAF-E5364197391F}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
@@ -5790,6 +6024,40 @@
         <v>953</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C13" t="s">
+        <v>432</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1105</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5798,7 +6066,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43E79052-7558-4F08-8689-6E3AEA3B2BB4}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.125" bestFit="1" customWidth="1"/>
@@ -6763,6 +7031,84 @@
       </c>
       <c r="L25">
         <f t="shared" ref="L25" si="6">F25/2</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>67</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26" s="12">
+        <v>70</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>67</v>
+      </c>
+      <c r="L26">
+        <f t="shared" ref="L26:L27" si="7">F26/2</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27" s="12">
+        <v>70</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
     </row>
@@ -7614,7 +7960,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7597F0DA-3C80-45CD-9238-9483A55F6DAB}">
-  <dimension ref="A1:C317"/>
+  <dimension ref="A1:C338"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.625" bestFit="1" customWidth="1"/>
@@ -10128,7 +10474,7 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="9" t="s">
-        <v>854</v>
+        <v>1131</v>
       </c>
       <c r="B314" s="8" t="s">
         <v>1066</v>
@@ -10136,7 +10482,7 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="9" t="s">
-        <v>856</v>
+        <v>1132</v>
       </c>
       <c r="B315" s="8" t="s">
         <v>1067</v>
@@ -10156,6 +10502,174 @@
       </c>
       <c r="B317" s="8" t="s">
         <v>1072</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A318" s="9" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B318" s="8" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A319" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A320" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B320" s="8" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A321" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A322" s="9" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B322" s="8" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A323" s="9" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A324" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B324" s="8" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A325" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B325" s="8" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A326" s="9" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B326" s="8" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A327" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A328" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B328" s="8" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A329" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A330" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B330" s="8" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A331" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A332" s="9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A333" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A334" s="9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A335" s="9" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A336" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A337" s="9" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A338" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>1127</v>
       </c>
     </row>
   </sheetData>
@@ -10512,7 +11026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64AF268D-9FFB-412F-8C93-B96648EAFB36}">
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:V113"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.125" customWidth="1"/>
@@ -12241,10 +12755,10 @@
     </row>
     <row r="34" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>234</v>
+        <v>1073</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>234</v>
+        <v>1073</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>223</v>
@@ -12256,19 +12770,19 @@
         <v>13</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>235</v>
+        <v>157</v>
       </c>
       <c r="G34" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>236</v>
+        <v>1075</v>
       </c>
       <c r="I34" s="9">
         <v>10</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>311</v>
+        <v>1074</v>
       </c>
       <c r="K34" t="s">
         <v>67</v>
@@ -12291,10 +12805,10 @@
     </row>
     <row r="35" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>601</v>
+        <v>234</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>601</v>
+        <v>234</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>223</v>
@@ -12306,17 +12820,19 @@
         <v>13</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>602</v>
+        <v>235</v>
       </c>
       <c r="G35" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>236</v>
+      </c>
       <c r="I35" s="9">
         <v>10</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>603</v>
+        <v>311</v>
       </c>
       <c r="K35" t="s">
         <v>67</v>
@@ -12339,10 +12855,10 @@
     </row>
     <row r="36" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>256</v>
+        <v>601</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>223</v>
@@ -12354,19 +12870,17 @@
         <v>13</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>257</v>
+        <v>602</v>
       </c>
       <c r="G36" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>258</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H36" s="9"/>
       <c r="I36" s="9">
         <v>10</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>312</v>
+        <v>603</v>
       </c>
       <c r="K36" t="s">
         <v>67</v>
@@ -12389,10 +12903,10 @@
     </row>
     <row r="37" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>404</v>
+        <v>256</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>404</v>
+        <v>256</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>223</v>
@@ -12410,13 +12924,13 @@
         <v>1</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>397</v>
+        <v>258</v>
       </c>
       <c r="I37" s="9">
         <v>10</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>405</v>
+        <v>312</v>
       </c>
       <c r="K37" t="s">
         <v>67</v>
@@ -12439,43 +12953,43 @@
     </row>
     <row r="38" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>413</v>
+        <v>257</v>
       </c>
       <c r="G38" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="I38" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="K38" t="s">
         <v>67</v>
       </c>
       <c r="L38">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N38" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="O38">
         <v>5</v>
@@ -12489,43 +13003,43 @@
     </row>
     <row r="39" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>506</v>
+        <v>412</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>506</v>
+        <v>412</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>507</v>
+        <v>413</v>
       </c>
       <c r="G39" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>508</v>
+        <v>414</v>
       </c>
       <c r="I39" s="9">
+        <v>7</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="K39" t="s">
+        <v>67</v>
+      </c>
+      <c r="L39">
         <v>10</v>
       </c>
-      <c r="J39" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="K39" t="s">
-        <v>67</v>
-      </c>
-      <c r="L39">
-        <v>5</v>
-      </c>
       <c r="N39" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="O39">
         <v>5</v>
@@ -12539,41 +13053,43 @@
     </row>
     <row r="40" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>551</v>
+        <v>506</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>551</v>
+        <v>506</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>547</v>
+        <v>223</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>548</v>
+        <v>50</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>552</v>
+        <v>507</v>
       </c>
       <c r="G40" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>508</v>
+      </c>
       <c r="I40" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>553</v>
+        <v>509</v>
       </c>
       <c r="K40" t="s">
         <v>67</v>
       </c>
       <c r="L40">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N40" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="O40">
         <v>5</v>
@@ -12587,43 +13103,41 @@
     </row>
     <row r="41" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>626</v>
+        <v>551</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>626</v>
+        <v>551</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>224</v>
+        <v>547</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>148</v>
+        <v>548</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="17" t="s">
-        <v>624</v>
+      <c r="F41" s="10" t="s">
+        <v>552</v>
       </c>
       <c r="G41" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H41" s="9"/>
       <c r="I41" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>627</v>
+        <v>553</v>
       </c>
       <c r="K41" t="s">
         <v>67</v>
       </c>
       <c r="L41">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N41" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="O41">
         <v>5</v>
@@ -12637,41 +13151,43 @@
     </row>
     <row r="42" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>160</v>
+        <v>626</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>160</v>
+        <v>626</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>158</v>
+        <v>13</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>624</v>
       </c>
       <c r="G42" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>625</v>
+      </c>
       <c r="I42" s="9">
+        <v>7</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="K42" t="s">
+        <v>67</v>
+      </c>
+      <c r="L42">
         <v>10</v>
       </c>
-      <c r="J42" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="K42" t="s">
-        <v>67</v>
-      </c>
-      <c r="L42">
-        <v>5</v>
-      </c>
       <c r="N42" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="O42">
         <v>5</v>
@@ -12685,10 +13201,10 @@
     </row>
     <row r="43" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>223</v>
@@ -12700,7 +13216,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
       <c r="G43" s="9" t="b">
         <v>0</v>
@@ -12710,7 +13226,7 @@
         <v>10</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K43" t="s">
         <v>67</v>
@@ -12733,10 +13249,10 @@
     </row>
     <row r="44" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>223</v>
@@ -12748,7 +13264,7 @@
         <v>14</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G44" s="9" t="b">
         <v>0</v>
@@ -12758,7 +13274,7 @@
         <v>10</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K44" t="s">
         <v>67</v>
@@ -12781,10 +13297,10 @@
     </row>
     <row r="45" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>223</v>
@@ -12796,7 +13312,7 @@
         <v>14</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G45" s="9" t="b">
         <v>0</v>
@@ -12806,7 +13322,7 @@
         <v>10</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K45" t="s">
         <v>67</v>
@@ -12829,10 +13345,10 @@
     </row>
     <row r="46" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>406</v>
+        <v>218</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>406</v>
+        <v>218</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>223</v>
@@ -12844,7 +13360,7 @@
         <v>14</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>407</v>
+        <v>221</v>
       </c>
       <c r="G46" s="9" t="b">
         <v>0</v>
@@ -12854,7 +13370,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>408</v>
+        <v>316</v>
       </c>
       <c r="K46" t="s">
         <v>67</v>
@@ -12875,12 +13391,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>590</v>
+        <v>406</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>590</v>
+        <v>406</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>223</v>
@@ -12891,8 +13407,8 @@
       <c r="E47" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F47" s="17" t="s">
-        <v>589</v>
+      <c r="F47" s="10" t="s">
+        <v>407</v>
       </c>
       <c r="G47" s="9" t="b">
         <v>0</v>
@@ -12902,7 +13418,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>591</v>
+        <v>408</v>
       </c>
       <c r="K47" t="s">
         <v>67</v>
@@ -12925,10 +13441,10 @@
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>223</v>
@@ -12940,7 +13456,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>1064</v>
+        <v>589</v>
       </c>
       <c r="G48" s="9" t="b">
         <v>0</v>
@@ -12950,7 +13466,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="K48" t="s">
         <v>67</v>
@@ -12973,10 +13489,10 @@
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
-        <v>647</v>
+        <v>610</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>647</v>
+        <v>610</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>223</v>
@@ -12988,7 +13504,7 @@
         <v>14</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G49" s="9" t="b">
         <v>0</v>
@@ -12998,7 +13514,7 @@
         <v>10</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="K49" t="s">
         <v>67</v>
@@ -13019,12 +13535,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
-        <v>854</v>
+        <v>647</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>854</v>
+        <v>647</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>223</v>
@@ -13036,7 +13552,7 @@
         <v>14</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>855</v>
+        <v>1065</v>
       </c>
       <c r="G50" s="9" t="b">
         <v>0</v>
@@ -13046,7 +13562,7 @@
         <v>10</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>856</v>
+        <v>648</v>
       </c>
       <c r="K50" t="s">
         <v>67</v>
@@ -13069,41 +13585,41 @@
     </row>
     <row r="51" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>546</v>
+        <v>1131</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>546</v>
+        <v>1131</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>547</v>
+        <v>223</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>548</v>
+        <v>50</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>549</v>
+      <c r="F51" s="17" t="s">
+        <v>1133</v>
       </c>
       <c r="G51" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>550</v>
+        <v>1132</v>
       </c>
       <c r="K51" t="s">
         <v>67</v>
       </c>
       <c r="L51">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N51" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="O51">
         <v>5</v>
@@ -13117,43 +13633,41 @@
     </row>
     <row r="52" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>166</v>
+        <v>546</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>166</v>
+        <v>546</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>223</v>
+        <v>547</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>50</v>
+        <v>548</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>167</v>
+        <v>549</v>
       </c>
       <c r="G52" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>194</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H52" s="9"/>
       <c r="I52" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="K52" t="s">
         <v>67</v>
       </c>
       <c r="L52">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N52" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="O52">
         <v>5</v>
@@ -13167,10 +13681,10 @@
     </row>
     <row r="53" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>443</v>
+        <v>166</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>443</v>
+        <v>166</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>223</v>
@@ -13182,17 +13696,19 @@
         <v>152</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="G53" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>194</v>
+      </c>
       <c r="I53" s="9">
         <v>10</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>445</v>
+        <v>519</v>
       </c>
       <c r="K53" t="s">
         <v>67</v>
@@ -13215,10 +13731,10 @@
     </row>
     <row r="54" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>262</v>
+        <v>443</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>262</v>
+        <v>443</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>223</v>
@@ -13230,19 +13746,17 @@
         <v>152</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G54" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>161</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H54" s="9"/>
       <c r="I54" s="9">
         <v>10</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K54" t="s">
         <v>67</v>
@@ -13265,10 +13779,10 @@
     </row>
     <row r="55" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>223</v>
@@ -13280,19 +13794,19 @@
         <v>152</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G55" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I55" s="9">
         <v>10</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>320</v>
+        <v>444</v>
       </c>
       <c r="K55" t="s">
         <v>67</v>
@@ -13315,41 +13829,43 @@
     </row>
     <row r="56" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
-        <v>545</v>
+        <v>232</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>545</v>
+        <v>232</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>547</v>
+        <v>223</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>548</v>
+        <v>50</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>152</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>543</v>
+        <v>195</v>
       </c>
       <c r="G56" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="9"/>
+        <v>1</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>162</v>
+      </c>
       <c r="I56" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>544</v>
+        <v>320</v>
       </c>
       <c r="K56" t="s">
         <v>67</v>
       </c>
       <c r="L56">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N56" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="O56">
         <v>5</v>
@@ -13361,43 +13877,43 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>613</v>
+        <v>545</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>613</v>
+        <v>545</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>223</v>
+        <v>547</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>50</v>
+        <v>548</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F57" s="17" t="s">
-        <v>612</v>
+      <c r="F57" s="10" t="s">
+        <v>543</v>
       </c>
       <c r="G57" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="9"/>
       <c r="I57" s="9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>614</v>
+        <v>544</v>
       </c>
       <c r="K57" t="s">
         <v>67</v>
       </c>
       <c r="L57">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="N57" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="O57">
         <v>5</v>
@@ -13411,10 +13927,10 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
-        <v>580</v>
+        <v>613</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>580</v>
+        <v>613</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>223</v>
@@ -13425,8 +13941,8 @@
       <c r="E58" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="F58" t="s">
-        <v>579</v>
+      <c r="F58" s="17" t="s">
+        <v>612</v>
       </c>
       <c r="G58" s="9" t="b">
         <v>0</v>
@@ -13436,13 +13952,13 @@
         <v>10</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>581</v>
+        <v>614</v>
       </c>
       <c r="K58" t="s">
         <v>67</v>
       </c>
       <c r="L58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N58" t="s">
         <v>906</v>
@@ -13459,10 +13975,10 @@
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>223</v>
@@ -13471,10 +13987,10 @@
         <v>50</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>584</v>
+        <v>152</v>
+      </c>
+      <c r="F59" t="s">
+        <v>579</v>
       </c>
       <c r="G59" s="9" t="b">
         <v>0</v>
@@ -13484,7 +14000,7 @@
         <v>10</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="K59" t="s">
         <v>67</v>
@@ -13493,7 +14009,7 @@
         <v>6</v>
       </c>
       <c r="N59" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="O59">
         <v>5</v>
@@ -13507,47 +14023,44 @@
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="G60" s="9" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="9"/>
       <c r="I60" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="K60" t="s">
         <v>67</v>
       </c>
       <c r="L60">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N60" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="O60">
         <v>5</v>
-      </c>
-      <c r="P60" t="s">
-        <v>916</v>
       </c>
       <c r="Q60" t="s">
         <v>67</v>
@@ -13558,10 +14071,10 @@
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>643</v>
+        <v>595</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>643</v>
+        <v>595</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>224</v>
@@ -13570,10 +14083,10 @@
         <v>148</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>642</v>
+        <v>594</v>
       </c>
       <c r="G61" s="9" t="b">
         <v>0</v>
@@ -13583,19 +14096,22 @@
         <v>7</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>644</v>
+        <v>596</v>
       </c>
       <c r="K61" t="s">
         <v>67</v>
       </c>
       <c r="L61">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N61" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="O61">
         <v>5</v>
+      </c>
+      <c r="P61" t="s">
+        <v>916</v>
       </c>
       <c r="Q61" t="s">
         <v>67</v>
@@ -13606,10 +14122,10 @@
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>224</v>
@@ -13618,10 +14134,10 @@
         <v>148</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="G62" s="9" t="b">
         <v>0</v>
@@ -13631,7 +14147,7 @@
         <v>7</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="K62" t="s">
         <v>67</v>
@@ -13640,7 +14156,7 @@
         <v>6</v>
       </c>
       <c r="N62" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="O62">
         <v>5</v>
@@ -13654,10 +14170,10 @@
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>224</v>
@@ -13669,7 +14185,7 @@
         <v>14</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="G63" s="9" t="b">
         <v>0</v>
@@ -13679,7 +14195,7 @@
         <v>7</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="K63" t="s">
         <v>67</v>
@@ -13702,10 +14218,10 @@
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>224</v>
@@ -13714,22 +14230,20 @@
         <v>148</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="G64" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" s="9" t="s">
-        <v>663</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H64" s="9"/>
       <c r="I64" s="9">
         <v>7</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="K64" t="s">
         <v>67</v>
@@ -13738,7 +14252,7 @@
         <v>6</v>
       </c>
       <c r="N64" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="O64">
         <v>5</v>
@@ -13752,10 +14266,10 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>224</v>
@@ -13764,22 +14278,22 @@
         <v>148</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G65" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H65" t="s">
-        <v>668</v>
+      <c r="H65" s="9" t="s">
+        <v>663</v>
       </c>
       <c r="I65" s="9">
         <v>7</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="K65" t="s">
         <v>67</v>
@@ -13788,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="N65" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="O65">
         <v>5</v>
@@ -13802,10 +14316,10 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>224</v>
@@ -13814,19 +14328,22 @@
         <v>148</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="G66" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>668</v>
       </c>
       <c r="I66" s="9">
         <v>7</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="K66" t="s">
         <v>67</v>
@@ -13835,7 +14352,7 @@
         <v>6</v>
       </c>
       <c r="N66" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="O66">
         <v>5</v>
@@ -13849,10 +14366,10 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
-        <v>739</v>
+        <v>670</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>739</v>
+        <v>670</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>224</v>
@@ -13861,22 +14378,19 @@
         <v>148</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" t="s">
-        <v>738</v>
+        <v>152</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>669</v>
       </c>
       <c r="G67" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="I67" s="9">
         <v>7</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>741</v>
+        <v>671</v>
       </c>
       <c r="K67" t="s">
         <v>67</v>
@@ -13885,7 +14399,7 @@
         <v>6</v>
       </c>
       <c r="N67" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="O67">
         <v>5</v>
@@ -13899,10 +14413,10 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>224</v>
@@ -13920,13 +14434,13 @@
         <v>1</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="I68" s="9">
         <v>7</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="K68" t="s">
         <v>67</v>
@@ -13949,10 +14463,10 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>224</v>
@@ -13963,17 +14477,20 @@
       <c r="E69" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="17" t="s">
-        <v>761</v>
+      <c r="F69" t="s">
+        <v>738</v>
       </c>
       <c r="G69" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>745</v>
       </c>
       <c r="I69" s="9">
         <v>7</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="K69" t="s">
         <v>67</v>
@@ -13996,10 +14513,10 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>224</v>
@@ -14011,7 +14528,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="G70" s="9" t="b">
         <v>0</v>
@@ -14020,7 +14537,7 @@
         <v>7</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="K70" t="s">
         <v>67</v>
@@ -14043,40 +14560,40 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="G71" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I71" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="K71" t="s">
         <v>67</v>
       </c>
       <c r="L71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N71" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="O71">
         <v>5</v>
@@ -14090,10 +14607,10 @@
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>223</v>
@@ -14105,7 +14622,7 @@
         <v>11</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="G72" s="9" t="b">
         <v>0</v>
@@ -14114,7 +14631,7 @@
         <v>10</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="K72" t="s">
         <v>67</v>
@@ -14135,42 +14652,42 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
-        <v>827</v>
+        <v>780</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>827</v>
+        <v>780</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>826</v>
+        <v>781</v>
       </c>
       <c r="G73" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I73" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>828</v>
+        <v>782</v>
       </c>
       <c r="K73" t="s">
         <v>67</v>
       </c>
       <c r="L73">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N73" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="O73">
         <v>5</v>
@@ -14184,10 +14701,10 @@
     </row>
     <row r="74" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>224</v>
@@ -14198,20 +14715,17 @@
       <c r="E74" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="10" t="s">
-        <v>157</v>
+      <c r="F74" s="17" t="s">
+        <v>826</v>
       </c>
       <c r="G74" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H74" t="s">
-        <v>831</v>
+        <v>0</v>
       </c>
       <c r="I74" s="9">
         <v>7</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="K74" t="s">
         <v>67</v>
@@ -14234,10 +14748,10 @@
     </row>
     <row r="75" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
-        <v>922</v>
+        <v>832</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>922</v>
+        <v>832</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>224</v>
@@ -14255,7 +14769,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>923</v>
+        <v>831</v>
       </c>
       <c r="I75" s="9">
         <v>7</v>
@@ -14282,42 +14796,45 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
-        <v>837</v>
+        <v>922</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>837</v>
+        <v>922</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>836</v>
+        <v>13</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>157</v>
       </c>
       <c r="G76" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>923</v>
       </c>
       <c r="I76" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="K76" t="s">
         <v>67</v>
       </c>
       <c r="L76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N76" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="O76">
         <v>5</v>
@@ -14331,10 +14848,10 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>223</v>
@@ -14343,10 +14860,10 @@
         <v>50</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="G77" s="9" t="b">
         <v>0</v>
@@ -14355,7 +14872,7 @@
         <v>10</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="K77" t="s">
         <v>67</v>
@@ -14364,7 +14881,7 @@
         <v>5</v>
       </c>
       <c r="N77" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="O77">
         <v>5</v>
@@ -14378,10 +14895,10 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>223</v>
@@ -14390,10 +14907,10 @@
         <v>50</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="G78" s="9" t="b">
         <v>0</v>
@@ -14402,7 +14919,7 @@
         <v>10</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="K78" t="s">
         <v>67</v>
@@ -14411,7 +14928,7 @@
         <v>5</v>
       </c>
       <c r="N78" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="O78">
         <v>5</v>
@@ -14425,10 +14942,10 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C79" s="9" t="s">
         <v>223</v>
@@ -14440,7 +14957,7 @@
         <v>11</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G79" s="9" t="b">
         <v>0</v>
@@ -14472,10 +14989,10 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>223</v>
@@ -14484,10 +15001,10 @@
         <v>50</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="G80" s="9" t="b">
         <v>0</v>
@@ -14496,7 +15013,7 @@
         <v>10</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="K80" t="s">
         <v>67</v>
@@ -14505,7 +15022,7 @@
         <v>5</v>
       </c>
       <c r="N80" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="O80">
         <v>5</v>
@@ -14519,43 +15036,40 @@
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="G81" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I81" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="K81" t="s">
         <v>67</v>
       </c>
       <c r="L81">
-        <v>7</v>
-      </c>
-      <c r="M81">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N81" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="O81">
         <v>5</v>
@@ -14569,43 +15083,43 @@
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>547</v>
+        <v>224</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>548</v>
+        <v>148</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="G82" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>870</v>
+        <v>0</v>
       </c>
       <c r="I82" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="K82" t="s">
         <v>67</v>
       </c>
       <c r="L82">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="M82">
+        <v>14</v>
       </c>
       <c r="N82" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="O82">
         <v>5</v>
@@ -14619,43 +15133,43 @@
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>224</v>
+        <v>547</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>148</v>
+        <v>548</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G83" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="H83" t="s">
-        <v>872</v>
+      <c r="H83" s="9" t="s">
+        <v>870</v>
       </c>
       <c r="I83" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="K83" t="s">
         <v>67</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N83" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="O83">
         <v>5</v>
@@ -14669,10 +15183,10 @@
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>925</v>
+        <v>874</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>925</v>
+        <v>874</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>224</v>
@@ -14690,7 +15204,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>926</v>
+        <v>872</v>
       </c>
       <c r="I84" s="9">
         <v>7</v>
@@ -14719,40 +15233,43 @@
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
-        <v>880</v>
+        <v>925</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>880</v>
+        <v>925</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="G85" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>926</v>
       </c>
       <c r="I85" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="K85" t="s">
         <v>67</v>
       </c>
       <c r="L85">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N85" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="O85">
         <v>5</v>
@@ -14766,43 +15283,40 @@
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G86" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H86" s="9" t="s">
-        <v>885</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="K86" t="s">
         <v>67</v>
       </c>
       <c r="L86">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N86" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="O86">
         <v>5</v>
@@ -14816,10 +15330,10 @@
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>224</v>
@@ -14837,7 +15351,7 @@
         <v>1</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="I87" s="9">
         <v>7</v>
@@ -14866,10 +15380,10 @@
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
-        <v>917</v>
+        <v>887</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>917</v>
+        <v>887</v>
       </c>
       <c r="C88" s="9" t="s">
         <v>224</v>
@@ -14881,16 +15395,19 @@
         <v>11</v>
       </c>
       <c r="F88" s="17" t="s">
-        <v>918</v>
+        <v>883</v>
       </c>
       <c r="G88" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>888</v>
       </c>
       <c r="I88" s="9">
         <v>7</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>919</v>
+        <v>886</v>
       </c>
       <c r="K88" t="s">
         <v>67</v>
@@ -14913,43 +15430,40 @@
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>547</v>
+        <v>224</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>548</v>
+        <v>148</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
       <c r="G89" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>942</v>
+        <v>0</v>
       </c>
       <c r="I89" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>943</v>
+        <v>919</v>
       </c>
       <c r="K89" t="s">
         <v>67</v>
       </c>
       <c r="L89">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N89" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="O89">
         <v>5</v>
@@ -14963,10 +15477,10 @@
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>547</v>
@@ -14984,13 +15498,13 @@
         <v>1</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="I90" s="9">
         <v>5</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="K90" t="s">
         <v>67</v>
@@ -15013,10 +15527,10 @@
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
-        <v>1003</v>
+        <v>944</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>1003</v>
+        <v>944</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>547</v>
@@ -15025,19 +15539,22 @@
         <v>548</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>1005</v>
+        <v>941</v>
       </c>
       <c r="G91" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>945</v>
       </c>
       <c r="I91" s="9">
         <v>5</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>1004</v>
+        <v>946</v>
       </c>
       <c r="K91" t="s">
         <v>67</v>
@@ -15046,7 +15563,7 @@
         <v>20</v>
       </c>
       <c r="N91" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="O91">
         <v>5</v>
@@ -15060,10 +15577,10 @@
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="9" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>547</v>
@@ -15075,7 +15592,7 @@
         <v>11</v>
       </c>
       <c r="F92" s="17" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G92" s="9" t="b">
         <v>0</v>
@@ -15084,7 +15601,7 @@
         <v>5</v>
       </c>
       <c r="J92" s="9" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="K92" t="s">
         <v>67</v>
@@ -15107,40 +15624,40 @@
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="9" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>224</v>
+        <v>547</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>148</v>
+        <v>548</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="G93" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I93" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J93" s="9" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="K93" t="s">
         <v>67</v>
       </c>
       <c r="L93">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N93" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="O93">
         <v>5</v>
@@ -15154,40 +15671,40 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="F94" s="17" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="G94" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I94" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J94" s="9" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="K94" t="s">
         <v>67</v>
       </c>
       <c r="L94">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N94" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="O94">
         <v>5</v>
@@ -15201,43 +15718,40 @@
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>547</v>
+        <v>223</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>548</v>
+        <v>50</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="G95" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>1025</v>
+        <v>0</v>
       </c>
       <c r="I95" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J95" s="9" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="K95" t="s">
         <v>67</v>
       </c>
       <c r="L95">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N95" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="O95">
         <v>5</v>
@@ -15251,10 +15765,10 @@
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C96" s="9" t="s">
         <v>547</v>
@@ -15272,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="I96" s="9">
         <v>5</v>
@@ -15301,10 +15815,10 @@
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="C97" s="9" t="s">
         <v>547</v>
@@ -15313,22 +15827,22 @@
         <v>548</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="G97" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="I97" s="9">
         <v>5</v>
       </c>
       <c r="J97" s="9" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="K97" t="s">
         <v>67</v>
@@ -15337,7 +15851,7 @@
         <v>20</v>
       </c>
       <c r="N97" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="O97">
         <v>5</v>
@@ -15351,10 +15865,10 @@
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C98" s="9" t="s">
         <v>547</v>
@@ -15372,13 +15886,13 @@
         <v>1</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="I98" s="9">
         <v>5</v>
       </c>
       <c r="J98" s="9" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="K98" t="s">
         <v>67</v>
@@ -15401,10 +15915,10 @@
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
       <c r="C99" s="9" t="s">
         <v>547</v>
@@ -15413,22 +15927,22 @@
         <v>548</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
       <c r="G99" s="9" t="b">
         <v>1</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="I99" s="9">
         <v>5</v>
       </c>
       <c r="J99" s="9" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
       <c r="K99" t="s">
         <v>67</v>
@@ -15437,7 +15951,7 @@
         <v>20</v>
       </c>
       <c r="N99" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="O99">
         <v>5</v>
@@ -15451,10 +15965,10 @@
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>547</v>
@@ -15472,13 +15986,13 @@
         <v>1</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="I100" s="9">
         <v>5</v>
       </c>
       <c r="J100" s="9" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="K100" t="s">
         <v>67</v>
@@ -15492,6 +16006,9 @@
       <c r="O100">
         <v>5</v>
       </c>
+      <c r="P100" t="s">
+        <v>1130</v>
+      </c>
       <c r="Q100" t="s">
         <v>67</v>
       </c>
@@ -15501,43 +16018,49 @@
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>224</v>
+        <v>547</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>148</v>
+        <v>548</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F101" s="17" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="G101" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>1051</v>
       </c>
       <c r="I101" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J101" s="9" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="K101" t="s">
         <v>67</v>
       </c>
       <c r="L101">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="N101" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="O101">
         <v>5</v>
+      </c>
+      <c r="P101" t="s">
+        <v>1130</v>
       </c>
       <c r="Q101" t="s">
         <v>67</v>
@@ -15548,48 +16071,586 @@
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>547</v>
+        <v>224</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>548</v>
+        <v>148</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F102" s="17" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="G102" s="9" t="b">
         <v>0</v>
       </c>
       <c r="I102" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J102" s="9" t="s">
+        <v>1056</v>
+      </c>
+      <c r="K102" t="s">
+        <v>67</v>
+      </c>
+      <c r="L102">
+        <v>7</v>
+      </c>
+      <c r="N102" t="s">
+        <v>898</v>
+      </c>
+      <c r="O102">
+        <v>5</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>67</v>
+      </c>
+      <c r="R102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A103" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="17" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G103" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I103" s="9">
+        <v>5</v>
+      </c>
+      <c r="J103" s="9" t="s">
         <v>1061</v>
       </c>
-      <c r="K102" t="s">
-        <v>67</v>
-      </c>
-      <c r="L102">
+      <c r="K103" t="s">
+        <v>67</v>
+      </c>
+      <c r="L103">
         <v>20</v>
       </c>
-      <c r="N102" t="s">
+      <c r="N103" t="s">
         <v>903</v>
       </c>
-      <c r="O102">
-        <v>5</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>67</v>
-      </c>
-      <c r="R102">
+      <c r="O103">
+        <v>5</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>67</v>
+      </c>
+      <c r="R103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A104" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G104" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H104" s="17" t="s">
+        <v>1080</v>
+      </c>
+      <c r="I104" s="9">
+        <v>7</v>
+      </c>
+      <c r="J104" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K104" t="s">
+        <v>67</v>
+      </c>
+      <c r="L104">
+        <v>7</v>
+      </c>
+      <c r="N104" t="s">
+        <v>898</v>
+      </c>
+      <c r="O104">
+        <v>5</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>67</v>
+      </c>
+      <c r="R104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A105" s="9" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G105" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105" s="17" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I105" s="9">
+        <v>7</v>
+      </c>
+      <c r="J105" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K105" t="s">
+        <v>67</v>
+      </c>
+      <c r="L105">
+        <v>7</v>
+      </c>
+      <c r="N105" t="s">
+        <v>898</v>
+      </c>
+      <c r="O105">
+        <v>5</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>67</v>
+      </c>
+      <c r="R105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A106" s="9" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G106" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H106" s="17" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I106" s="9">
+        <v>7</v>
+      </c>
+      <c r="J106" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K106" t="s">
+        <v>67</v>
+      </c>
+      <c r="L106">
+        <v>7</v>
+      </c>
+      <c r="N106" t="s">
+        <v>898</v>
+      </c>
+      <c r="O106">
+        <v>5</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>67</v>
+      </c>
+      <c r="R106">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A107" s="9" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G107" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H107" s="17" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I107" s="9">
+        <v>7</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K107" t="s">
+        <v>67</v>
+      </c>
+      <c r="L107">
+        <v>7</v>
+      </c>
+      <c r="N107" t="s">
+        <v>898</v>
+      </c>
+      <c r="O107">
+        <v>5</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>67</v>
+      </c>
+      <c r="R107">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A108" s="9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G108" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H108" s="17" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I108" s="9">
+        <v>7</v>
+      </c>
+      <c r="J108" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="K108" t="s">
+        <v>67</v>
+      </c>
+      <c r="L108">
+        <v>7</v>
+      </c>
+      <c r="N108" t="s">
+        <v>898</v>
+      </c>
+      <c r="O108">
+        <v>5</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>67</v>
+      </c>
+      <c r="R108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A109" s="9" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="17" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G109" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I109" s="9">
+        <v>5</v>
+      </c>
+      <c r="J109" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="K109" t="s">
+        <v>67</v>
+      </c>
+      <c r="L109">
+        <v>20</v>
+      </c>
+      <c r="N109" t="s">
+        <v>903</v>
+      </c>
+      <c r="O109">
+        <v>5</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>67</v>
+      </c>
+      <c r="R109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A110" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="17" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G110" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I110" s="9">
+        <v>5</v>
+      </c>
+      <c r="J110" s="9" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K110" t="s">
+        <v>67</v>
+      </c>
+      <c r="L110">
+        <v>20</v>
+      </c>
+      <c r="N110" t="s">
+        <v>903</v>
+      </c>
+      <c r="O110">
+        <v>5</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>67</v>
+      </c>
+      <c r="R110">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A111" s="9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G111" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I111" s="9">
+        <v>5</v>
+      </c>
+      <c r="J111" s="9" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K111" t="s">
+        <v>67</v>
+      </c>
+      <c r="L111">
+        <v>20</v>
+      </c>
+      <c r="N111" t="s">
+        <v>903</v>
+      </c>
+      <c r="O111">
+        <v>5</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>67</v>
+      </c>
+      <c r="R111">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A112" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E112" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="17" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G112" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I112" s="9">
+        <v>5</v>
+      </c>
+      <c r="J112" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K112" t="s">
+        <v>67</v>
+      </c>
+      <c r="L112">
+        <v>20</v>
+      </c>
+      <c r="N112" t="s">
+        <v>910</v>
+      </c>
+      <c r="O112">
+        <v>5</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>67</v>
+      </c>
+      <c r="R112">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A113" s="9" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="17" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G113" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>1124</v>
+      </c>
+      <c r="I113" s="9">
+        <v>5</v>
+      </c>
+      <c r="J113" s="9" t="s">
+        <v>1125</v>
+      </c>
+      <c r="K113" t="s">
+        <v>67</v>
+      </c>
+      <c r="L113">
+        <v>20</v>
+      </c>
+      <c r="N113" t="s">
+        <v>910</v>
+      </c>
+      <c r="O113">
+        <v>5</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>67</v>
+      </c>
+      <c r="R113">
         <v>5</v>
       </c>
     </row>

--- a/SnailData.xlsx
+++ b/SnailData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjwog\Desktop\SnailProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAFF78E-30B7-4F76-87D6-6AF1C00F8305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3606CC46-D68C-4AFC-942B-DF86B22933CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="866" activeTab="1" xr2:uid="{5EE1C0BB-DAD6-4BF1-AA41-9BEEACC3D6EF}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" tabRatio="866" firstSheet="1" activeTa